--- a/slots/resources/sample/SpecialPlay.xlsx
+++ b/slots/resources/sample/SpecialPlay.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="27945" windowHeight="12375"/>
+    <workbookView windowWidth="27945" windowHeight="12255"/>
   </bookViews>
   <sheets>
     <sheet name="SpecialPlay" sheetId="1" r:id="rId1"/>
@@ -137,7 +137,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="311" uniqueCount="215">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="307" uniqueCount="214">
   <si>
     <t>被动游戏ID</t>
   </si>
@@ -553,10 +553,7 @@
     <t>寻宝黄金城</t>
   </si>
   <si>
-    <t>1,1_1|2_2|3_3|4_4|5_5|6_6|7_7|8_8|9_9|10_10;2,1_2|2_4|3_6|4_8|5_10|6_12|7_14|8_16|9_18|10_20</t>
-  </si>
-  <si>
-    <t>2,13,4_12_10000|5_14_10000|6_16_10000</t>
+    <t>1,1_10;2,2_20</t>
   </si>
   <si>
     <t>常规模式下，金矿符号转换为百搭符号或黏性百搭符号</t>
@@ -571,7 +568,7 @@
     <t>澳门壕梦</t>
   </si>
   <si>
-    <t>2,13,4_15_10000|5_17_10000|6_19_10000</t>
+    <t>4,13,4_15_10000|5_17_10000|6_19_10000</t>
   </si>
   <si>
     <t>SpecialMode模式ID，目标图案，目标图案个数_中奖增加免费次数_中奖万分比</t>
@@ -580,7 +577,7 @@
     <t>免费模式下，获得连续中奖次数对应的中奖倍数，原倍率上乘以此倍率</t>
   </si>
   <si>
-    <t>2,1_1|2_2|3_3|4_4|5_5|6_6|7_7|8_8|9_9|10_10|11_11|12_12|…….</t>
+    <t>4,1_1|2_2|3_3|4_4|5_5|6_6|7_7|8_8|9_9|10_10|11_11|12_12|…….</t>
   </si>
   <si>
     <t>SpecialMode模式ID，中奖次数_中奖倍率|中奖次数_中奖倍率|…….</t>
@@ -965,13 +962,13 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
-      <sz val="9"/>
+      <sz val="10"/>
       <name val="宋体"/>
       <charset val="134"/>
     </font>
     <font>
-      <sz val="10"/>
+      <b/>
+      <sz val="9"/>
       <name val="宋体"/>
       <charset val="134"/>
     </font>
@@ -1824,7 +1821,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:J62"/>
+  <dimension ref="A1:J61"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25"/>
   <cols>
     <col min="4" max="4" width="9.50833333333333" style="4" customWidth="1"/>
@@ -3203,7 +3200,7 @@
     </row>
     <row r="56" customFormat="1" ht="16.5" spans="1:9">
       <c r="A56" s="2">
-        <v>5026002</v>
+        <v>5026003</v>
       </c>
       <c r="B56" s="17">
         <v>102600</v>
@@ -3212,169 +3209,144 @@
         <v>137</v>
       </c>
       <c r="D56" s="1">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E56" t="s">
-        <v>33</v>
-      </c>
-      <c r="F56" s="3" t="s">
         <v>139</v>
       </c>
-      <c r="G56" s="3" t="s">
-        <v>35</v>
+      <c r="F56" s="15" t="s">
+        <v>140</v>
+      </c>
+      <c r="G56" s="1" t="s">
+        <v>141</v>
       </c>
       <c r="H56" s="5"/>
       <c r="I56" s="5"/>
     </row>
     <row r="57" customFormat="1" ht="16.5" spans="1:9">
       <c r="A57" s="2">
-        <v>5026003</v>
+        <v>5050001</v>
       </c>
       <c r="B57" s="17">
-        <v>102600</v>
+        <v>105000</v>
       </c>
       <c r="C57" t="s">
-        <v>137</v>
+        <v>142</v>
       </c>
       <c r="D57" s="1">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E57" t="s">
-        <v>140</v>
+        <v>33</v>
       </c>
       <c r="F57" s="15" t="s">
-        <v>141</v>
+        <v>143</v>
       </c>
       <c r="G57" s="1" t="s">
-        <v>142</v>
+        <v>144</v>
       </c>
       <c r="H57" s="5"/>
       <c r="I57" s="5"/>
     </row>
     <row r="58" customFormat="1" ht="16.5" spans="1:9">
       <c r="A58" s="2">
-        <v>5050001</v>
+        <v>5050002</v>
       </c>
       <c r="B58" s="17">
         <v>105000</v>
       </c>
       <c r="C58" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="D58" s="1">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E58" t="s">
-        <v>33</v>
+        <v>145</v>
       </c>
       <c r="F58" s="15" t="s">
-        <v>144</v>
+        <v>146</v>
       </c>
       <c r="G58" s="1" t="s">
-        <v>145</v>
+        <v>147</v>
       </c>
       <c r="H58" s="5"/>
       <c r="I58" s="5"/>
     </row>
     <row r="59" customFormat="1" ht="16.5" spans="1:9">
       <c r="A59" s="2">
-        <v>5050002</v>
+        <v>5051001</v>
       </c>
       <c r="B59" s="17">
-        <v>105000</v>
+        <v>105100</v>
       </c>
       <c r="C59" t="s">
-        <v>143</v>
+        <v>148</v>
       </c>
       <c r="D59" s="1">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E59" t="s">
-        <v>146</v>
+        <v>149</v>
       </c>
       <c r="F59" s="15" t="s">
-        <v>147</v>
+        <v>150</v>
       </c>
       <c r="G59" s="1" t="s">
-        <v>148</v>
+        <v>151</v>
       </c>
       <c r="H59" s="5"/>
       <c r="I59" s="5"/>
     </row>
     <row r="60" customFormat="1" ht="16.5" spans="1:9">
       <c r="A60" s="2">
-        <v>5051001</v>
+        <v>5051002</v>
       </c>
       <c r="B60" s="17">
         <v>105100</v>
       </c>
       <c r="C60" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="D60" s="1">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E60" t="s">
-        <v>150</v>
+        <v>152</v>
       </c>
       <c r="F60" s="15" t="s">
-        <v>151</v>
+        <v>153</v>
       </c>
       <c r="G60" s="1" t="s">
-        <v>152</v>
+        <v>154</v>
       </c>
       <c r="H60" s="5"/>
       <c r="I60" s="5"/>
     </row>
     <row r="61" customFormat="1" ht="16.5" spans="1:9">
       <c r="A61" s="2">
-        <v>5051002</v>
+        <v>5051003</v>
       </c>
       <c r="B61" s="17">
         <v>105100</v>
       </c>
       <c r="C61" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="D61" s="1">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E61" t="s">
-        <v>153</v>
+        <v>155</v>
       </c>
       <c r="F61" s="15" t="s">
-        <v>154</v>
+        <v>156</v>
       </c>
       <c r="G61" s="1" t="s">
-        <v>155</v>
+        <v>157</v>
       </c>
       <c r="H61" s="5"/>
       <c r="I61" s="5"/>
-    </row>
-    <row r="62" customFormat="1" ht="16.5" spans="1:9">
-      <c r="A62" s="2">
-        <v>5051003</v>
-      </c>
-      <c r="B62" s="17">
-        <v>105100</v>
-      </c>
-      <c r="C62" t="s">
-        <v>149</v>
-      </c>
-      <c r="D62" s="1">
-        <v>3</v>
-      </c>
-      <c r="E62" t="s">
-        <v>156</v>
-      </c>
-      <c r="F62" s="15" t="s">
-        <v>157</v>
-      </c>
-      <c r="G62" s="1" t="s">
-        <v>158</v>
-      </c>
-      <c r="H62" s="5"/>
-      <c r="I62" s="5"/>
     </row>
   </sheetData>
   <conditionalFormatting sqref="H2">
@@ -3401,24 +3373,24 @@
   <sheetData>
     <row r="1" spans="1:5">
       <c r="A1" t="s">
+        <v>158</v>
+      </c>
+      <c r="D1" t="s">
         <v>159</v>
-      </c>
-      <c r="D1" t="s">
-        <v>160</v>
       </c>
     </row>
     <row r="2" spans="1:5">
       <c r="A2" t="s">
+        <v>160</v>
+      </c>
+      <c r="B2" t="s">
         <v>161</v>
       </c>
-      <c r="B2" t="s">
-        <v>162</v>
-      </c>
       <c r="D2" t="s">
+        <v>160</v>
+      </c>
+      <c r="E2" t="s">
         <v>161</v>
-      </c>
-      <c r="E2" t="s">
-        <v>162</v>
       </c>
     </row>
     <row r="3" spans="1:5">
@@ -3426,13 +3398,13 @@
         <v>0</v>
       </c>
       <c r="B3" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="D3">
         <v>0</v>
       </c>
       <c r="E3" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
     </row>
     <row r="4" spans="1:5">
@@ -3440,13 +3412,13 @@
         <v>1</v>
       </c>
       <c r="B4" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="D4">
         <v>1</v>
       </c>
       <c r="E4" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
     </row>
     <row r="5" spans="1:5">
@@ -3454,13 +3426,13 @@
         <v>2</v>
       </c>
       <c r="B5" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="D5">
         <v>2</v>
       </c>
       <c r="E5" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
     </row>
     <row r="6" spans="1:5">
@@ -3468,13 +3440,13 @@
         <v>3</v>
       </c>
       <c r="B6" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="D6">
         <v>3</v>
       </c>
       <c r="E6" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
     </row>
     <row r="7" spans="1:5">
@@ -3482,13 +3454,13 @@
         <v>4</v>
       </c>
       <c r="B7" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="D7">
         <v>4</v>
       </c>
       <c r="E7" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
     </row>
     <row r="8" spans="1:5">
@@ -3496,13 +3468,13 @@
         <v>5</v>
       </c>
       <c r="B8" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="D8">
         <v>5</v>
       </c>
       <c r="E8" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
     </row>
     <row r="9" spans="1:5">
@@ -3510,7 +3482,7 @@
         <v>6</v>
       </c>
       <c r="B9" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
     </row>
     <row r="10" spans="1:5">
@@ -3518,7 +3490,7 @@
         <v>7</v>
       </c>
       <c r="B10" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
     </row>
     <row r="11" spans="1:5">
@@ -3526,7 +3498,7 @@
         <v>8</v>
       </c>
       <c r="B11" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
     </row>
     <row r="12" spans="1:5">
@@ -3534,7 +3506,7 @@
         <v>9</v>
       </c>
       <c r="B12" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
     </row>
     <row r="13" spans="1:5">
@@ -3542,7 +3514,7 @@
         <v>10</v>
       </c>
       <c r="B13" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
     </row>
     <row r="14" spans="1:5">
@@ -3550,7 +3522,7 @@
         <v>11</v>
       </c>
       <c r="B14" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
     </row>
     <row r="15" spans="1:5">
@@ -3558,7 +3530,7 @@
         <v>12</v>
       </c>
       <c r="B15" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
     </row>
     <row r="16" spans="1:5">
@@ -3566,7 +3538,7 @@
         <v>13</v>
       </c>
       <c r="B16" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
     </row>
     <row r="17" spans="1:2">
@@ -3574,7 +3546,7 @@
         <v>14</v>
       </c>
       <c r="B17" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
     </row>
     <row r="18" spans="1:2">
@@ -3582,7 +3554,7 @@
         <v>15</v>
       </c>
       <c r="B18" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
     </row>
     <row r="19" spans="1:2">
@@ -3590,7 +3562,7 @@
         <v>16</v>
       </c>
       <c r="B19" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
     </row>
     <row r="20" spans="1:2">
@@ -3598,7 +3570,7 @@
         <v>17</v>
       </c>
       <c r="B20" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
     </row>
     <row r="21" spans="1:2">
@@ -3606,7 +3578,7 @@
         <v>18</v>
       </c>
       <c r="B21" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
     </row>
     <row r="22" spans="1:2">
@@ -3614,7 +3586,7 @@
         <v>19</v>
       </c>
       <c r="B22" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
     </row>
     <row r="23" spans="1:2">
@@ -3622,7 +3594,7 @@
         <v>20</v>
       </c>
       <c r="B23" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
     </row>
     <row r="24" spans="1:2">
@@ -3630,7 +3602,7 @@
         <v>21</v>
       </c>
       <c r="B24" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
     </row>
     <row r="25" spans="1:2">
@@ -3638,7 +3610,7 @@
         <v>22</v>
       </c>
       <c r="B25" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
     </row>
     <row r="26" spans="1:2">
@@ -3646,7 +3618,7 @@
         <v>23</v>
       </c>
       <c r="B26" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
     </row>
     <row r="27" spans="1:2">
@@ -3654,7 +3626,7 @@
         <v>24</v>
       </c>
       <c r="B27" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
     </row>
     <row r="28" spans="1:2">
@@ -3662,7 +3634,7 @@
         <v>25</v>
       </c>
       <c r="B28" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
     </row>
     <row r="29" spans="1:2">
@@ -3670,7 +3642,7 @@
         <v>26</v>
       </c>
       <c r="B29" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
     </row>
     <row r="30" spans="1:2">
@@ -3678,7 +3650,7 @@
         <v>27</v>
       </c>
       <c r="B30" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
     </row>
     <row r="31" spans="1:2">
@@ -3686,7 +3658,7 @@
         <v>28</v>
       </c>
       <c r="B31" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
     </row>
     <row r="32" spans="1:2">
@@ -3694,7 +3666,7 @@
         <v>29</v>
       </c>
       <c r="B32" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
     </row>
     <row r="33" spans="1:2">
@@ -3702,7 +3674,7 @@
         <v>30</v>
       </c>
       <c r="B33" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
     </row>
     <row r="34" spans="1:2">
@@ -3710,7 +3682,7 @@
         <v>31</v>
       </c>
       <c r="B34" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
     </row>
     <row r="35" spans="1:2">
@@ -3718,7 +3690,7 @@
         <v>32</v>
       </c>
       <c r="B35" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
     </row>
     <row r="36" spans="1:2">
@@ -3726,7 +3698,7 @@
         <v>33</v>
       </c>
       <c r="B36" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
     </row>
     <row r="37" spans="1:2">
@@ -3734,7 +3706,7 @@
         <v>34</v>
       </c>
       <c r="B37" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
     </row>
     <row r="38" spans="1:2">
@@ -3742,7 +3714,7 @@
         <v>35</v>
       </c>
       <c r="B38" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
     </row>
     <row r="39" spans="1:2">
@@ -3750,7 +3722,7 @@
         <v>36</v>
       </c>
       <c r="B39" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
     </row>
     <row r="40" spans="1:2">
@@ -3758,7 +3730,7 @@
         <v>37</v>
       </c>
       <c r="B40" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
     </row>
     <row r="41" spans="1:2">
@@ -3766,7 +3738,7 @@
         <v>38</v>
       </c>
       <c r="B41" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
     </row>
     <row r="42" spans="1:2">
@@ -3774,7 +3746,7 @@
         <v>39</v>
       </c>
       <c r="B42" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
     </row>
     <row r="43" spans="1:2">
@@ -3782,7 +3754,7 @@
         <v>40</v>
       </c>
       <c r="B43" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
     </row>
     <row r="44" spans="1:2">
@@ -3790,7 +3762,7 @@
         <v>41</v>
       </c>
       <c r="B44" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
     </row>
     <row r="45" spans="1:2">
@@ -3798,7 +3770,7 @@
         <v>42</v>
       </c>
       <c r="B45" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
     </row>
     <row r="46" spans="1:2">
@@ -3806,7 +3778,7 @@
         <v>43</v>
       </c>
       <c r="B46" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
     </row>
     <row r="47" spans="1:2">
@@ -3814,7 +3786,7 @@
         <v>44</v>
       </c>
       <c r="B47" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
     </row>
     <row r="48" spans="1:2">
@@ -3822,7 +3794,7 @@
         <v>45</v>
       </c>
       <c r="B48" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
     </row>
   </sheetData>

--- a/slots/resources/sample/SpecialPlay.xlsx
+++ b/slots/resources/sample/SpecialPlay.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="21000" windowHeight="12375"/>
+    <workbookView windowWidth="27945" windowHeight="12375"/>
   </bookViews>
   <sheets>
     <sheet name="SpecialPlay" sheetId="1" r:id="rId1"/>
@@ -137,7 +137,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="351" uniqueCount="236">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="343" uniqueCount="234">
   <si>
     <t>被动游戏ID</t>
   </si>
@@ -532,24 +532,21 @@
     <t>狼月</t>
   </si>
   <si>
-    <t>手动选择小游戏：中奖ID,小游戏1_小游戏2_小游戏3|中奖ID,小游戏1_小游戏2……</t>
-  </si>
-  <si>
-    <t>1015400314,30150001_30150002_30150003</t>
-  </si>
-  <si>
-    <t>BaseElementReward表中中奖ID，小游戏1_小游戏2_小游戏3|……</t>
-  </si>
-  <si>
     <t>免费递增奖励倍数模式下，每次免费旋转结算时原赔率乘以此倍率值</t>
   </si>
   <si>
-    <t>7_5</t>
+    <t>5_100</t>
   </si>
   <si>
     <t>免费游戏中，初始获得5的乘倍值，每次旋转结算后乘倍值曾加5，最多可增加值100</t>
   </si>
   <si>
+    <t>15_1</t>
+  </si>
+  <si>
+    <t>元素id_次数</t>
+  </si>
+  <si>
     <t>寻宝黄金城</t>
   </si>
   <si>
@@ -641,9 +638,6 @@
   </si>
   <si>
     <t>麻将胡了2</t>
-  </si>
-  <si>
-    <t>11_3_10_10000|4_12_10000|5_14_10000</t>
   </si>
   <si>
     <t>赏金大对决</t>
@@ -1028,13 +1022,13 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
-      <sz val="9"/>
+      <sz val="10"/>
       <name val="宋体"/>
       <charset val="134"/>
     </font>
     <font>
-      <sz val="10"/>
+      <b/>
+      <sz val="9"/>
       <name val="宋体"/>
       <charset val="134"/>
     </font>
@@ -1887,7 +1881,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:J72"/>
+  <dimension ref="A1:J70"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25"/>
   <cols>
     <col min="4" max="4" width="9.50833333333333" style="4" customWidth="1"/>
@@ -3183,7 +3177,7 @@
       <c r="F52" s="15" t="s">
         <v>132</v>
       </c>
-      <c r="G52" s="1" t="s">
+      <c r="G52" t="s">
         <v>133</v>
       </c>
       <c r="H52" s="5"/>
@@ -3203,335 +3197,335 @@
         <v>2</v>
       </c>
       <c r="E53" t="s">
+        <v>33</v>
+      </c>
+      <c r="F53" s="3" t="s">
         <v>134</v>
       </c>
-      <c r="F53" s="15" t="s">
+      <c r="G53" s="1" t="s">
         <v>135</v>
-      </c>
-      <c r="G53" t="s">
-        <v>136</v>
       </c>
       <c r="H53" s="5"/>
       <c r="I53" s="5"/>
     </row>
     <row r="54" customFormat="1" ht="16.5" spans="1:9">
       <c r="A54" s="2">
-        <v>5015003</v>
+        <v>5026001</v>
       </c>
       <c r="B54" s="17">
-        <v>101500</v>
+        <v>102600</v>
       </c>
       <c r="C54" t="s">
-        <v>130</v>
+        <v>136</v>
       </c>
       <c r="D54" s="1">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E54" t="s">
-        <v>33</v>
-      </c>
-      <c r="F54" s="3" t="s">
-        <v>105</v>
+        <v>30</v>
+      </c>
+      <c r="F54" s="15" t="s">
+        <v>137</v>
       </c>
       <c r="G54" s="1" t="s">
-        <v>35</v>
+        <v>32</v>
       </c>
       <c r="H54" s="5"/>
       <c r="I54" s="5"/>
     </row>
     <row r="55" customFormat="1" ht="16.5" spans="1:9">
       <c r="A55" s="2">
-        <v>5026001</v>
+        <v>5026003</v>
       </c>
       <c r="B55" s="17">
         <v>102600</v>
       </c>
       <c r="C55" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="D55" s="1">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E55" t="s">
-        <v>30</v>
+        <v>138</v>
       </c>
       <c r="F55" s="15" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="G55" s="1" t="s">
-        <v>32</v>
+        <v>140</v>
       </c>
       <c r="H55" s="5"/>
       <c r="I55" s="5"/>
     </row>
     <row r="56" customFormat="1" ht="16.5" spans="1:9">
       <c r="A56" s="2">
-        <v>5026003</v>
+        <v>5050001</v>
       </c>
       <c r="B56" s="17">
-        <v>102600</v>
+        <v>105000</v>
       </c>
       <c r="C56" t="s">
-        <v>137</v>
+        <v>141</v>
       </c>
       <c r="D56" s="1">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E56" t="s">
-        <v>139</v>
+        <v>33</v>
       </c>
       <c r="F56" s="15" t="s">
-        <v>140</v>
+        <v>142</v>
       </c>
       <c r="G56" s="1" t="s">
-        <v>141</v>
+        <v>143</v>
       </c>
       <c r="H56" s="5"/>
       <c r="I56" s="5"/>
     </row>
     <row r="57" customFormat="1" ht="16.5" spans="1:9">
       <c r="A57" s="2">
-        <v>5050001</v>
+        <v>5050002</v>
       </c>
       <c r="B57" s="17">
         <v>105000</v>
       </c>
       <c r="C57" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="D57" s="1">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E57" t="s">
-        <v>33</v>
+        <v>144</v>
       </c>
       <c r="F57" s="15" t="s">
-        <v>143</v>
+        <v>145</v>
       </c>
       <c r="G57" s="1" t="s">
-        <v>144</v>
+        <v>146</v>
       </c>
       <c r="H57" s="5"/>
       <c r="I57" s="5"/>
     </row>
     <row r="58" customFormat="1" ht="16.5" spans="1:9">
       <c r="A58" s="2">
-        <v>5050002</v>
+        <v>5051001</v>
       </c>
       <c r="B58" s="17">
-        <v>105000</v>
+        <v>105100</v>
       </c>
       <c r="C58" t="s">
-        <v>142</v>
+        <v>147</v>
       </c>
       <c r="D58" s="1">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E58" t="s">
-        <v>145</v>
+        <v>148</v>
       </c>
       <c r="F58" s="15" t="s">
-        <v>146</v>
+        <v>149</v>
       </c>
       <c r="G58" s="1" t="s">
-        <v>147</v>
+        <v>150</v>
       </c>
       <c r="H58" s="5"/>
       <c r="I58" s="5"/>
     </row>
     <row r="59" customFormat="1" ht="16.5" spans="1:9">
       <c r="A59" s="2">
-        <v>5051001</v>
+        <v>5051002</v>
       </c>
       <c r="B59" s="17">
         <v>105100</v>
       </c>
       <c r="C59" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="D59" s="1">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E59" t="s">
-        <v>149</v>
+        <v>151</v>
       </c>
       <c r="F59" s="15" t="s">
-        <v>150</v>
+        <v>152</v>
       </c>
       <c r="G59" s="1" t="s">
-        <v>151</v>
+        <v>153</v>
       </c>
       <c r="H59" s="5"/>
       <c r="I59" s="5"/>
     </row>
     <row r="60" customFormat="1" ht="16.5" spans="1:9">
       <c r="A60" s="2">
-        <v>5051002</v>
+        <v>5051003</v>
       </c>
       <c r="B60" s="17">
         <v>105100</v>
       </c>
       <c r="C60" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="D60" s="1">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E60" t="s">
-        <v>152</v>
+        <v>154</v>
       </c>
       <c r="F60" s="15" t="s">
-        <v>153</v>
+        <v>155</v>
       </c>
       <c r="G60" s="1" t="s">
-        <v>154</v>
+        <v>156</v>
       </c>
       <c r="H60" s="5"/>
       <c r="I60" s="5"/>
     </row>
     <row r="61" customFormat="1" ht="16.5" spans="1:9">
       <c r="A61" s="2">
-        <v>5051003</v>
+        <v>5054001</v>
       </c>
       <c r="B61" s="17">
-        <v>105100</v>
+        <v>105400</v>
       </c>
       <c r="C61" t="s">
-        <v>148</v>
+        <v>157</v>
       </c>
       <c r="D61" s="1">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E61" t="s">
-        <v>155</v>
+        <v>158</v>
       </c>
       <c r="F61" s="15" t="s">
-        <v>156</v>
+        <v>145</v>
       </c>
       <c r="G61" s="1" t="s">
-        <v>157</v>
+        <v>159</v>
       </c>
       <c r="H61" s="5"/>
       <c r="I61" s="5"/>
     </row>
     <row r="62" customFormat="1" ht="16.5" spans="1:9">
       <c r="A62" s="2">
-        <v>5054001</v>
+        <v>5054002</v>
       </c>
       <c r="B62" s="17">
         <v>105400</v>
       </c>
       <c r="C62" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="D62" s="1">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E62" t="s">
-        <v>159</v>
+        <v>33</v>
       </c>
       <c r="F62" s="15" t="s">
-        <v>146</v>
+        <v>160</v>
       </c>
       <c r="G62" s="1" t="s">
-        <v>160</v>
+        <v>143</v>
       </c>
       <c r="H62" s="5"/>
       <c r="I62" s="5"/>
     </row>
     <row r="63" customFormat="1" ht="16.5" spans="1:9">
       <c r="A63" s="2">
-        <v>5054002</v>
+        <v>5008001</v>
       </c>
       <c r="B63" s="17">
-        <v>105400</v>
+        <v>100800</v>
       </c>
       <c r="C63" t="s">
-        <v>158</v>
+        <v>161</v>
       </c>
       <c r="D63" s="1">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E63" t="s">
-        <v>33</v>
+        <v>162</v>
       </c>
       <c r="F63" s="15" t="s">
-        <v>161</v>
+        <v>163</v>
       </c>
       <c r="G63" s="1" t="s">
-        <v>144</v>
+        <v>164</v>
       </c>
       <c r="H63" s="5"/>
       <c r="I63" s="5"/>
     </row>
     <row r="64" customFormat="1" ht="16.5" spans="1:9">
       <c r="A64" s="2">
-        <v>5008001</v>
+        <v>5008002</v>
       </c>
       <c r="B64" s="17">
         <v>100800</v>
       </c>
       <c r="C64" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="D64" s="1">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E64" t="s">
-        <v>163</v>
-      </c>
-      <c r="F64" s="15" t="s">
-        <v>164</v>
-      </c>
-      <c r="G64" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="F64" s="3" t="s">
         <v>165</v>
+      </c>
+      <c r="G64" s="3" t="s">
+        <v>35</v>
       </c>
       <c r="H64" s="5"/>
       <c r="I64" s="5"/>
     </row>
     <row r="65" customFormat="1" ht="16.5" spans="1:9">
       <c r="A65" s="2">
-        <v>5008002</v>
+        <v>5053001</v>
       </c>
       <c r="B65" s="17">
-        <v>100800</v>
+        <v>105300</v>
       </c>
       <c r="C65" t="s">
-        <v>162</v>
+        <v>166</v>
       </c>
       <c r="D65" s="1">
-        <v>2</v>
-      </c>
-      <c r="E65" t="s">
-        <v>33</v>
-      </c>
-      <c r="F65" s="3" t="s">
-        <v>166</v>
-      </c>
-      <c r="G65" s="3" t="s">
-        <v>35</v>
+        <v>4</v>
+      </c>
+      <c r="E65" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="F65" s="15" t="s">
+        <v>31</v>
+      </c>
+      <c r="G65" s="1" t="s">
+        <v>32</v>
       </c>
       <c r="H65" s="5"/>
       <c r="I65" s="5"/>
     </row>
     <row r="66" customFormat="1" ht="16.5" spans="1:9">
       <c r="A66" s="2">
-        <v>5053001</v>
+        <v>5057001</v>
       </c>
       <c r="B66" s="17">
-        <v>105300</v>
+        <v>105700</v>
       </c>
       <c r="C66" t="s">
         <v>167</v>
       </c>
       <c r="D66" s="1">
-        <v>4</v>
-      </c>
-      <c r="E66" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="E66" t="s">
         <v>30</v>
       </c>
       <c r="F66" s="15" t="s">
-        <v>31</v>
+        <v>168</v>
       </c>
       <c r="G66" s="1" t="s">
         <v>32</v>
@@ -3541,24 +3535,24 @@
     </row>
     <row r="67" customFormat="1" ht="16.5" spans="1:9">
       <c r="A67" s="2">
-        <v>5053002</v>
+        <v>5057002</v>
       </c>
       <c r="B67" s="17">
-        <v>105300</v>
+        <v>105700</v>
       </c>
       <c r="C67" t="s">
         <v>167</v>
       </c>
       <c r="D67" s="1">
-        <v>5</v>
-      </c>
-      <c r="E67" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="E67" t="s">
         <v>33</v>
       </c>
-      <c r="F67" s="15" t="s">
-        <v>168</v>
-      </c>
-      <c r="G67" s="1" t="s">
+      <c r="F67" s="3" t="s">
+        <v>169</v>
+      </c>
+      <c r="G67" s="3" t="s">
         <v>35</v>
       </c>
       <c r="H67" s="5"/>
@@ -3566,47 +3560,47 @@
     </row>
     <row r="68" customFormat="1" ht="16.5" spans="1:9">
       <c r="A68" s="2">
-        <v>5057001</v>
+        <v>5057003</v>
       </c>
       <c r="B68" s="17">
         <v>105700</v>
       </c>
       <c r="C68" t="s">
-        <v>169</v>
+        <v>167</v>
       </c>
       <c r="D68" s="1">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E68" t="s">
-        <v>30</v>
+        <v>170</v>
       </c>
       <c r="F68" s="15" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="G68" s="1" t="s">
-        <v>32</v>
+        <v>172</v>
       </c>
       <c r="H68" s="5"/>
       <c r="I68" s="5"/>
     </row>
     <row r="69" customFormat="1" ht="16.5" spans="1:9">
       <c r="A69" s="2">
-        <v>5057002</v>
+        <v>5058001</v>
       </c>
       <c r="B69" s="17">
-        <v>105700</v>
+        <v>105800</v>
       </c>
       <c r="C69" t="s">
-        <v>169</v>
+        <v>173</v>
       </c>
       <c r="D69" s="1">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E69" t="s">
         <v>33</v>
       </c>
       <c r="F69" s="3" t="s">
-        <v>171</v>
+        <v>174</v>
       </c>
       <c r="G69" s="3" t="s">
         <v>35</v>
@@ -3616,78 +3610,28 @@
     </row>
     <row r="70" customFormat="1" ht="16.5" spans="1:9">
       <c r="A70" s="2">
-        <v>5057003</v>
+        <v>5058002</v>
       </c>
       <c r="B70" s="17">
-        <v>105700</v>
+        <v>105800</v>
       </c>
       <c r="C70" t="s">
-        <v>169</v>
+        <v>173</v>
       </c>
       <c r="D70" s="1">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E70" t="s">
-        <v>172</v>
-      </c>
-      <c r="F70" s="15" t="s">
-        <v>173</v>
-      </c>
-      <c r="G70" s="1" t="s">
-        <v>174</v>
+        <v>175</v>
+      </c>
+      <c r="F70" s="3" t="s">
+        <v>176</v>
+      </c>
+      <c r="G70" s="3" t="s">
+        <v>177</v>
       </c>
       <c r="H70" s="5"/>
       <c r="I70" s="5"/>
-    </row>
-    <row r="71" customFormat="1" ht="16.5" spans="1:9">
-      <c r="A71" s="2">
-        <v>5058001</v>
-      </c>
-      <c r="B71" s="17">
-        <v>105800</v>
-      </c>
-      <c r="C71" t="s">
-        <v>175</v>
-      </c>
-      <c r="D71" s="1">
-        <v>1</v>
-      </c>
-      <c r="E71" t="s">
-        <v>33</v>
-      </c>
-      <c r="F71" s="3" t="s">
-        <v>176</v>
-      </c>
-      <c r="G71" s="3" t="s">
-        <v>35</v>
-      </c>
-      <c r="H71" s="5"/>
-      <c r="I71" s="5"/>
-    </row>
-    <row r="72" customFormat="1" ht="16.5" spans="1:9">
-      <c r="A72" s="2">
-        <v>5058002</v>
-      </c>
-      <c r="B72" s="17">
-        <v>105800</v>
-      </c>
-      <c r="C72" t="s">
-        <v>175</v>
-      </c>
-      <c r="D72" s="1">
-        <v>2</v>
-      </c>
-      <c r="E72" t="s">
-        <v>177</v>
-      </c>
-      <c r="F72" s="3" t="s">
-        <v>178</v>
-      </c>
-      <c r="G72" s="3" t="s">
-        <v>179</v>
-      </c>
-      <c r="H72" s="5"/>
-      <c r="I72" s="5"/>
     </row>
   </sheetData>
   <conditionalFormatting sqref="H2">
@@ -3714,24 +3658,24 @@
   <sheetData>
     <row r="1" spans="1:5">
       <c r="A1" t="s">
-        <v>180</v>
+        <v>178</v>
       </c>
       <c r="D1" t="s">
-        <v>181</v>
+        <v>179</v>
       </c>
     </row>
     <row r="2" spans="1:5">
       <c r="A2" t="s">
-        <v>182</v>
+        <v>180</v>
       </c>
       <c r="B2" t="s">
-        <v>183</v>
+        <v>181</v>
       </c>
       <c r="D2" t="s">
-        <v>182</v>
+        <v>180</v>
       </c>
       <c r="E2" t="s">
-        <v>183</v>
+        <v>181</v>
       </c>
     </row>
     <row r="3" spans="1:5">
@@ -3739,13 +3683,13 @@
         <v>0</v>
       </c>
       <c r="B3" t="s">
-        <v>184</v>
+        <v>182</v>
       </c>
       <c r="D3">
         <v>0</v>
       </c>
       <c r="E3" t="s">
-        <v>185</v>
+        <v>183</v>
       </c>
     </row>
     <row r="4" spans="1:5">
@@ -3753,13 +3697,13 @@
         <v>1</v>
       </c>
       <c r="B4" t="s">
-        <v>186</v>
+        <v>184</v>
       </c>
       <c r="D4">
         <v>1</v>
       </c>
       <c r="E4" t="s">
-        <v>187</v>
+        <v>185</v>
       </c>
     </row>
     <row r="5" spans="1:5">
@@ -3767,13 +3711,13 @@
         <v>2</v>
       </c>
       <c r="B5" t="s">
-        <v>188</v>
+        <v>186</v>
       </c>
       <c r="D5">
         <v>2</v>
       </c>
       <c r="E5" t="s">
-        <v>189</v>
+        <v>187</v>
       </c>
     </row>
     <row r="6" spans="1:5">
@@ -3781,13 +3725,13 @@
         <v>3</v>
       </c>
       <c r="B6" t="s">
-        <v>190</v>
+        <v>188</v>
       </c>
       <c r="D6">
         <v>3</v>
       </c>
       <c r="E6" t="s">
-        <v>191</v>
+        <v>189</v>
       </c>
     </row>
     <row r="7" spans="1:5">
@@ -3795,13 +3739,13 @@
         <v>4</v>
       </c>
       <c r="B7" t="s">
-        <v>192</v>
+        <v>190</v>
       </c>
       <c r="D7">
         <v>4</v>
       </c>
       <c r="E7" t="s">
-        <v>193</v>
+        <v>191</v>
       </c>
     </row>
     <row r="8" spans="1:5">
@@ -3809,13 +3753,13 @@
         <v>5</v>
       </c>
       <c r="B8" t="s">
-        <v>194</v>
+        <v>192</v>
       </c>
       <c r="D8">
         <v>5</v>
       </c>
       <c r="E8" t="s">
-        <v>195</v>
+        <v>193</v>
       </c>
     </row>
     <row r="9" spans="1:5">
@@ -3823,7 +3767,7 @@
         <v>6</v>
       </c>
       <c r="B9" t="s">
-        <v>196</v>
+        <v>194</v>
       </c>
     </row>
     <row r="10" spans="1:5">
@@ -3831,7 +3775,7 @@
         <v>7</v>
       </c>
       <c r="B10" t="s">
-        <v>197</v>
+        <v>195</v>
       </c>
     </row>
     <row r="11" spans="1:5">
@@ -3839,7 +3783,7 @@
         <v>8</v>
       </c>
       <c r="B11" t="s">
-        <v>198</v>
+        <v>196</v>
       </c>
     </row>
     <row r="12" spans="1:5">
@@ -3847,7 +3791,7 @@
         <v>9</v>
       </c>
       <c r="B12" t="s">
-        <v>199</v>
+        <v>197</v>
       </c>
     </row>
     <row r="13" spans="1:5">
@@ -3855,7 +3799,7 @@
         <v>10</v>
       </c>
       <c r="B13" t="s">
-        <v>200</v>
+        <v>198</v>
       </c>
     </row>
     <row r="14" spans="1:5">
@@ -3863,7 +3807,7 @@
         <v>11</v>
       </c>
       <c r="B14" t="s">
-        <v>201</v>
+        <v>199</v>
       </c>
     </row>
     <row r="15" spans="1:5">
@@ -3871,7 +3815,7 @@
         <v>12</v>
       </c>
       <c r="B15" t="s">
-        <v>202</v>
+        <v>200</v>
       </c>
     </row>
     <row r="16" spans="1:5">
@@ -3879,7 +3823,7 @@
         <v>13</v>
       </c>
       <c r="B16" t="s">
-        <v>203</v>
+        <v>201</v>
       </c>
     </row>
     <row r="17" spans="1:2">
@@ -3887,7 +3831,7 @@
         <v>14</v>
       </c>
       <c r="B17" t="s">
-        <v>204</v>
+        <v>202</v>
       </c>
     </row>
     <row r="18" spans="1:2">
@@ -3895,7 +3839,7 @@
         <v>15</v>
       </c>
       <c r="B18" t="s">
-        <v>205</v>
+        <v>203</v>
       </c>
     </row>
     <row r="19" spans="1:2">
@@ -3903,7 +3847,7 @@
         <v>16</v>
       </c>
       <c r="B19" t="s">
-        <v>206</v>
+        <v>204</v>
       </c>
     </row>
     <row r="20" spans="1:2">
@@ -3911,7 +3855,7 @@
         <v>17</v>
       </c>
       <c r="B20" t="s">
-        <v>207</v>
+        <v>205</v>
       </c>
     </row>
     <row r="21" spans="1:2">
@@ -3919,7 +3863,7 @@
         <v>18</v>
       </c>
       <c r="B21" t="s">
-        <v>208</v>
+        <v>206</v>
       </c>
     </row>
     <row r="22" spans="1:2">
@@ -3927,7 +3871,7 @@
         <v>19</v>
       </c>
       <c r="B22" t="s">
-        <v>209</v>
+        <v>207</v>
       </c>
     </row>
     <row r="23" spans="1:2">
@@ -3935,7 +3879,7 @@
         <v>20</v>
       </c>
       <c r="B23" t="s">
-        <v>210</v>
+        <v>208</v>
       </c>
     </row>
     <row r="24" spans="1:2">
@@ -3943,7 +3887,7 @@
         <v>21</v>
       </c>
       <c r="B24" t="s">
-        <v>211</v>
+        <v>209</v>
       </c>
     </row>
     <row r="25" spans="1:2">
@@ -3951,7 +3895,7 @@
         <v>22</v>
       </c>
       <c r="B25" t="s">
-        <v>212</v>
+        <v>210</v>
       </c>
     </row>
     <row r="26" spans="1:2">
@@ -3959,7 +3903,7 @@
         <v>23</v>
       </c>
       <c r="B26" t="s">
-        <v>213</v>
+        <v>211</v>
       </c>
     </row>
     <row r="27" spans="1:2">
@@ -3967,7 +3911,7 @@
         <v>24</v>
       </c>
       <c r="B27" t="s">
-        <v>214</v>
+        <v>212</v>
       </c>
     </row>
     <row r="28" spans="1:2">
@@ -3975,7 +3919,7 @@
         <v>25</v>
       </c>
       <c r="B28" t="s">
-        <v>215</v>
+        <v>213</v>
       </c>
     </row>
     <row r="29" spans="1:2">
@@ -3983,7 +3927,7 @@
         <v>26</v>
       </c>
       <c r="B29" t="s">
-        <v>216</v>
+        <v>214</v>
       </c>
     </row>
     <row r="30" spans="1:2">
@@ -3991,7 +3935,7 @@
         <v>27</v>
       </c>
       <c r="B30" t="s">
-        <v>217</v>
+        <v>215</v>
       </c>
     </row>
     <row r="31" spans="1:2">
@@ -3999,7 +3943,7 @@
         <v>28</v>
       </c>
       <c r="B31" t="s">
-        <v>218</v>
+        <v>216</v>
       </c>
     </row>
     <row r="32" spans="1:2">
@@ -4007,7 +3951,7 @@
         <v>29</v>
       </c>
       <c r="B32" t="s">
-        <v>219</v>
+        <v>217</v>
       </c>
     </row>
     <row r="33" spans="1:2">
@@ -4015,7 +3959,7 @@
         <v>30</v>
       </c>
       <c r="B33" t="s">
-        <v>220</v>
+        <v>218</v>
       </c>
     </row>
     <row r="34" spans="1:2">
@@ -4023,7 +3967,7 @@
         <v>31</v>
       </c>
       <c r="B34" t="s">
-        <v>221</v>
+        <v>219</v>
       </c>
     </row>
     <row r="35" spans="1:2">
@@ -4031,7 +3975,7 @@
         <v>32</v>
       </c>
       <c r="B35" t="s">
-        <v>222</v>
+        <v>220</v>
       </c>
     </row>
     <row r="36" spans="1:2">
@@ -4039,7 +3983,7 @@
         <v>33</v>
       </c>
       <c r="B36" t="s">
-        <v>223</v>
+        <v>221</v>
       </c>
     </row>
     <row r="37" spans="1:2">
@@ -4047,7 +3991,7 @@
         <v>34</v>
       </c>
       <c r="B37" t="s">
-        <v>224</v>
+        <v>222</v>
       </c>
     </row>
     <row r="38" spans="1:2">
@@ -4055,7 +3999,7 @@
         <v>35</v>
       </c>
       <c r="B38" t="s">
-        <v>225</v>
+        <v>223</v>
       </c>
     </row>
     <row r="39" spans="1:2">
@@ -4063,7 +4007,7 @@
         <v>36</v>
       </c>
       <c r="B39" t="s">
-        <v>226</v>
+        <v>224</v>
       </c>
     </row>
     <row r="40" spans="1:2">
@@ -4071,7 +4015,7 @@
         <v>37</v>
       </c>
       <c r="B40" t="s">
-        <v>227</v>
+        <v>225</v>
       </c>
     </row>
     <row r="41" spans="1:2">
@@ -4079,7 +4023,7 @@
         <v>38</v>
       </c>
       <c r="B41" t="s">
-        <v>228</v>
+        <v>226</v>
       </c>
     </row>
     <row r="42" spans="1:2">
@@ -4087,7 +4031,7 @@
         <v>39</v>
       </c>
       <c r="B42" t="s">
-        <v>229</v>
+        <v>227</v>
       </c>
     </row>
     <row r="43" spans="1:2">
@@ -4095,7 +4039,7 @@
         <v>40</v>
       </c>
       <c r="B43" t="s">
-        <v>230</v>
+        <v>228</v>
       </c>
     </row>
     <row r="44" spans="1:2">
@@ -4103,7 +4047,7 @@
         <v>41</v>
       </c>
       <c r="B44" t="s">
-        <v>231</v>
+        <v>229</v>
       </c>
     </row>
     <row r="45" spans="1:2">
@@ -4111,7 +4055,7 @@
         <v>42</v>
       </c>
       <c r="B45" t="s">
-        <v>232</v>
+        <v>230</v>
       </c>
     </row>
     <row r="46" spans="1:2">
@@ -4119,7 +4063,7 @@
         <v>43</v>
       </c>
       <c r="B46" t="s">
-        <v>233</v>
+        <v>231</v>
       </c>
     </row>
     <row r="47" spans="1:2">
@@ -4127,7 +4071,7 @@
         <v>44</v>
       </c>
       <c r="B47" t="s">
-        <v>234</v>
+        <v>232</v>
       </c>
     </row>
     <row r="48" spans="1:2">
@@ -4135,7 +4079,7 @@
         <v>45</v>
       </c>
       <c r="B48" t="s">
-        <v>235</v>
+        <v>233</v>
       </c>
     </row>
   </sheetData>

--- a/slots/resources/sample/SpecialPlay.xlsx
+++ b/slots/resources/sample/SpecialPlay.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="27945" windowHeight="12375"/>
+    <workbookView windowWidth="27945" windowHeight="12255"/>
   </bookViews>
   <sheets>
     <sheet name="SpecialPlay" sheetId="1" r:id="rId1"/>
@@ -137,7 +137,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="343" uniqueCount="234">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="339" uniqueCount="232">
   <si>
     <t>被动游戏ID</t>
   </si>
@@ -583,31 +583,13 @@
     <t>糖果派对</t>
   </si>
   <si>
-    <t>游戏开局就为第一层，第一层的常规和免费模式下，累计获得15个过关图标1会进入第二层，且过关图标1超过15个时，多余的会转变为过关图标2</t>
-  </si>
-  <si>
-    <t>3,16_15_17</t>
-  </si>
-  <si>
-    <t>SpecialMode模式ID，过关图标1_累计获得次数_过关图标2</t>
-  </si>
-  <si>
-    <t>第二层的常规和免费模式下，累计获得15个过关图标2会进入第三层，且过关图标2超过15个时，多余的会转变为过关图标3</t>
-  </si>
-  <si>
-    <t>2,17_15_18</t>
-  </si>
-  <si>
-    <t>SpecialMode模式ID，过关图标2_累计获得次数_过关图标2</t>
-  </si>
-  <si>
-    <t>第三层的常规和免费模式下，累计获得15个过关图标2会进入第一层，且过关图标3超过15个时，多余的会归零</t>
-  </si>
-  <si>
-    <t>1,18_15</t>
-  </si>
-  <si>
-    <t>SpecialMode模式ID，过关图标3_累计获得次数</t>
+    <t>游戏共三层，开局为第一层，累计获得15个过关图标会循环进入下一层，且当前层数过关图标超过15个时，多余的会转变为下一层过关图标（第三层到第一层不会继承过关图标）</t>
+  </si>
+  <si>
+    <t>1_16_15|2_17_15|3_18_15</t>
+  </si>
+  <si>
+    <t>层数_图案_累计个数|层数_图案_累计个数|层数_图案_累计个数</t>
   </si>
   <si>
     <t>黄金帝国</t>
@@ -646,7 +628,7 @@
     <t>1,1_1|2_2|3_3|4_4|5_5|6_6|7_7|8_8|9_9|10_10;2,1_2|2_4|3_6|4_8|5_10|6_12|7_14|8_16|9_18|10_20</t>
   </si>
   <si>
-    <t>3_10_10000|4_12_10000|5_14_10000</t>
+    <t>10,3_10_10000|4_12_10000|5_14_10000</t>
   </si>
   <si>
     <t>常规模式下，金框符号转换为百搭符号</t>
@@ -661,7 +643,7 @@
     <t>极速糖果1000</t>
   </si>
   <si>
-    <t>3_10_10000</t>
+    <t>8,3_10_10000</t>
   </si>
   <si>
     <t>相同位置中奖连续消除2次，此位置处获得x2，之后在此位置消除，每次消除乘倍值+2，最多增加至x32</t>
@@ -671,6 +653,18 @@
   </si>
   <si>
     <t>初始倍数_最高倍数</t>
+  </si>
+  <si>
+    <t>伽罗宝石</t>
+  </si>
+  <si>
+    <t>第四轴出现的图标的倍数及权重</t>
+  </si>
+  <si>
+    <t>10_1_5000|11_2_3000|12_3_0000|13_5_500|14_10_400|15_15_100</t>
+  </si>
+  <si>
+    <t>元素ID_图标倍数_权重</t>
   </si>
   <si>
     <t>旋转标识</t>
@@ -1022,13 +1016,13 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="10"/>
+      <b/>
+      <sz val="9"/>
       <name val="宋体"/>
       <charset val="134"/>
     </font>
     <font>
-      <b/>
-      <sz val="9"/>
+      <sz val="10"/>
       <name val="宋体"/>
       <charset val="134"/>
     </font>
@@ -1501,7 +1495,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="18">
+  <cellXfs count="23">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
@@ -1510,6 +1504,10 @@
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
@@ -1549,6 +1547,13 @@
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left"/>
     </xf>
   </cellXfs>
   <cellStyles count="52">
@@ -1881,185 +1886,185 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:J70"/>
+  <dimension ref="A1:J69"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25"/>
   <cols>
-    <col min="4" max="4" width="9.50833333333333" style="4" customWidth="1"/>
+    <col min="4" max="4" width="9.50833333333333" style="6" customWidth="1"/>
     <col min="5" max="5" width="61.75" customWidth="1"/>
     <col min="6" max="6" width="50.875" customWidth="1"/>
     <col min="7" max="7" width="74.7" customWidth="1"/>
-    <col min="8" max="8" width="26.3" style="5" customWidth="1"/>
-    <col min="9" max="9" width="19.375" style="5" customWidth="1"/>
+    <col min="8" max="8" width="26.3" style="7" customWidth="1"/>
+    <col min="9" max="9" width="19.375" style="7" customWidth="1"/>
     <col min="10" max="10" width="7.81666666666667" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" ht="16.5" spans="1:10">
-      <c r="A1" s="6" t="s">
+      <c r="A1" s="8" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="6" t="s">
+      <c r="B1" s="8" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="6"/>
-      <c r="D1" s="7" t="s">
+      <c r="C1" s="8"/>
+      <c r="D1" s="9" t="s">
         <v>2</v>
       </c>
-      <c r="E1" s="6"/>
-      <c r="F1" s="6" t="s">
+      <c r="E1" s="8"/>
+      <c r="F1" s="8" t="s">
         <v>3</v>
       </c>
-      <c r="G1" s="6" t="s">
+      <c r="G1" s="8" t="s">
         <v>4</v>
       </c>
-      <c r="H1" s="8" t="s">
+      <c r="H1" s="10" t="s">
         <v>5</v>
       </c>
-      <c r="I1" s="8" t="s">
+      <c r="I1" s="10" t="s">
         <v>6</v>
       </c>
-      <c r="J1" s="6"/>
+      <c r="J1" s="8"/>
     </row>
     <row r="2" ht="16.5" spans="1:10">
-      <c r="A2" s="6" t="s">
+      <c r="A2" s="8" t="s">
         <v>7</v>
       </c>
-      <c r="B2" s="6" t="s">
+      <c r="B2" s="8" t="s">
         <v>7</v>
       </c>
-      <c r="C2" s="6"/>
-      <c r="D2" s="7" t="s">
+      <c r="C2" s="8"/>
+      <c r="D2" s="9" t="s">
         <v>7</v>
       </c>
-      <c r="E2" s="6"/>
-      <c r="F2" s="6" t="s">
+      <c r="E2" s="8"/>
+      <c r="F2" s="8" t="s">
         <v>8</v>
       </c>
-      <c r="G2" s="6"/>
-      <c r="H2" s="9" t="s">
+      <c r="G2" s="8"/>
+      <c r="H2" s="11" t="s">
         <v>9</v>
       </c>
-      <c r="I2" s="10" t="s">
+      <c r="I2" s="12" t="s">
         <v>10</v>
       </c>
-      <c r="J2" s="6"/>
+      <c r="J2" s="8"/>
     </row>
     <row r="3" ht="16.5" spans="1:10">
-      <c r="A3" s="6" t="s">
+      <c r="A3" s="8" t="s">
         <v>11</v>
       </c>
-      <c r="B3" s="6" t="s">
+      <c r="B3" s="8" t="s">
         <v>12</v>
       </c>
-      <c r="C3" s="6"/>
-      <c r="D3" s="7" t="s">
+      <c r="C3" s="8"/>
+      <c r="D3" s="9" t="s">
         <v>13</v>
       </c>
-      <c r="E3" s="6"/>
-      <c r="F3" s="6" t="s">
+      <c r="E3" s="8"/>
+      <c r="F3" s="8" t="s">
         <v>14</v>
       </c>
-      <c r="G3" s="6"/>
-      <c r="H3" s="8" t="s">
+      <c r="G3" s="8"/>
+      <c r="H3" s="10" t="s">
         <v>15</v>
       </c>
-      <c r="I3" s="8" t="s">
+      <c r="I3" s="10" t="s">
         <v>16</v>
       </c>
-      <c r="J3" s="6"/>
+      <c r="J3" s="8"/>
     </row>
     <row r="4" ht="16.5" spans="1:10">
-      <c r="A4" s="6"/>
-      <c r="B4" s="6"/>
-      <c r="C4" s="6"/>
-      <c r="D4" s="7"/>
-      <c r="E4" s="6"/>
-      <c r="F4" s="6"/>
-      <c r="G4" s="6"/>
-      <c r="H4" s="8"/>
-      <c r="I4" s="8"/>
-      <c r="J4" s="6"/>
+      <c r="A4" s="8"/>
+      <c r="B4" s="8"/>
+      <c r="C4" s="8"/>
+      <c r="D4" s="9"/>
+      <c r="E4" s="8"/>
+      <c r="F4" s="8"/>
+      <c r="G4" s="8"/>
+      <c r="H4" s="10"/>
+      <c r="I4" s="10"/>
+      <c r="J4" s="8"/>
     </row>
     <row r="5" s="1" customFormat="1" ht="18" customHeight="1" spans="1:10">
       <c r="A5" s="2">
         <v>5001001</v>
       </c>
-      <c r="B5" s="11">
+      <c r="B5" s="13">
         <v>100100</v>
       </c>
-      <c r="C5" s="12" t="s">
+      <c r="C5" s="14" t="s">
         <v>17</v>
       </c>
-      <c r="D5" s="11">
+      <c r="D5" s="13">
         <v>1</v>
       </c>
       <c r="E5" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="F5" s="13" t="s">
+      <c r="F5" s="15" t="s">
         <v>19</v>
       </c>
-      <c r="G5" s="11" t="s">
+      <c r="G5" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="H5" s="14" t="s">
+      <c r="H5" s="16" t="s">
         <v>21</v>
       </c>
-      <c r="I5" s="14" t="s">
+      <c r="I5" s="16" t="s">
         <v>22</v>
       </c>
-      <c r="J5" s="11"/>
+      <c r="J5" s="13"/>
     </row>
     <row r="6" s="1" customFormat="1" ht="18" customHeight="1" spans="1:10">
       <c r="A6" s="2">
         <v>5001002</v>
       </c>
-      <c r="B6" s="11">
+      <c r="B6" s="13">
         <v>100100</v>
       </c>
-      <c r="C6" s="12" t="s">
+      <c r="C6" s="14" t="s">
         <v>17</v>
       </c>
-      <c r="D6" s="11">
+      <c r="D6" s="13">
         <v>2</v>
       </c>
       <c r="E6" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="F6" s="13" t="s">
+      <c r="F6" s="15" t="s">
         <v>24</v>
       </c>
-      <c r="G6" s="11" t="s">
+      <c r="G6" s="13" t="s">
         <v>25</v>
       </c>
-      <c r="H6" s="14"/>
-      <c r="I6" s="14"/>
-      <c r="J6" s="11"/>
+      <c r="H6" s="16"/>
+      <c r="I6" s="16"/>
+      <c r="J6" s="13"/>
     </row>
     <row r="7" s="1" customFormat="1" ht="18" customHeight="1" spans="1:10">
       <c r="A7" s="2">
         <v>5001007</v>
       </c>
-      <c r="B7" s="11">
+      <c r="B7" s="13">
         <v>100100</v>
       </c>
-      <c r="C7" s="12" t="s">
+      <c r="C7" s="14" t="s">
         <v>17</v>
       </c>
-      <c r="D7" s="11">
+      <c r="D7" s="13">
         <v>7</v>
       </c>
       <c r="E7" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="F7" s="13" t="s">
+      <c r="F7" s="15" t="s">
         <v>27</v>
       </c>
-      <c r="G7" s="11" t="s">
+      <c r="G7" s="13" t="s">
         <v>28</v>
       </c>
-      <c r="H7" s="14"/>
-      <c r="I7" s="14"/>
-      <c r="J7" s="11"/>
+      <c r="H7" s="16"/>
+      <c r="I7" s="16"/>
+      <c r="J7" s="13"/>
     </row>
     <row r="8" s="1" customFormat="1" ht="18" customHeight="1" spans="1:10">
       <c r="A8" s="2">
@@ -2077,14 +2082,14 @@
       <c r="E8" s="1" t="s">
         <v>30</v>
       </c>
-      <c r="F8" s="15" t="s">
+      <c r="F8" s="17" t="s">
         <v>31</v>
       </c>
       <c r="G8" s="1" t="s">
         <v>32</v>
       </c>
-      <c r="H8" s="16"/>
-      <c r="I8" s="16"/>
+      <c r="H8" s="18"/>
+      <c r="I8" s="18"/>
     </row>
     <row r="9" s="1" customFormat="1" ht="18" customHeight="1" spans="1:10">
       <c r="A9" s="2">
@@ -2102,14 +2107,14 @@
       <c r="E9" s="1" t="s">
         <v>33</v>
       </c>
-      <c r="F9" s="15" t="s">
+      <c r="F9" s="17" t="s">
         <v>34</v>
       </c>
       <c r="G9" s="1" t="s">
         <v>35</v>
       </c>
-      <c r="H9" s="16"/>
-      <c r="I9" s="16"/>
+      <c r="H9" s="18"/>
+      <c r="I9" s="18"/>
     </row>
     <row r="10" s="1" customFormat="1" ht="18" customHeight="1" spans="1:10">
       <c r="A10" s="2">
@@ -2127,96 +2132,96 @@
       <c r="E10" s="1" t="s">
         <v>37</v>
       </c>
-      <c r="F10" s="15" t="s">
+      <c r="F10" s="17" t="s">
         <v>38</v>
       </c>
       <c r="G10" s="1" t="s">
         <v>39</v>
       </c>
-      <c r="H10" s="16"/>
-      <c r="I10" s="16"/>
+      <c r="H10" s="18"/>
+      <c r="I10" s="18"/>
     </row>
     <row r="11" s="1" customFormat="1" ht="18" customHeight="1" spans="1:10">
       <c r="A11" s="2">
         <v>5024001</v>
       </c>
-      <c r="B11" s="11">
+      <c r="B11" s="13">
         <v>102400</v>
       </c>
-      <c r="C11" s="12" t="s">
+      <c r="C11" s="14" t="s">
         <v>17</v>
       </c>
-      <c r="D11" s="11">
+      <c r="D11" s="13">
         <v>1</v>
       </c>
       <c r="E11" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="F11" s="13" t="s">
+      <c r="F11" s="15" t="s">
         <v>40</v>
       </c>
-      <c r="G11" s="11" t="s">
+      <c r="G11" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="H11" s="14" t="s">
+      <c r="H11" s="16" t="s">
         <v>21</v>
       </c>
-      <c r="I11" s="14" t="s">
+      <c r="I11" s="16" t="s">
         <v>41</v>
       </c>
-      <c r="J11" s="11"/>
+      <c r="J11" s="13"/>
     </row>
     <row r="12" s="1" customFormat="1" ht="18" customHeight="1" spans="1:10">
       <c r="A12" s="2">
         <v>5024002</v>
       </c>
-      <c r="B12" s="11">
+      <c r="B12" s="13">
         <v>102400</v>
       </c>
-      <c r="C12" s="12" t="s">
+      <c r="C12" s="14" t="s">
         <v>17</v>
       </c>
-      <c r="D12" s="11">
+      <c r="D12" s="13">
         <v>2</v>
       </c>
       <c r="E12" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="F12" s="13" t="s">
+      <c r="F12" s="15" t="s">
         <v>42</v>
       </c>
-      <c r="G12" s="11" t="s">
+      <c r="G12" s="13" t="s">
         <v>25</v>
       </c>
-      <c r="H12" s="14"/>
-      <c r="I12" s="14"/>
-      <c r="J12" s="11"/>
+      <c r="H12" s="16"/>
+      <c r="I12" s="16"/>
+      <c r="J12" s="13"/>
     </row>
     <row r="13" s="1" customFormat="1" ht="18" customHeight="1" spans="1:10">
       <c r="A13" s="2">
         <v>5024007</v>
       </c>
-      <c r="B13" s="11">
+      <c r="B13" s="13">
         <v>102400</v>
       </c>
-      <c r="C13" s="12" t="s">
+      <c r="C13" s="14" t="s">
         <v>17</v>
       </c>
-      <c r="D13" s="11">
+      <c r="D13" s="13">
         <v>7</v>
       </c>
       <c r="E13" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="F13" s="13" t="s">
+      <c r="F13" s="15" t="s">
         <v>43</v>
       </c>
-      <c r="G13" s="11" t="s">
+      <c r="G13" s="13" t="s">
         <v>28</v>
       </c>
-      <c r="H13" s="14"/>
-      <c r="I13" s="14"/>
-      <c r="J13" s="11"/>
+      <c r="H13" s="16"/>
+      <c r="I13" s="16"/>
+      <c r="J13" s="13"/>
     </row>
     <row r="14" s="1" customFormat="1" ht="18" customHeight="1" spans="1:10">
       <c r="A14" s="2">
@@ -2234,14 +2239,14 @@
       <c r="E14" s="1" t="s">
         <v>30</v>
       </c>
-      <c r="F14" s="15" t="s">
+      <c r="F14" s="17" t="s">
         <v>31</v>
       </c>
       <c r="G14" s="1" t="s">
         <v>32</v>
       </c>
-      <c r="H14" s="16"/>
-      <c r="I14" s="16"/>
+      <c r="H14" s="18"/>
+      <c r="I14" s="18"/>
     </row>
     <row r="15" s="1" customFormat="1" ht="18" customHeight="1" spans="1:10">
       <c r="A15" s="2">
@@ -2259,98 +2264,98 @@
       <c r="E15" s="1" t="s">
         <v>33</v>
       </c>
-      <c r="F15" s="15" t="s">
+      <c r="F15" s="17" t="s">
         <v>34</v>
       </c>
       <c r="G15" s="1" t="s">
         <v>35</v>
       </c>
-      <c r="H15" s="16"/>
-      <c r="I15" s="16"/>
+      <c r="H15" s="18"/>
+      <c r="I15" s="18"/>
     </row>
     <row r="16" s="2" customFormat="1" ht="18" customHeight="1" spans="1:10">
       <c r="A16" s="2">
         <v>5022007</v>
       </c>
-      <c r="B16" s="17">
+      <c r="B16" s="19">
         <v>102200</v>
       </c>
-      <c r="C16" s="12" t="s">
+      <c r="C16" s="14" t="s">
         <v>45</v>
       </c>
-      <c r="D16" s="17">
+      <c r="D16" s="19">
         <v>7</v>
       </c>
       <c r="E16" s="2" t="s">
         <v>26</v>
       </c>
-      <c r="F16" s="13" t="s">
+      <c r="F16" s="15" t="s">
         <v>46</v>
       </c>
-      <c r="G16" s="17" t="s">
+      <c r="G16" s="19" t="s">
         <v>28</v>
       </c>
-      <c r="H16" s="12"/>
-      <c r="I16" s="12"/>
-      <c r="J16" s="17"/>
+      <c r="H16" s="14"/>
+      <c r="I16" s="14"/>
+      <c r="J16" s="19"/>
     </row>
     <row r="17" s="2" customFormat="1" ht="18" customHeight="1" spans="1:10">
       <c r="A17" s="2">
         <v>5022008</v>
       </c>
-      <c r="B17" s="17">
+      <c r="B17" s="19">
         <v>102200</v>
       </c>
-      <c r="C17" s="12" t="s">
+      <c r="C17" s="14" t="s">
         <v>45</v>
       </c>
-      <c r="D17" s="17">
+      <c r="D17" s="19">
         <v>8</v>
       </c>
       <c r="E17" s="2" t="s">
         <v>47</v>
       </c>
-      <c r="F17" s="13" t="s">
+      <c r="F17" s="15" t="s">
         <v>48</v>
       </c>
-      <c r="G17" s="17" t="s">
+      <c r="G17" s="19" t="s">
         <v>49</v>
       </c>
-      <c r="H17" s="12"/>
-      <c r="I17" s="12"/>
-      <c r="J17" s="17"/>
+      <c r="H17" s="14"/>
+      <c r="I17" s="14"/>
+      <c r="J17" s="19"/>
     </row>
     <row r="18" s="2" customFormat="1" ht="18" customHeight="1" spans="1:10">
       <c r="A18" s="2">
         <v>5021001</v>
       </c>
-      <c r="B18" s="17">
+      <c r="B18" s="19">
         <v>102100</v>
       </c>
-      <c r="C18" s="12" t="s">
+      <c r="C18" s="14" t="s">
         <v>50</v>
       </c>
-      <c r="D18" s="17">
+      <c r="D18" s="19">
         <v>4</v>
       </c>
       <c r="E18" s="2" t="s">
         <v>51</v>
       </c>
-      <c r="F18" s="13" t="s">
+      <c r="F18" s="15" t="s">
         <v>52</v>
       </c>
-      <c r="G18" s="17" t="s">
+      <c r="G18" s="19" t="s">
         <v>53</v>
       </c>
-      <c r="H18" s="12"/>
-      <c r="I18" s="12"/>
-      <c r="J18" s="17"/>
+      <c r="H18" s="14"/>
+      <c r="I18" s="14"/>
+      <c r="J18" s="19"/>
     </row>
     <row r="19" ht="16.5" spans="1:10">
       <c r="A19" s="2">
         <v>5021002</v>
       </c>
-      <c r="B19" s="17">
+      <c r="B19" s="19">
         <v>102100</v>
       </c>
       <c r="C19" t="s">
@@ -2362,7 +2367,7 @@
       <c r="E19" t="s">
         <v>33</v>
       </c>
-      <c r="F19" s="15" t="s">
+      <c r="F19" s="17" t="s">
         <v>54</v>
       </c>
       <c r="G19" s="1" t="s">
@@ -2373,7 +2378,7 @@
       <c r="A20" s="2">
         <v>5018001</v>
       </c>
-      <c r="B20" s="17">
+      <c r="B20" s="19">
         <v>101800</v>
       </c>
       <c r="C20" t="s">
@@ -2385,20 +2390,20 @@
       <c r="E20" t="s">
         <v>56</v>
       </c>
-      <c r="F20" s="15" t="s">
+      <c r="F20" s="17" t="s">
         <v>57</v>
       </c>
       <c r="G20" s="1" t="s">
         <v>58</v>
       </c>
-      <c r="H20" s="5"/>
-      <c r="I20" s="5"/>
+      <c r="H20" s="7"/>
+      <c r="I20" s="7"/>
     </row>
     <row r="21" customFormat="1" ht="16.5" spans="1:10">
       <c r="A21" s="2">
         <v>5018002</v>
       </c>
-      <c r="B21" s="17">
+      <c r="B21" s="19">
         <v>101800</v>
       </c>
       <c r="C21" t="s">
@@ -2410,20 +2415,20 @@
       <c r="E21" t="s">
         <v>33</v>
       </c>
-      <c r="F21" s="15" t="s">
+      <c r="F21" s="17" t="s">
         <v>59</v>
       </c>
       <c r="G21" s="1" t="s">
         <v>35</v>
       </c>
-      <c r="H21" s="5"/>
-      <c r="I21" s="5"/>
+      <c r="H21" s="7"/>
+      <c r="I21" s="7"/>
     </row>
     <row r="22" customFormat="1" ht="16.5" spans="1:10">
       <c r="A22" s="2">
         <v>5025001</v>
       </c>
-      <c r="B22" s="17">
+      <c r="B22" s="19">
         <v>102500</v>
       </c>
       <c r="C22" t="s">
@@ -2435,20 +2440,20 @@
       <c r="E22" t="s">
         <v>33</v>
       </c>
-      <c r="F22" s="15" t="s">
+      <c r="F22" s="17" t="s">
         <v>61</v>
       </c>
       <c r="G22" s="1" t="s">
         <v>35</v>
       </c>
-      <c r="H22" s="5"/>
-      <c r="I22" s="5"/>
+      <c r="H22" s="7"/>
+      <c r="I22" s="7"/>
     </row>
     <row r="23" customFormat="1" ht="16.5" spans="1:10">
       <c r="A23" s="2">
         <v>5023005</v>
       </c>
-      <c r="B23" s="17">
+      <c r="B23" s="19">
         <v>102300</v>
       </c>
       <c r="C23" t="s">
@@ -2460,20 +2465,20 @@
       <c r="E23" t="s">
         <v>33</v>
       </c>
-      <c r="F23" s="15" t="s">
+      <c r="F23" s="17" t="s">
         <v>63</v>
       </c>
       <c r="G23" s="1" t="s">
         <v>35</v>
       </c>
-      <c r="H23" s="5"/>
-      <c r="I23" s="5"/>
+      <c r="H23" s="7"/>
+      <c r="I23" s="7"/>
     </row>
     <row r="24" customFormat="1" ht="16.5" spans="1:10">
       <c r="A24" s="2">
         <v>5023008</v>
       </c>
-      <c r="B24" s="17">
+      <c r="B24" s="19">
         <v>102300</v>
       </c>
       <c r="C24" t="s">
@@ -2485,20 +2490,20 @@
       <c r="E24" t="s">
         <v>64</v>
       </c>
-      <c r="F24" s="15" t="s">
+      <c r="F24" s="17" t="s">
         <v>65</v>
       </c>
       <c r="G24" s="1" t="s">
         <v>66</v>
       </c>
-      <c r="H24" s="5"/>
-      <c r="I24" s="5"/>
+      <c r="H24" s="7"/>
+      <c r="I24" s="7"/>
     </row>
     <row r="25" customFormat="1" ht="16.5" spans="1:10">
       <c r="A25" s="2">
         <v>5023009</v>
       </c>
-      <c r="B25" s="17">
+      <c r="B25" s="19">
         <v>102300</v>
       </c>
       <c r="C25" t="s">
@@ -2516,14 +2521,14 @@
       <c r="G25" s="1" t="s">
         <v>66</v>
       </c>
-      <c r="H25" s="5"/>
-      <c r="I25" s="5"/>
+      <c r="H25" s="7"/>
+      <c r="I25" s="7"/>
     </row>
     <row r="26" customFormat="1" ht="16.5" spans="1:10">
       <c r="A26" s="2">
         <v>5034001</v>
       </c>
-      <c r="B26" s="17">
+      <c r="B26" s="19">
         <v>103400</v>
       </c>
       <c r="C26" t="s">
@@ -2535,20 +2540,20 @@
       <c r="E26" t="s">
         <v>70</v>
       </c>
-      <c r="F26" s="15" t="s">
+      <c r="F26" s="17" t="s">
         <v>71</v>
       </c>
       <c r="G26" s="1" t="s">
         <v>72</v>
       </c>
-      <c r="H26" s="5"/>
-      <c r="I26" s="5"/>
+      <c r="H26" s="7"/>
+      <c r="I26" s="7"/>
     </row>
     <row r="27" customFormat="1" ht="16.5" spans="1:10">
       <c r="A27" s="2">
         <v>5034002</v>
       </c>
-      <c r="B27" s="17">
+      <c r="B27" s="19">
         <v>103400</v>
       </c>
       <c r="C27" t="s">
@@ -2560,20 +2565,20 @@
       <c r="E27" t="s">
         <v>73</v>
       </c>
-      <c r="F27" s="15" t="s">
+      <c r="F27" s="17" t="s">
         <v>74</v>
       </c>
       <c r="G27" s="1" t="s">
         <v>75</v>
       </c>
-      <c r="H27" s="5"/>
-      <c r="I27" s="5"/>
+      <c r="H27" s="7"/>
+      <c r="I27" s="7"/>
     </row>
     <row r="28" customFormat="1" ht="16.5" spans="1:10">
       <c r="A28" s="2">
         <v>5034003</v>
       </c>
-      <c r="B28" s="17">
+      <c r="B28" s="19">
         <v>103400</v>
       </c>
       <c r="C28" t="s">
@@ -2585,20 +2590,20 @@
       <c r="E28" t="s">
         <v>76</v>
       </c>
-      <c r="F28" s="15" t="s">
+      <c r="F28" s="17" t="s">
         <v>77</v>
       </c>
       <c r="G28" s="1" t="s">
         <v>78</v>
       </c>
-      <c r="H28" s="5"/>
-      <c r="I28" s="5"/>
+      <c r="H28" s="7"/>
+      <c r="I28" s="7"/>
     </row>
     <row r="29" customFormat="1" ht="16.5" spans="1:10">
       <c r="A29" s="2">
         <v>5034004</v>
       </c>
-      <c r="B29" s="17">
+      <c r="B29" s="19">
         <v>103400</v>
       </c>
       <c r="C29" t="s">
@@ -2610,20 +2615,20 @@
       <c r="E29" t="s">
         <v>79</v>
       </c>
-      <c r="F29" s="15" t="s">
+      <c r="F29" s="17" t="s">
         <v>80</v>
       </c>
       <c r="G29" s="1" t="s">
         <v>81</v>
       </c>
-      <c r="H29" s="5"/>
-      <c r="I29" s="5"/>
+      <c r="H29" s="7"/>
+      <c r="I29" s="7"/>
     </row>
     <row r="30" customFormat="1" ht="16.5" spans="1:10">
       <c r="A30" s="2">
         <v>5035001</v>
       </c>
-      <c r="B30" s="17">
+      <c r="B30" s="19">
         <v>103500</v>
       </c>
       <c r="C30" t="s">
@@ -2635,20 +2640,20 @@
       <c r="E30" t="s">
         <v>83</v>
       </c>
-      <c r="F30" s="15" t="s">
+      <c r="F30" s="17" t="s">
         <v>84</v>
       </c>
       <c r="G30" s="1" t="s">
         <v>85</v>
       </c>
-      <c r="H30" s="5"/>
-      <c r="I30" s="5"/>
+      <c r="H30" s="7"/>
+      <c r="I30" s="7"/>
     </row>
     <row r="31" customFormat="1" ht="16.5" spans="1:10">
       <c r="A31" s="2">
         <v>5035011</v>
       </c>
-      <c r="B31" s="17">
+      <c r="B31" s="19">
         <v>103501</v>
       </c>
       <c r="C31" t="s">
@@ -2660,20 +2665,20 @@
       <c r="E31" t="s">
         <v>83</v>
       </c>
-      <c r="F31" s="15" t="s">
+      <c r="F31" s="17" t="s">
         <v>84</v>
       </c>
       <c r="G31" s="1" t="s">
         <v>85</v>
       </c>
-      <c r="H31" s="5"/>
-      <c r="I31" s="5"/>
+      <c r="H31" s="7"/>
+      <c r="I31" s="7"/>
     </row>
     <row r="32" customFormat="1" ht="16.5" spans="1:10">
       <c r="A32" s="2">
         <v>5036001</v>
       </c>
-      <c r="B32" s="17">
+      <c r="B32" s="19">
         <v>103600</v>
       </c>
       <c r="C32" t="s">
@@ -2685,20 +2690,20 @@
       <c r="E32" t="s">
         <v>88</v>
       </c>
-      <c r="F32" s="15" t="s">
+      <c r="F32" s="17" t="s">
         <v>84</v>
       </c>
       <c r="G32" s="1" t="s">
         <v>89</v>
       </c>
-      <c r="H32" s="5"/>
-      <c r="I32" s="5"/>
+      <c r="H32" s="7"/>
+      <c r="I32" s="7"/>
     </row>
     <row r="33" customFormat="1" ht="16.5" spans="1:10">
       <c r="A33" s="2">
         <v>5036002</v>
       </c>
-      <c r="B33" s="17">
+      <c r="B33" s="19">
         <v>103600</v>
       </c>
       <c r="C33" t="s">
@@ -2710,20 +2715,20 @@
       <c r="E33" t="s">
         <v>90</v>
       </c>
-      <c r="F33" s="15" t="s">
+      <c r="F33" s="17" t="s">
         <v>91</v>
       </c>
       <c r="G33" s="1" t="s">
         <v>92</v>
       </c>
-      <c r="H33" s="5"/>
-      <c r="I33" s="5"/>
+      <c r="H33" s="7"/>
+      <c r="I33" s="7"/>
     </row>
     <row r="34" customFormat="1" ht="16.5" spans="1:10">
       <c r="A34" s="2">
         <v>5028001</v>
       </c>
-      <c r="B34" s="17">
+      <c r="B34" s="19">
         <v>102800</v>
       </c>
       <c r="C34" t="s">
@@ -2735,20 +2740,20 @@
       <c r="E34" t="s">
         <v>33</v>
       </c>
-      <c r="F34" s="15" t="s">
+      <c r="F34" s="17" t="s">
         <v>94</v>
       </c>
       <c r="G34" s="1" t="s">
         <v>35</v>
       </c>
-      <c r="H34" s="5"/>
-      <c r="I34" s="5"/>
+      <c r="H34" s="7"/>
+      <c r="I34" s="7"/>
     </row>
     <row r="35" customFormat="1" ht="16.5" spans="1:10">
       <c r="A35" s="2">
         <v>5028002</v>
       </c>
-      <c r="B35" s="17">
+      <c r="B35" s="19">
         <v>102800</v>
       </c>
       <c r="C35" t="s">
@@ -2760,20 +2765,20 @@
       <c r="E35" t="s">
         <v>95</v>
       </c>
-      <c r="F35" s="15" t="s">
+      <c r="F35" s="17" t="s">
         <v>96</v>
       </c>
       <c r="G35" s="1" t="s">
         <v>97</v>
       </c>
-      <c r="H35" s="5"/>
-      <c r="I35" s="5"/>
+      <c r="H35" s="7"/>
+      <c r="I35" s="7"/>
     </row>
     <row r="36" customFormat="1" ht="16.5" spans="1:10">
       <c r="A36" s="2">
         <v>5034011</v>
       </c>
-      <c r="B36" s="17">
+      <c r="B36" s="19">
         <v>103401</v>
       </c>
       <c r="C36" t="s">
@@ -2785,20 +2790,20 @@
       <c r="E36" t="s">
         <v>70</v>
       </c>
-      <c r="F36" s="15" t="s">
+      <c r="F36" s="17" t="s">
         <v>71</v>
       </c>
       <c r="G36" s="1" t="s">
         <v>72</v>
       </c>
-      <c r="H36" s="5"/>
-      <c r="I36" s="5"/>
+      <c r="H36" s="7"/>
+      <c r="I36" s="7"/>
     </row>
     <row r="37" customFormat="1" ht="16.5" spans="1:10">
       <c r="A37" s="2">
         <v>5034012</v>
       </c>
-      <c r="B37" s="17">
+      <c r="B37" s="19">
         <v>103402</v>
       </c>
       <c r="C37" t="s">
@@ -2810,20 +2815,20 @@
       <c r="E37" t="s">
         <v>73</v>
       </c>
-      <c r="F37" s="15" t="s">
+      <c r="F37" s="17" t="s">
         <v>99</v>
       </c>
       <c r="G37" s="1" t="s">
         <v>75</v>
       </c>
-      <c r="H37" s="5"/>
-      <c r="I37" s="5"/>
+      <c r="H37" s="7"/>
+      <c r="I37" s="7"/>
     </row>
     <row r="38" customFormat="1" ht="16.5" spans="1:10">
       <c r="A38" s="2">
         <v>5034013</v>
       </c>
-      <c r="B38" s="17">
+      <c r="B38" s="19">
         <v>103403</v>
       </c>
       <c r="C38" t="s">
@@ -2835,20 +2840,20 @@
       <c r="E38" t="s">
         <v>76</v>
       </c>
-      <c r="F38" s="15" t="s">
+      <c r="F38" s="17" t="s">
         <v>100</v>
       </c>
       <c r="G38" s="1" t="s">
         <v>78</v>
       </c>
-      <c r="H38" s="5"/>
-      <c r="I38" s="5"/>
+      <c r="H38" s="7"/>
+      <c r="I38" s="7"/>
     </row>
     <row r="39" customFormat="1" ht="16.5" spans="1:10">
       <c r="A39" s="2">
         <v>5034014</v>
       </c>
-      <c r="B39" s="17">
+      <c r="B39" s="19">
         <v>103404</v>
       </c>
       <c r="C39" t="s">
@@ -2860,52 +2865,52 @@
       <c r="E39" t="s">
         <v>79</v>
       </c>
-      <c r="F39" s="15" t="s">
+      <c r="F39" s="17" t="s">
         <v>80</v>
       </c>
       <c r="G39" s="1" t="s">
         <v>81</v>
       </c>
-      <c r="H39" s="5"/>
-      <c r="I39" s="5"/>
+      <c r="H39" s="7"/>
+      <c r="I39" s="7"/>
     </row>
     <row r="40" s="2" customFormat="1" ht="18" customHeight="1" spans="1:10">
       <c r="A40" s="2">
         <v>5020001</v>
       </c>
-      <c r="B40" s="17">
+      <c r="B40" s="19">
         <v>102000</v>
       </c>
-      <c r="C40" s="12" t="s">
+      <c r="C40" s="14" t="s">
         <v>101</v>
       </c>
-      <c r="D40" s="17">
+      <c r="D40" s="19">
         <v>1</v>
       </c>
       <c r="E40" s="2" t="s">
         <v>26</v>
       </c>
-      <c r="F40" s="13" t="s">
+      <c r="F40" s="15" t="s">
         <v>102</v>
       </c>
-      <c r="G40" s="17" t="s">
+      <c r="G40" s="19" t="s">
         <v>28</v>
       </c>
-      <c r="H40" s="12"/>
-      <c r="I40" s="12"/>
-      <c r="J40" s="17"/>
+      <c r="H40" s="14"/>
+      <c r="I40" s="14"/>
+      <c r="J40" s="19"/>
     </row>
     <row r="41" s="3" customFormat="1" ht="16.5" spans="1:10">
       <c r="A41" s="2">
         <v>5020002</v>
       </c>
-      <c r="B41" s="17">
+      <c r="B41" s="19">
         <v>102000</v>
       </c>
-      <c r="C41" s="12" t="s">
+      <c r="C41" s="14" t="s">
         <v>101</v>
       </c>
-      <c r="D41" s="17">
+      <c r="D41" s="19">
         <v>2</v>
       </c>
       <c r="F41" s="3" t="s">
@@ -2916,13 +2921,13 @@
       <c r="A42" s="2">
         <v>5027001</v>
       </c>
-      <c r="B42" s="17">
+      <c r="B42" s="19">
         <v>102700</v>
       </c>
-      <c r="C42" s="12" t="s">
+      <c r="C42" s="14" t="s">
         <v>104</v>
       </c>
-      <c r="D42" s="17">
+      <c r="D42" s="19">
         <v>1</v>
       </c>
       <c r="E42" s="3" t="s">
@@ -2939,13 +2944,13 @@
       <c r="A43" s="2">
         <v>5027002</v>
       </c>
-      <c r="B43" s="17">
+      <c r="B43" s="19">
         <v>102700</v>
       </c>
-      <c r="C43" s="12" t="s">
+      <c r="C43" s="14" t="s">
         <v>104</v>
       </c>
-      <c r="D43" s="17">
+      <c r="D43" s="19">
         <v>2</v>
       </c>
       <c r="E43" s="3" t="s">
@@ -2962,7 +2967,7 @@
       <c r="A44" s="2">
         <v>5037001</v>
       </c>
-      <c r="B44" s="17">
+      <c r="B44" s="19">
         <v>103700</v>
       </c>
       <c r="C44" t="s">
@@ -2974,20 +2979,20 @@
       <c r="E44" t="s">
         <v>110</v>
       </c>
-      <c r="F44" s="15" t="s">
+      <c r="F44" s="17" t="s">
         <v>84</v>
       </c>
       <c r="G44" s="1" t="s">
         <v>89</v>
       </c>
-      <c r="H44" s="5"/>
-      <c r="I44" s="5"/>
+      <c r="H44" s="7"/>
+      <c r="I44" s="7"/>
     </row>
     <row r="45" customFormat="1" ht="16.5" spans="1:10">
       <c r="A45" s="2">
         <v>5037002</v>
       </c>
-      <c r="B45" s="17">
+      <c r="B45" s="19">
         <v>103700</v>
       </c>
       <c r="C45" t="s">
@@ -2999,20 +3004,20 @@
       <c r="E45" t="s">
         <v>111</v>
       </c>
-      <c r="F45" s="15" t="s">
+      <c r="F45" s="17" t="s">
         <v>112</v>
       </c>
       <c r="G45" s="1" t="s">
         <v>113</v>
       </c>
-      <c r="H45" s="5"/>
-      <c r="I45" s="5"/>
+      <c r="H45" s="7"/>
+      <c r="I45" s="7"/>
     </row>
     <row r="46" customFormat="1" ht="16.5" spans="1:10">
       <c r="A46" s="2">
         <v>5037003</v>
       </c>
-      <c r="B46" s="17">
+      <c r="B46" s="19">
         <v>103700</v>
       </c>
       <c r="C46" t="s">
@@ -3024,20 +3029,20 @@
       <c r="E46" t="s">
         <v>114</v>
       </c>
-      <c r="F46" s="15" t="s">
+      <c r="F46" s="17" t="s">
         <v>115</v>
       </c>
       <c r="G46" s="1" t="s">
         <v>116</v>
       </c>
-      <c r="H46" s="5"/>
-      <c r="I46" s="5"/>
+      <c r="H46" s="7"/>
+      <c r="I46" s="7"/>
     </row>
     <row r="47" customFormat="1" ht="16.5" spans="1:10">
       <c r="A47" s="2">
         <v>5031001</v>
       </c>
-      <c r="B47" s="17">
+      <c r="B47" s="19">
         <v>103100</v>
       </c>
       <c r="C47" t="s">
@@ -3049,20 +3054,20 @@
       <c r="E47" t="s">
         <v>33</v>
       </c>
-      <c r="F47" s="15" t="s">
+      <c r="F47" s="17" t="s">
         <v>118</v>
       </c>
       <c r="G47" s="1" t="s">
         <v>35</v>
       </c>
-      <c r="H47" s="5"/>
-      <c r="I47" s="5"/>
+      <c r="H47" s="7"/>
+      <c r="I47" s="7"/>
     </row>
     <row r="48" customFormat="1" ht="16.5" spans="1:10">
       <c r="A48" s="2">
         <v>5040001</v>
       </c>
-      <c r="B48" s="17">
+      <c r="B48" s="19">
         <v>104000</v>
       </c>
       <c r="C48" t="s">
@@ -3074,20 +3079,20 @@
       <c r="E48" t="s">
         <v>33</v>
       </c>
-      <c r="F48" s="15" t="s">
+      <c r="F48" s="17" t="s">
         <v>120</v>
       </c>
       <c r="G48" s="1" t="s">
         <v>35</v>
       </c>
-      <c r="H48" s="5"/>
-      <c r="I48" s="5"/>
+      <c r="H48" s="7"/>
+      <c r="I48" s="7"/>
     </row>
     <row r="49" customFormat="1" ht="16.5" spans="1:9">
       <c r="A49" s="2">
         <v>5039001</v>
       </c>
-      <c r="B49" s="17">
+      <c r="B49" s="19">
         <v>103900</v>
       </c>
       <c r="C49" t="s">
@@ -3099,20 +3104,20 @@
       <c r="E49" t="s">
         <v>122</v>
       </c>
-      <c r="F49" s="15" t="s">
+      <c r="F49" s="17" t="s">
         <v>123</v>
       </c>
       <c r="G49" s="1" t="s">
         <v>124</v>
       </c>
-      <c r="H49" s="5"/>
-      <c r="I49" s="5"/>
+      <c r="H49" s="7"/>
+      <c r="I49" s="7"/>
     </row>
     <row r="50" customFormat="1" ht="16.5" spans="1:9">
       <c r="A50" s="2">
         <v>5016001</v>
       </c>
-      <c r="B50" s="17">
+      <c r="B50" s="19">
         <v>101600</v>
       </c>
       <c r="C50" t="s">
@@ -3124,20 +3129,20 @@
       <c r="E50" t="s">
         <v>33</v>
       </c>
-      <c r="F50" s="15" t="s">
+      <c r="F50" s="17" t="s">
         <v>126</v>
       </c>
       <c r="G50" s="1" t="s">
         <v>35</v>
       </c>
-      <c r="H50" s="5"/>
-      <c r="I50" s="5"/>
+      <c r="H50" s="7"/>
+      <c r="I50" s="7"/>
     </row>
     <row r="51" customFormat="1" ht="16.5" spans="1:9">
       <c r="A51" s="2">
         <v>5016002</v>
       </c>
-      <c r="B51" s="17">
+      <c r="B51" s="19">
         <v>101600</v>
       </c>
       <c r="C51" t="s">
@@ -3149,20 +3154,20 @@
       <c r="E51" t="s">
         <v>127</v>
       </c>
-      <c r="F51" s="15" t="s">
+      <c r="F51" s="17" t="s">
         <v>128</v>
       </c>
       <c r="G51" s="1" t="s">
         <v>129</v>
       </c>
-      <c r="H51" s="5"/>
-      <c r="I51" s="5"/>
+      <c r="H51" s="7"/>
+      <c r="I51" s="7"/>
     </row>
     <row r="52" customFormat="1" ht="16.5" spans="1:9">
       <c r="A52" s="2">
         <v>5015001</v>
       </c>
-      <c r="B52" s="17">
+      <c r="B52" s="19">
         <v>101500</v>
       </c>
       <c r="C52" t="s">
@@ -3174,20 +3179,20 @@
       <c r="E52" t="s">
         <v>131</v>
       </c>
-      <c r="F52" s="15" t="s">
+      <c r="F52" s="17" t="s">
         <v>132</v>
       </c>
       <c r="G52" t="s">
         <v>133</v>
       </c>
-      <c r="H52" s="5"/>
-      <c r="I52" s="5"/>
+      <c r="H52" s="7"/>
+      <c r="I52" s="7"/>
     </row>
     <row r="53" customFormat="1" ht="16.5" spans="1:9">
       <c r="A53" s="2">
         <v>5015002</v>
       </c>
-      <c r="B53" s="17">
+      <c r="B53" s="19">
         <v>101500</v>
       </c>
       <c r="C53" t="s">
@@ -3205,14 +3210,14 @@
       <c r="G53" s="1" t="s">
         <v>135</v>
       </c>
-      <c r="H53" s="5"/>
-      <c r="I53" s="5"/>
+      <c r="H53" s="7"/>
+      <c r="I53" s="7"/>
     </row>
     <row r="54" customFormat="1" ht="16.5" spans="1:9">
       <c r="A54" s="2">
         <v>5026001</v>
       </c>
-      <c r="B54" s="17">
+      <c r="B54" s="19">
         <v>102600</v>
       </c>
       <c r="C54" t="s">
@@ -3224,20 +3229,20 @@
       <c r="E54" t="s">
         <v>30</v>
       </c>
-      <c r="F54" s="15" t="s">
+      <c r="F54" s="17" t="s">
         <v>137</v>
       </c>
       <c r="G54" s="1" t="s">
         <v>32</v>
       </c>
-      <c r="H54" s="5"/>
-      <c r="I54" s="5"/>
+      <c r="H54" s="7"/>
+      <c r="I54" s="7"/>
     </row>
     <row r="55" customFormat="1" ht="16.5" spans="1:9">
       <c r="A55" s="2">
         <v>5026003</v>
       </c>
-      <c r="B55" s="17">
+      <c r="B55" s="19">
         <v>102600</v>
       </c>
       <c r="C55" t="s">
@@ -3249,20 +3254,20 @@
       <c r="E55" t="s">
         <v>138</v>
       </c>
-      <c r="F55" s="15" t="s">
+      <c r="F55" s="17" t="s">
         <v>139</v>
       </c>
       <c r="G55" s="1" t="s">
         <v>140</v>
       </c>
-      <c r="H55" s="5"/>
-      <c r="I55" s="5"/>
+      <c r="H55" s="7"/>
+      <c r="I55" s="7"/>
     </row>
     <row r="56" customFormat="1" ht="16.5" spans="1:9">
       <c r="A56" s="2">
         <v>5050001</v>
       </c>
-      <c r="B56" s="17">
+      <c r="B56" s="19">
         <v>105000</v>
       </c>
       <c r="C56" t="s">
@@ -3274,20 +3279,20 @@
       <c r="E56" t="s">
         <v>33</v>
       </c>
-      <c r="F56" s="15" t="s">
+      <c r="F56" s="17" t="s">
         <v>142</v>
       </c>
       <c r="G56" s="1" t="s">
         <v>143</v>
       </c>
-      <c r="H56" s="5"/>
-      <c r="I56" s="5"/>
+      <c r="H56" s="7"/>
+      <c r="I56" s="7"/>
     </row>
     <row r="57" customFormat="1" ht="16.5" spans="1:9">
       <c r="A57" s="2">
         <v>5050002</v>
       </c>
-      <c r="B57" s="17">
+      <c r="B57" s="19">
         <v>105000</v>
       </c>
       <c r="C57" t="s">
@@ -3299,124 +3304,124 @@
       <c r="E57" t="s">
         <v>144</v>
       </c>
-      <c r="F57" s="15" t="s">
+      <c r="F57" s="17" t="s">
         <v>145</v>
       </c>
       <c r="G57" s="1" t="s">
         <v>146</v>
       </c>
-      <c r="H57" s="5"/>
-      <c r="I57" s="5"/>
-    </row>
-    <row r="58" customFormat="1" ht="16.5" spans="1:9">
+      <c r="H57" s="7"/>
+      <c r="I57" s="7"/>
+    </row>
+    <row r="58" s="4" customFormat="1" ht="16.5" spans="1:9">
       <c r="A58" s="2">
         <v>5051001</v>
       </c>
-      <c r="B58" s="17">
+      <c r="B58" s="19">
         <v>105100</v>
       </c>
-      <c r="C58" t="s">
+      <c r="C58" s="4" t="s">
         <v>147</v>
       </c>
-      <c r="D58" s="1">
+      <c r="D58" s="2">
         <v>1</v>
       </c>
-      <c r="E58" t="s">
+      <c r="E58" s="4" t="s">
         <v>148</v>
       </c>
-      <c r="F58" s="15" t="s">
+      <c r="F58" s="20" t="s">
         <v>149</v>
       </c>
-      <c r="G58" s="1" t="s">
+      <c r="G58" s="2" t="s">
         <v>150</v>
       </c>
-      <c r="H58" s="5"/>
-      <c r="I58" s="5"/>
+      <c r="H58" s="21"/>
+      <c r="I58" s="21"/>
     </row>
     <row r="59" customFormat="1" ht="16.5" spans="1:9">
       <c r="A59" s="2">
-        <v>5051002</v>
-      </c>
-      <c r="B59" s="17">
-        <v>105100</v>
+        <v>5054001</v>
+      </c>
+      <c r="B59" s="19">
+        <v>105400</v>
       </c>
       <c r="C59" t="s">
-        <v>147</v>
+        <v>151</v>
       </c>
       <c r="D59" s="1">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E59" t="s">
-        <v>151</v>
-      </c>
-      <c r="F59" s="15" t="s">
         <v>152</v>
+      </c>
+      <c r="F59" s="17" t="s">
+        <v>145</v>
       </c>
       <c r="G59" s="1" t="s">
         <v>153</v>
       </c>
-      <c r="H59" s="5"/>
-      <c r="I59" s="5"/>
+      <c r="H59" s="7"/>
+      <c r="I59" s="7"/>
     </row>
     <row r="60" customFormat="1" ht="16.5" spans="1:9">
       <c r="A60" s="2">
-        <v>5051003</v>
-      </c>
-      <c r="B60" s="17">
-        <v>105100</v>
+        <v>5054002</v>
+      </c>
+      <c r="B60" s="19">
+        <v>105400</v>
       </c>
       <c r="C60" t="s">
-        <v>147</v>
+        <v>151</v>
       </c>
       <c r="D60" s="1">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E60" t="s">
+        <v>33</v>
+      </c>
+      <c r="F60" s="17" t="s">
         <v>154</v>
       </c>
-      <c r="F60" s="15" t="s">
-        <v>155</v>
-      </c>
       <c r="G60" s="1" t="s">
-        <v>156</v>
-      </c>
-      <c r="H60" s="5"/>
-      <c r="I60" s="5"/>
+        <v>143</v>
+      </c>
+      <c r="H60" s="7"/>
+      <c r="I60" s="7"/>
     </row>
     <row r="61" customFormat="1" ht="16.5" spans="1:9">
       <c r="A61" s="2">
-        <v>5054001</v>
-      </c>
-      <c r="B61" s="17">
-        <v>105400</v>
+        <v>5008001</v>
+      </c>
+      <c r="B61" s="19">
+        <v>100800</v>
       </c>
       <c r="C61" t="s">
-        <v>157</v>
+        <v>155</v>
       </c>
       <c r="D61" s="1">
         <v>1</v>
       </c>
       <c r="E61" t="s">
+        <v>156</v>
+      </c>
+      <c r="F61" s="17" t="s">
+        <v>157</v>
+      </c>
+      <c r="G61" s="1" t="s">
         <v>158</v>
       </c>
-      <c r="F61" s="15" t="s">
-        <v>145</v>
-      </c>
-      <c r="G61" s="1" t="s">
-        <v>159</v>
-      </c>
-      <c r="H61" s="5"/>
-      <c r="I61" s="5"/>
+      <c r="H61" s="7"/>
+      <c r="I61" s="7"/>
     </row>
     <row r="62" customFormat="1" ht="16.5" spans="1:9">
       <c r="A62" s="2">
-        <v>5054002</v>
-      </c>
-      <c r="B62" s="17">
-        <v>105400</v>
+        <v>5008002</v>
+      </c>
+      <c r="B62" s="19">
+        <v>100800</v>
       </c>
       <c r="C62" t="s">
-        <v>157</v>
+        <v>155</v>
       </c>
       <c r="D62" s="1">
         <v>2</v>
@@ -3424,214 +3429,189 @@
       <c r="E62" t="s">
         <v>33</v>
       </c>
-      <c r="F62" s="15" t="s">
-        <v>160</v>
-      </c>
-      <c r="G62" s="1" t="s">
-        <v>143</v>
-      </c>
-      <c r="H62" s="5"/>
-      <c r="I62" s="5"/>
+      <c r="F62" s="3" t="s">
+        <v>159</v>
+      </c>
+      <c r="G62" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="H62" s="7"/>
+      <c r="I62" s="7"/>
     </row>
     <row r="63" customFormat="1" ht="16.5" spans="1:9">
       <c r="A63" s="2">
-        <v>5008001</v>
-      </c>
-      <c r="B63" s="17">
-        <v>100800</v>
+        <v>5053001</v>
+      </c>
+      <c r="B63" s="19">
+        <v>105300</v>
       </c>
       <c r="C63" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="D63" s="1">
-        <v>1</v>
-      </c>
-      <c r="E63" t="s">
-        <v>162</v>
-      </c>
-      <c r="F63" s="15" t="s">
-        <v>163</v>
+        <v>4</v>
+      </c>
+      <c r="E63" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="F63" s="17" t="s">
+        <v>31</v>
       </c>
       <c r="G63" s="1" t="s">
-        <v>164</v>
-      </c>
-      <c r="H63" s="5"/>
-      <c r="I63" s="5"/>
+        <v>32</v>
+      </c>
+      <c r="H63" s="7"/>
+      <c r="I63" s="7"/>
     </row>
     <row r="64" customFormat="1" ht="16.5" spans="1:9">
       <c r="A64" s="2">
-        <v>5008002</v>
-      </c>
-      <c r="B64" s="17">
-        <v>100800</v>
+        <v>5057001</v>
+      </c>
+      <c r="B64" s="19">
+        <v>105700</v>
       </c>
       <c r="C64" t="s">
         <v>161</v>
       </c>
       <c r="D64" s="1">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E64" t="s">
-        <v>33</v>
-      </c>
-      <c r="F64" s="3" t="s">
-        <v>165</v>
-      </c>
-      <c r="G64" s="3" t="s">
-        <v>35</v>
-      </c>
-      <c r="H64" s="5"/>
-      <c r="I64" s="5"/>
+        <v>30</v>
+      </c>
+      <c r="F64" s="17" t="s">
+        <v>162</v>
+      </c>
+      <c r="G64" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="H64" s="7"/>
+      <c r="I64" s="7"/>
     </row>
     <row r="65" customFormat="1" ht="16.5" spans="1:9">
       <c r="A65" s="2">
-        <v>5053001</v>
-      </c>
-      <c r="B65" s="17">
-        <v>105300</v>
+        <v>5057002</v>
+      </c>
+      <c r="B65" s="19">
+        <v>105700</v>
       </c>
       <c r="C65" t="s">
-        <v>166</v>
+        <v>161</v>
       </c>
       <c r="D65" s="1">
-        <v>4</v>
-      </c>
-      <c r="E65" s="1" t="s">
-        <v>30</v>
-      </c>
-      <c r="F65" s="15" t="s">
-        <v>31</v>
-      </c>
-      <c r="G65" s="1" t="s">
-        <v>32</v>
-      </c>
-      <c r="H65" s="5"/>
-      <c r="I65" s="5"/>
+        <v>2</v>
+      </c>
+      <c r="E65" t="s">
+        <v>33</v>
+      </c>
+      <c r="F65" s="3" t="s">
+        <v>163</v>
+      </c>
+      <c r="G65" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="H65" s="7"/>
+      <c r="I65" s="7"/>
     </row>
     <row r="66" customFormat="1" ht="16.5" spans="1:9">
       <c r="A66" s="2">
-        <v>5057001</v>
-      </c>
-      <c r="B66" s="17">
+        <v>5057003</v>
+      </c>
+      <c r="B66" s="19">
         <v>105700</v>
       </c>
       <c r="C66" t="s">
-        <v>167</v>
+        <v>161</v>
       </c>
       <c r="D66" s="1">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E66" t="s">
-        <v>30</v>
-      </c>
-      <c r="F66" s="15" t="s">
-        <v>168</v>
+        <v>164</v>
+      </c>
+      <c r="F66" s="17" t="s">
+        <v>165</v>
       </c>
       <c r="G66" s="1" t="s">
-        <v>32</v>
-      </c>
-      <c r="H66" s="5"/>
-      <c r="I66" s="5"/>
+        <v>166</v>
+      </c>
+      <c r="H66" s="7"/>
+      <c r="I66" s="7"/>
     </row>
     <row r="67" customFormat="1" ht="16.5" spans="1:9">
       <c r="A67" s="2">
-        <v>5057002</v>
-      </c>
-      <c r="B67" s="17">
-        <v>105700</v>
+        <v>5058001</v>
+      </c>
+      <c r="B67" s="19">
+        <v>105800</v>
       </c>
       <c r="C67" t="s">
         <v>167</v>
       </c>
       <c r="D67" s="1">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E67" t="s">
         <v>33</v>
       </c>
       <c r="F67" s="3" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="G67" s="3" t="s">
         <v>35</v>
       </c>
-      <c r="H67" s="5"/>
-      <c r="I67" s="5"/>
+      <c r="H67" s="7"/>
+      <c r="I67" s="7"/>
     </row>
     <row r="68" customFormat="1" ht="16.5" spans="1:9">
       <c r="A68" s="2">
-        <v>5057003</v>
-      </c>
-      <c r="B68" s="17">
-        <v>105700</v>
+        <v>5058002</v>
+      </c>
+      <c r="B68" s="19">
+        <v>105800</v>
       </c>
       <c r="C68" t="s">
         <v>167</v>
       </c>
       <c r="D68" s="1">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E68" t="s">
+        <v>169</v>
+      </c>
+      <c r="F68" s="3" t="s">
         <v>170</v>
       </c>
-      <c r="F68" s="15" t="s">
+      <c r="G68" s="3" t="s">
         <v>171</v>
       </c>
-      <c r="G68" s="1" t="s">
+      <c r="H68" s="7"/>
+      <c r="I68" s="7"/>
+    </row>
+    <row r="69" s="5" customFormat="1" spans="1:9">
+      <c r="A69" s="5">
+        <v>5055001</v>
+      </c>
+      <c r="B69" s="5">
+        <v>105500</v>
+      </c>
+      <c r="C69" s="5" t="s">
         <v>172</v>
       </c>
-      <c r="H68" s="5"/>
-      <c r="I68" s="5"/>
-    </row>
-    <row r="69" customFormat="1" ht="16.5" spans="1:9">
-      <c r="A69" s="2">
-        <v>5058001</v>
-      </c>
-      <c r="B69" s="17">
-        <v>105800</v>
-      </c>
-      <c r="C69" t="s">
+      <c r="D69" s="5">
+        <v>1</v>
+      </c>
+      <c r="E69" s="5" t="s">
         <v>173</v>
       </c>
-      <c r="D69" s="1">
-        <v>1</v>
-      </c>
-      <c r="E69" t="s">
-        <v>33</v>
-      </c>
-      <c r="F69" s="3" t="s">
+      <c r="F69" s="5" t="s">
         <v>174</v>
       </c>
-      <c r="G69" s="3" t="s">
-        <v>35</v>
-      </c>
-      <c r="H69" s="5"/>
-      <c r="I69" s="5"/>
-    </row>
-    <row r="70" customFormat="1" ht="16.5" spans="1:9">
-      <c r="A70" s="2">
-        <v>5058002</v>
-      </c>
-      <c r="B70" s="17">
-        <v>105800</v>
-      </c>
-      <c r="C70" t="s">
-        <v>173</v>
-      </c>
-      <c r="D70" s="1">
-        <v>2</v>
-      </c>
-      <c r="E70" t="s">
+      <c r="G69" s="5" t="s">
         <v>175</v>
       </c>
-      <c r="F70" s="3" t="s">
-        <v>176</v>
-      </c>
-      <c r="G70" s="3" t="s">
-        <v>177</v>
-      </c>
-      <c r="H70" s="5"/>
-      <c r="I70" s="5"/>
+      <c r="H69" s="22"/>
+      <c r="I69" s="22"/>
     </row>
   </sheetData>
   <conditionalFormatting sqref="H2">
@@ -3658,24 +3638,24 @@
   <sheetData>
     <row r="1" spans="1:5">
       <c r="A1" t="s">
-        <v>178</v>
+        <v>176</v>
       </c>
       <c r="D1" t="s">
-        <v>179</v>
+        <v>177</v>
       </c>
     </row>
     <row r="2" spans="1:5">
       <c r="A2" t="s">
-        <v>180</v>
+        <v>178</v>
       </c>
       <c r="B2" t="s">
-        <v>181</v>
+        <v>179</v>
       </c>
       <c r="D2" t="s">
-        <v>180</v>
+        <v>178</v>
       </c>
       <c r="E2" t="s">
-        <v>181</v>
+        <v>179</v>
       </c>
     </row>
     <row r="3" spans="1:5">
@@ -3683,13 +3663,13 @@
         <v>0</v>
       </c>
       <c r="B3" t="s">
-        <v>182</v>
+        <v>180</v>
       </c>
       <c r="D3">
         <v>0</v>
       </c>
       <c r="E3" t="s">
-        <v>183</v>
+        <v>181</v>
       </c>
     </row>
     <row r="4" spans="1:5">
@@ -3697,13 +3677,13 @@
         <v>1</v>
       </c>
       <c r="B4" t="s">
-        <v>184</v>
+        <v>182</v>
       </c>
       <c r="D4">
         <v>1</v>
       </c>
       <c r="E4" t="s">
-        <v>185</v>
+        <v>183</v>
       </c>
     </row>
     <row r="5" spans="1:5">
@@ -3711,13 +3691,13 @@
         <v>2</v>
       </c>
       <c r="B5" t="s">
-        <v>186</v>
+        <v>184</v>
       </c>
       <c r="D5">
         <v>2</v>
       </c>
       <c r="E5" t="s">
-        <v>187</v>
+        <v>185</v>
       </c>
     </row>
     <row r="6" spans="1:5">
@@ -3725,13 +3705,13 @@
         <v>3</v>
       </c>
       <c r="B6" t="s">
-        <v>188</v>
+        <v>186</v>
       </c>
       <c r="D6">
         <v>3</v>
       </c>
       <c r="E6" t="s">
-        <v>189</v>
+        <v>187</v>
       </c>
     </row>
     <row r="7" spans="1:5">
@@ -3739,13 +3719,13 @@
         <v>4</v>
       </c>
       <c r="B7" t="s">
-        <v>190</v>
+        <v>188</v>
       </c>
       <c r="D7">
         <v>4</v>
       </c>
       <c r="E7" t="s">
-        <v>191</v>
+        <v>189</v>
       </c>
     </row>
     <row r="8" spans="1:5">
@@ -3753,13 +3733,13 @@
         <v>5</v>
       </c>
       <c r="B8" t="s">
-        <v>192</v>
+        <v>190</v>
       </c>
       <c r="D8">
         <v>5</v>
       </c>
       <c r="E8" t="s">
-        <v>193</v>
+        <v>191</v>
       </c>
     </row>
     <row r="9" spans="1:5">
@@ -3767,7 +3747,7 @@
         <v>6</v>
       </c>
       <c r="B9" t="s">
-        <v>194</v>
+        <v>192</v>
       </c>
     </row>
     <row r="10" spans="1:5">
@@ -3775,7 +3755,7 @@
         <v>7</v>
       </c>
       <c r="B10" t="s">
-        <v>195</v>
+        <v>193</v>
       </c>
     </row>
     <row r="11" spans="1:5">
@@ -3783,7 +3763,7 @@
         <v>8</v>
       </c>
       <c r="B11" t="s">
-        <v>196</v>
+        <v>194</v>
       </c>
     </row>
     <row r="12" spans="1:5">
@@ -3791,7 +3771,7 @@
         <v>9</v>
       </c>
       <c r="B12" t="s">
-        <v>197</v>
+        <v>195</v>
       </c>
     </row>
     <row r="13" spans="1:5">
@@ -3799,7 +3779,7 @@
         <v>10</v>
       </c>
       <c r="B13" t="s">
-        <v>198</v>
+        <v>196</v>
       </c>
     </row>
     <row r="14" spans="1:5">
@@ -3807,7 +3787,7 @@
         <v>11</v>
       </c>
       <c r="B14" t="s">
-        <v>199</v>
+        <v>197</v>
       </c>
     </row>
     <row r="15" spans="1:5">
@@ -3815,7 +3795,7 @@
         <v>12</v>
       </c>
       <c r="B15" t="s">
-        <v>200</v>
+        <v>198</v>
       </c>
     </row>
     <row r="16" spans="1:5">
@@ -3823,7 +3803,7 @@
         <v>13</v>
       </c>
       <c r="B16" t="s">
-        <v>201</v>
+        <v>199</v>
       </c>
     </row>
     <row r="17" spans="1:2">
@@ -3831,7 +3811,7 @@
         <v>14</v>
       </c>
       <c r="B17" t="s">
-        <v>202</v>
+        <v>200</v>
       </c>
     </row>
     <row r="18" spans="1:2">
@@ -3839,7 +3819,7 @@
         <v>15</v>
       </c>
       <c r="B18" t="s">
-        <v>203</v>
+        <v>201</v>
       </c>
     </row>
     <row r="19" spans="1:2">
@@ -3847,7 +3827,7 @@
         <v>16</v>
       </c>
       <c r="B19" t="s">
-        <v>204</v>
+        <v>202</v>
       </c>
     </row>
     <row r="20" spans="1:2">
@@ -3855,7 +3835,7 @@
         <v>17</v>
       </c>
       <c r="B20" t="s">
-        <v>205</v>
+        <v>203</v>
       </c>
     </row>
     <row r="21" spans="1:2">
@@ -3863,7 +3843,7 @@
         <v>18</v>
       </c>
       <c r="B21" t="s">
-        <v>206</v>
+        <v>204</v>
       </c>
     </row>
     <row r="22" spans="1:2">
@@ -3871,7 +3851,7 @@
         <v>19</v>
       </c>
       <c r="B22" t="s">
-        <v>207</v>
+        <v>205</v>
       </c>
     </row>
     <row r="23" spans="1:2">
@@ -3879,7 +3859,7 @@
         <v>20</v>
       </c>
       <c r="B23" t="s">
-        <v>208</v>
+        <v>206</v>
       </c>
     </row>
     <row r="24" spans="1:2">
@@ -3887,7 +3867,7 @@
         <v>21</v>
       </c>
       <c r="B24" t="s">
-        <v>209</v>
+        <v>207</v>
       </c>
     </row>
     <row r="25" spans="1:2">
@@ -3895,7 +3875,7 @@
         <v>22</v>
       </c>
       <c r="B25" t="s">
-        <v>210</v>
+        <v>208</v>
       </c>
     </row>
     <row r="26" spans="1:2">
@@ -3903,7 +3883,7 @@
         <v>23</v>
       </c>
       <c r="B26" t="s">
-        <v>211</v>
+        <v>209</v>
       </c>
     </row>
     <row r="27" spans="1:2">
@@ -3911,7 +3891,7 @@
         <v>24</v>
       </c>
       <c r="B27" t="s">
-        <v>212</v>
+        <v>210</v>
       </c>
     </row>
     <row r="28" spans="1:2">
@@ -3919,7 +3899,7 @@
         <v>25</v>
       </c>
       <c r="B28" t="s">
-        <v>213</v>
+        <v>211</v>
       </c>
     </row>
     <row r="29" spans="1:2">
@@ -3927,7 +3907,7 @@
         <v>26</v>
       </c>
       <c r="B29" t="s">
-        <v>214</v>
+        <v>212</v>
       </c>
     </row>
     <row r="30" spans="1:2">
@@ -3935,7 +3915,7 @@
         <v>27</v>
       </c>
       <c r="B30" t="s">
-        <v>215</v>
+        <v>213</v>
       </c>
     </row>
     <row r="31" spans="1:2">
@@ -3943,7 +3923,7 @@
         <v>28</v>
       </c>
       <c r="B31" t="s">
-        <v>216</v>
+        <v>214</v>
       </c>
     </row>
     <row r="32" spans="1:2">
@@ -3951,7 +3931,7 @@
         <v>29</v>
       </c>
       <c r="B32" t="s">
-        <v>217</v>
+        <v>215</v>
       </c>
     </row>
     <row r="33" spans="1:2">
@@ -3959,7 +3939,7 @@
         <v>30</v>
       </c>
       <c r="B33" t="s">
-        <v>218</v>
+        <v>216</v>
       </c>
     </row>
     <row r="34" spans="1:2">
@@ -3967,7 +3947,7 @@
         <v>31</v>
       </c>
       <c r="B34" t="s">
-        <v>219</v>
+        <v>217</v>
       </c>
     </row>
     <row r="35" spans="1:2">
@@ -3975,7 +3955,7 @@
         <v>32</v>
       </c>
       <c r="B35" t="s">
-        <v>220</v>
+        <v>218</v>
       </c>
     </row>
     <row r="36" spans="1:2">
@@ -3983,7 +3963,7 @@
         <v>33</v>
       </c>
       <c r="B36" t="s">
-        <v>221</v>
+        <v>219</v>
       </c>
     </row>
     <row r="37" spans="1:2">
@@ -3991,7 +3971,7 @@
         <v>34</v>
       </c>
       <c r="B37" t="s">
-        <v>222</v>
+        <v>220</v>
       </c>
     </row>
     <row r="38" spans="1:2">
@@ -3999,7 +3979,7 @@
         <v>35</v>
       </c>
       <c r="B38" t="s">
-        <v>223</v>
+        <v>221</v>
       </c>
     </row>
     <row r="39" spans="1:2">
@@ -4007,7 +3987,7 @@
         <v>36</v>
       </c>
       <c r="B39" t="s">
-        <v>224</v>
+        <v>222</v>
       </c>
     </row>
     <row r="40" spans="1:2">
@@ -4015,7 +3995,7 @@
         <v>37</v>
       </c>
       <c r="B40" t="s">
-        <v>225</v>
+        <v>223</v>
       </c>
     </row>
     <row r="41" spans="1:2">
@@ -4023,7 +4003,7 @@
         <v>38</v>
       </c>
       <c r="B41" t="s">
-        <v>226</v>
+        <v>224</v>
       </c>
     </row>
     <row r="42" spans="1:2">
@@ -4031,7 +4011,7 @@
         <v>39</v>
       </c>
       <c r="B42" t="s">
-        <v>227</v>
+        <v>225</v>
       </c>
     </row>
     <row r="43" spans="1:2">
@@ -4039,7 +4019,7 @@
         <v>40</v>
       </c>
       <c r="B43" t="s">
-        <v>228</v>
+        <v>226</v>
       </c>
     </row>
     <row r="44" spans="1:2">
@@ -4047,7 +4027,7 @@
         <v>41</v>
       </c>
       <c r="B44" t="s">
-        <v>229</v>
+        <v>227</v>
       </c>
     </row>
     <row r="45" spans="1:2">
@@ -4055,7 +4035,7 @@
         <v>42</v>
       </c>
       <c r="B45" t="s">
-        <v>230</v>
+        <v>228</v>
       </c>
     </row>
     <row r="46" spans="1:2">
@@ -4063,7 +4043,7 @@
         <v>43</v>
       </c>
       <c r="B46" t="s">
-        <v>231</v>
+        <v>229</v>
       </c>
     </row>
     <row r="47" spans="1:2">
@@ -4071,7 +4051,7 @@
         <v>44</v>
       </c>
       <c r="B47" t="s">
-        <v>232</v>
+        <v>230</v>
       </c>
     </row>
     <row r="48" spans="1:2">
@@ -4079,7 +4059,7 @@
         <v>45</v>
       </c>
       <c r="B48" t="s">
-        <v>233</v>
+        <v>231</v>
       </c>
     </row>
   </sheetData>

--- a/slots/resources/sample/SpecialPlay.xlsx
+++ b/slots/resources/sample/SpecialPlay.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="27945" windowHeight="12255"/>
+    <workbookView windowWidth="28800" windowHeight="11925"/>
   </bookViews>
   <sheets>
     <sheet name="SpecialPlay" sheetId="1" r:id="rId1"/>
@@ -137,7 +137,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="307" uniqueCount="214">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="343" uniqueCount="234">
   <si>
     <t>被动游戏ID</t>
   </si>
@@ -532,24 +532,21 @@
     <t>狼月</t>
   </si>
   <si>
-    <t>手动选择小游戏：中奖ID,小游戏1_小游戏2_小游戏3|中奖ID,小游戏1_小游戏2……</t>
-  </si>
-  <si>
-    <t>1015400314,30150001_30150002_30150003</t>
-  </si>
-  <si>
-    <t>BaseElementReward表中中奖ID，小游戏1_小游戏2_小游戏3|……</t>
-  </si>
-  <si>
     <t>免费递增奖励倍数模式下，每次免费旋转结算时原赔率乘以此倍率值</t>
   </si>
   <si>
-    <t>7_5</t>
+    <t>5_100</t>
   </si>
   <si>
     <t>免费游戏中，初始获得5的乘倍值，每次旋转结算后乘倍值曾加5，最多可增加值100</t>
   </si>
   <si>
+    <t>15_1</t>
+  </si>
+  <si>
+    <t>元素id_次数</t>
+  </si>
+  <si>
     <t>寻宝黄金城</t>
   </si>
   <si>
@@ -611,6 +608,69 @@
   </si>
   <si>
     <t>SpecialMode模式ID，过关图标3_累计获得次数</t>
+  </si>
+  <si>
+    <t>黄金帝国</t>
+  </si>
+  <si>
+    <t>免费模式下，乘倍率随着中奖次数增加</t>
+  </si>
+  <si>
+    <t>SpecialMode模式ID,中奖次数_中奖倍率|中奖次数_中奖倍率|……</t>
+  </si>
+  <si>
+    <t>4,13,4_8_10000|5_10_10000|6_12_10000</t>
+  </si>
+  <si>
+    <t>招财猫</t>
+  </si>
+  <si>
+    <t>出现招财猫符号时，乘倍值+2,出现多个此符号，倍数相加</t>
+  </si>
+  <si>
+    <t>11_2</t>
+  </si>
+  <si>
+    <t>符号id_乘倍值，普通模式每局结算乘倍值清零，免费模式乘倍值将累加</t>
+  </si>
+  <si>
+    <t>13,4_10_10000|5_12_10000|6_14_10000</t>
+  </si>
+  <si>
+    <t>麻将胡了2</t>
+  </si>
+  <si>
+    <t>赏金大对决</t>
+  </si>
+  <si>
+    <t>1,1_1|2_2|3_3|4_4|5_5|6_6|7_7|8_8|9_9|10_10;2,1_2|2_4|3_6|4_8|5_10|6_12|7_14|8_16|9_18|10_20</t>
+  </si>
+  <si>
+    <t>10,3_10_10000|4_12_10000|5_14_10000</t>
+  </si>
+  <si>
+    <t>常规模式下，金框符号转换为百搭符号</t>
+  </si>
+  <si>
+    <t>9_1_1</t>
+  </si>
+  <si>
+    <t>元素id_金框符号权重_百搭符号权重|元素id_金框符号权重_百搭符号权重|元素id_金框符号权重_百搭符号权重</t>
+  </si>
+  <si>
+    <t>极速糖果1000</t>
+  </si>
+  <si>
+    <t>8,3_10_10000</t>
+  </si>
+  <si>
+    <t>相同位置中奖连续消除2次，此位置处获得x2，之后在此位置消除，每次消除乘倍值+2，最多增加至x32</t>
+  </si>
+  <si>
+    <t>2_32</t>
+  </si>
+  <si>
+    <t>初始倍数_最高倍数</t>
   </si>
   <si>
     <t>旋转标识</t>
@@ -1821,7 +1881,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:J61"/>
+  <dimension ref="A1:J70"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25"/>
   <cols>
     <col min="4" max="4" width="9.50833333333333" style="4" customWidth="1"/>
@@ -3117,7 +3177,7 @@
       <c r="F52" s="15" t="s">
         <v>132</v>
       </c>
-      <c r="G52" s="1" t="s">
+      <c r="G52" t="s">
         <v>133</v>
       </c>
       <c r="H52" s="5"/>
@@ -3137,216 +3197,441 @@
         <v>2</v>
       </c>
       <c r="E53" t="s">
+        <v>33</v>
+      </c>
+      <c r="F53" s="3" t="s">
         <v>134</v>
       </c>
-      <c r="F53" s="15" t="s">
+      <c r="G53" s="1" t="s">
         <v>135</v>
-      </c>
-      <c r="G53" t="s">
-        <v>136</v>
       </c>
       <c r="H53" s="5"/>
       <c r="I53" s="5"/>
     </row>
     <row r="54" customFormat="1" ht="16.5" spans="1:9">
       <c r="A54" s="2">
-        <v>5015003</v>
+        <v>5026001</v>
       </c>
       <c r="B54" s="17">
-        <v>101500</v>
+        <v>102600</v>
       </c>
       <c r="C54" t="s">
-        <v>130</v>
+        <v>136</v>
       </c>
       <c r="D54" s="1">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E54" t="s">
-        <v>33</v>
-      </c>
-      <c r="F54" s="3" t="s">
-        <v>105</v>
+        <v>30</v>
+      </c>
+      <c r="F54" s="15" t="s">
+        <v>137</v>
       </c>
       <c r="G54" s="1" t="s">
-        <v>35</v>
+        <v>32</v>
       </c>
       <c r="H54" s="5"/>
       <c r="I54" s="5"/>
     </row>
     <row r="55" customFormat="1" ht="16.5" spans="1:9">
       <c r="A55" s="2">
-        <v>5026001</v>
+        <v>5026003</v>
       </c>
       <c r="B55" s="17">
         <v>102600</v>
       </c>
       <c r="C55" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="D55" s="1">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E55" t="s">
-        <v>30</v>
+        <v>138</v>
       </c>
       <c r="F55" s="15" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="G55" s="1" t="s">
-        <v>32</v>
+        <v>140</v>
       </c>
       <c r="H55" s="5"/>
       <c r="I55" s="5"/>
     </row>
     <row r="56" customFormat="1" ht="16.5" spans="1:9">
       <c r="A56" s="2">
-        <v>5026003</v>
+        <v>5050001</v>
       </c>
       <c r="B56" s="17">
-        <v>102600</v>
+        <v>105000</v>
       </c>
       <c r="C56" t="s">
-        <v>137</v>
+        <v>141</v>
       </c>
       <c r="D56" s="1">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E56" t="s">
-        <v>139</v>
+        <v>33</v>
       </c>
       <c r="F56" s="15" t="s">
-        <v>140</v>
+        <v>142</v>
       </c>
       <c r="G56" s="1" t="s">
-        <v>141</v>
+        <v>143</v>
       </c>
       <c r="H56" s="5"/>
       <c r="I56" s="5"/>
     </row>
     <row r="57" customFormat="1" ht="16.5" spans="1:9">
       <c r="A57" s="2">
-        <v>5050001</v>
+        <v>5050002</v>
       </c>
       <c r="B57" s="17">
         <v>105000</v>
       </c>
       <c r="C57" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="D57" s="1">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E57" t="s">
-        <v>33</v>
+        <v>144</v>
       </c>
       <c r="F57" s="15" t="s">
-        <v>143</v>
+        <v>145</v>
       </c>
       <c r="G57" s="1" t="s">
-        <v>144</v>
+        <v>146</v>
       </c>
       <c r="H57" s="5"/>
       <c r="I57" s="5"/>
     </row>
     <row r="58" customFormat="1" ht="16.5" spans="1:9">
       <c r="A58" s="2">
-        <v>5050002</v>
+        <v>5051001</v>
       </c>
       <c r="B58" s="17">
-        <v>105000</v>
+        <v>105100</v>
       </c>
       <c r="C58" t="s">
-        <v>142</v>
+        <v>147</v>
       </c>
       <c r="D58" s="1">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E58" t="s">
-        <v>145</v>
+        <v>148</v>
       </c>
       <c r="F58" s="15" t="s">
-        <v>146</v>
+        <v>149</v>
       </c>
       <c r="G58" s="1" t="s">
-        <v>147</v>
+        <v>150</v>
       </c>
       <c r="H58" s="5"/>
       <c r="I58" s="5"/>
     </row>
     <row r="59" customFormat="1" ht="16.5" spans="1:9">
       <c r="A59" s="2">
-        <v>5051001</v>
+        <v>5051002</v>
       </c>
       <c r="B59" s="17">
         <v>105100</v>
       </c>
       <c r="C59" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="D59" s="1">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E59" t="s">
-        <v>149</v>
+        <v>151</v>
       </c>
       <c r="F59" s="15" t="s">
-        <v>150</v>
+        <v>152</v>
       </c>
       <c r="G59" s="1" t="s">
-        <v>151</v>
+        <v>153</v>
       </c>
       <c r="H59" s="5"/>
       <c r="I59" s="5"/>
     </row>
     <row r="60" customFormat="1" ht="16.5" spans="1:9">
       <c r="A60" s="2">
-        <v>5051002</v>
+        <v>5051003</v>
       </c>
       <c r="B60" s="17">
         <v>105100</v>
       </c>
       <c r="C60" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="D60" s="1">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E60" t="s">
-        <v>152</v>
+        <v>154</v>
       </c>
       <c r="F60" s="15" t="s">
-        <v>153</v>
+        <v>155</v>
       </c>
       <c r="G60" s="1" t="s">
-        <v>154</v>
+        <v>156</v>
       </c>
       <c r="H60" s="5"/>
       <c r="I60" s="5"/>
     </row>
     <row r="61" customFormat="1" ht="16.5" spans="1:9">
       <c r="A61" s="2">
-        <v>5051003</v>
+        <v>5054001</v>
       </c>
       <c r="B61" s="17">
-        <v>105100</v>
+        <v>105400</v>
       </c>
       <c r="C61" t="s">
-        <v>148</v>
+        <v>157</v>
       </c>
       <c r="D61" s="1">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E61" t="s">
-        <v>155</v>
+        <v>158</v>
       </c>
       <c r="F61" s="15" t="s">
-        <v>156</v>
+        <v>145</v>
       </c>
       <c r="G61" s="1" t="s">
-        <v>157</v>
+        <v>159</v>
       </c>
       <c r="H61" s="5"/>
       <c r="I61" s="5"/>
+    </row>
+    <row r="62" customFormat="1" ht="16.5" spans="1:9">
+      <c r="A62" s="2">
+        <v>5054002</v>
+      </c>
+      <c r="B62" s="17">
+        <v>105400</v>
+      </c>
+      <c r="C62" t="s">
+        <v>157</v>
+      </c>
+      <c r="D62" s="1">
+        <v>2</v>
+      </c>
+      <c r="E62" t="s">
+        <v>33</v>
+      </c>
+      <c r="F62" s="15" t="s">
+        <v>160</v>
+      </c>
+      <c r="G62" s="1" t="s">
+        <v>143</v>
+      </c>
+      <c r="H62" s="5"/>
+      <c r="I62" s="5"/>
+    </row>
+    <row r="63" customFormat="1" ht="16.5" spans="1:9">
+      <c r="A63" s="2">
+        <v>5008001</v>
+      </c>
+      <c r="B63" s="17">
+        <v>100800</v>
+      </c>
+      <c r="C63" t="s">
+        <v>161</v>
+      </c>
+      <c r="D63" s="1">
+        <v>1</v>
+      </c>
+      <c r="E63" t="s">
+        <v>162</v>
+      </c>
+      <c r="F63" s="15" t="s">
+        <v>163</v>
+      </c>
+      <c r="G63" s="1" t="s">
+        <v>164</v>
+      </c>
+      <c r="H63" s="5"/>
+      <c r="I63" s="5"/>
+    </row>
+    <row r="64" customFormat="1" ht="16.5" spans="1:9">
+      <c r="A64" s="2">
+        <v>5008002</v>
+      </c>
+      <c r="B64" s="17">
+        <v>100800</v>
+      </c>
+      <c r="C64" t="s">
+        <v>161</v>
+      </c>
+      <c r="D64" s="1">
+        <v>2</v>
+      </c>
+      <c r="E64" t="s">
+        <v>33</v>
+      </c>
+      <c r="F64" s="3" t="s">
+        <v>165</v>
+      </c>
+      <c r="G64" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="H64" s="5"/>
+      <c r="I64" s="5"/>
+    </row>
+    <row r="65" customFormat="1" ht="16.5" spans="1:9">
+      <c r="A65" s="2">
+        <v>5053001</v>
+      </c>
+      <c r="B65" s="17">
+        <v>105300</v>
+      </c>
+      <c r="C65" t="s">
+        <v>166</v>
+      </c>
+      <c r="D65" s="1">
+        <v>4</v>
+      </c>
+      <c r="E65" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="F65" s="15" t="s">
+        <v>31</v>
+      </c>
+      <c r="G65" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="H65" s="5"/>
+      <c r="I65" s="5"/>
+    </row>
+    <row r="66" customFormat="1" ht="16.5" spans="1:9">
+      <c r="A66" s="2">
+        <v>5057001</v>
+      </c>
+      <c r="B66" s="17">
+        <v>105700</v>
+      </c>
+      <c r="C66" t="s">
+        <v>167</v>
+      </c>
+      <c r="D66" s="1">
+        <v>1</v>
+      </c>
+      <c r="E66" t="s">
+        <v>30</v>
+      </c>
+      <c r="F66" s="15" t="s">
+        <v>168</v>
+      </c>
+      <c r="G66" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="H66" s="5"/>
+      <c r="I66" s="5"/>
+    </row>
+    <row r="67" customFormat="1" ht="16.5" spans="1:9">
+      <c r="A67" s="2">
+        <v>5057002</v>
+      </c>
+      <c r="B67" s="17">
+        <v>105700</v>
+      </c>
+      <c r="C67" t="s">
+        <v>167</v>
+      </c>
+      <c r="D67" s="1">
+        <v>2</v>
+      </c>
+      <c r="E67" t="s">
+        <v>33</v>
+      </c>
+      <c r="F67" s="3" t="s">
+        <v>169</v>
+      </c>
+      <c r="G67" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="H67" s="5"/>
+      <c r="I67" s="5"/>
+    </row>
+    <row r="68" customFormat="1" ht="16.5" spans="1:9">
+      <c r="A68" s="2">
+        <v>5057003</v>
+      </c>
+      <c r="B68" s="17">
+        <v>105700</v>
+      </c>
+      <c r="C68" t="s">
+        <v>167</v>
+      </c>
+      <c r="D68" s="1">
+        <v>3</v>
+      </c>
+      <c r="E68" t="s">
+        <v>170</v>
+      </c>
+      <c r="F68" s="15" t="s">
+        <v>171</v>
+      </c>
+      <c r="G68" s="1" t="s">
+        <v>172</v>
+      </c>
+      <c r="H68" s="5"/>
+      <c r="I68" s="5"/>
+    </row>
+    <row r="69" customFormat="1" ht="16.5" spans="1:9">
+      <c r="A69" s="2">
+        <v>5058001</v>
+      </c>
+      <c r="B69" s="17">
+        <v>105800</v>
+      </c>
+      <c r="C69" t="s">
+        <v>173</v>
+      </c>
+      <c r="D69" s="1">
+        <v>1</v>
+      </c>
+      <c r="E69" t="s">
+        <v>33</v>
+      </c>
+      <c r="F69" s="3" t="s">
+        <v>174</v>
+      </c>
+      <c r="G69" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="H69" s="5"/>
+      <c r="I69" s="5"/>
+    </row>
+    <row r="70" customFormat="1" ht="16.5" spans="1:9">
+      <c r="A70" s="2">
+        <v>5058002</v>
+      </c>
+      <c r="B70" s="17">
+        <v>105800</v>
+      </c>
+      <c r="C70" t="s">
+        <v>173</v>
+      </c>
+      <c r="D70" s="1">
+        <v>2</v>
+      </c>
+      <c r="E70" t="s">
+        <v>175</v>
+      </c>
+      <c r="F70" s="3" t="s">
+        <v>176</v>
+      </c>
+      <c r="G70" s="3" t="s">
+        <v>177</v>
+      </c>
+      <c r="H70" s="5"/>
+      <c r="I70" s="5"/>
     </row>
   </sheetData>
   <conditionalFormatting sqref="H2">
@@ -3373,24 +3658,24 @@
   <sheetData>
     <row r="1" spans="1:5">
       <c r="A1" t="s">
-        <v>158</v>
+        <v>178</v>
       </c>
       <c r="D1" t="s">
-        <v>159</v>
+        <v>179</v>
       </c>
     </row>
     <row r="2" spans="1:5">
       <c r="A2" t="s">
-        <v>160</v>
+        <v>180</v>
       </c>
       <c r="B2" t="s">
-        <v>161</v>
+        <v>181</v>
       </c>
       <c r="D2" t="s">
-        <v>160</v>
+        <v>180</v>
       </c>
       <c r="E2" t="s">
-        <v>161</v>
+        <v>181</v>
       </c>
     </row>
     <row r="3" spans="1:5">
@@ -3398,13 +3683,13 @@
         <v>0</v>
       </c>
       <c r="B3" t="s">
-        <v>162</v>
+        <v>182</v>
       </c>
       <c r="D3">
         <v>0</v>
       </c>
       <c r="E3" t="s">
-        <v>163</v>
+        <v>183</v>
       </c>
     </row>
     <row r="4" spans="1:5">
@@ -3412,13 +3697,13 @@
         <v>1</v>
       </c>
       <c r="B4" t="s">
-        <v>164</v>
+        <v>184</v>
       </c>
       <c r="D4">
         <v>1</v>
       </c>
       <c r="E4" t="s">
-        <v>165</v>
+        <v>185</v>
       </c>
     </row>
     <row r="5" spans="1:5">
@@ -3426,13 +3711,13 @@
         <v>2</v>
       </c>
       <c r="B5" t="s">
-        <v>166</v>
+        <v>186</v>
       </c>
       <c r="D5">
         <v>2</v>
       </c>
       <c r="E5" t="s">
-        <v>167</v>
+        <v>187</v>
       </c>
     </row>
     <row r="6" spans="1:5">
@@ -3440,13 +3725,13 @@
         <v>3</v>
       </c>
       <c r="B6" t="s">
-        <v>168</v>
+        <v>188</v>
       </c>
       <c r="D6">
         <v>3</v>
       </c>
       <c r="E6" t="s">
-        <v>169</v>
+        <v>189</v>
       </c>
     </row>
     <row r="7" spans="1:5">
@@ -3454,13 +3739,13 @@
         <v>4</v>
       </c>
       <c r="B7" t="s">
-        <v>170</v>
+        <v>190</v>
       </c>
       <c r="D7">
         <v>4</v>
       </c>
       <c r="E7" t="s">
-        <v>171</v>
+        <v>191</v>
       </c>
     </row>
     <row r="8" spans="1:5">
@@ -3468,13 +3753,13 @@
         <v>5</v>
       </c>
       <c r="B8" t="s">
-        <v>172</v>
+        <v>192</v>
       </c>
       <c r="D8">
         <v>5</v>
       </c>
       <c r="E8" t="s">
-        <v>173</v>
+        <v>193</v>
       </c>
     </row>
     <row r="9" spans="1:5">
@@ -3482,7 +3767,7 @@
         <v>6</v>
       </c>
       <c r="B9" t="s">
-        <v>174</v>
+        <v>194</v>
       </c>
     </row>
     <row r="10" spans="1:5">
@@ -3490,7 +3775,7 @@
         <v>7</v>
       </c>
       <c r="B10" t="s">
-        <v>175</v>
+        <v>195</v>
       </c>
     </row>
     <row r="11" spans="1:5">
@@ -3498,7 +3783,7 @@
         <v>8</v>
       </c>
       <c r="B11" t="s">
-        <v>176</v>
+        <v>196</v>
       </c>
     </row>
     <row r="12" spans="1:5">
@@ -3506,7 +3791,7 @@
         <v>9</v>
       </c>
       <c r="B12" t="s">
-        <v>177</v>
+        <v>197</v>
       </c>
     </row>
     <row r="13" spans="1:5">
@@ -3514,7 +3799,7 @@
         <v>10</v>
       </c>
       <c r="B13" t="s">
-        <v>178</v>
+        <v>198</v>
       </c>
     </row>
     <row r="14" spans="1:5">
@@ -3522,7 +3807,7 @@
         <v>11</v>
       </c>
       <c r="B14" t="s">
-        <v>179</v>
+        <v>199</v>
       </c>
     </row>
     <row r="15" spans="1:5">
@@ -3530,7 +3815,7 @@
         <v>12</v>
       </c>
       <c r="B15" t="s">
-        <v>180</v>
+        <v>200</v>
       </c>
     </row>
     <row r="16" spans="1:5">
@@ -3538,7 +3823,7 @@
         <v>13</v>
       </c>
       <c r="B16" t="s">
-        <v>181</v>
+        <v>201</v>
       </c>
     </row>
     <row r="17" spans="1:2">
@@ -3546,7 +3831,7 @@
         <v>14</v>
       </c>
       <c r="B17" t="s">
-        <v>182</v>
+        <v>202</v>
       </c>
     </row>
     <row r="18" spans="1:2">
@@ -3554,7 +3839,7 @@
         <v>15</v>
       </c>
       <c r="B18" t="s">
-        <v>183</v>
+        <v>203</v>
       </c>
     </row>
     <row r="19" spans="1:2">
@@ -3562,7 +3847,7 @@
         <v>16</v>
       </c>
       <c r="B19" t="s">
-        <v>184</v>
+        <v>204</v>
       </c>
     </row>
     <row r="20" spans="1:2">
@@ -3570,7 +3855,7 @@
         <v>17</v>
       </c>
       <c r="B20" t="s">
-        <v>185</v>
+        <v>205</v>
       </c>
     </row>
     <row r="21" spans="1:2">
@@ -3578,7 +3863,7 @@
         <v>18</v>
       </c>
       <c r="B21" t="s">
-        <v>186</v>
+        <v>206</v>
       </c>
     </row>
     <row r="22" spans="1:2">
@@ -3586,7 +3871,7 @@
         <v>19</v>
       </c>
       <c r="B22" t="s">
-        <v>187</v>
+        <v>207</v>
       </c>
     </row>
     <row r="23" spans="1:2">
@@ -3594,7 +3879,7 @@
         <v>20</v>
       </c>
       <c r="B23" t="s">
-        <v>188</v>
+        <v>208</v>
       </c>
     </row>
     <row r="24" spans="1:2">
@@ -3602,7 +3887,7 @@
         <v>21</v>
       </c>
       <c r="B24" t="s">
-        <v>189</v>
+        <v>209</v>
       </c>
     </row>
     <row r="25" spans="1:2">
@@ -3610,7 +3895,7 @@
         <v>22</v>
       </c>
       <c r="B25" t="s">
-        <v>190</v>
+        <v>210</v>
       </c>
     </row>
     <row r="26" spans="1:2">
@@ -3618,7 +3903,7 @@
         <v>23</v>
       </c>
       <c r="B26" t="s">
-        <v>191</v>
+        <v>211</v>
       </c>
     </row>
     <row r="27" spans="1:2">
@@ -3626,7 +3911,7 @@
         <v>24</v>
       </c>
       <c r="B27" t="s">
-        <v>192</v>
+        <v>212</v>
       </c>
     </row>
     <row r="28" spans="1:2">
@@ -3634,7 +3919,7 @@
         <v>25</v>
       </c>
       <c r="B28" t="s">
-        <v>193</v>
+        <v>213</v>
       </c>
     </row>
     <row r="29" spans="1:2">
@@ -3642,7 +3927,7 @@
         <v>26</v>
       </c>
       <c r="B29" t="s">
-        <v>194</v>
+        <v>214</v>
       </c>
     </row>
     <row r="30" spans="1:2">
@@ -3650,7 +3935,7 @@
         <v>27</v>
       </c>
       <c r="B30" t="s">
-        <v>195</v>
+        <v>215</v>
       </c>
     </row>
     <row r="31" spans="1:2">
@@ -3658,7 +3943,7 @@
         <v>28</v>
       </c>
       <c r="B31" t="s">
-        <v>196</v>
+        <v>216</v>
       </c>
     </row>
     <row r="32" spans="1:2">
@@ -3666,7 +3951,7 @@
         <v>29</v>
       </c>
       <c r="B32" t="s">
-        <v>197</v>
+        <v>217</v>
       </c>
     </row>
     <row r="33" spans="1:2">
@@ -3674,7 +3959,7 @@
         <v>30</v>
       </c>
       <c r="B33" t="s">
-        <v>198</v>
+        <v>218</v>
       </c>
     </row>
     <row r="34" spans="1:2">
@@ -3682,7 +3967,7 @@
         <v>31</v>
       </c>
       <c r="B34" t="s">
-        <v>199</v>
+        <v>219</v>
       </c>
     </row>
     <row r="35" spans="1:2">
@@ -3690,7 +3975,7 @@
         <v>32</v>
       </c>
       <c r="B35" t="s">
-        <v>200</v>
+        <v>220</v>
       </c>
     </row>
     <row r="36" spans="1:2">
@@ -3698,7 +3983,7 @@
         <v>33</v>
       </c>
       <c r="B36" t="s">
-        <v>201</v>
+        <v>221</v>
       </c>
     </row>
     <row r="37" spans="1:2">
@@ -3706,7 +3991,7 @@
         <v>34</v>
       </c>
       <c r="B37" t="s">
-        <v>202</v>
+        <v>222</v>
       </c>
     </row>
     <row r="38" spans="1:2">
@@ -3714,7 +3999,7 @@
         <v>35</v>
       </c>
       <c r="B38" t="s">
-        <v>203</v>
+        <v>223</v>
       </c>
     </row>
     <row r="39" spans="1:2">
@@ -3722,7 +4007,7 @@
         <v>36</v>
       </c>
       <c r="B39" t="s">
-        <v>204</v>
+        <v>224</v>
       </c>
     </row>
     <row r="40" spans="1:2">
@@ -3730,7 +4015,7 @@
         <v>37</v>
       </c>
       <c r="B40" t="s">
-        <v>205</v>
+        <v>225</v>
       </c>
     </row>
     <row r="41" spans="1:2">
@@ -3738,7 +4023,7 @@
         <v>38</v>
       </c>
       <c r="B41" t="s">
-        <v>206</v>
+        <v>226</v>
       </c>
     </row>
     <row r="42" spans="1:2">
@@ -3746,7 +4031,7 @@
         <v>39</v>
       </c>
       <c r="B42" t="s">
-        <v>207</v>
+        <v>227</v>
       </c>
     </row>
     <row r="43" spans="1:2">
@@ -3754,7 +4039,7 @@
         <v>40</v>
       </c>
       <c r="B43" t="s">
-        <v>208</v>
+        <v>228</v>
       </c>
     </row>
     <row r="44" spans="1:2">
@@ -3762,7 +4047,7 @@
         <v>41</v>
       </c>
       <c r="B44" t="s">
-        <v>209</v>
+        <v>229</v>
       </c>
     </row>
     <row r="45" spans="1:2">
@@ -3770,7 +4055,7 @@
         <v>42</v>
       </c>
       <c r="B45" t="s">
-        <v>210</v>
+        <v>230</v>
       </c>
     </row>
     <row r="46" spans="1:2">
@@ -3778,7 +4063,7 @@
         <v>43</v>
       </c>
       <c r="B46" t="s">
-        <v>211</v>
+        <v>231</v>
       </c>
     </row>
     <row r="47" spans="1:2">
@@ -3786,7 +4071,7 @@
         <v>44</v>
       </c>
       <c r="B47" t="s">
-        <v>212</v>
+        <v>232</v>
       </c>
     </row>
     <row r="48" spans="1:2">
@@ -3794,7 +4079,7 @@
         <v>45</v>
       </c>
       <c r="B48" t="s">
-        <v>213</v>
+        <v>233</v>
       </c>
     </row>
   </sheetData>

--- a/slots/resources/sample/SpecialPlay.xlsx
+++ b/slots/resources/sample/SpecialPlay.xlsx
@@ -137,7 +137,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="339" uniqueCount="232">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="351" uniqueCount="236">
   <si>
     <t>被动游戏ID</t>
   </si>
@@ -665,6 +665,18 @@
   </si>
   <si>
     <t>元素ID_图标倍数_权重</t>
+  </si>
+  <si>
+    <t>超级高尔夫</t>
+  </si>
+  <si>
+    <t>消除带有方框符号，获得神秘符号奖励乘以神秘符号个数，出现多个此符号，倍数相加</t>
+  </si>
+  <si>
+    <t>14_1</t>
+  </si>
+  <si>
+    <t>伽罗宝石1</t>
   </si>
   <si>
     <t>旋转标识</t>
@@ -1016,13 +1028,13 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
-      <sz val="9"/>
+      <sz val="10"/>
       <name val="宋体"/>
       <charset val="134"/>
     </font>
     <font>
-      <sz val="10"/>
+      <b/>
+      <sz val="9"/>
       <name val="宋体"/>
       <charset val="134"/>
     </font>
@@ -1886,7 +1898,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:J69"/>
+  <dimension ref="A1:J72"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25"/>
   <cols>
     <col min="4" max="4" width="9.50833333333333" style="6" customWidth="1"/>
@@ -3612,6 +3624,81 @@
       </c>
       <c r="H69" s="22"/>
       <c r="I69" s="22"/>
+    </row>
+    <row r="70" customFormat="1" ht="18" customHeight="1" spans="1:9">
+      <c r="A70" s="2">
+        <v>5048001</v>
+      </c>
+      <c r="B70" s="19">
+        <v>104800</v>
+      </c>
+      <c r="C70" t="s">
+        <v>176</v>
+      </c>
+      <c r="D70" s="1">
+        <v>1</v>
+      </c>
+      <c r="E70" t="s">
+        <v>33</v>
+      </c>
+      <c r="F70" s="3" t="s">
+        <v>159</v>
+      </c>
+      <c r="G70" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="H70" s="7"/>
+      <c r="I70" s="7"/>
+    </row>
+    <row r="71" customFormat="1" ht="16.5" spans="1:9">
+      <c r="A71" s="2">
+        <v>5048002</v>
+      </c>
+      <c r="B71" s="19">
+        <v>104800</v>
+      </c>
+      <c r="C71" t="s">
+        <v>176</v>
+      </c>
+      <c r="D71" s="1">
+        <v>2</v>
+      </c>
+      <c r="E71" t="s">
+        <v>177</v>
+      </c>
+      <c r="F71" s="3" t="s">
+        <v>178</v>
+      </c>
+      <c r="G71" s="3" t="s">
+        <v>158</v>
+      </c>
+      <c r="H71" s="7"/>
+      <c r="I71" s="7"/>
+    </row>
+    <row r="72" s="5" customFormat="1" spans="1:9">
+      <c r="A72" s="5">
+        <v>5055011</v>
+      </c>
+      <c r="B72" s="5">
+        <v>105501</v>
+      </c>
+      <c r="C72" s="5" t="s">
+        <v>179</v>
+      </c>
+      <c r="D72" s="5">
+        <v>1</v>
+      </c>
+      <c r="E72" s="5" t="s">
+        <v>173</v>
+      </c>
+      <c r="F72" s="5" t="s">
+        <v>174</v>
+      </c>
+      <c r="G72" s="5" t="s">
+        <v>175</v>
+      </c>
+      <c r="H72" s="22"/>
+      <c r="I72" s="22"/>
     </row>
   </sheetData>
   <conditionalFormatting sqref="H2">
@@ -3638,24 +3725,24 @@
   <sheetData>
     <row r="1" spans="1:5">
       <c r="A1" t="s">
-        <v>176</v>
+        <v>180</v>
       </c>
       <c r="D1" t="s">
-        <v>177</v>
+        <v>181</v>
       </c>
     </row>
     <row r="2" spans="1:5">
       <c r="A2" t="s">
-        <v>178</v>
+        <v>182</v>
       </c>
       <c r="B2" t="s">
-        <v>179</v>
+        <v>183</v>
       </c>
       <c r="D2" t="s">
-        <v>178</v>
+        <v>182</v>
       </c>
       <c r="E2" t="s">
-        <v>179</v>
+        <v>183</v>
       </c>
     </row>
     <row r="3" spans="1:5">
@@ -3663,13 +3750,13 @@
         <v>0</v>
       </c>
       <c r="B3" t="s">
-        <v>180</v>
+        <v>184</v>
       </c>
       <c r="D3">
         <v>0</v>
       </c>
       <c r="E3" t="s">
-        <v>181</v>
+        <v>185</v>
       </c>
     </row>
     <row r="4" spans="1:5">
@@ -3677,13 +3764,13 @@
         <v>1</v>
       </c>
       <c r="B4" t="s">
-        <v>182</v>
+        <v>186</v>
       </c>
       <c r="D4">
         <v>1</v>
       </c>
       <c r="E4" t="s">
-        <v>183</v>
+        <v>187</v>
       </c>
     </row>
     <row r="5" spans="1:5">
@@ -3691,13 +3778,13 @@
         <v>2</v>
       </c>
       <c r="B5" t="s">
-        <v>184</v>
+        <v>188</v>
       </c>
       <c r="D5">
         <v>2</v>
       </c>
       <c r="E5" t="s">
-        <v>185</v>
+        <v>189</v>
       </c>
     </row>
     <row r="6" spans="1:5">
@@ -3705,13 +3792,13 @@
         <v>3</v>
       </c>
       <c r="B6" t="s">
-        <v>186</v>
+        <v>190</v>
       </c>
       <c r="D6">
         <v>3</v>
       </c>
       <c r="E6" t="s">
-        <v>187</v>
+        <v>191</v>
       </c>
     </row>
     <row r="7" spans="1:5">
@@ -3719,13 +3806,13 @@
         <v>4</v>
       </c>
       <c r="B7" t="s">
-        <v>188</v>
+        <v>192</v>
       </c>
       <c r="D7">
         <v>4</v>
       </c>
       <c r="E7" t="s">
-        <v>189</v>
+        <v>193</v>
       </c>
     </row>
     <row r="8" spans="1:5">
@@ -3733,13 +3820,13 @@
         <v>5</v>
       </c>
       <c r="B8" t="s">
-        <v>190</v>
+        <v>194</v>
       </c>
       <c r="D8">
         <v>5</v>
       </c>
       <c r="E8" t="s">
-        <v>191</v>
+        <v>195</v>
       </c>
     </row>
     <row r="9" spans="1:5">
@@ -3747,7 +3834,7 @@
         <v>6</v>
       </c>
       <c r="B9" t="s">
-        <v>192</v>
+        <v>196</v>
       </c>
     </row>
     <row r="10" spans="1:5">
@@ -3755,7 +3842,7 @@
         <v>7</v>
       </c>
       <c r="B10" t="s">
-        <v>193</v>
+        <v>197</v>
       </c>
     </row>
     <row r="11" spans="1:5">
@@ -3763,7 +3850,7 @@
         <v>8</v>
       </c>
       <c r="B11" t="s">
-        <v>194</v>
+        <v>198</v>
       </c>
     </row>
     <row r="12" spans="1:5">
@@ -3771,7 +3858,7 @@
         <v>9</v>
       </c>
       <c r="B12" t="s">
-        <v>195</v>
+        <v>199</v>
       </c>
     </row>
     <row r="13" spans="1:5">
@@ -3779,7 +3866,7 @@
         <v>10</v>
       </c>
       <c r="B13" t="s">
-        <v>196</v>
+        <v>200</v>
       </c>
     </row>
     <row r="14" spans="1:5">
@@ -3787,7 +3874,7 @@
         <v>11</v>
       </c>
       <c r="B14" t="s">
-        <v>197</v>
+        <v>201</v>
       </c>
     </row>
     <row r="15" spans="1:5">
@@ -3795,7 +3882,7 @@
         <v>12</v>
       </c>
       <c r="B15" t="s">
-        <v>198</v>
+        <v>202</v>
       </c>
     </row>
     <row r="16" spans="1:5">
@@ -3803,7 +3890,7 @@
         <v>13</v>
       </c>
       <c r="B16" t="s">
-        <v>199</v>
+        <v>203</v>
       </c>
     </row>
     <row r="17" spans="1:2">
@@ -3811,7 +3898,7 @@
         <v>14</v>
       </c>
       <c r="B17" t="s">
-        <v>200</v>
+        <v>204</v>
       </c>
     </row>
     <row r="18" spans="1:2">
@@ -3819,7 +3906,7 @@
         <v>15</v>
       </c>
       <c r="B18" t="s">
-        <v>201</v>
+        <v>205</v>
       </c>
     </row>
     <row r="19" spans="1:2">
@@ -3827,7 +3914,7 @@
         <v>16</v>
       </c>
       <c r="B19" t="s">
-        <v>202</v>
+        <v>206</v>
       </c>
     </row>
     <row r="20" spans="1:2">
@@ -3835,7 +3922,7 @@
         <v>17</v>
       </c>
       <c r="B20" t="s">
-        <v>203</v>
+        <v>207</v>
       </c>
     </row>
     <row r="21" spans="1:2">
@@ -3843,7 +3930,7 @@
         <v>18</v>
       </c>
       <c r="B21" t="s">
-        <v>204</v>
+        <v>208</v>
       </c>
     </row>
     <row r="22" spans="1:2">
@@ -3851,7 +3938,7 @@
         <v>19</v>
       </c>
       <c r="B22" t="s">
-        <v>205</v>
+        <v>209</v>
       </c>
     </row>
     <row r="23" spans="1:2">
@@ -3859,7 +3946,7 @@
         <v>20</v>
       </c>
       <c r="B23" t="s">
-        <v>206</v>
+        <v>210</v>
       </c>
     </row>
     <row r="24" spans="1:2">
@@ -3867,7 +3954,7 @@
         <v>21</v>
       </c>
       <c r="B24" t="s">
-        <v>207</v>
+        <v>211</v>
       </c>
     </row>
     <row r="25" spans="1:2">
@@ -3875,7 +3962,7 @@
         <v>22</v>
       </c>
       <c r="B25" t="s">
-        <v>208</v>
+        <v>212</v>
       </c>
     </row>
     <row r="26" spans="1:2">
@@ -3883,7 +3970,7 @@
         <v>23</v>
       </c>
       <c r="B26" t="s">
-        <v>209</v>
+        <v>213</v>
       </c>
     </row>
     <row r="27" spans="1:2">
@@ -3891,7 +3978,7 @@
         <v>24</v>
       </c>
       <c r="B27" t="s">
-        <v>210</v>
+        <v>214</v>
       </c>
     </row>
     <row r="28" spans="1:2">
@@ -3899,7 +3986,7 @@
         <v>25</v>
       </c>
       <c r="B28" t="s">
-        <v>211</v>
+        <v>215</v>
       </c>
     </row>
     <row r="29" spans="1:2">
@@ -3907,7 +3994,7 @@
         <v>26</v>
       </c>
       <c r="B29" t="s">
-        <v>212</v>
+        <v>216</v>
       </c>
     </row>
     <row r="30" spans="1:2">
@@ -3915,7 +4002,7 @@
         <v>27</v>
       </c>
       <c r="B30" t="s">
-        <v>213</v>
+        <v>217</v>
       </c>
     </row>
     <row r="31" spans="1:2">
@@ -3923,7 +4010,7 @@
         <v>28</v>
       </c>
       <c r="B31" t="s">
-        <v>214</v>
+        <v>218</v>
       </c>
     </row>
     <row r="32" spans="1:2">
@@ -3931,7 +4018,7 @@
         <v>29</v>
       </c>
       <c r="B32" t="s">
-        <v>215</v>
+        <v>219</v>
       </c>
     </row>
     <row r="33" spans="1:2">
@@ -3939,7 +4026,7 @@
         <v>30</v>
       </c>
       <c r="B33" t="s">
-        <v>216</v>
+        <v>220</v>
       </c>
     </row>
     <row r="34" spans="1:2">
@@ -3947,7 +4034,7 @@
         <v>31</v>
       </c>
       <c r="B34" t="s">
-        <v>217</v>
+        <v>221</v>
       </c>
     </row>
     <row r="35" spans="1:2">
@@ -3955,7 +4042,7 @@
         <v>32</v>
       </c>
       <c r="B35" t="s">
-        <v>218</v>
+        <v>222</v>
       </c>
     </row>
     <row r="36" spans="1:2">
@@ -3963,7 +4050,7 @@
         <v>33</v>
       </c>
       <c r="B36" t="s">
-        <v>219</v>
+        <v>223</v>
       </c>
     </row>
     <row r="37" spans="1:2">
@@ -3971,7 +4058,7 @@
         <v>34</v>
       </c>
       <c r="B37" t="s">
-        <v>220</v>
+        <v>224</v>
       </c>
     </row>
     <row r="38" spans="1:2">
@@ -3979,7 +4066,7 @@
         <v>35</v>
       </c>
       <c r="B38" t="s">
-        <v>221</v>
+        <v>225</v>
       </c>
     </row>
     <row r="39" spans="1:2">
@@ -3987,7 +4074,7 @@
         <v>36</v>
       </c>
       <c r="B39" t="s">
-        <v>222</v>
+        <v>226</v>
       </c>
     </row>
     <row r="40" spans="1:2">
@@ -3995,7 +4082,7 @@
         <v>37</v>
       </c>
       <c r="B40" t="s">
-        <v>223</v>
+        <v>227</v>
       </c>
     </row>
     <row r="41" spans="1:2">
@@ -4003,7 +4090,7 @@
         <v>38</v>
       </c>
       <c r="B41" t="s">
-        <v>224</v>
+        <v>228</v>
       </c>
     </row>
     <row r="42" spans="1:2">
@@ -4011,7 +4098,7 @@
         <v>39</v>
       </c>
       <c r="B42" t="s">
-        <v>225</v>
+        <v>229</v>
       </c>
     </row>
     <row r="43" spans="1:2">
@@ -4019,7 +4106,7 @@
         <v>40</v>
       </c>
       <c r="B43" t="s">
-        <v>226</v>
+        <v>230</v>
       </c>
     </row>
     <row r="44" spans="1:2">
@@ -4027,7 +4114,7 @@
         <v>41</v>
       </c>
       <c r="B44" t="s">
-        <v>227</v>
+        <v>231</v>
       </c>
     </row>
     <row r="45" spans="1:2">
@@ -4035,7 +4122,7 @@
         <v>42</v>
       </c>
       <c r="B45" t="s">
-        <v>228</v>
+        <v>232</v>
       </c>
     </row>
     <row r="46" spans="1:2">
@@ -4043,7 +4130,7 @@
         <v>43</v>
       </c>
       <c r="B46" t="s">
-        <v>229</v>
+        <v>233</v>
       </c>
     </row>
     <row r="47" spans="1:2">
@@ -4051,7 +4138,7 @@
         <v>44</v>
       </c>
       <c r="B47" t="s">
-        <v>230</v>
+        <v>234</v>
       </c>
     </row>
     <row r="48" spans="1:2">
@@ -4059,7 +4146,7 @@
         <v>45</v>
       </c>
       <c r="B48" t="s">
-        <v>231</v>
+        <v>235</v>
       </c>
     </row>
   </sheetData>

--- a/slots/resources/sample/SpecialPlay.xlsx
+++ b/slots/resources/sample/SpecialPlay.xlsx
@@ -1,10 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet">
-  <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="29822"/>
   <workbookPr/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\cehua\gamedoc\游戏配置表\slot\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="11_627BD6E2A550FBFA6ABA060465B62B58CDA14E12" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView windowWidth="27945" windowHeight="12255"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="SpecialPlay" sheetId="1" r:id="rId1"/>
@@ -28,16 +34,16 @@
 </file>
 
 <file path=xl/comments1.xml><?xml version="1.0" encoding="utf-8"?>
-<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr">
   <authors>
     <author>Administrator</author>
     <author>C</author>
   </authors>
   <commentList>
-    <comment ref="D1" authorId="0">
+    <comment ref="D1" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-000001000000}">
       <text/>
     </comment>
-    <comment ref="H1" authorId="1">
+    <comment ref="H1" authorId="1" shapeId="0" xr:uid="{00000000-0006-0000-0000-000002000000}">
       <text>
         <r>
           <rPr>
@@ -59,7 +65,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I1" authorId="1">
+    <comment ref="I1" authorId="1" shapeId="0" xr:uid="{00000000-0006-0000-0000-000003000000}">
       <text>
         <r>
           <rPr>
@@ -82,7 +88,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="G24" authorId="0">
+    <comment ref="G24" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-000004000000}">
       <text>
         <r>
           <rPr>
@@ -107,7 +113,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="G25" authorId="0">
+    <comment ref="G25" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-000005000000}">
       <text>
         <r>
           <rPr>
@@ -850,15 +856,11 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="xr9">
-  <numFmts count="5">
-    <numFmt numFmtId="41" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
-    <numFmt numFmtId="42" formatCode="_ &quot;￥&quot;* #,##0_ ;_ &quot;￥&quot;* \-#,##0_ ;_ &quot;￥&quot;* &quot;-&quot;_ ;_ @_ "/>
-    <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="176" formatCode="0_ "/>
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <numFmts count="1">
+    <numFmt numFmtId="178" formatCode="0_ "/>
   </numFmts>
-  <fonts count="26">
+  <fonts count="8" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -884,153 +886,11 @@
       <charset val="134"/>
     </font>
     <font>
-      <u/>
       <sz val="11"/>
-      <color rgb="FF0000FF"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF800080"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFF0000"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="18"/>
-      <color theme="3"/>
+      <color theme="1"/>
       <name val="等线"/>
       <charset val="134"/>
       <scheme val="minor"/>
-    </font>
-    <font>
-      <i/>
-      <sz val="11"/>
-      <color rgb="FF7F7F7F"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="15"/>
-      <color theme="3"/>
-      <name val="等线"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="13"/>
-      <color theme="3"/>
-      <name val="等线"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="3"/>
-      <name val="等线"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF3F3F76"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FF3F3F3F"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFFFFFF"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF006100"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C0006"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C6500"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="0"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <name val="宋体"/>
-      <charset val="134"/>
     </font>
     <font>
       <b/>
@@ -1043,8 +903,14 @@
       <name val="宋体"/>
       <charset val="134"/>
     </font>
+    <font>
+      <sz val="9"/>
+      <name val="等线"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
-  <fills count="35">
+  <fills count="4">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -1053,7 +919,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.8"/>
+        <fgColor theme="9" tint="0.79998168889431442"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -1063,194 +929,8 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFCC"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFCC99"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF2F2F2"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA5A5A5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFEB9C"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
   </fills>
-  <borders count="9">
+  <borders count="1">
     <border>
       <left/>
       <right/>
@@ -1258,265 +938,18 @@
       <bottom/>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin">
-        <color rgb="FFB2B2B2"/>
-      </left>
-      <right style="thin">
-        <color rgb="FFB2B2B2"/>
-      </right>
-      <top style="thin">
-        <color rgb="FFB2B2B2"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FFB2B2B2"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4" tint="0.499984740745262"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF7F7F7F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF7F7F7F"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF7F7F7F"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF7F7F7F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF3F3F3F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="double">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="double">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="double">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="double">
-        <color rgb="FF3F3F3F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="double">
-        <color rgb="FFFF8001"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top style="thin">
-        <color theme="4"/>
-      </top>
-      <bottom style="double">
-        <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
   </borders>
-  <cellStyleXfs count="52">
+  <cellStyleXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="41" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="5" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="6" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="6" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="7" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="23">
+  <cellXfs count="17">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
@@ -1533,7 +966,7 @@
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
-    <xf numFmtId="176" fontId="1" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="178" fontId="1" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -1542,10 +975,10 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="49" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
@@ -1557,76 +990,28 @@
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
   </cellXfs>
-  <cellStyles count="52">
+  <cellStyles count="4">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
-    <cellStyle name="千位分隔" xfId="1" builtinId="3"/>
-    <cellStyle name="货币" xfId="2" builtinId="4"/>
-    <cellStyle name="百分比" xfId="3" builtinId="5"/>
-    <cellStyle name="千位分隔[0]" xfId="4" builtinId="6"/>
-    <cellStyle name="货币[0]" xfId="5" builtinId="7"/>
-    <cellStyle name="超链接" xfId="6" builtinId="8"/>
-    <cellStyle name="已访问的超链接" xfId="7" builtinId="9"/>
-    <cellStyle name="注释" xfId="8" builtinId="10"/>
-    <cellStyle name="警告文本" xfId="9" builtinId="11"/>
-    <cellStyle name="标题" xfId="10" builtinId="15"/>
-    <cellStyle name="解释性文本" xfId="11" builtinId="53"/>
-    <cellStyle name="标题 1" xfId="12" builtinId="16"/>
-    <cellStyle name="标题 2" xfId="13" builtinId="17"/>
-    <cellStyle name="标题 3" xfId="14" builtinId="18"/>
-    <cellStyle name="标题 4" xfId="15" builtinId="19"/>
-    <cellStyle name="输入" xfId="16" builtinId="20"/>
-    <cellStyle name="输出" xfId="17" builtinId="21"/>
-    <cellStyle name="计算" xfId="18" builtinId="22"/>
-    <cellStyle name="检查单元格" xfId="19" builtinId="23"/>
-    <cellStyle name="链接单元格" xfId="20" builtinId="24"/>
-    <cellStyle name="汇总" xfId="21" builtinId="25"/>
-    <cellStyle name="好" xfId="22" builtinId="26"/>
-    <cellStyle name="差" xfId="23" builtinId="27"/>
-    <cellStyle name="适中" xfId="24" builtinId="28"/>
-    <cellStyle name="强调文字颜色 1" xfId="25" builtinId="29"/>
-    <cellStyle name="20% - 强调文字颜色 1" xfId="26" builtinId="30"/>
-    <cellStyle name="40% - 强调文字颜色 1" xfId="27" builtinId="31"/>
-    <cellStyle name="60% - 强调文字颜色 1" xfId="28" builtinId="32"/>
-    <cellStyle name="强调文字颜色 2" xfId="29" builtinId="33"/>
-    <cellStyle name="20% - 强调文字颜色 2" xfId="30" builtinId="34"/>
-    <cellStyle name="40% - 强调文字颜色 2" xfId="31" builtinId="35"/>
-    <cellStyle name="60% - 强调文字颜色 2" xfId="32" builtinId="36"/>
-    <cellStyle name="强调文字颜色 3" xfId="33" builtinId="37"/>
-    <cellStyle name="20% - 强调文字颜色 3" xfId="34" builtinId="38"/>
-    <cellStyle name="40% - 强调文字颜色 3" xfId="35" builtinId="39"/>
-    <cellStyle name="60% - 强调文字颜色 3" xfId="36" builtinId="40"/>
-    <cellStyle name="强调文字颜色 4" xfId="37" builtinId="41"/>
-    <cellStyle name="20% - 强调文字颜色 4" xfId="38" builtinId="42"/>
-    <cellStyle name="40% - 强调文字颜色 4" xfId="39" builtinId="43"/>
-    <cellStyle name="60% - 强调文字颜色 4" xfId="40" builtinId="44"/>
-    <cellStyle name="强调文字颜色 5" xfId="41" builtinId="45"/>
-    <cellStyle name="20% - 强调文字颜色 5" xfId="42" builtinId="46"/>
-    <cellStyle name="40% - 强调文字颜色 5" xfId="43" builtinId="47"/>
-    <cellStyle name="60% - 强调文字颜色 5" xfId="44" builtinId="48"/>
-    <cellStyle name="强调文字颜色 6" xfId="45" builtinId="49"/>
-    <cellStyle name="20% - 强调文字颜色 6" xfId="46" builtinId="50"/>
-    <cellStyle name="40% - 强调文字颜色 6" xfId="47" builtinId="51"/>
-    <cellStyle name="60% - 强调文字颜色 6" xfId="48" builtinId="52"/>
-    <cellStyle name="常规 73" xfId="49"/>
-    <cellStyle name="常规 80" xfId="50"/>
-    <cellStyle name="常规 2" xfId="51"/>
+    <cellStyle name="常规 2" xfId="3" xr:uid="{00000000-0005-0000-0000-000033000000}"/>
+    <cellStyle name="常规 73" xfId="1" xr:uid="{00000000-0005-0000-0000-000031000000}"/>
+    <cellStyle name="常规 80" xfId="2" xr:uid="{00000000-0005-0000-0000-000032000000}"/>
   </cellStyles>
-  <dxfs count="1">
+  <dxfs count="2">
     <dxf>
       <fill>
         <patternFill patternType="solid">
-          <bgColor theme="8" tint="0.799340800195319"/>
+          <bgColor theme="8" tint="0.7993408001953185"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor theme="8" tint="0.7993408001953185"/>
         </patternFill>
       </fill>
     </dxf>
@@ -1635,6 +1020,9 @@
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
       <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
     </ext>
   </extLst>
 </styleSheet>
@@ -1892,200 +1280,200 @@
     </a:fmtScheme>
   </a:themeElements>
   <a:objectDefaults/>
+  <a:extraClrSchemeLst/>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
-  <sheetPr/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:J72"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="4" max="4" width="9.50833333333333" style="6" customWidth="1"/>
+    <col min="4" max="4" width="9.5" style="3" customWidth="1"/>
     <col min="5" max="5" width="61.75" customWidth="1"/>
     <col min="6" max="6" width="50.875" customWidth="1"/>
-    <col min="7" max="7" width="74.7" customWidth="1"/>
-    <col min="8" max="8" width="26.3" style="7" customWidth="1"/>
-    <col min="9" max="9" width="19.375" style="7" customWidth="1"/>
-    <col min="10" max="10" width="7.81666666666667" customWidth="1"/>
+    <col min="7" max="7" width="74.75" customWidth="1"/>
+    <col min="8" max="8" width="26.25" style="4" customWidth="1"/>
+    <col min="9" max="9" width="19.375" style="4" customWidth="1"/>
+    <col min="10" max="10" width="7.875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="16.5" spans="1:10">
-      <c r="A1" s="8" t="s">
+    <row r="1" spans="1:10" ht="16.5" x14ac:dyDescent="0.2">
+      <c r="A1" s="5" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="8" t="s">
+      <c r="B1" s="5" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="8"/>
-      <c r="D1" s="9" t="s">
+      <c r="C1" s="5"/>
+      <c r="D1" s="6" t="s">
         <v>2</v>
       </c>
-      <c r="E1" s="8"/>
-      <c r="F1" s="8" t="s">
+      <c r="E1" s="5"/>
+      <c r="F1" s="5" t="s">
         <v>3</v>
       </c>
-      <c r="G1" s="8" t="s">
+      <c r="G1" s="5" t="s">
         <v>4</v>
       </c>
-      <c r="H1" s="10" t="s">
+      <c r="H1" s="7" t="s">
         <v>5</v>
       </c>
-      <c r="I1" s="10" t="s">
+      <c r="I1" s="7" t="s">
         <v>6</v>
       </c>
-      <c r="J1" s="8"/>
-    </row>
-    <row r="2" ht="16.5" spans="1:10">
-      <c r="A2" s="8" t="s">
+      <c r="J1" s="5"/>
+    </row>
+    <row r="2" spans="1:10" ht="16.5" x14ac:dyDescent="0.35">
+      <c r="A2" s="5" t="s">
         <v>7</v>
       </c>
-      <c r="B2" s="8" t="s">
+      <c r="B2" s="5" t="s">
         <v>7</v>
       </c>
-      <c r="C2" s="8"/>
-      <c r="D2" s="9" t="s">
+      <c r="C2" s="5"/>
+      <c r="D2" s="6" t="s">
         <v>7</v>
       </c>
-      <c r="E2" s="8"/>
-      <c r="F2" s="8" t="s">
+      <c r="E2" s="5"/>
+      <c r="F2" s="5" t="s">
         <v>8</v>
       </c>
-      <c r="G2" s="8"/>
-      <c r="H2" s="11" t="s">
+      <c r="G2" s="5"/>
+      <c r="H2" s="8" t="s">
         <v>9</v>
       </c>
-      <c r="I2" s="12" t="s">
+      <c r="I2" s="9" t="s">
         <v>10</v>
       </c>
-      <c r="J2" s="8"/>
-    </row>
-    <row r="3" ht="16.5" spans="1:10">
-      <c r="A3" s="8" t="s">
+      <c r="J2" s="5"/>
+    </row>
+    <row r="3" spans="1:10" ht="16.5" x14ac:dyDescent="0.2">
+      <c r="A3" s="5" t="s">
         <v>11</v>
       </c>
-      <c r="B3" s="8" t="s">
+      <c r="B3" s="5" t="s">
         <v>12</v>
       </c>
-      <c r="C3" s="8"/>
-      <c r="D3" s="9" t="s">
+      <c r="C3" s="5"/>
+      <c r="D3" s="6" t="s">
         <v>13</v>
       </c>
-      <c r="E3" s="8"/>
-      <c r="F3" s="8" t="s">
+      <c r="E3" s="5"/>
+      <c r="F3" s="5" t="s">
         <v>14</v>
       </c>
-      <c r="G3" s="8"/>
-      <c r="H3" s="10" t="s">
+      <c r="G3" s="5"/>
+      <c r="H3" s="7" t="s">
         <v>15</v>
       </c>
-      <c r="I3" s="10" t="s">
+      <c r="I3" s="7" t="s">
         <v>16</v>
       </c>
-      <c r="J3" s="8"/>
-    </row>
-    <row r="4" ht="16.5" spans="1:10">
-      <c r="A4" s="8"/>
-      <c r="B4" s="8"/>
-      <c r="C4" s="8"/>
-      <c r="D4" s="9"/>
-      <c r="E4" s="8"/>
-      <c r="F4" s="8"/>
-      <c r="G4" s="8"/>
-      <c r="H4" s="10"/>
-      <c r="I4" s="10"/>
-      <c r="J4" s="8"/>
-    </row>
-    <row r="5" s="1" customFormat="1" ht="18" customHeight="1" spans="1:10">
-      <c r="A5" s="2">
+      <c r="J3" s="5"/>
+    </row>
+    <row r="4" spans="1:10" ht="16.5" x14ac:dyDescent="0.2">
+      <c r="A4" s="5"/>
+      <c r="B4" s="5"/>
+      <c r="C4" s="5"/>
+      <c r="D4" s="6"/>
+      <c r="E4" s="5"/>
+      <c r="F4" s="5"/>
+      <c r="G4" s="5"/>
+      <c r="H4" s="7"/>
+      <c r="I4" s="7"/>
+      <c r="J4" s="5"/>
+    </row>
+    <row r="5" spans="1:10" s="1" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A5" s="1">
         <v>5001001</v>
       </c>
-      <c r="B5" s="13">
+      <c r="B5" s="10">
         <v>100100</v>
       </c>
-      <c r="C5" s="14" t="s">
+      <c r="C5" s="11" t="s">
         <v>17</v>
       </c>
-      <c r="D5" s="13">
+      <c r="D5" s="10">
         <v>1</v>
       </c>
       <c r="E5" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="F5" s="15" t="s">
+      <c r="F5" s="12" t="s">
         <v>19</v>
       </c>
-      <c r="G5" s="13" t="s">
+      <c r="G5" s="10" t="s">
         <v>20</v>
       </c>
-      <c r="H5" s="16" t="s">
+      <c r="H5" s="13" t="s">
         <v>21</v>
       </c>
-      <c r="I5" s="16" t="s">
+      <c r="I5" s="13" t="s">
         <v>22</v>
       </c>
-      <c r="J5" s="13"/>
-    </row>
-    <row r="6" s="1" customFormat="1" ht="18" customHeight="1" spans="1:10">
-      <c r="A6" s="2">
+      <c r="J5" s="10"/>
+    </row>
+    <row r="6" spans="1:10" s="1" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A6" s="1">
         <v>5001002</v>
       </c>
-      <c r="B6" s="13">
+      <c r="B6" s="10">
         <v>100100</v>
       </c>
-      <c r="C6" s="14" t="s">
+      <c r="C6" s="11" t="s">
         <v>17</v>
       </c>
-      <c r="D6" s="13">
+      <c r="D6" s="10">
         <v>2</v>
       </c>
       <c r="E6" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="F6" s="15" t="s">
+      <c r="F6" s="12" t="s">
         <v>24</v>
       </c>
-      <c r="G6" s="13" t="s">
+      <c r="G6" s="10" t="s">
         <v>25</v>
       </c>
-      <c r="H6" s="16"/>
-      <c r="I6" s="16"/>
-      <c r="J6" s="13"/>
-    </row>
-    <row r="7" s="1" customFormat="1" ht="18" customHeight="1" spans="1:10">
-      <c r="A7" s="2">
+      <c r="H6" s="13"/>
+      <c r="I6" s="13"/>
+      <c r="J6" s="10"/>
+    </row>
+    <row r="7" spans="1:10" s="1" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A7" s="1">
         <v>5001007</v>
       </c>
-      <c r="B7" s="13">
+      <c r="B7" s="10">
         <v>100100</v>
       </c>
-      <c r="C7" s="14" t="s">
+      <c r="C7" s="11" t="s">
         <v>17</v>
       </c>
-      <c r="D7" s="13">
+      <c r="D7" s="10">
         <v>7</v>
       </c>
       <c r="E7" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="F7" s="15" t="s">
+      <c r="F7" s="12" t="s">
         <v>27</v>
       </c>
-      <c r="G7" s="13" t="s">
+      <c r="G7" s="10" t="s">
         <v>28</v>
       </c>
-      <c r="H7" s="16"/>
-      <c r="I7" s="16"/>
-      <c r="J7" s="13"/>
-    </row>
-    <row r="8" s="1" customFormat="1" ht="18" customHeight="1" spans="1:10">
-      <c r="A8" s="2">
+      <c r="H7" s="13"/>
+      <c r="I7" s="13"/>
+      <c r="J7" s="10"/>
+    </row>
+    <row r="8" spans="1:10" s="1" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A8" s="1">
         <v>5007004</v>
       </c>
       <c r="B8" s="1">
         <v>100700</v>
       </c>
-      <c r="C8" s="2" t="s">
+      <c r="C8" s="1" t="s">
         <v>29</v>
       </c>
       <c r="D8" s="1">
@@ -2094,23 +1482,23 @@
       <c r="E8" s="1" t="s">
         <v>30</v>
       </c>
-      <c r="F8" s="17" t="s">
+      <c r="F8" s="14" t="s">
         <v>31</v>
       </c>
       <c r="G8" s="1" t="s">
         <v>32</v>
       </c>
-      <c r="H8" s="18"/>
-      <c r="I8" s="18"/>
-    </row>
-    <row r="9" s="1" customFormat="1" ht="18" customHeight="1" spans="1:10">
-      <c r="A9" s="2">
+      <c r="H8" s="15"/>
+      <c r="I8" s="15"/>
+    </row>
+    <row r="9" spans="1:10" s="1" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A9" s="1">
         <v>5007005</v>
       </c>
       <c r="B9" s="1">
         <v>100700</v>
       </c>
-      <c r="C9" s="2" t="s">
+      <c r="C9" s="1" t="s">
         <v>29</v>
       </c>
       <c r="D9" s="1">
@@ -2119,17 +1507,17 @@
       <c r="E9" s="1" t="s">
         <v>33</v>
       </c>
-      <c r="F9" s="17" t="s">
+      <c r="F9" s="14" t="s">
         <v>34</v>
       </c>
       <c r="G9" s="1" t="s">
         <v>35</v>
       </c>
-      <c r="H9" s="18"/>
-      <c r="I9" s="18"/>
-    </row>
-    <row r="10" s="1" customFormat="1" ht="18" customHeight="1" spans="1:10">
-      <c r="A10" s="2">
+      <c r="H9" s="15"/>
+      <c r="I9" s="15"/>
+    </row>
+    <row r="10" spans="1:10" s="1" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A10" s="1">
         <v>5014006</v>
       </c>
       <c r="B10" s="1">
@@ -2144,105 +1532,105 @@
       <c r="E10" s="1" t="s">
         <v>37</v>
       </c>
-      <c r="F10" s="17" t="s">
+      <c r="F10" s="14" t="s">
         <v>38</v>
       </c>
       <c r="G10" s="1" t="s">
         <v>39</v>
       </c>
-      <c r="H10" s="18"/>
-      <c r="I10" s="18"/>
-    </row>
-    <row r="11" s="1" customFormat="1" ht="18" customHeight="1" spans="1:10">
-      <c r="A11" s="2">
+      <c r="H10" s="15"/>
+      <c r="I10" s="15"/>
+    </row>
+    <row r="11" spans="1:10" s="1" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A11" s="1">
         <v>5024001</v>
       </c>
-      <c r="B11" s="13">
+      <c r="B11" s="10">
         <v>102400</v>
       </c>
-      <c r="C11" s="14" t="s">
+      <c r="C11" s="11" t="s">
         <v>17</v>
       </c>
-      <c r="D11" s="13">
+      <c r="D11" s="10">
         <v>1</v>
       </c>
       <c r="E11" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="F11" s="15" t="s">
+      <c r="F11" s="12" t="s">
         <v>40</v>
       </c>
-      <c r="G11" s="13" t="s">
+      <c r="G11" s="10" t="s">
         <v>20</v>
       </c>
-      <c r="H11" s="16" t="s">
+      <c r="H11" s="13" t="s">
         <v>21</v>
       </c>
-      <c r="I11" s="16" t="s">
+      <c r="I11" s="13" t="s">
         <v>41</v>
       </c>
-      <c r="J11" s="13"/>
-    </row>
-    <row r="12" s="1" customFormat="1" ht="18" customHeight="1" spans="1:10">
-      <c r="A12" s="2">
+      <c r="J11" s="10"/>
+    </row>
+    <row r="12" spans="1:10" s="1" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A12" s="1">
         <v>5024002</v>
       </c>
-      <c r="B12" s="13">
+      <c r="B12" s="10">
         <v>102400</v>
       </c>
-      <c r="C12" s="14" t="s">
+      <c r="C12" s="11" t="s">
         <v>17</v>
       </c>
-      <c r="D12" s="13">
+      <c r="D12" s="10">
         <v>2</v>
       </c>
       <c r="E12" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="F12" s="15" t="s">
+      <c r="F12" s="12" t="s">
         <v>42</v>
       </c>
-      <c r="G12" s="13" t="s">
+      <c r="G12" s="10" t="s">
         <v>25</v>
       </c>
-      <c r="H12" s="16"/>
-      <c r="I12" s="16"/>
-      <c r="J12" s="13"/>
-    </row>
-    <row r="13" s="1" customFormat="1" ht="18" customHeight="1" spans="1:10">
-      <c r="A13" s="2">
+      <c r="H12" s="13"/>
+      <c r="I12" s="13"/>
+      <c r="J12" s="10"/>
+    </row>
+    <row r="13" spans="1:10" s="1" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A13" s="1">
         <v>5024007</v>
       </c>
-      <c r="B13" s="13">
+      <c r="B13" s="10">
         <v>102400</v>
       </c>
-      <c r="C13" s="14" t="s">
+      <c r="C13" s="11" t="s">
         <v>17</v>
       </c>
-      <c r="D13" s="13">
+      <c r="D13" s="10">
         <v>7</v>
       </c>
       <c r="E13" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="F13" s="15" t="s">
+      <c r="F13" s="12" t="s">
         <v>43</v>
       </c>
-      <c r="G13" s="13" t="s">
+      <c r="G13" s="10" t="s">
         <v>28</v>
       </c>
-      <c r="H13" s="16"/>
-      <c r="I13" s="16"/>
-      <c r="J13" s="13"/>
-    </row>
-    <row r="14" s="1" customFormat="1" ht="18" customHeight="1" spans="1:10">
-      <c r="A14" s="2">
+      <c r="H13" s="13"/>
+      <c r="I13" s="13"/>
+      <c r="J13" s="10"/>
+    </row>
+    <row r="14" spans="1:10" s="1" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A14" s="1">
         <v>5017004</v>
       </c>
       <c r="B14" s="1">
         <v>101700</v>
       </c>
-      <c r="C14" s="2" t="s">
+      <c r="C14" s="1" t="s">
         <v>44</v>
       </c>
       <c r="D14" s="1">
@@ -2251,23 +1639,23 @@
       <c r="E14" s="1" t="s">
         <v>30</v>
       </c>
-      <c r="F14" s="17" t="s">
+      <c r="F14" s="14" t="s">
         <v>31</v>
       </c>
       <c r="G14" s="1" t="s">
         <v>32</v>
       </c>
-      <c r="H14" s="18"/>
-      <c r="I14" s="18"/>
-    </row>
-    <row r="15" s="1" customFormat="1" ht="18" customHeight="1" spans="1:10">
-      <c r="A15" s="2">
+      <c r="H14" s="15"/>
+      <c r="I14" s="15"/>
+    </row>
+    <row r="15" spans="1:10" s="1" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A15" s="1">
         <v>5017005</v>
       </c>
       <c r="B15" s="1">
         <v>101700</v>
       </c>
-      <c r="C15" s="2" t="s">
+      <c r="C15" s="1" t="s">
         <v>44</v>
       </c>
       <c r="D15" s="1">
@@ -2276,98 +1664,98 @@
       <c r="E15" s="1" t="s">
         <v>33</v>
       </c>
-      <c r="F15" s="17" t="s">
+      <c r="F15" s="14" t="s">
         <v>34</v>
       </c>
       <c r="G15" s="1" t="s">
         <v>35</v>
       </c>
-      <c r="H15" s="18"/>
-      <c r="I15" s="18"/>
-    </row>
-    <row r="16" s="2" customFormat="1" ht="18" customHeight="1" spans="1:10">
-      <c r="A16" s="2">
+      <c r="H15" s="15"/>
+      <c r="I15" s="15"/>
+    </row>
+    <row r="16" spans="1:10" s="1" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A16" s="1">
         <v>5022007</v>
       </c>
-      <c r="B16" s="19">
+      <c r="B16" s="10">
         <v>102200</v>
       </c>
-      <c r="C16" s="14" t="s">
+      <c r="C16" s="11" t="s">
         <v>45</v>
       </c>
-      <c r="D16" s="19">
+      <c r="D16" s="10">
         <v>7</v>
       </c>
-      <c r="E16" s="2" t="s">
+      <c r="E16" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="F16" s="15" t="s">
+      <c r="F16" s="12" t="s">
         <v>46</v>
       </c>
-      <c r="G16" s="19" t="s">
+      <c r="G16" s="10" t="s">
         <v>28</v>
       </c>
-      <c r="H16" s="14"/>
-      <c r="I16" s="14"/>
-      <c r="J16" s="19"/>
-    </row>
-    <row r="17" s="2" customFormat="1" ht="18" customHeight="1" spans="1:10">
-      <c r="A17" s="2">
+      <c r="H16" s="11"/>
+      <c r="I16" s="11"/>
+      <c r="J16" s="10"/>
+    </row>
+    <row r="17" spans="1:10" s="1" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A17" s="1">
         <v>5022008</v>
       </c>
-      <c r="B17" s="19">
+      <c r="B17" s="10">
         <v>102200</v>
       </c>
-      <c r="C17" s="14" t="s">
+      <c r="C17" s="11" t="s">
         <v>45</v>
       </c>
-      <c r="D17" s="19">
+      <c r="D17" s="10">
         <v>8</v>
       </c>
-      <c r="E17" s="2" t="s">
+      <c r="E17" s="1" t="s">
         <v>47</v>
       </c>
-      <c r="F17" s="15" t="s">
+      <c r="F17" s="12" t="s">
         <v>48</v>
       </c>
-      <c r="G17" s="19" t="s">
+      <c r="G17" s="10" t="s">
         <v>49</v>
       </c>
-      <c r="H17" s="14"/>
-      <c r="I17" s="14"/>
-      <c r="J17" s="19"/>
-    </row>
-    <row r="18" s="2" customFormat="1" ht="18" customHeight="1" spans="1:10">
-      <c r="A18" s="2">
+      <c r="H17" s="11"/>
+      <c r="I17" s="11"/>
+      <c r="J17" s="10"/>
+    </row>
+    <row r="18" spans="1:10" s="1" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A18" s="1">
         <v>5021001</v>
       </c>
-      <c r="B18" s="19">
+      <c r="B18" s="10">
         <v>102100</v>
       </c>
-      <c r="C18" s="14" t="s">
+      <c r="C18" s="11" t="s">
         <v>50</v>
       </c>
-      <c r="D18" s="19">
+      <c r="D18" s="10">
         <v>4</v>
       </c>
-      <c r="E18" s="2" t="s">
+      <c r="E18" s="1" t="s">
         <v>51</v>
       </c>
-      <c r="F18" s="15" t="s">
+      <c r="F18" s="12" t="s">
         <v>52</v>
       </c>
-      <c r="G18" s="19" t="s">
+      <c r="G18" s="10" t="s">
         <v>53</v>
       </c>
-      <c r="H18" s="14"/>
-      <c r="I18" s="14"/>
-      <c r="J18" s="19"/>
-    </row>
-    <row r="19" ht="16.5" spans="1:10">
-      <c r="A19" s="2">
+      <c r="H18" s="11"/>
+      <c r="I18" s="11"/>
+      <c r="J18" s="10"/>
+    </row>
+    <row r="19" spans="1:10" ht="16.5" x14ac:dyDescent="0.2">
+      <c r="A19" s="1">
         <v>5021002</v>
       </c>
-      <c r="B19" s="19">
+      <c r="B19" s="10">
         <v>102100</v>
       </c>
       <c r="C19" t="s">
@@ -2379,18 +1767,18 @@
       <c r="E19" t="s">
         <v>33</v>
       </c>
-      <c r="F19" s="17" t="s">
+      <c r="F19" s="14" t="s">
         <v>54</v>
       </c>
       <c r="G19" s="1" t="s">
         <v>35</v>
       </c>
     </row>
-    <row r="20" customFormat="1" ht="16.5" spans="1:10">
-      <c r="A20" s="2">
+    <row r="20" spans="1:10" ht="16.5" x14ac:dyDescent="0.2">
+      <c r="A20" s="1">
         <v>5018001</v>
       </c>
-      <c r="B20" s="19">
+      <c r="B20" s="10">
         <v>101800</v>
       </c>
       <c r="C20" t="s">
@@ -2402,20 +1790,18 @@
       <c r="E20" t="s">
         <v>56</v>
       </c>
-      <c r="F20" s="17" t="s">
+      <c r="F20" s="14" t="s">
         <v>57</v>
       </c>
       <c r="G20" s="1" t="s">
         <v>58</v>
       </c>
-      <c r="H20" s="7"/>
-      <c r="I20" s="7"/>
-    </row>
-    <row r="21" customFormat="1" ht="16.5" spans="1:10">
-      <c r="A21" s="2">
+    </row>
+    <row r="21" spans="1:10" ht="16.5" x14ac:dyDescent="0.2">
+      <c r="A21" s="1">
         <v>5018002</v>
       </c>
-      <c r="B21" s="19">
+      <c r="B21" s="10">
         <v>101800</v>
       </c>
       <c r="C21" t="s">
@@ -2427,20 +1813,18 @@
       <c r="E21" t="s">
         <v>33</v>
       </c>
-      <c r="F21" s="17" t="s">
+      <c r="F21" s="14" t="s">
         <v>59</v>
       </c>
       <c r="G21" s="1" t="s">
         <v>35</v>
       </c>
-      <c r="H21" s="7"/>
-      <c r="I21" s="7"/>
-    </row>
-    <row r="22" customFormat="1" ht="16.5" spans="1:10">
-      <c r="A22" s="2">
+    </row>
+    <row r="22" spans="1:10" ht="16.5" x14ac:dyDescent="0.2">
+      <c r="A22" s="1">
         <v>5025001</v>
       </c>
-      <c r="B22" s="19">
+      <c r="B22" s="10">
         <v>102500</v>
       </c>
       <c r="C22" t="s">
@@ -2452,20 +1836,18 @@
       <c r="E22" t="s">
         <v>33</v>
       </c>
-      <c r="F22" s="17" t="s">
+      <c r="F22" s="14" t="s">
         <v>61</v>
       </c>
       <c r="G22" s="1" t="s">
         <v>35</v>
       </c>
-      <c r="H22" s="7"/>
-      <c r="I22" s="7"/>
-    </row>
-    <row r="23" customFormat="1" ht="16.5" spans="1:10">
-      <c r="A23" s="2">
+    </row>
+    <row r="23" spans="1:10" ht="16.5" x14ac:dyDescent="0.2">
+      <c r="A23" s="1">
         <v>5023005</v>
       </c>
-      <c r="B23" s="19">
+      <c r="B23" s="10">
         <v>102300</v>
       </c>
       <c r="C23" t="s">
@@ -2477,20 +1859,18 @@
       <c r="E23" t="s">
         <v>33</v>
       </c>
-      <c r="F23" s="17" t="s">
+      <c r="F23" s="14" t="s">
         <v>63</v>
       </c>
       <c r="G23" s="1" t="s">
         <v>35</v>
       </c>
-      <c r="H23" s="7"/>
-      <c r="I23" s="7"/>
-    </row>
-    <row r="24" customFormat="1" ht="16.5" spans="1:10">
-      <c r="A24" s="2">
+    </row>
+    <row r="24" spans="1:10" ht="16.5" x14ac:dyDescent="0.2">
+      <c r="A24" s="1">
         <v>5023008</v>
       </c>
-      <c r="B24" s="19">
+      <c r="B24" s="10">
         <v>102300</v>
       </c>
       <c r="C24" t="s">
@@ -2502,20 +1882,18 @@
       <c r="E24" t="s">
         <v>64</v>
       </c>
-      <c r="F24" s="17" t="s">
+      <c r="F24" s="14" t="s">
         <v>65</v>
       </c>
       <c r="G24" s="1" t="s">
         <v>66</v>
       </c>
-      <c r="H24" s="7"/>
-      <c r="I24" s="7"/>
-    </row>
-    <row r="25" customFormat="1" ht="16.5" spans="1:10">
-      <c r="A25" s="2">
+    </row>
+    <row r="25" spans="1:10" ht="16.5" x14ac:dyDescent="0.2">
+      <c r="A25" s="1">
         <v>5023009</v>
       </c>
-      <c r="B25" s="19">
+      <c r="B25" s="10">
         <v>102300</v>
       </c>
       <c r="C25" t="s">
@@ -2533,14 +1911,12 @@
       <c r="G25" s="1" t="s">
         <v>66</v>
       </c>
-      <c r="H25" s="7"/>
-      <c r="I25" s="7"/>
-    </row>
-    <row r="26" customFormat="1" ht="16.5" spans="1:10">
-      <c r="A26" s="2">
+    </row>
+    <row r="26" spans="1:10" ht="16.5" x14ac:dyDescent="0.2">
+      <c r="A26" s="1">
         <v>5034001</v>
       </c>
-      <c r="B26" s="19">
+      <c r="B26" s="10">
         <v>103400</v>
       </c>
       <c r="C26" t="s">
@@ -2552,20 +1928,18 @@
       <c r="E26" t="s">
         <v>70</v>
       </c>
-      <c r="F26" s="17" t="s">
+      <c r="F26" s="14" t="s">
         <v>71</v>
       </c>
       <c r="G26" s="1" t="s">
         <v>72</v>
       </c>
-      <c r="H26" s="7"/>
-      <c r="I26" s="7"/>
-    </row>
-    <row r="27" customFormat="1" ht="16.5" spans="1:10">
-      <c r="A27" s="2">
+    </row>
+    <row r="27" spans="1:10" ht="16.5" x14ac:dyDescent="0.2">
+      <c r="A27" s="1">
         <v>5034002</v>
       </c>
-      <c r="B27" s="19">
+      <c r="B27" s="10">
         <v>103400</v>
       </c>
       <c r="C27" t="s">
@@ -2577,20 +1951,18 @@
       <c r="E27" t="s">
         <v>73</v>
       </c>
-      <c r="F27" s="17" t="s">
+      <c r="F27" s="14" t="s">
         <v>74</v>
       </c>
       <c r="G27" s="1" t="s">
         <v>75</v>
       </c>
-      <c r="H27" s="7"/>
-      <c r="I27" s="7"/>
-    </row>
-    <row r="28" customFormat="1" ht="16.5" spans="1:10">
-      <c r="A28" s="2">
+    </row>
+    <row r="28" spans="1:10" ht="16.5" x14ac:dyDescent="0.2">
+      <c r="A28" s="1">
         <v>5034003</v>
       </c>
-      <c r="B28" s="19">
+      <c r="B28" s="10">
         <v>103400</v>
       </c>
       <c r="C28" t="s">
@@ -2602,20 +1974,18 @@
       <c r="E28" t="s">
         <v>76</v>
       </c>
-      <c r="F28" s="17" t="s">
+      <c r="F28" s="14" t="s">
         <v>77</v>
       </c>
       <c r="G28" s="1" t="s">
         <v>78</v>
       </c>
-      <c r="H28" s="7"/>
-      <c r="I28" s="7"/>
-    </row>
-    <row r="29" customFormat="1" ht="16.5" spans="1:10">
-      <c r="A29" s="2">
+    </row>
+    <row r="29" spans="1:10" ht="16.5" x14ac:dyDescent="0.2">
+      <c r="A29" s="1">
         <v>5034004</v>
       </c>
-      <c r="B29" s="19">
+      <c r="B29" s="10">
         <v>103400</v>
       </c>
       <c r="C29" t="s">
@@ -2627,20 +1997,18 @@
       <c r="E29" t="s">
         <v>79</v>
       </c>
-      <c r="F29" s="17" t="s">
+      <c r="F29" s="14" t="s">
         <v>80</v>
       </c>
       <c r="G29" s="1" t="s">
         <v>81</v>
       </c>
-      <c r="H29" s="7"/>
-      <c r="I29" s="7"/>
-    </row>
-    <row r="30" customFormat="1" ht="16.5" spans="1:10">
-      <c r="A30" s="2">
+    </row>
+    <row r="30" spans="1:10" ht="16.5" x14ac:dyDescent="0.2">
+      <c r="A30" s="1">
         <v>5035001</v>
       </c>
-      <c r="B30" s="19">
+      <c r="B30" s="10">
         <v>103500</v>
       </c>
       <c r="C30" t="s">
@@ -2652,20 +2020,18 @@
       <c r="E30" t="s">
         <v>83</v>
       </c>
-      <c r="F30" s="17" t="s">
+      <c r="F30" s="14" t="s">
         <v>84</v>
       </c>
       <c r="G30" s="1" t="s">
         <v>85</v>
       </c>
-      <c r="H30" s="7"/>
-      <c r="I30" s="7"/>
-    </row>
-    <row r="31" customFormat="1" ht="16.5" spans="1:10">
-      <c r="A31" s="2">
+    </row>
+    <row r="31" spans="1:10" ht="16.5" x14ac:dyDescent="0.2">
+      <c r="A31" s="1">
         <v>5035011</v>
       </c>
-      <c r="B31" s="19">
+      <c r="B31" s="10">
         <v>103501</v>
       </c>
       <c r="C31" t="s">
@@ -2677,20 +2043,18 @@
       <c r="E31" t="s">
         <v>83</v>
       </c>
-      <c r="F31" s="17" t="s">
+      <c r="F31" s="14" t="s">
         <v>84</v>
       </c>
       <c r="G31" s="1" t="s">
         <v>85</v>
       </c>
-      <c r="H31" s="7"/>
-      <c r="I31" s="7"/>
-    </row>
-    <row r="32" customFormat="1" ht="16.5" spans="1:10">
-      <c r="A32" s="2">
+    </row>
+    <row r="32" spans="1:10" ht="16.5" x14ac:dyDescent="0.2">
+      <c r="A32" s="1">
         <v>5036001</v>
       </c>
-      <c r="B32" s="19">
+      <c r="B32" s="10">
         <v>103600</v>
       </c>
       <c r="C32" t="s">
@@ -2702,20 +2066,18 @@
       <c r="E32" t="s">
         <v>88</v>
       </c>
-      <c r="F32" s="17" t="s">
+      <c r="F32" s="14" t="s">
         <v>84</v>
       </c>
       <c r="G32" s="1" t="s">
         <v>89</v>
       </c>
-      <c r="H32" s="7"/>
-      <c r="I32" s="7"/>
-    </row>
-    <row r="33" customFormat="1" ht="16.5" spans="1:10">
-      <c r="A33" s="2">
+    </row>
+    <row r="33" spans="1:10" ht="16.5" x14ac:dyDescent="0.2">
+      <c r="A33" s="1">
         <v>5036002</v>
       </c>
-      <c r="B33" s="19">
+      <c r="B33" s="10">
         <v>103600</v>
       </c>
       <c r="C33" t="s">
@@ -2727,20 +2089,18 @@
       <c r="E33" t="s">
         <v>90</v>
       </c>
-      <c r="F33" s="17" t="s">
+      <c r="F33" s="14" t="s">
         <v>91</v>
       </c>
       <c r="G33" s="1" t="s">
         <v>92</v>
       </c>
-      <c r="H33" s="7"/>
-      <c r="I33" s="7"/>
-    </row>
-    <row r="34" customFormat="1" ht="16.5" spans="1:10">
-      <c r="A34" s="2">
+    </row>
+    <row r="34" spans="1:10" ht="16.5" x14ac:dyDescent="0.2">
+      <c r="A34" s="1">
         <v>5028001</v>
       </c>
-      <c r="B34" s="19">
+      <c r="B34" s="10">
         <v>102800</v>
       </c>
       <c r="C34" t="s">
@@ -2752,20 +2112,18 @@
       <c r="E34" t="s">
         <v>33</v>
       </c>
-      <c r="F34" s="17" t="s">
+      <c r="F34" s="14" t="s">
         <v>94</v>
       </c>
       <c r="G34" s="1" t="s">
         <v>35</v>
       </c>
-      <c r="H34" s="7"/>
-      <c r="I34" s="7"/>
-    </row>
-    <row r="35" customFormat="1" ht="16.5" spans="1:10">
-      <c r="A35" s="2">
+    </row>
+    <row r="35" spans="1:10" ht="16.5" x14ac:dyDescent="0.2">
+      <c r="A35" s="1">
         <v>5028002</v>
       </c>
-      <c r="B35" s="19">
+      <c r="B35" s="10">
         <v>102800</v>
       </c>
       <c r="C35" t="s">
@@ -2777,20 +2135,18 @@
       <c r="E35" t="s">
         <v>95</v>
       </c>
-      <c r="F35" s="17" t="s">
+      <c r="F35" s="14" t="s">
         <v>96</v>
       </c>
       <c r="G35" s="1" t="s">
         <v>97</v>
       </c>
-      <c r="H35" s="7"/>
-      <c r="I35" s="7"/>
-    </row>
-    <row r="36" customFormat="1" ht="16.5" spans="1:10">
-      <c r="A36" s="2">
+    </row>
+    <row r="36" spans="1:10" ht="16.5" x14ac:dyDescent="0.2">
+      <c r="A36" s="1">
         <v>5034011</v>
       </c>
-      <c r="B36" s="19">
+      <c r="B36" s="10">
         <v>103401</v>
       </c>
       <c r="C36" t="s">
@@ -2802,20 +2158,18 @@
       <c r="E36" t="s">
         <v>70</v>
       </c>
-      <c r="F36" s="17" t="s">
+      <c r="F36" s="14" t="s">
         <v>71</v>
       </c>
       <c r="G36" s="1" t="s">
         <v>72</v>
       </c>
-      <c r="H36" s="7"/>
-      <c r="I36" s="7"/>
-    </row>
-    <row r="37" customFormat="1" ht="16.5" spans="1:10">
-      <c r="A37" s="2">
+    </row>
+    <row r="37" spans="1:10" ht="16.5" x14ac:dyDescent="0.2">
+      <c r="A37" s="1">
         <v>5034012</v>
       </c>
-      <c r="B37" s="19">
+      <c r="B37" s="10">
         <v>103402</v>
       </c>
       <c r="C37" t="s">
@@ -2827,20 +2181,18 @@
       <c r="E37" t="s">
         <v>73</v>
       </c>
-      <c r="F37" s="17" t="s">
+      <c r="F37" s="14" t="s">
         <v>99</v>
       </c>
       <c r="G37" s="1" t="s">
         <v>75</v>
       </c>
-      <c r="H37" s="7"/>
-      <c r="I37" s="7"/>
-    </row>
-    <row r="38" customFormat="1" ht="16.5" spans="1:10">
-      <c r="A38" s="2">
+    </row>
+    <row r="38" spans="1:10" ht="16.5" x14ac:dyDescent="0.2">
+      <c r="A38" s="1">
         <v>5034013</v>
       </c>
-      <c r="B38" s="19">
+      <c r="B38" s="10">
         <v>103403</v>
       </c>
       <c r="C38" t="s">
@@ -2852,20 +2204,18 @@
       <c r="E38" t="s">
         <v>76</v>
       </c>
-      <c r="F38" s="17" t="s">
+      <c r="F38" s="14" t="s">
         <v>100</v>
       </c>
       <c r="G38" s="1" t="s">
         <v>78</v>
       </c>
-      <c r="H38" s="7"/>
-      <c r="I38" s="7"/>
-    </row>
-    <row r="39" customFormat="1" ht="16.5" spans="1:10">
-      <c r="A39" s="2">
+    </row>
+    <row r="39" spans="1:10" ht="16.5" x14ac:dyDescent="0.2">
+      <c r="A39" s="1">
         <v>5034014</v>
       </c>
-      <c r="B39" s="19">
+      <c r="B39" s="10">
         <v>103404</v>
       </c>
       <c r="C39" t="s">
@@ -2877,109 +2227,113 @@
       <c r="E39" t="s">
         <v>79</v>
       </c>
-      <c r="F39" s="17" t="s">
+      <c r="F39" s="14" t="s">
         <v>80</v>
       </c>
       <c r="G39" s="1" t="s">
         <v>81</v>
       </c>
-      <c r="H39" s="7"/>
-      <c r="I39" s="7"/>
-    </row>
-    <row r="40" s="2" customFormat="1" ht="18" customHeight="1" spans="1:10">
-      <c r="A40" s="2">
+    </row>
+    <row r="40" spans="1:10" s="1" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A40" s="1">
         <v>5020001</v>
       </c>
-      <c r="B40" s="19">
+      <c r="B40" s="10">
         <v>102000</v>
       </c>
-      <c r="C40" s="14" t="s">
+      <c r="C40" s="11" t="s">
         <v>101</v>
       </c>
-      <c r="D40" s="19">
+      <c r="D40" s="10">
         <v>1</v>
       </c>
-      <c r="E40" s="2" t="s">
+      <c r="E40" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="F40" s="15" t="s">
+      <c r="F40" s="12" t="s">
         <v>102</v>
       </c>
-      <c r="G40" s="19" t="s">
+      <c r="G40" s="10" t="s">
         <v>28</v>
       </c>
-      <c r="H40" s="14"/>
-      <c r="I40" s="14"/>
-      <c r="J40" s="19"/>
-    </row>
-    <row r="41" s="3" customFormat="1" ht="16.5" spans="1:10">
-      <c r="A41" s="2">
+      <c r="H40" s="11"/>
+      <c r="I40" s="11"/>
+      <c r="J40" s="10"/>
+    </row>
+    <row r="41" spans="1:10" ht="16.5" x14ac:dyDescent="0.2">
+      <c r="A41" s="1">
         <v>5020002</v>
       </c>
-      <c r="B41" s="19">
+      <c r="B41" s="10">
         <v>102000</v>
       </c>
-      <c r="C41" s="14" t="s">
+      <c r="C41" s="11" t="s">
         <v>101</v>
       </c>
-      <c r="D41" s="19">
+      <c r="D41" s="10">
         <v>2</v>
       </c>
-      <c r="F41" s="3" t="s">
+      <c r="F41" t="s">
         <v>103</v>
       </c>
-    </row>
-    <row r="42" s="3" customFormat="1" ht="16.5" spans="1:10">
-      <c r="A42" s="2">
+      <c r="H41"/>
+      <c r="I41"/>
+    </row>
+    <row r="42" spans="1:10" ht="16.5" x14ac:dyDescent="0.2">
+      <c r="A42" s="1">
         <v>5027001</v>
       </c>
-      <c r="B42" s="19">
+      <c r="B42" s="10">
         <v>102700</v>
       </c>
-      <c r="C42" s="14" t="s">
+      <c r="C42" s="11" t="s">
         <v>104</v>
       </c>
-      <c r="D42" s="19">
+      <c r="D42" s="10">
         <v>1</v>
       </c>
-      <c r="E42" s="3" t="s">
+      <c r="E42" t="s">
         <v>33</v>
       </c>
-      <c r="F42" s="3" t="s">
+      <c r="F42" t="s">
         <v>105</v>
       </c>
-      <c r="G42" s="3" t="s">
+      <c r="G42" t="s">
         <v>35</v>
       </c>
-    </row>
-    <row r="43" s="3" customFormat="1" ht="16.5" spans="1:10">
-      <c r="A43" s="2">
+      <c r="H42"/>
+      <c r="I42"/>
+    </row>
+    <row r="43" spans="1:10" ht="16.5" x14ac:dyDescent="0.2">
+      <c r="A43" s="1">
         <v>5027002</v>
       </c>
-      <c r="B43" s="19">
+      <c r="B43" s="10">
         <v>102700</v>
       </c>
-      <c r="C43" s="14" t="s">
+      <c r="C43" s="11" t="s">
         <v>104</v>
       </c>
-      <c r="D43" s="19">
+      <c r="D43" s="10">
         <v>2</v>
       </c>
-      <c r="E43" s="3" t="s">
+      <c r="E43" t="s">
         <v>106</v>
       </c>
-      <c r="F43" s="3" t="s">
+      <c r="F43" t="s">
         <v>107</v>
       </c>
-      <c r="G43" s="3" t="s">
+      <c r="G43" t="s">
         <v>108</v>
       </c>
-    </row>
-    <row r="44" customFormat="1" ht="16.5" spans="1:10">
-      <c r="A44" s="2">
+      <c r="H43"/>
+      <c r="I43"/>
+    </row>
+    <row r="44" spans="1:10" ht="16.5" x14ac:dyDescent="0.2">
+      <c r="A44" s="1">
         <v>5037001</v>
       </c>
-      <c r="B44" s="19">
+      <c r="B44" s="10">
         <v>103700</v>
       </c>
       <c r="C44" t="s">
@@ -2991,20 +2345,18 @@
       <c r="E44" t="s">
         <v>110</v>
       </c>
-      <c r="F44" s="17" t="s">
+      <c r="F44" s="14" t="s">
         <v>84</v>
       </c>
       <c r="G44" s="1" t="s">
         <v>89</v>
       </c>
-      <c r="H44" s="7"/>
-      <c r="I44" s="7"/>
-    </row>
-    <row r="45" customFormat="1" ht="16.5" spans="1:10">
-      <c r="A45" s="2">
+    </row>
+    <row r="45" spans="1:10" ht="16.5" x14ac:dyDescent="0.2">
+      <c r="A45" s="1">
         <v>5037002</v>
       </c>
-      <c r="B45" s="19">
+      <c r="B45" s="10">
         <v>103700</v>
       </c>
       <c r="C45" t="s">
@@ -3016,20 +2368,18 @@
       <c r="E45" t="s">
         <v>111</v>
       </c>
-      <c r="F45" s="17" t="s">
+      <c r="F45" s="14" t="s">
         <v>112</v>
       </c>
       <c r="G45" s="1" t="s">
         <v>113</v>
       </c>
-      <c r="H45" s="7"/>
-      <c r="I45" s="7"/>
-    </row>
-    <row r="46" customFormat="1" ht="16.5" spans="1:10">
-      <c r="A46" s="2">
+    </row>
+    <row r="46" spans="1:10" ht="16.5" x14ac:dyDescent="0.2">
+      <c r="A46" s="1">
         <v>5037003</v>
       </c>
-      <c r="B46" s="19">
+      <c r="B46" s="10">
         <v>103700</v>
       </c>
       <c r="C46" t="s">
@@ -3041,20 +2391,18 @@
       <c r="E46" t="s">
         <v>114</v>
       </c>
-      <c r="F46" s="17" t="s">
+      <c r="F46" s="14" t="s">
         <v>115</v>
       </c>
       <c r="G46" s="1" t="s">
         <v>116</v>
       </c>
-      <c r="H46" s="7"/>
-      <c r="I46" s="7"/>
-    </row>
-    <row r="47" customFormat="1" ht="16.5" spans="1:10">
-      <c r="A47" s="2">
+    </row>
+    <row r="47" spans="1:10" ht="16.5" x14ac:dyDescent="0.2">
+      <c r="A47" s="1">
         <v>5031001</v>
       </c>
-      <c r="B47" s="19">
+      <c r="B47" s="10">
         <v>103100</v>
       </c>
       <c r="C47" t="s">
@@ -3066,20 +2414,18 @@
       <c r="E47" t="s">
         <v>33</v>
       </c>
-      <c r="F47" s="17" t="s">
+      <c r="F47" s="14" t="s">
         <v>118</v>
       </c>
       <c r="G47" s="1" t="s">
         <v>35</v>
       </c>
-      <c r="H47" s="7"/>
-      <c r="I47" s="7"/>
-    </row>
-    <row r="48" customFormat="1" ht="16.5" spans="1:10">
-      <c r="A48" s="2">
+    </row>
+    <row r="48" spans="1:10" ht="16.5" x14ac:dyDescent="0.2">
+      <c r="A48" s="1">
         <v>5040001</v>
       </c>
-      <c r="B48" s="19">
+      <c r="B48" s="10">
         <v>104000</v>
       </c>
       <c r="C48" t="s">
@@ -3091,20 +2437,18 @@
       <c r="E48" t="s">
         <v>33</v>
       </c>
-      <c r="F48" s="17" t="s">
+      <c r="F48" s="14" t="s">
         <v>120</v>
       </c>
       <c r="G48" s="1" t="s">
         <v>35</v>
       </c>
-      <c r="H48" s="7"/>
-      <c r="I48" s="7"/>
-    </row>
-    <row r="49" customFormat="1" ht="16.5" spans="1:9">
-      <c r="A49" s="2">
+    </row>
+    <row r="49" spans="1:7" ht="16.5" x14ac:dyDescent="0.2">
+      <c r="A49" s="1">
         <v>5039001</v>
       </c>
-      <c r="B49" s="19">
+      <c r="B49" s="10">
         <v>103900</v>
       </c>
       <c r="C49" t="s">
@@ -3116,20 +2460,18 @@
       <c r="E49" t="s">
         <v>122</v>
       </c>
-      <c r="F49" s="17" t="s">
+      <c r="F49" s="14" t="s">
         <v>123</v>
       </c>
       <c r="G49" s="1" t="s">
         <v>124</v>
       </c>
-      <c r="H49" s="7"/>
-      <c r="I49" s="7"/>
-    </row>
-    <row r="50" customFormat="1" ht="16.5" spans="1:9">
-      <c r="A50" s="2">
+    </row>
+    <row r="50" spans="1:7" ht="16.5" x14ac:dyDescent="0.2">
+      <c r="A50" s="1">
         <v>5016001</v>
       </c>
-      <c r="B50" s="19">
+      <c r="B50" s="10">
         <v>101600</v>
       </c>
       <c r="C50" t="s">
@@ -3141,20 +2483,18 @@
       <c r="E50" t="s">
         <v>33</v>
       </c>
-      <c r="F50" s="17" t="s">
+      <c r="F50" s="14" t="s">
         <v>126</v>
       </c>
       <c r="G50" s="1" t="s">
         <v>35</v>
       </c>
-      <c r="H50" s="7"/>
-      <c r="I50" s="7"/>
-    </row>
-    <row r="51" customFormat="1" ht="16.5" spans="1:9">
-      <c r="A51" s="2">
+    </row>
+    <row r="51" spans="1:7" ht="16.5" x14ac:dyDescent="0.2">
+      <c r="A51" s="1">
         <v>5016002</v>
       </c>
-      <c r="B51" s="19">
+      <c r="B51" s="10">
         <v>101600</v>
       </c>
       <c r="C51" t="s">
@@ -3166,20 +2506,18 @@
       <c r="E51" t="s">
         <v>127</v>
       </c>
-      <c r="F51" s="17" t="s">
+      <c r="F51" s="14" t="s">
         <v>128</v>
       </c>
       <c r="G51" s="1" t="s">
         <v>129</v>
       </c>
-      <c r="H51" s="7"/>
-      <c r="I51" s="7"/>
-    </row>
-    <row r="52" customFormat="1" ht="16.5" spans="1:9">
-      <c r="A52" s="2">
+    </row>
+    <row r="52" spans="1:7" ht="16.5" x14ac:dyDescent="0.2">
+      <c r="A52" s="1">
         <v>5015001</v>
       </c>
-      <c r="B52" s="19">
+      <c r="B52" s="10">
         <v>101500</v>
       </c>
       <c r="C52" t="s">
@@ -3191,20 +2529,18 @@
       <c r="E52" t="s">
         <v>131</v>
       </c>
-      <c r="F52" s="17" t="s">
+      <c r="F52" s="14" t="s">
         <v>132</v>
       </c>
       <c r="G52" t="s">
         <v>133</v>
       </c>
-      <c r="H52" s="7"/>
-      <c r="I52" s="7"/>
-    </row>
-    <row r="53" customFormat="1" ht="16.5" spans="1:9">
-      <c r="A53" s="2">
+    </row>
+    <row r="53" spans="1:7" ht="16.5" x14ac:dyDescent="0.2">
+      <c r="A53" s="1">
         <v>5015002</v>
       </c>
-      <c r="B53" s="19">
+      <c r="B53" s="10">
         <v>101500</v>
       </c>
       <c r="C53" t="s">
@@ -3216,20 +2552,18 @@
       <c r="E53" t="s">
         <v>33</v>
       </c>
-      <c r="F53" s="3" t="s">
+      <c r="F53" t="s">
         <v>134</v>
       </c>
       <c r="G53" s="1" t="s">
         <v>135</v>
       </c>
-      <c r="H53" s="7"/>
-      <c r="I53" s="7"/>
-    </row>
-    <row r="54" customFormat="1" ht="16.5" spans="1:9">
-      <c r="A54" s="2">
+    </row>
+    <row r="54" spans="1:7" ht="16.5" x14ac:dyDescent="0.2">
+      <c r="A54" s="1">
         <v>5026001</v>
       </c>
-      <c r="B54" s="19">
+      <c r="B54" s="10">
         <v>102600</v>
       </c>
       <c r="C54" t="s">
@@ -3241,20 +2575,18 @@
       <c r="E54" t="s">
         <v>30</v>
       </c>
-      <c r="F54" s="17" t="s">
+      <c r="F54" s="14" t="s">
         <v>137</v>
       </c>
       <c r="G54" s="1" t="s">
         <v>32</v>
       </c>
-      <c r="H54" s="7"/>
-      <c r="I54" s="7"/>
-    </row>
-    <row r="55" customFormat="1" ht="16.5" spans="1:9">
-      <c r="A55" s="2">
+    </row>
+    <row r="55" spans="1:7" ht="16.5" x14ac:dyDescent="0.2">
+      <c r="A55" s="1">
         <v>5026003</v>
       </c>
-      <c r="B55" s="19">
+      <c r="B55" s="10">
         <v>102600</v>
       </c>
       <c r="C55" t="s">
@@ -3266,20 +2598,18 @@
       <c r="E55" t="s">
         <v>138</v>
       </c>
-      <c r="F55" s="17" t="s">
+      <c r="F55" s="14" t="s">
         <v>139</v>
       </c>
       <c r="G55" s="1" t="s">
         <v>140</v>
       </c>
-      <c r="H55" s="7"/>
-      <c r="I55" s="7"/>
-    </row>
-    <row r="56" customFormat="1" ht="16.5" spans="1:9">
-      <c r="A56" s="2">
+    </row>
+    <row r="56" spans="1:7" ht="16.5" x14ac:dyDescent="0.2">
+      <c r="A56" s="1">
         <v>5050001</v>
       </c>
-      <c r="B56" s="19">
+      <c r="B56" s="10">
         <v>105000</v>
       </c>
       <c r="C56" t="s">
@@ -3291,20 +2621,18 @@
       <c r="E56" t="s">
         <v>33</v>
       </c>
-      <c r="F56" s="17" t="s">
+      <c r="F56" s="14" t="s">
         <v>142</v>
       </c>
       <c r="G56" s="1" t="s">
         <v>143</v>
       </c>
-      <c r="H56" s="7"/>
-      <c r="I56" s="7"/>
-    </row>
-    <row r="57" customFormat="1" ht="16.5" spans="1:9">
-      <c r="A57" s="2">
+    </row>
+    <row r="57" spans="1:7" ht="16.5" x14ac:dyDescent="0.2">
+      <c r="A57" s="1">
         <v>5050002</v>
       </c>
-      <c r="B57" s="19">
+      <c r="B57" s="10">
         <v>105000</v>
       </c>
       <c r="C57" t="s">
@@ -3316,45 +2644,41 @@
       <c r="E57" t="s">
         <v>144</v>
       </c>
-      <c r="F57" s="17" t="s">
+      <c r="F57" s="14" t="s">
         <v>145</v>
       </c>
       <c r="G57" s="1" t="s">
         <v>146</v>
       </c>
-      <c r="H57" s="7"/>
-      <c r="I57" s="7"/>
-    </row>
-    <row r="58" s="4" customFormat="1" ht="16.5" spans="1:9">
-      <c r="A58" s="2">
+    </row>
+    <row r="58" spans="1:7" ht="16.5" x14ac:dyDescent="0.2">
+      <c r="A58" s="1">
         <v>5051001</v>
       </c>
-      <c r="B58" s="19">
+      <c r="B58" s="10">
         <v>105100</v>
       </c>
-      <c r="C58" s="4" t="s">
+      <c r="C58" t="s">
         <v>147</v>
       </c>
-      <c r="D58" s="2">
+      <c r="D58" s="1">
         <v>1</v>
       </c>
-      <c r="E58" s="4" t="s">
+      <c r="E58" t="s">
         <v>148</v>
       </c>
-      <c r="F58" s="20" t="s">
+      <c r="F58" s="14" t="s">
         <v>149</v>
       </c>
-      <c r="G58" s="2" t="s">
+      <c r="G58" s="1" t="s">
         <v>150</v>
       </c>
-      <c r="H58" s="21"/>
-      <c r="I58" s="21"/>
-    </row>
-    <row r="59" customFormat="1" ht="16.5" spans="1:9">
-      <c r="A59" s="2">
+    </row>
+    <row r="59" spans="1:7" ht="16.5" x14ac:dyDescent="0.2">
+      <c r="A59" s="1">
         <v>5054001</v>
       </c>
-      <c r="B59" s="19">
+      <c r="B59" s="10">
         <v>105400</v>
       </c>
       <c r="C59" t="s">
@@ -3366,20 +2690,18 @@
       <c r="E59" t="s">
         <v>152</v>
       </c>
-      <c r="F59" s="17" t="s">
+      <c r="F59" s="14" t="s">
         <v>145</v>
       </c>
       <c r="G59" s="1" t="s">
         <v>153</v>
       </c>
-      <c r="H59" s="7"/>
-      <c r="I59" s="7"/>
-    </row>
-    <row r="60" customFormat="1" ht="16.5" spans="1:9">
-      <c r="A60" s="2">
+    </row>
+    <row r="60" spans="1:7" ht="16.5" x14ac:dyDescent="0.2">
+      <c r="A60" s="1">
         <v>5054002</v>
       </c>
-      <c r="B60" s="19">
+      <c r="B60" s="10">
         <v>105400</v>
       </c>
       <c r="C60" t="s">
@@ -3391,20 +2713,18 @@
       <c r="E60" t="s">
         <v>33</v>
       </c>
-      <c r="F60" s="17" t="s">
+      <c r="F60" s="14" t="s">
         <v>154</v>
       </c>
       <c r="G60" s="1" t="s">
         <v>143</v>
       </c>
-      <c r="H60" s="7"/>
-      <c r="I60" s="7"/>
-    </row>
-    <row r="61" customFormat="1" ht="16.5" spans="1:9">
-      <c r="A61" s="2">
+    </row>
+    <row r="61" spans="1:7" ht="16.5" x14ac:dyDescent="0.2">
+      <c r="A61" s="1">
         <v>5008001</v>
       </c>
-      <c r="B61" s="19">
+      <c r="B61" s="10">
         <v>100800</v>
       </c>
       <c r="C61" t="s">
@@ -3416,20 +2736,18 @@
       <c r="E61" t="s">
         <v>156</v>
       </c>
-      <c r="F61" s="17" t="s">
+      <c r="F61" s="14" t="s">
         <v>157</v>
       </c>
       <c r="G61" s="1" t="s">
         <v>158</v>
       </c>
-      <c r="H61" s="7"/>
-      <c r="I61" s="7"/>
-    </row>
-    <row r="62" customFormat="1" ht="16.5" spans="1:9">
-      <c r="A62" s="2">
+    </row>
+    <row r="62" spans="1:7" ht="16.5" x14ac:dyDescent="0.2">
+      <c r="A62" s="1">
         <v>5008002</v>
       </c>
-      <c r="B62" s="19">
+      <c r="B62" s="10">
         <v>100800</v>
       </c>
       <c r="C62" t="s">
@@ -3441,20 +2759,18 @@
       <c r="E62" t="s">
         <v>33</v>
       </c>
-      <c r="F62" s="3" t="s">
+      <c r="F62" t="s">
         <v>159</v>
       </c>
-      <c r="G62" s="3" t="s">
+      <c r="G62" t="s">
         <v>35</v>
       </c>
-      <c r="H62" s="7"/>
-      <c r="I62" s="7"/>
-    </row>
-    <row r="63" customFormat="1" ht="16.5" spans="1:9">
-      <c r="A63" s="2">
+    </row>
+    <row r="63" spans="1:7" ht="16.5" x14ac:dyDescent="0.2">
+      <c r="A63" s="1">
         <v>5053001</v>
       </c>
-      <c r="B63" s="19">
+      <c r="B63" s="10">
         <v>105300</v>
       </c>
       <c r="C63" t="s">
@@ -3466,20 +2782,18 @@
       <c r="E63" s="1" t="s">
         <v>30</v>
       </c>
-      <c r="F63" s="17" t="s">
+      <c r="F63" s="14" t="s">
         <v>31</v>
       </c>
       <c r="G63" s="1" t="s">
         <v>32</v>
       </c>
-      <c r="H63" s="7"/>
-      <c r="I63" s="7"/>
-    </row>
-    <row r="64" customFormat="1" ht="16.5" spans="1:9">
-      <c r="A64" s="2">
+    </row>
+    <row r="64" spans="1:7" ht="16.5" x14ac:dyDescent="0.2">
+      <c r="A64" s="1">
         <v>5057001</v>
       </c>
-      <c r="B64" s="19">
+      <c r="B64" s="10">
         <v>105700</v>
       </c>
       <c r="C64" t="s">
@@ -3491,20 +2805,18 @@
       <c r="E64" t="s">
         <v>30</v>
       </c>
-      <c r="F64" s="17" t="s">
+      <c r="F64" s="14" t="s">
         <v>162</v>
       </c>
       <c r="G64" s="1" t="s">
         <v>32</v>
       </c>
-      <c r="H64" s="7"/>
-      <c r="I64" s="7"/>
-    </row>
-    <row r="65" customFormat="1" ht="16.5" spans="1:9">
-      <c r="A65" s="2">
+    </row>
+    <row r="65" spans="1:9" ht="16.5" x14ac:dyDescent="0.2">
+      <c r="A65" s="1">
         <v>5057002</v>
       </c>
-      <c r="B65" s="19">
+      <c r="B65" s="10">
         <v>105700</v>
       </c>
       <c r="C65" t="s">
@@ -3516,20 +2828,18 @@
       <c r="E65" t="s">
         <v>33</v>
       </c>
-      <c r="F65" s="3" t="s">
+      <c r="F65" t="s">
         <v>163</v>
       </c>
-      <c r="G65" s="3" t="s">
+      <c r="G65" t="s">
         <v>35</v>
       </c>
-      <c r="H65" s="7"/>
-      <c r="I65" s="7"/>
-    </row>
-    <row r="66" customFormat="1" ht="16.5" spans="1:9">
-      <c r="A66" s="2">
+    </row>
+    <row r="66" spans="1:9" ht="16.5" x14ac:dyDescent="0.2">
+      <c r="A66" s="1">
         <v>5057003</v>
       </c>
-      <c r="B66" s="19">
+      <c r="B66" s="10">
         <v>105700</v>
       </c>
       <c r="C66" t="s">
@@ -3541,20 +2851,18 @@
       <c r="E66" t="s">
         <v>164</v>
       </c>
-      <c r="F66" s="17" t="s">
+      <c r="F66" s="14" t="s">
         <v>165</v>
       </c>
       <c r="G66" s="1" t="s">
         <v>166</v>
       </c>
-      <c r="H66" s="7"/>
-      <c r="I66" s="7"/>
-    </row>
-    <row r="67" customFormat="1" ht="16.5" spans="1:9">
-      <c r="A67" s="2">
+    </row>
+    <row r="67" spans="1:9" ht="16.5" x14ac:dyDescent="0.2">
+      <c r="A67" s="1">
         <v>5058001</v>
       </c>
-      <c r="B67" s="19">
+      <c r="B67" s="10">
         <v>105800</v>
       </c>
       <c r="C67" t="s">
@@ -3566,20 +2874,18 @@
       <c r="E67" t="s">
         <v>33</v>
       </c>
-      <c r="F67" s="3" t="s">
+      <c r="F67" t="s">
         <v>168</v>
       </c>
-      <c r="G67" s="3" t="s">
+      <c r="G67" t="s">
         <v>35</v>
       </c>
-      <c r="H67" s="7"/>
-      <c r="I67" s="7"/>
-    </row>
-    <row r="68" customFormat="1" ht="16.5" spans="1:9">
-      <c r="A68" s="2">
+    </row>
+    <row r="68" spans="1:9" ht="16.5" x14ac:dyDescent="0.2">
+      <c r="A68" s="1">
         <v>5058002</v>
       </c>
-      <c r="B68" s="19">
+      <c r="B68" s="10">
         <v>105800</v>
       </c>
       <c r="C68" t="s">
@@ -3591,45 +2897,43 @@
       <c r="E68" t="s">
         <v>169</v>
       </c>
-      <c r="F68" s="3" t="s">
+      <c r="F68" t="s">
         <v>170</v>
       </c>
-      <c r="G68" s="3" t="s">
+      <c r="G68" t="s">
         <v>171</v>
       </c>
-      <c r="H68" s="7"/>
-      <c r="I68" s="7"/>
-    </row>
-    <row r="69" s="5" customFormat="1" spans="1:9">
-      <c r="A69" s="5">
+    </row>
+    <row r="69" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A69" s="2">
         <v>5055001</v>
       </c>
-      <c r="B69" s="5">
+      <c r="B69" s="2">
         <v>105500</v>
       </c>
-      <c r="C69" s="5" t="s">
+      <c r="C69" s="2" t="s">
         <v>172</v>
       </c>
-      <c r="D69" s="5">
+      <c r="D69" s="2">
         <v>1</v>
       </c>
-      <c r="E69" s="5" t="s">
+      <c r="E69" s="2" t="s">
         <v>173</v>
       </c>
-      <c r="F69" s="5" t="s">
+      <c r="F69" s="2" t="s">
         <v>174</v>
       </c>
-      <c r="G69" s="5" t="s">
+      <c r="G69" s="2" t="s">
         <v>175</v>
       </c>
-      <c r="H69" s="22"/>
-      <c r="I69" s="22"/>
-    </row>
-    <row r="70" customFormat="1" ht="18" customHeight="1" spans="1:9">
-      <c r="A70" s="2">
+      <c r="H69" s="16"/>
+      <c r="I69" s="16"/>
+    </row>
+    <row r="70" spans="1:9" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A70" s="1">
         <v>5048001</v>
       </c>
-      <c r="B70" s="19">
+      <c r="B70" s="10">
         <v>104800</v>
       </c>
       <c r="C70" t="s">
@@ -3641,20 +2945,18 @@
       <c r="E70" t="s">
         <v>33</v>
       </c>
-      <c r="F70" s="3" t="s">
+      <c r="F70" t="s">
         <v>159</v>
       </c>
-      <c r="G70" s="3" t="s">
+      <c r="G70" t="s">
         <v>35</v>
       </c>
-      <c r="H70" s="7"/>
-      <c r="I70" s="7"/>
-    </row>
-    <row r="71" customFormat="1" ht="16.5" spans="1:9">
-      <c r="A71" s="2">
+    </row>
+    <row r="71" spans="1:9" ht="16.5" x14ac:dyDescent="0.2">
+      <c r="A71" s="1">
         <v>5048002</v>
       </c>
-      <c r="B71" s="19">
+      <c r="B71" s="10">
         <v>104800</v>
       </c>
       <c r="C71" t="s">
@@ -3666,64 +2968,61 @@
       <c r="E71" t="s">
         <v>177</v>
       </c>
-      <c r="F71" s="3" t="s">
+      <c r="F71" t="s">
         <v>178</v>
       </c>
-      <c r="G71" s="3" t="s">
+      <c r="G71" t="s">
         <v>158</v>
       </c>
-      <c r="H71" s="7"/>
-      <c r="I71" s="7"/>
-    </row>
-    <row r="72" s="5" customFormat="1" spans="1:9">
-      <c r="A72" s="5">
+    </row>
+    <row r="72" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A72" s="2">
         <v>5055011</v>
       </c>
-      <c r="B72" s="5">
+      <c r="B72" s="2">
         <v>105501</v>
       </c>
-      <c r="C72" s="5" t="s">
+      <c r="C72" s="2" t="s">
         <v>179</v>
       </c>
-      <c r="D72" s="5">
+      <c r="D72" s="2">
         <v>1</v>
       </c>
-      <c r="E72" s="5" t="s">
+      <c r="E72" s="2" t="s">
         <v>173</v>
       </c>
-      <c r="F72" s="5" t="s">
+      <c r="F72" s="2" t="s">
         <v>174</v>
       </c>
-      <c r="G72" s="5" t="s">
+      <c r="G72" s="2" t="s">
         <v>175</v>
       </c>
-      <c r="H72" s="22"/>
-      <c r="I72" s="22"/>
+      <c r="H72" s="16"/>
+      <c r="I72" s="16"/>
     </row>
   </sheetData>
+  <phoneticPr fontId="7" type="noConversion"/>
   <conditionalFormatting sqref="H2">
-    <cfRule type="expression" dxfId="0" priority="1">
+    <cfRule type="expression" dxfId="1" priority="1">
       <formula>MOD(MID($A2,1,4),2)=1</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B1:C4 H1:I1 I2 H3:I4">
+  <conditionalFormatting sqref="H1:I1 B1:C4 I2 H3:I4">
     <cfRule type="expression" dxfId="0" priority="2">
       <formula>MOD($B1,2)=1</formula>
     </cfRule>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <headerFooter/>
-  <legacyDrawing r:id="rId2"/>
+  <legacyDrawing r:id="rId1"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
-  <sheetPr/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:E48"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25" outlineLevelCol="4"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <sheetData>
-    <row r="1" spans="1:5">
+    <row r="1" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A1" t="s">
         <v>180</v>
       </c>
@@ -3731,7 +3030,7 @@
         <v>181</v>
       </c>
     </row>
-    <row r="2" spans="1:5">
+    <row r="2" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
         <v>182</v>
       </c>
@@ -3745,7 +3044,7 @@
         <v>183</v>
       </c>
     </row>
-    <row r="3" spans="1:5">
+    <row r="3" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A3">
         <v>0</v>
       </c>
@@ -3759,7 +3058,7 @@
         <v>185</v>
       </c>
     </row>
-    <row r="4" spans="1:5">
+    <row r="4" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A4">
         <v>1</v>
       </c>
@@ -3773,7 +3072,7 @@
         <v>187</v>
       </c>
     </row>
-    <row r="5" spans="1:5">
+    <row r="5" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A5">
         <v>2</v>
       </c>
@@ -3787,7 +3086,7 @@
         <v>189</v>
       </c>
     </row>
-    <row r="6" spans="1:5">
+    <row r="6" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A6">
         <v>3</v>
       </c>
@@ -3801,7 +3100,7 @@
         <v>191</v>
       </c>
     </row>
-    <row r="7" spans="1:5">
+    <row r="7" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A7">
         <v>4</v>
       </c>
@@ -3815,7 +3114,7 @@
         <v>193</v>
       </c>
     </row>
-    <row r="8" spans="1:5">
+    <row r="8" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A8">
         <v>5</v>
       </c>
@@ -3829,7 +3128,7 @@
         <v>195</v>
       </c>
     </row>
-    <row r="9" spans="1:5">
+    <row r="9" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A9">
         <v>6</v>
       </c>
@@ -3837,7 +3136,7 @@
         <v>196</v>
       </c>
     </row>
-    <row r="10" spans="1:5">
+    <row r="10" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A10">
         <v>7</v>
       </c>
@@ -3845,7 +3144,7 @@
         <v>197</v>
       </c>
     </row>
-    <row r="11" spans="1:5">
+    <row r="11" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A11">
         <v>8</v>
       </c>
@@ -3853,7 +3152,7 @@
         <v>198</v>
       </c>
     </row>
-    <row r="12" spans="1:5">
+    <row r="12" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A12">
         <v>9</v>
       </c>
@@ -3861,7 +3160,7 @@
         <v>199</v>
       </c>
     </row>
-    <row r="13" spans="1:5">
+    <row r="13" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A13">
         <v>10</v>
       </c>
@@ -3869,7 +3168,7 @@
         <v>200</v>
       </c>
     </row>
-    <row r="14" spans="1:5">
+    <row r="14" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A14">
         <v>11</v>
       </c>
@@ -3877,7 +3176,7 @@
         <v>201</v>
       </c>
     </row>
-    <row r="15" spans="1:5">
+    <row r="15" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A15">
         <v>12</v>
       </c>
@@ -3885,7 +3184,7 @@
         <v>202</v>
       </c>
     </row>
-    <row r="16" spans="1:5">
+    <row r="16" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A16">
         <v>13</v>
       </c>
@@ -3893,7 +3192,7 @@
         <v>203</v>
       </c>
     </row>
-    <row r="17" spans="1:2">
+    <row r="17" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A17">
         <v>14</v>
       </c>
@@ -3901,7 +3200,7 @@
         <v>204</v>
       </c>
     </row>
-    <row r="18" spans="1:2">
+    <row r="18" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A18">
         <v>15</v>
       </c>
@@ -3909,7 +3208,7 @@
         <v>205</v>
       </c>
     </row>
-    <row r="19" spans="1:2">
+    <row r="19" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A19">
         <v>16</v>
       </c>
@@ -3917,7 +3216,7 @@
         <v>206</v>
       </c>
     </row>
-    <row r="20" spans="1:2">
+    <row r="20" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A20">
         <v>17</v>
       </c>
@@ -3925,7 +3224,7 @@
         <v>207</v>
       </c>
     </row>
-    <row r="21" spans="1:2">
+    <row r="21" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A21">
         <v>18</v>
       </c>
@@ -3933,7 +3232,7 @@
         <v>208</v>
       </c>
     </row>
-    <row r="22" spans="1:2">
+    <row r="22" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A22">
         <v>19</v>
       </c>
@@ -3941,7 +3240,7 @@
         <v>209</v>
       </c>
     </row>
-    <row r="23" spans="1:2">
+    <row r="23" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A23">
         <v>20</v>
       </c>
@@ -3949,7 +3248,7 @@
         <v>210</v>
       </c>
     </row>
-    <row r="24" spans="1:2">
+    <row r="24" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A24">
         <v>21</v>
       </c>
@@ -3957,7 +3256,7 @@
         <v>211</v>
       </c>
     </row>
-    <row r="25" spans="1:2">
+    <row r="25" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A25">
         <v>22</v>
       </c>
@@ -3965,7 +3264,7 @@
         <v>212</v>
       </c>
     </row>
-    <row r="26" spans="1:2">
+    <row r="26" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A26">
         <v>23</v>
       </c>
@@ -3973,7 +3272,7 @@
         <v>213</v>
       </c>
     </row>
-    <row r="27" spans="1:2">
+    <row r="27" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A27">
         <v>24</v>
       </c>
@@ -3981,7 +3280,7 @@
         <v>214</v>
       </c>
     </row>
-    <row r="28" spans="1:2">
+    <row r="28" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A28">
         <v>25</v>
       </c>
@@ -3989,7 +3288,7 @@
         <v>215</v>
       </c>
     </row>
-    <row r="29" spans="1:2">
+    <row r="29" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A29">
         <v>26</v>
       </c>
@@ -3997,7 +3296,7 @@
         <v>216</v>
       </c>
     </row>
-    <row r="30" spans="1:2">
+    <row r="30" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A30">
         <v>27</v>
       </c>
@@ -4005,7 +3304,7 @@
         <v>217</v>
       </c>
     </row>
-    <row r="31" spans="1:2">
+    <row r="31" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A31">
         <v>28</v>
       </c>
@@ -4013,7 +3312,7 @@
         <v>218</v>
       </c>
     </row>
-    <row r="32" spans="1:2">
+    <row r="32" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A32">
         <v>29</v>
       </c>
@@ -4021,7 +3320,7 @@
         <v>219</v>
       </c>
     </row>
-    <row r="33" spans="1:2">
+    <row r="33" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A33">
         <v>30</v>
       </c>
@@ -4029,7 +3328,7 @@
         <v>220</v>
       </c>
     </row>
-    <row r="34" spans="1:2">
+    <row r="34" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A34">
         <v>31</v>
       </c>
@@ -4037,7 +3336,7 @@
         <v>221</v>
       </c>
     </row>
-    <row r="35" spans="1:2">
+    <row r="35" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A35">
         <v>32</v>
       </c>
@@ -4045,7 +3344,7 @@
         <v>222</v>
       </c>
     </row>
-    <row r="36" spans="1:2">
+    <row r="36" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A36">
         <v>33</v>
       </c>
@@ -4053,7 +3352,7 @@
         <v>223</v>
       </c>
     </row>
-    <row r="37" spans="1:2">
+    <row r="37" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A37">
         <v>34</v>
       </c>
@@ -4061,7 +3360,7 @@
         <v>224</v>
       </c>
     </row>
-    <row r="38" spans="1:2">
+    <row r="38" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A38">
         <v>35</v>
       </c>
@@ -4069,7 +3368,7 @@
         <v>225</v>
       </c>
     </row>
-    <row r="39" spans="1:2">
+    <row r="39" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A39">
         <v>36</v>
       </c>
@@ -4077,7 +3376,7 @@
         <v>226</v>
       </c>
     </row>
-    <row r="40" spans="1:2">
+    <row r="40" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A40">
         <v>37</v>
       </c>
@@ -4085,7 +3384,7 @@
         <v>227</v>
       </c>
     </row>
-    <row r="41" spans="1:2">
+    <row r="41" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A41">
         <v>38</v>
       </c>
@@ -4093,7 +3392,7 @@
         <v>228</v>
       </c>
     </row>
-    <row r="42" spans="1:2">
+    <row r="42" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A42">
         <v>39</v>
       </c>
@@ -4101,7 +3400,7 @@
         <v>229</v>
       </c>
     </row>
-    <row r="43" spans="1:2">
+    <row r="43" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A43">
         <v>40</v>
       </c>
@@ -4109,7 +3408,7 @@
         <v>230</v>
       </c>
     </row>
-    <row r="44" spans="1:2">
+    <row r="44" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A44">
         <v>41</v>
       </c>
@@ -4117,7 +3416,7 @@
         <v>231</v>
       </c>
     </row>
-    <row r="45" spans="1:2">
+    <row r="45" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A45">
         <v>42</v>
       </c>
@@ -4125,7 +3424,7 @@
         <v>232</v>
       </c>
     </row>
-    <row r="46" spans="1:2">
+    <row r="46" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A46">
         <v>43</v>
       </c>
@@ -4133,7 +3432,7 @@
         <v>233</v>
       </c>
     </row>
-    <row r="47" spans="1:2">
+    <row r="47" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A47">
         <v>44</v>
       </c>
@@ -4141,7 +3440,7 @@
         <v>234</v>
       </c>
     </row>
-    <row r="48" spans="1:2">
+    <row r="48" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A48">
         <v>45</v>
       </c>
@@ -4150,7 +3449,7 @@
       </c>
     </row>
   </sheetData>
+  <phoneticPr fontId="7" type="noConversion"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-  <headerFooter/>
 </worksheet>
 </file>
--- a/slots/resources/sample/SpecialPlay.xlsx
+++ b/slots/resources/sample/SpecialPlay.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\cehua\gamedoc\游戏配置表\slot\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\gamedoc\游戏配置表\slot\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="11_627BD6E2A550FBFA6ABA060465B62B58CDA14E12" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E486CA56-EE51-4A06-A936-927C40165F60}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="5280" yWindow="4170" windowWidth="21600" windowHeight="11295" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="SpecialPlay" sheetId="1" r:id="rId1"/>
@@ -143,7 +143,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="351" uniqueCount="236">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="359" uniqueCount="243">
   <si>
     <t>被动游戏ID</t>
   </si>
@@ -851,6 +851,34 @@
   </si>
   <si>
     <t>通用普通10</t>
+  </si>
+  <si>
+    <t>伽罗宝石21</t>
+    <phoneticPr fontId="10" type="noConversion"/>
+  </si>
+  <si>
+    <t>前三轴出现的多格图标及权重</t>
+    <phoneticPr fontId="10" type="noConversion"/>
+  </si>
+  <si>
+    <t>16_2_3000|17_2_3000|18_2_2000|19_2_2000|20_2_300|21_2_250|22_2_200|23_2_50|24_3_1500|25_3_1500|26_3_1200|27_3_1200|28_3_200|29_3_150|30_3_100|31_3_10</t>
+    <phoneticPr fontId="10" type="noConversion"/>
+  </si>
+  <si>
+    <t>元素ID_图标连线中奖的额外倍数_权重</t>
+    <phoneticPr fontId="10" type="noConversion"/>
+  </si>
+  <si>
+    <t>前三轴出现的多格图标个数及权重</t>
+    <phoneticPr fontId="10" type="noConversion"/>
+  </si>
+  <si>
+    <t>1_6000|2_4000|3_3000|4_1500|5_1000|6_200|7_100|8_0|9_0</t>
+    <phoneticPr fontId="10" type="noConversion"/>
+  </si>
+  <si>
+    <t>多格图标个数_权重</t>
+    <phoneticPr fontId="10" type="noConversion"/>
   </si>
 </sst>
 </file>
@@ -858,9 +886,9 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="1">
-    <numFmt numFmtId="178" formatCode="0_ "/>
+    <numFmt numFmtId="176" formatCode="0_ "/>
   </numFmts>
-  <fonts count="8" x14ac:knownFonts="1">
+  <fonts count="11" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -909,6 +937,28 @@
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <sz val="10"/>
+      <color theme="1"/>
+      <name val="微软雅黑"/>
+      <family val="2"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="等线"/>
+      <family val="3"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="9"/>
+      <name val="等线"/>
+      <family val="3"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
   <fills count="4">
     <fill>
@@ -945,7 +995,7 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="17">
+  <cellXfs count="20">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
@@ -966,7 +1016,7 @@
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
-    <xf numFmtId="178" fontId="1" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="176" fontId="1" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -991,6 +1041,13 @@
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
   </cellXfs>
@@ -1286,7 +1343,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:J72"/>
+  <dimension ref="A1:J74"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="4" max="4" width="9.5" style="3" customWidth="1"/>
@@ -2999,6 +3056,52 @@
       </c>
       <c r="H72" s="16"/>
       <c r="I72" s="16"/>
+    </row>
+    <row r="73" spans="1:9" ht="16.5" x14ac:dyDescent="0.2">
+      <c r="A73" s="1">
+        <v>5055021</v>
+      </c>
+      <c r="B73" s="17">
+        <v>105502</v>
+      </c>
+      <c r="C73" s="18" t="s">
+        <v>236</v>
+      </c>
+      <c r="D73" s="2">
+        <v>1</v>
+      </c>
+      <c r="E73" s="18" t="s">
+        <v>237</v>
+      </c>
+      <c r="F73" s="18" t="s">
+        <v>238</v>
+      </c>
+      <c r="G73" s="19" t="s">
+        <v>239</v>
+      </c>
+    </row>
+    <row r="74" spans="1:9" ht="16.5" x14ac:dyDescent="0.2">
+      <c r="A74" s="1">
+        <v>5055022</v>
+      </c>
+      <c r="B74" s="17">
+        <v>105502</v>
+      </c>
+      <c r="C74" s="18" t="s">
+        <v>236</v>
+      </c>
+      <c r="D74" s="2">
+        <v>2</v>
+      </c>
+      <c r="E74" s="18" t="s">
+        <v>240</v>
+      </c>
+      <c r="F74" s="18" t="s">
+        <v>241</v>
+      </c>
+      <c r="G74" s="19" t="s">
+        <v>242</v>
+      </c>
     </row>
   </sheetData>
   <phoneticPr fontId="7" type="noConversion"/>

--- a/slots/resources/sample/SpecialPlay.xlsx
+++ b/slots/resources/sample/SpecialPlay.xlsx
@@ -391,85 +391,85 @@
     <t>常规模式下，概率触发金钱兔模式特效</t>
   </si>
   <si>
+    <t>模式，概率假进金钱兔模式万分比</t>
+  </si>
+  <si>
+    <t>金钱兔</t>
+  </si>
+  <si>
+    <t>鼠鼠福福</t>
+  </si>
+  <si>
+    <t>常规模式下，概率触发福鼠模式特效</t>
+  </si>
+  <si>
+    <t>模式，概率假进福鼠模式万分比</t>
+  </si>
+  <si>
+    <t>福鼠模式下，获得连线奖励奖返回常规模式</t>
+  </si>
+  <si>
+    <t>2,0_1</t>
+  </si>
+  <si>
+    <t>SpecialMode模式ID，中奖倍率大于x时回到常规模式</t>
+  </si>
+  <si>
+    <t>王牌dj</t>
+  </si>
+  <si>
+    <t>2,13,4_10_10000|5_15_10000|6_20_10000</t>
+  </si>
+  <si>
+    <t>带wild中奖对应得中奖倍率，原赔率乘以此倍率值</t>
+  </si>
+  <si>
+    <t>2_2_2_2_4_6_8_10_12_14_16_18_20_22_24_26_28_30</t>
+  </si>
+  <si>
+    <t>初始为2，2，2，2，每次销毁加2，到达最大值30时，之后每次都为30</t>
+  </si>
+  <si>
+    <t>虎虎生财</t>
+  </si>
+  <si>
+    <t>1_1;2_1;3_1;4_1;5_1;6_1</t>
+  </si>
+  <si>
+    <t>5_3000_2000</t>
+  </si>
+  <si>
+    <t>宙斯vs哈迪斯</t>
+  </si>
+  <si>
+    <t>1020400334,30200009_30200014</t>
+  </si>
+  <si>
+    <t>30200003,30200007|30200008;30200004,30200007|30200008;30200005,30200007|30200006;30200006,30200007|30200008</t>
+  </si>
+  <si>
+    <t>象财神</t>
+  </si>
+  <si>
+    <t>2,10,3_12_10000|4_15_10000|5_20_10000</t>
+  </si>
+  <si>
+    <t>免费游戏下，收集wild个数增加倍率值</t>
+  </si>
+  <si>
+    <t>3_2</t>
+  </si>
+  <si>
+    <t>免费游戏中，每收集3个百搭符号乘倍值将增加2（增加2后将清零重新收集），最多增加至20倍</t>
+  </si>
+  <si>
+    <t>10倍金牛</t>
+  </si>
+  <si>
+    <t>常规模式下，概率触发金牛赐福模式特效</t>
+  </si>
+  <si>
     <t>1,500</t>
-  </si>
-  <si>
-    <t>模式，概率假进金钱兔模式万分比</t>
-  </si>
-  <si>
-    <t>金钱兔</t>
-  </si>
-  <si>
-    <t>鼠鼠福福</t>
-  </si>
-  <si>
-    <t>常规模式下，概率触发福鼠模式特效</t>
-  </si>
-  <si>
-    <t>模式，概率假进福鼠模式万分比</t>
-  </si>
-  <si>
-    <t>福鼠模式下，获得连线奖励奖返回常规模式</t>
-  </si>
-  <si>
-    <t>2,0_1</t>
-  </si>
-  <si>
-    <t>SpecialMode模式ID，中奖倍率大于x时回到常规模式</t>
-  </si>
-  <si>
-    <t>王牌dj</t>
-  </si>
-  <si>
-    <t>2,13,4_10_10000|5_15_10000|6_20_10000</t>
-  </si>
-  <si>
-    <t>带wild中奖对应得中奖倍率，原赔率乘以此倍率值</t>
-  </si>
-  <si>
-    <t>2_2_2_2_4_6_8_10_12_14_16_18_20_22_24_26_28_30</t>
-  </si>
-  <si>
-    <t>初始为2，2，2，2，每次销毁加2，到达最大值30时，之后每次都为30</t>
-  </si>
-  <si>
-    <t>虎虎生财</t>
-  </si>
-  <si>
-    <t>1_1;2_1;3_1;4_1;5_1;6_1</t>
-  </si>
-  <si>
-    <t>5_3000_2000</t>
-  </si>
-  <si>
-    <t>宙斯vs哈迪斯</t>
-  </si>
-  <si>
-    <t>1020400334,30200009_30200014</t>
-  </si>
-  <si>
-    <t>30200003,30200007|30200008;30200004,30200007|30200008;30200005,30200007|30200006;30200006,30200007|30200008</t>
-  </si>
-  <si>
-    <t>象财神</t>
-  </si>
-  <si>
-    <t>2,10,3_12_10000|4_15_10000|5_20_10000</t>
-  </si>
-  <si>
-    <t>免费游戏下，收集wild个数增加倍率值</t>
-  </si>
-  <si>
-    <t>3_2</t>
-  </si>
-  <si>
-    <t>免费游戏中，每收集3个百搭符号乘倍值将增加2（增加2后将清零重新收集），最多增加至20倍</t>
-  </si>
-  <si>
-    <t>10倍金牛</t>
-  </si>
-  <si>
-    <t>常规模式下，概率触发金牛赐福模式特效</t>
   </si>
   <si>
     <t>金牛赐福模式下，玩家获得全屏奖出现的元素及权重</t>
@@ -962,13 +962,13 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="10"/>
+      <b/>
+      <sz val="9"/>
       <name val="宋体"/>
       <charset val="134"/>
     </font>
     <font>
-      <b/>
-      <sz val="9"/>
+      <sz val="10"/>
       <name val="宋体"/>
       <charset val="134"/>
     </font>
@@ -2576,10 +2576,10 @@
         <v>83</v>
       </c>
       <c r="F30" s="15" t="s">
+        <v>71</v>
+      </c>
+      <c r="G30" s="1" t="s">
         <v>84</v>
-      </c>
-      <c r="G30" s="1" t="s">
-        <v>85</v>
       </c>
       <c r="H30" s="5"/>
       <c r="I30" s="5"/>
@@ -2592,7 +2592,7 @@
         <v>103501</v>
       </c>
       <c r="C31" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="D31" s="1">
         <v>1</v>
@@ -2601,10 +2601,10 @@
         <v>83</v>
       </c>
       <c r="F31" s="15" t="s">
+        <v>71</v>
+      </c>
+      <c r="G31" s="1" t="s">
         <v>84</v>
-      </c>
-      <c r="G31" s="1" t="s">
-        <v>85</v>
       </c>
       <c r="H31" s="5"/>
       <c r="I31" s="5"/>
@@ -2617,19 +2617,19 @@
         <v>103600</v>
       </c>
       <c r="C32" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="D32" s="1">
         <v>1</v>
       </c>
       <c r="E32" t="s">
+        <v>87</v>
+      </c>
+      <c r="F32" s="15" t="s">
+        <v>71</v>
+      </c>
+      <c r="G32" s="1" t="s">
         <v>88</v>
-      </c>
-      <c r="F32" s="15" t="s">
-        <v>84</v>
-      </c>
-      <c r="G32" s="1" t="s">
-        <v>89</v>
       </c>
       <c r="H32" s="5"/>
       <c r="I32" s="5"/>
@@ -2642,19 +2642,19 @@
         <v>103600</v>
       </c>
       <c r="C33" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="D33" s="1">
         <v>2</v>
       </c>
       <c r="E33" t="s">
+        <v>89</v>
+      </c>
+      <c r="F33" s="15" t="s">
         <v>90</v>
       </c>
-      <c r="F33" s="15" t="s">
+      <c r="G33" s="1" t="s">
         <v>91</v>
-      </c>
-      <c r="G33" s="1" t="s">
-        <v>92</v>
       </c>
       <c r="H33" s="5"/>
       <c r="I33" s="5"/>
@@ -2667,7 +2667,7 @@
         <v>102800</v>
       </c>
       <c r="C34" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="D34" s="1">
         <v>1</v>
@@ -2676,7 +2676,7 @@
         <v>33</v>
       </c>
       <c r="F34" s="15" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="G34" s="1" t="s">
         <v>35</v>
@@ -2692,19 +2692,19 @@
         <v>102800</v>
       </c>
       <c r="C35" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="D35" s="1">
         <v>2</v>
       </c>
       <c r="E35" t="s">
+        <v>94</v>
+      </c>
+      <c r="F35" s="15" t="s">
         <v>95</v>
       </c>
-      <c r="F35" s="15" t="s">
+      <c r="G35" s="1" t="s">
         <v>96</v>
-      </c>
-      <c r="G35" s="1" t="s">
-        <v>97</v>
       </c>
       <c r="H35" s="5"/>
       <c r="I35" s="5"/>
@@ -2717,7 +2717,7 @@
         <v>103401</v>
       </c>
       <c r="C36" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="D36" s="1">
         <v>1</v>
@@ -2742,7 +2742,7 @@
         <v>103402</v>
       </c>
       <c r="C37" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="D37" s="1">
         <v>2</v>
@@ -2751,7 +2751,7 @@
         <v>73</v>
       </c>
       <c r="F37" s="15" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="G37" s="1" t="s">
         <v>75</v>
@@ -2767,7 +2767,7 @@
         <v>103403</v>
       </c>
       <c r="C38" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="D38" s="1">
         <v>3</v>
@@ -2776,7 +2776,7 @@
         <v>76</v>
       </c>
       <c r="F38" s="15" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="G38" s="1" t="s">
         <v>78</v>
@@ -2792,7 +2792,7 @@
         <v>103404</v>
       </c>
       <c r="C39" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="D39" s="1">
         <v>4</v>
@@ -2817,7 +2817,7 @@
         <v>102000</v>
       </c>
       <c r="C40" s="12" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="D40" s="17">
         <v>1</v>
@@ -2826,7 +2826,7 @@
         <v>26</v>
       </c>
       <c r="F40" s="13" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="G40" s="17" t="s">
         <v>28</v>
@@ -2843,13 +2843,13 @@
         <v>102000</v>
       </c>
       <c r="C41" s="12" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="D41" s="17">
         <v>2</v>
       </c>
       <c r="F41" s="3" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
     </row>
     <row r="42" s="3" customFormat="1" ht="16.5" spans="1:10">
@@ -2860,7 +2860,7 @@
         <v>102700</v>
       </c>
       <c r="C42" s="12" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="D42" s="17">
         <v>1</v>
@@ -2869,7 +2869,7 @@
         <v>33</v>
       </c>
       <c r="F42" s="3" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="G42" s="3" t="s">
         <v>35</v>
@@ -2883,19 +2883,19 @@
         <v>102700</v>
       </c>
       <c r="C43" s="12" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="D43" s="17">
         <v>2</v>
       </c>
       <c r="E43" s="3" t="s">
+        <v>105</v>
+      </c>
+      <c r="F43" s="3" t="s">
         <v>106</v>
       </c>
-      <c r="F43" s="3" t="s">
+      <c r="G43" s="3" t="s">
         <v>107</v>
-      </c>
-      <c r="G43" s="3" t="s">
-        <v>108</v>
       </c>
     </row>
     <row r="44" customFormat="1" ht="16.5" spans="1:10">
@@ -2906,19 +2906,19 @@
         <v>103700</v>
       </c>
       <c r="C44" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="D44" s="1">
         <v>1</v>
       </c>
       <c r="E44" t="s">
+        <v>109</v>
+      </c>
+      <c r="F44" s="15" t="s">
         <v>110</v>
       </c>
-      <c r="F44" s="15" t="s">
-        <v>84</v>
-      </c>
       <c r="G44" s="1" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="H44" s="5"/>
       <c r="I44" s="5"/>
@@ -2931,7 +2931,7 @@
         <v>103700</v>
       </c>
       <c r="C45" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="D45" s="1">
         <v>2</v>
@@ -2956,7 +2956,7 @@
         <v>103700</v>
       </c>
       <c r="C46" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="D46" s="1">
         <v>3</v>
@@ -3165,7 +3165,7 @@
         <v>33</v>
       </c>
       <c r="F54" s="3" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="G54" s="1" t="s">
         <v>35</v>

--- a/slots/resources/sample/SpecialPlay.xlsx
+++ b/slots/resources/sample/SpecialPlay.xlsx
@@ -1,16 +1,10 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="29822"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet">
+  <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\gamedoc\游戏配置表\slot\"/>
-    </mc:Choice>
-  </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E486CA56-EE51-4A06-A936-927C40165F60}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="5280" yWindow="4170" windowWidth="21600" windowHeight="11295" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView windowWidth="14460" windowHeight="11655"/>
   </bookViews>
   <sheets>
     <sheet name="SpecialPlay" sheetId="1" r:id="rId1"/>
@@ -34,16 +28,16 @@
 </file>
 
 <file path=xl/comments1.xml><?xml version="1.0" encoding="utf-8"?>
-<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr">
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <authors>
     <author>Administrator</author>
     <author>C</author>
   </authors>
   <commentList>
-    <comment ref="D1" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-000001000000}">
+    <comment ref="D1" authorId="0">
       <text/>
     </comment>
-    <comment ref="H1" authorId="1" shapeId="0" xr:uid="{00000000-0006-0000-0000-000002000000}">
+    <comment ref="H1" authorId="1">
       <text>
         <r>
           <rPr>
@@ -65,7 +59,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I1" authorId="1" shapeId="0" xr:uid="{00000000-0006-0000-0000-000003000000}">
+    <comment ref="I1" authorId="1">
       <text>
         <r>
           <rPr>
@@ -88,7 +82,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="G24" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-000004000000}">
+    <comment ref="G24" authorId="0">
       <text>
         <r>
           <rPr>
@@ -113,7 +107,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="G25" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-000005000000}">
+    <comment ref="G25" authorId="0">
       <text>
         <r>
           <rPr>
@@ -143,7 +137,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="359" uniqueCount="243">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="371" uniqueCount="250">
   <si>
     <t>被动游戏ID</t>
   </si>
@@ -685,6 +679,48 @@
     <t>伽罗宝石1</t>
   </si>
   <si>
+    <t>伽罗宝石21</t>
+  </si>
+  <si>
+    <t>前三轴出现的多格图标及权重</t>
+  </si>
+  <si>
+    <t>16_2_3000|17_2_3000|18_2_2000|19_2_2000|20_2_300|21_2_250|22_2_200|23_2_50|24_3_1500|25_3_1500|26_3_1200|27_3_1200|28_3_200|29_3_150|30_3_100|31_3_10</t>
+  </si>
+  <si>
+    <t>元素ID_图标连线中奖的额外倍数_权重</t>
+  </si>
+  <si>
+    <t>前三轴出现的多格图标个数及权重</t>
+  </si>
+  <si>
+    <t>1_6000|2_4000|3_3000|4_1500|5_1000|6_200|7_100|8_0|9_0</t>
+  </si>
+  <si>
+    <t>多格图标个数_权重</t>
+  </si>
+  <si>
+    <t>嗨到底</t>
+  </si>
+  <si>
+    <t>10,3_12_10000</t>
+  </si>
+  <si>
+    <t>狂野沙滩</t>
+  </si>
+  <si>
+    <t>13,3_15_10000</t>
+  </si>
+  <si>
+    <t>常规游戏中，获得目标图案的连线奖励翻倍</t>
+  </si>
+  <si>
+    <t>12_2</t>
+  </si>
+  <si>
+    <t>目标图案_中奖翻倍</t>
+  </si>
+  <si>
     <t>旋转标识</t>
   </si>
   <si>
@@ -851,44 +887,20 @@
   </si>
   <si>
     <t>通用普通10</t>
-  </si>
-  <si>
-    <t>伽罗宝石21</t>
-    <phoneticPr fontId="10" type="noConversion"/>
-  </si>
-  <si>
-    <t>前三轴出现的多格图标及权重</t>
-    <phoneticPr fontId="10" type="noConversion"/>
-  </si>
-  <si>
-    <t>16_2_3000|17_2_3000|18_2_2000|19_2_2000|20_2_300|21_2_250|22_2_200|23_2_50|24_3_1500|25_3_1500|26_3_1200|27_3_1200|28_3_200|29_3_150|30_3_100|31_3_10</t>
-    <phoneticPr fontId="10" type="noConversion"/>
-  </si>
-  <si>
-    <t>元素ID_图标连线中奖的额外倍数_权重</t>
-    <phoneticPr fontId="10" type="noConversion"/>
-  </si>
-  <si>
-    <t>前三轴出现的多格图标个数及权重</t>
-    <phoneticPr fontId="10" type="noConversion"/>
-  </si>
-  <si>
-    <t>1_6000|2_4000|3_3000|4_1500|5_1000|6_200|7_100|8_0|9_0</t>
-    <phoneticPr fontId="10" type="noConversion"/>
-  </si>
-  <si>
-    <t>多格图标个数_权重</t>
-    <phoneticPr fontId="10" type="noConversion"/>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <numFmts count="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="xr9">
+  <numFmts count="5">
+    <numFmt numFmtId="41" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
+    <numFmt numFmtId="42" formatCode="_ &quot;￥&quot;* #,##0_ ;_ &quot;￥&quot;* \-#,##0_ ;_ &quot;￥&quot;* &quot;-&quot;_ ;_ @_ "/>
+    <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="176" formatCode="0_ "/>
   </numFmts>
-  <fonts count="11" x14ac:knownFonts="1">
+  <fonts count="28">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -914,6 +926,12 @@
       <charset val="134"/>
     </font>
     <font>
+      <sz val="10"/>
+      <color theme="1"/>
+      <name val="微软雅黑"/>
+      <charset val="134"/>
+    </font>
+    <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="等线"/>
@@ -921,10 +939,148 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF0000FF"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF800080"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <b/>
-      <sz val="9"/>
-      <name val="宋体"/>
+      <sz val="18"/>
+      <color theme="3"/>
+      <name val="等线"/>
       <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <i/>
+      <sz val="11"/>
+      <color rgb="FF7F7F7F"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="15"/>
+      <color theme="3"/>
+      <name val="等线"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="13"/>
+      <color theme="3"/>
+      <name val="等线"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="3"/>
+      <name val="等线"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF3F3F76"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FF3F3F3F"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF006100"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C0006"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C6500"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="0"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
     </font>
     <font>
       <sz val="9"/>
@@ -932,35 +1088,18 @@
       <charset val="134"/>
     </font>
     <font>
-      <sz val="9"/>
-      <name val="等线"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
       <sz val="10"/>
-      <color theme="1"/>
-      <name val="微软雅黑"/>
-      <family val="2"/>
+      <name val="宋体"/>
       <charset val="134"/>
     </font>
     <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="等线"/>
-      <family val="3"/>
+      <b/>
+      <sz val="9"/>
+      <name val="宋体"/>
       <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="9"/>
-      <name val="等线"/>
-      <family val="3"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="4">
+  <fills count="36">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -969,7 +1108,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.79998168889431442"/>
+        <fgColor theme="9" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -979,8 +1118,200 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFCC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFCC99"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2F2F2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA5A5A5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFEB9C"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="1">
+  <borders count="9">
     <border>
       <left/>
       <right/>
@@ -988,14 +1319,256 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFB2B2B2"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFB2B2B2"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFB2B2B2"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFB2B2B2"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4" tint="0.499984740745262"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF7F7F7F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF7F7F7F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF7F7F7F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF7F7F7F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="double">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="double">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="double">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="double">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="double">
+        <color rgb="FFFF8001"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color theme="4"/>
+      </top>
+      <bottom style="double">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
-  <cellStyleXfs count="4">
+  <cellStyleXfs count="52">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
+    <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="41" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="6" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="7" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="7" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="8" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="35" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="20">
+  <cellXfs count="21">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
@@ -1043,32 +1616,74 @@
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1"/>
   </cellXfs>
-  <cellStyles count="4">
+  <cellStyles count="52">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
-    <cellStyle name="常规 2" xfId="3" xr:uid="{00000000-0005-0000-0000-000033000000}"/>
-    <cellStyle name="常规 73" xfId="1" xr:uid="{00000000-0005-0000-0000-000031000000}"/>
-    <cellStyle name="常规 80" xfId="2" xr:uid="{00000000-0005-0000-0000-000032000000}"/>
+    <cellStyle name="千位分隔" xfId="1" builtinId="3"/>
+    <cellStyle name="货币" xfId="2" builtinId="4"/>
+    <cellStyle name="百分比" xfId="3" builtinId="5"/>
+    <cellStyle name="千位分隔[0]" xfId="4" builtinId="6"/>
+    <cellStyle name="货币[0]" xfId="5" builtinId="7"/>
+    <cellStyle name="超链接" xfId="6" builtinId="8"/>
+    <cellStyle name="已访问的超链接" xfId="7" builtinId="9"/>
+    <cellStyle name="注释" xfId="8" builtinId="10"/>
+    <cellStyle name="警告文本" xfId="9" builtinId="11"/>
+    <cellStyle name="标题" xfId="10" builtinId="15"/>
+    <cellStyle name="解释性文本" xfId="11" builtinId="53"/>
+    <cellStyle name="标题 1" xfId="12" builtinId="16"/>
+    <cellStyle name="标题 2" xfId="13" builtinId="17"/>
+    <cellStyle name="标题 3" xfId="14" builtinId="18"/>
+    <cellStyle name="标题 4" xfId="15" builtinId="19"/>
+    <cellStyle name="输入" xfId="16" builtinId="20"/>
+    <cellStyle name="输出" xfId="17" builtinId="21"/>
+    <cellStyle name="计算" xfId="18" builtinId="22"/>
+    <cellStyle name="检查单元格" xfId="19" builtinId="23"/>
+    <cellStyle name="链接单元格" xfId="20" builtinId="24"/>
+    <cellStyle name="汇总" xfId="21" builtinId="25"/>
+    <cellStyle name="好" xfId="22" builtinId="26"/>
+    <cellStyle name="差" xfId="23" builtinId="27"/>
+    <cellStyle name="适中" xfId="24" builtinId="28"/>
+    <cellStyle name="强调文字颜色 1" xfId="25" builtinId="29"/>
+    <cellStyle name="20% - 强调文字颜色 1" xfId="26" builtinId="30"/>
+    <cellStyle name="40% - 强调文字颜色 1" xfId="27" builtinId="31"/>
+    <cellStyle name="60% - 强调文字颜色 1" xfId="28" builtinId="32"/>
+    <cellStyle name="强调文字颜色 2" xfId="29" builtinId="33"/>
+    <cellStyle name="20% - 强调文字颜色 2" xfId="30" builtinId="34"/>
+    <cellStyle name="40% - 强调文字颜色 2" xfId="31" builtinId="35"/>
+    <cellStyle name="60% - 强调文字颜色 2" xfId="32" builtinId="36"/>
+    <cellStyle name="强调文字颜色 3" xfId="33" builtinId="37"/>
+    <cellStyle name="20% - 强调文字颜色 3" xfId="34" builtinId="38"/>
+    <cellStyle name="40% - 强调文字颜色 3" xfId="35" builtinId="39"/>
+    <cellStyle name="60% - 强调文字颜色 3" xfId="36" builtinId="40"/>
+    <cellStyle name="强调文字颜色 4" xfId="37" builtinId="41"/>
+    <cellStyle name="20% - 强调文字颜色 4" xfId="38" builtinId="42"/>
+    <cellStyle name="40% - 强调文字颜色 4" xfId="39" builtinId="43"/>
+    <cellStyle name="60% - 强调文字颜色 4" xfId="40" builtinId="44"/>
+    <cellStyle name="强调文字颜色 5" xfId="41" builtinId="45"/>
+    <cellStyle name="20% - 强调文字颜色 5" xfId="42" builtinId="46"/>
+    <cellStyle name="40% - 强调文字颜色 5" xfId="43" builtinId="47"/>
+    <cellStyle name="60% - 强调文字颜色 5" xfId="44" builtinId="48"/>
+    <cellStyle name="强调文字颜色 6" xfId="45" builtinId="49"/>
+    <cellStyle name="20% - 强调文字颜色 6" xfId="46" builtinId="50"/>
+    <cellStyle name="40% - 强调文字颜色 6" xfId="47" builtinId="51"/>
+    <cellStyle name="60% - 强调文字颜色 6" xfId="48" builtinId="52"/>
+    <cellStyle name="常规 2" xfId="49"/>
+    <cellStyle name="常规 73" xfId="50"/>
+    <cellStyle name="常规 80" xfId="51"/>
   </cellStyles>
-  <dxfs count="2">
+  <dxfs count="1">
     <dxf>
       <fill>
         <patternFill patternType="solid">
-          <bgColor theme="8" tint="0.7993408001953185"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor theme="8" tint="0.7993408001953185"/>
+          <bgColor theme="8" tint="0.799340800195319"/>
         </patternFill>
       </fill>
     </dxf>
@@ -1077,9 +1692,6 @@
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
       <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
-    </ext>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
-      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
     </ext>
   </extLst>
 </styleSheet>
@@ -1337,14 +1949,14 @@
     </a:fmtScheme>
   </a:themeElements>
   <a:objectDefaults/>
-  <a:extraClrSchemeLst/>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:J74"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
+  <dimension ref="A1:J77"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25"/>
   <cols>
     <col min="4" max="4" width="9.5" style="3" customWidth="1"/>
     <col min="5" max="5" width="61.75" customWidth="1"/>
@@ -1355,7 +1967,7 @@
     <col min="10" max="10" width="7.875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" ht="16.5" x14ac:dyDescent="0.2">
+    <row r="1" ht="16.5" spans="1:10">
       <c r="A1" s="5" t="s">
         <v>0</v>
       </c>
@@ -1381,7 +1993,7 @@
       </c>
       <c r="J1" s="5"/>
     </row>
-    <row r="2" spans="1:10" ht="16.5" x14ac:dyDescent="0.35">
+    <row r="2" ht="16.5" spans="1:10">
       <c r="A2" s="5" t="s">
         <v>7</v>
       </c>
@@ -1405,7 +2017,7 @@
       </c>
       <c r="J2" s="5"/>
     </row>
-    <row r="3" spans="1:10" ht="16.5" x14ac:dyDescent="0.2">
+    <row r="3" ht="16.5" spans="1:10">
       <c r="A3" s="5" t="s">
         <v>11</v>
       </c>
@@ -1429,7 +2041,7 @@
       </c>
       <c r="J3" s="5"/>
     </row>
-    <row r="4" spans="1:10" ht="16.5" x14ac:dyDescent="0.2">
+    <row r="4" ht="16.5" spans="1:10">
       <c r="A4" s="5"/>
       <c r="B4" s="5"/>
       <c r="C4" s="5"/>
@@ -1441,7 +2053,7 @@
       <c r="I4" s="7"/>
       <c r="J4" s="5"/>
     </row>
-    <row r="5" spans="1:10" s="1" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="5" s="1" customFormat="1" ht="18" customHeight="1" spans="1:10">
       <c r="A5" s="1">
         <v>5001001</v>
       </c>
@@ -1471,7 +2083,7 @@
       </c>
       <c r="J5" s="10"/>
     </row>
-    <row r="6" spans="1:10" s="1" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="6" s="1" customFormat="1" ht="18" customHeight="1" spans="1:10">
       <c r="A6" s="1">
         <v>5001002</v>
       </c>
@@ -1497,7 +2109,7 @@
       <c r="I6" s="13"/>
       <c r="J6" s="10"/>
     </row>
-    <row r="7" spans="1:10" s="1" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="7" s="1" customFormat="1" ht="18" customHeight="1" spans="1:10">
       <c r="A7" s="1">
         <v>5001007</v>
       </c>
@@ -1523,7 +2135,7 @@
       <c r="I7" s="13"/>
       <c r="J7" s="10"/>
     </row>
-    <row r="8" spans="1:10" s="1" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="8" s="1" customFormat="1" ht="18" customHeight="1" spans="1:10">
       <c r="A8" s="1">
         <v>5007004</v>
       </c>
@@ -1548,7 +2160,7 @@
       <c r="H8" s="15"/>
       <c r="I8" s="15"/>
     </row>
-    <row r="9" spans="1:10" s="1" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="9" s="1" customFormat="1" ht="18" customHeight="1" spans="1:10">
       <c r="A9" s="1">
         <v>5007005</v>
       </c>
@@ -1573,7 +2185,7 @@
       <c r="H9" s="15"/>
       <c r="I9" s="15"/>
     </row>
-    <row r="10" spans="1:10" s="1" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="10" s="1" customFormat="1" ht="18" customHeight="1" spans="1:10">
       <c r="A10" s="1">
         <v>5014006</v>
       </c>
@@ -1598,7 +2210,7 @@
       <c r="H10" s="15"/>
       <c r="I10" s="15"/>
     </row>
-    <row r="11" spans="1:10" s="1" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="11" s="1" customFormat="1" ht="18" customHeight="1" spans="1:10">
       <c r="A11" s="1">
         <v>5024001</v>
       </c>
@@ -1628,7 +2240,7 @@
       </c>
       <c r="J11" s="10"/>
     </row>
-    <row r="12" spans="1:10" s="1" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="12" s="1" customFormat="1" ht="18" customHeight="1" spans="1:10">
       <c r="A12" s="1">
         <v>5024002</v>
       </c>
@@ -1654,7 +2266,7 @@
       <c r="I12" s="13"/>
       <c r="J12" s="10"/>
     </row>
-    <row r="13" spans="1:10" s="1" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="13" s="1" customFormat="1" ht="18" customHeight="1" spans="1:10">
       <c r="A13" s="1">
         <v>5024007</v>
       </c>
@@ -1680,7 +2292,7 @@
       <c r="I13" s="13"/>
       <c r="J13" s="10"/>
     </row>
-    <row r="14" spans="1:10" s="1" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="14" s="1" customFormat="1" ht="18" customHeight="1" spans="1:10">
       <c r="A14" s="1">
         <v>5017004</v>
       </c>
@@ -1705,7 +2317,7 @@
       <c r="H14" s="15"/>
       <c r="I14" s="15"/>
     </row>
-    <row r="15" spans="1:10" s="1" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="15" s="1" customFormat="1" ht="18" customHeight="1" spans="1:10">
       <c r="A15" s="1">
         <v>5017005</v>
       </c>
@@ -1730,7 +2342,7 @@
       <c r="H15" s="15"/>
       <c r="I15" s="15"/>
     </row>
-    <row r="16" spans="1:10" s="1" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="16" s="1" customFormat="1" ht="18" customHeight="1" spans="1:10">
       <c r="A16" s="1">
         <v>5022007</v>
       </c>
@@ -1756,7 +2368,7 @@
       <c r="I16" s="11"/>
       <c r="J16" s="10"/>
     </row>
-    <row r="17" spans="1:10" s="1" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="17" s="1" customFormat="1" ht="18" customHeight="1" spans="1:10">
       <c r="A17" s="1">
         <v>5022008</v>
       </c>
@@ -1782,7 +2394,7 @@
       <c r="I17" s="11"/>
       <c r="J17" s="10"/>
     </row>
-    <row r="18" spans="1:10" s="1" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="18" s="1" customFormat="1" ht="18" customHeight="1" spans="1:10">
       <c r="A18" s="1">
         <v>5021001</v>
       </c>
@@ -1808,7 +2420,7 @@
       <c r="I18" s="11"/>
       <c r="J18" s="10"/>
     </row>
-    <row r="19" spans="1:10" ht="16.5" x14ac:dyDescent="0.2">
+    <row r="19" ht="16.5" spans="1:10">
       <c r="A19" s="1">
         <v>5021002</v>
       </c>
@@ -1831,7 +2443,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="20" spans="1:10" ht="16.5" x14ac:dyDescent="0.2">
+    <row r="20" ht="16.5" spans="1:10">
       <c r="A20" s="1">
         <v>5018001</v>
       </c>
@@ -1854,7 +2466,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="21" spans="1:10" ht="16.5" x14ac:dyDescent="0.2">
+    <row r="21" ht="16.5" spans="1:10">
       <c r="A21" s="1">
         <v>5018002</v>
       </c>
@@ -1877,7 +2489,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="22" spans="1:10" ht="16.5" x14ac:dyDescent="0.2">
+    <row r="22" ht="16.5" spans="1:10">
       <c r="A22" s="1">
         <v>5025001</v>
       </c>
@@ -1900,7 +2512,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="23" spans="1:10" ht="16.5" x14ac:dyDescent="0.2">
+    <row r="23" ht="16.5" spans="1:10">
       <c r="A23" s="1">
         <v>5023005</v>
       </c>
@@ -1923,7 +2535,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="24" spans="1:10" ht="16.5" x14ac:dyDescent="0.2">
+    <row r="24" ht="16.5" spans="1:10">
       <c r="A24" s="1">
         <v>5023008</v>
       </c>
@@ -1946,7 +2558,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="25" spans="1:10" ht="16.5" x14ac:dyDescent="0.2">
+    <row r="25" ht="16.5" spans="1:10">
       <c r="A25" s="1">
         <v>5023009</v>
       </c>
@@ -1969,7 +2581,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="26" spans="1:10" ht="16.5" x14ac:dyDescent="0.2">
+    <row r="26" ht="16.5" spans="1:10">
       <c r="A26" s="1">
         <v>5034001</v>
       </c>
@@ -1992,7 +2604,7 @@
         <v>72</v>
       </c>
     </row>
-    <row r="27" spans="1:10" ht="16.5" x14ac:dyDescent="0.2">
+    <row r="27" ht="16.5" spans="1:10">
       <c r="A27" s="1">
         <v>5034002</v>
       </c>
@@ -2015,7 +2627,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="28" spans="1:10" ht="16.5" x14ac:dyDescent="0.2">
+    <row r="28" ht="16.5" spans="1:10">
       <c r="A28" s="1">
         <v>5034003</v>
       </c>
@@ -2038,7 +2650,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="29" spans="1:10" ht="16.5" x14ac:dyDescent="0.2">
+    <row r="29" ht="16.5" spans="1:10">
       <c r="A29" s="1">
         <v>5034004</v>
       </c>
@@ -2061,7 +2673,7 @@
         <v>81</v>
       </c>
     </row>
-    <row r="30" spans="1:10" ht="16.5" x14ac:dyDescent="0.2">
+    <row r="30" ht="16.5" spans="1:10">
       <c r="A30" s="1">
         <v>5035001</v>
       </c>
@@ -2084,7 +2696,7 @@
         <v>85</v>
       </c>
     </row>
-    <row r="31" spans="1:10" ht="16.5" x14ac:dyDescent="0.2">
+    <row r="31" ht="16.5" spans="1:10">
       <c r="A31" s="1">
         <v>5035011</v>
       </c>
@@ -2107,7 +2719,7 @@
         <v>85</v>
       </c>
     </row>
-    <row r="32" spans="1:10" ht="16.5" x14ac:dyDescent="0.2">
+    <row r="32" ht="16.5" spans="1:10">
       <c r="A32" s="1">
         <v>5036001</v>
       </c>
@@ -2130,7 +2742,7 @@
         <v>89</v>
       </c>
     </row>
-    <row r="33" spans="1:10" ht="16.5" x14ac:dyDescent="0.2">
+    <row r="33" ht="16.5" spans="1:10">
       <c r="A33" s="1">
         <v>5036002</v>
       </c>
@@ -2153,7 +2765,7 @@
         <v>92</v>
       </c>
     </row>
-    <row r="34" spans="1:10" ht="16.5" x14ac:dyDescent="0.2">
+    <row r="34" ht="16.5" spans="1:10">
       <c r="A34" s="1">
         <v>5028001</v>
       </c>
@@ -2176,7 +2788,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="35" spans="1:10" ht="16.5" x14ac:dyDescent="0.2">
+    <row r="35" ht="16.5" spans="1:10">
       <c r="A35" s="1">
         <v>5028002</v>
       </c>
@@ -2199,7 +2811,7 @@
         <v>97</v>
       </c>
     </row>
-    <row r="36" spans="1:10" ht="16.5" x14ac:dyDescent="0.2">
+    <row r="36" ht="16.5" spans="1:10">
       <c r="A36" s="1">
         <v>5034011</v>
       </c>
@@ -2222,7 +2834,7 @@
         <v>72</v>
       </c>
     </row>
-    <row r="37" spans="1:10" ht="16.5" x14ac:dyDescent="0.2">
+    <row r="37" ht="16.5" spans="1:10">
       <c r="A37" s="1">
         <v>5034012</v>
       </c>
@@ -2245,7 +2857,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="38" spans="1:10" ht="16.5" x14ac:dyDescent="0.2">
+    <row r="38" ht="16.5" spans="1:10">
       <c r="A38" s="1">
         <v>5034013</v>
       </c>
@@ -2268,7 +2880,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="39" spans="1:10" ht="16.5" x14ac:dyDescent="0.2">
+    <row r="39" ht="16.5" spans="1:10">
       <c r="A39" s="1">
         <v>5034014</v>
       </c>
@@ -2291,7 +2903,7 @@
         <v>81</v>
       </c>
     </row>
-    <row r="40" spans="1:10" s="1" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="40" s="1" customFormat="1" ht="18" customHeight="1" spans="1:10">
       <c r="A40" s="1">
         <v>5020001</v>
       </c>
@@ -2317,7 +2929,7 @@
       <c r="I40" s="11"/>
       <c r="J40" s="10"/>
     </row>
-    <row r="41" spans="1:10" ht="16.5" x14ac:dyDescent="0.2">
+    <row r="41" ht="16.5" spans="1:10">
       <c r="A41" s="1">
         <v>5020002</v>
       </c>
@@ -2336,7 +2948,7 @@
       <c r="H41"/>
       <c r="I41"/>
     </row>
-    <row r="42" spans="1:10" ht="16.5" x14ac:dyDescent="0.2">
+    <row r="42" ht="16.5" spans="1:10">
       <c r="A42" s="1">
         <v>5027001</v>
       </c>
@@ -2361,7 +2973,7 @@
       <c r="H42"/>
       <c r="I42"/>
     </row>
-    <row r="43" spans="1:10" ht="16.5" x14ac:dyDescent="0.2">
+    <row r="43" ht="16.5" spans="1:10">
       <c r="A43" s="1">
         <v>5027002</v>
       </c>
@@ -2386,7 +2998,7 @@
       <c r="H43"/>
       <c r="I43"/>
     </row>
-    <row r="44" spans="1:10" ht="16.5" x14ac:dyDescent="0.2">
+    <row r="44" ht="16.5" spans="1:10">
       <c r="A44" s="1">
         <v>5037001</v>
       </c>
@@ -2409,7 +3021,7 @@
         <v>89</v>
       </c>
     </row>
-    <row r="45" spans="1:10" ht="16.5" x14ac:dyDescent="0.2">
+    <row r="45" ht="16.5" spans="1:10">
       <c r="A45" s="1">
         <v>5037002</v>
       </c>
@@ -2432,7 +3044,7 @@
         <v>113</v>
       </c>
     </row>
-    <row r="46" spans="1:10" ht="16.5" x14ac:dyDescent="0.2">
+    <row r="46" ht="16.5" spans="1:10">
       <c r="A46" s="1">
         <v>5037003</v>
       </c>
@@ -2455,7 +3067,7 @@
         <v>116</v>
       </c>
     </row>
-    <row r="47" spans="1:10" ht="16.5" x14ac:dyDescent="0.2">
+    <row r="47" ht="16.5" spans="1:10">
       <c r="A47" s="1">
         <v>5031001</v>
       </c>
@@ -2478,7 +3090,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="48" spans="1:10" ht="16.5" x14ac:dyDescent="0.2">
+    <row r="48" ht="16.5" spans="1:10">
       <c r="A48" s="1">
         <v>5040001</v>
       </c>
@@ -2501,7 +3113,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="49" spans="1:7" ht="16.5" x14ac:dyDescent="0.2">
+    <row r="49" ht="16.5" spans="1:7">
       <c r="A49" s="1">
         <v>5039001</v>
       </c>
@@ -2524,7 +3136,7 @@
         <v>124</v>
       </c>
     </row>
-    <row r="50" spans="1:7" ht="16.5" x14ac:dyDescent="0.2">
+    <row r="50" ht="16.5" spans="1:7">
       <c r="A50" s="1">
         <v>5016001</v>
       </c>
@@ -2547,7 +3159,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="51" spans="1:7" ht="16.5" x14ac:dyDescent="0.2">
+    <row r="51" ht="16.5" spans="1:7">
       <c r="A51" s="1">
         <v>5016002</v>
       </c>
@@ -2570,7 +3182,7 @@
         <v>129</v>
       </c>
     </row>
-    <row r="52" spans="1:7" ht="16.5" x14ac:dyDescent="0.2">
+    <row r="52" ht="16.5" spans="1:7">
       <c r="A52" s="1">
         <v>5015001</v>
       </c>
@@ -2593,7 +3205,7 @@
         <v>133</v>
       </c>
     </row>
-    <row r="53" spans="1:7" ht="16.5" x14ac:dyDescent="0.2">
+    <row r="53" ht="16.5" spans="1:7">
       <c r="A53" s="1">
         <v>5015002</v>
       </c>
@@ -2616,7 +3228,7 @@
         <v>135</v>
       </c>
     </row>
-    <row r="54" spans="1:7" ht="16.5" x14ac:dyDescent="0.2">
+    <row r="54" ht="16.5" spans="1:7">
       <c r="A54" s="1">
         <v>5026001</v>
       </c>
@@ -2639,7 +3251,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="55" spans="1:7" ht="16.5" x14ac:dyDescent="0.2">
+    <row r="55" ht="16.5" spans="1:7">
       <c r="A55" s="1">
         <v>5026003</v>
       </c>
@@ -2662,7 +3274,7 @@
         <v>140</v>
       </c>
     </row>
-    <row r="56" spans="1:7" ht="16.5" x14ac:dyDescent="0.2">
+    <row r="56" ht="16.5" spans="1:7">
       <c r="A56" s="1">
         <v>5050001</v>
       </c>
@@ -2685,7 +3297,7 @@
         <v>143</v>
       </c>
     </row>
-    <row r="57" spans="1:7" ht="16.5" x14ac:dyDescent="0.2">
+    <row r="57" ht="16.5" spans="1:7">
       <c r="A57" s="1">
         <v>5050002</v>
       </c>
@@ -2708,7 +3320,7 @@
         <v>146</v>
       </c>
     </row>
-    <row r="58" spans="1:7" ht="16.5" x14ac:dyDescent="0.2">
+    <row r="58" ht="16.5" spans="1:7">
       <c r="A58" s="1">
         <v>5051001</v>
       </c>
@@ -2731,7 +3343,7 @@
         <v>150</v>
       </c>
     </row>
-    <row r="59" spans="1:7" ht="16.5" x14ac:dyDescent="0.2">
+    <row r="59" ht="16.5" spans="1:7">
       <c r="A59" s="1">
         <v>5054001</v>
       </c>
@@ -2754,7 +3366,7 @@
         <v>153</v>
       </c>
     </row>
-    <row r="60" spans="1:7" ht="16.5" x14ac:dyDescent="0.2">
+    <row r="60" ht="16.5" spans="1:7">
       <c r="A60" s="1">
         <v>5054002</v>
       </c>
@@ -2777,7 +3389,7 @@
         <v>143</v>
       </c>
     </row>
-    <row r="61" spans="1:7" ht="16.5" x14ac:dyDescent="0.2">
+    <row r="61" ht="16.5" spans="1:7">
       <c r="A61" s="1">
         <v>5008001</v>
       </c>
@@ -2800,7 +3412,7 @@
         <v>158</v>
       </c>
     </row>
-    <row r="62" spans="1:7" ht="16.5" x14ac:dyDescent="0.2">
+    <row r="62" ht="16.5" spans="1:7">
       <c r="A62" s="1">
         <v>5008002</v>
       </c>
@@ -2823,7 +3435,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="63" spans="1:7" ht="16.5" x14ac:dyDescent="0.2">
+    <row r="63" ht="16.5" spans="1:7">
       <c r="A63" s="1">
         <v>5053001</v>
       </c>
@@ -2846,7 +3458,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="64" spans="1:7" ht="16.5" x14ac:dyDescent="0.2">
+    <row r="64" ht="16.5" spans="1:7">
       <c r="A64" s="1">
         <v>5057001</v>
       </c>
@@ -2869,7 +3481,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="65" spans="1:9" ht="16.5" x14ac:dyDescent="0.2">
+    <row r="65" ht="16.5" spans="1:9">
       <c r="A65" s="1">
         <v>5057002</v>
       </c>
@@ -2892,7 +3504,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="66" spans="1:9" ht="16.5" x14ac:dyDescent="0.2">
+    <row r="66" ht="16.5" spans="1:9">
       <c r="A66" s="1">
         <v>5057003</v>
       </c>
@@ -2915,7 +3527,7 @@
         <v>166</v>
       </c>
     </row>
-    <row r="67" spans="1:9" ht="16.5" x14ac:dyDescent="0.2">
+    <row r="67" ht="16.5" spans="1:9">
       <c r="A67" s="1">
         <v>5058001</v>
       </c>
@@ -2938,7 +3550,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="68" spans="1:9" ht="16.5" x14ac:dyDescent="0.2">
+    <row r="68" ht="16.5" spans="1:9">
       <c r="A68" s="1">
         <v>5058002</v>
       </c>
@@ -2961,7 +3573,7 @@
         <v>171</v>
       </c>
     </row>
-    <row r="69" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="69" s="2" customFormat="1" spans="1:9">
       <c r="A69" s="2">
         <v>5055001</v>
       </c>
@@ -2986,7 +3598,7 @@
       <c r="H69" s="16"/>
       <c r="I69" s="16"/>
     </row>
-    <row r="70" spans="1:9" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="70" ht="18" customHeight="1" spans="1:9">
       <c r="A70" s="1">
         <v>5048001</v>
       </c>
@@ -3009,7 +3621,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="71" spans="1:9" ht="16.5" x14ac:dyDescent="0.2">
+    <row r="71" ht="16.5" spans="1:9">
       <c r="A71" s="1">
         <v>5048002</v>
       </c>
@@ -3032,7 +3644,7 @@
         <v>158</v>
       </c>
     </row>
-    <row r="72" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="72" s="2" customFormat="1" spans="1:9">
       <c r="A72" s="2">
         <v>5055011</v>
       </c>
@@ -3057,7 +3669,7 @@
       <c r="H72" s="16"/>
       <c r="I72" s="16"/>
     </row>
-    <row r="73" spans="1:9" ht="16.5" x14ac:dyDescent="0.2">
+    <row r="73" ht="16.5" spans="1:9">
       <c r="A73" s="1">
         <v>5055021</v>
       </c>
@@ -3065,22 +3677,22 @@
         <v>105502</v>
       </c>
       <c r="C73" s="18" t="s">
-        <v>236</v>
+        <v>180</v>
       </c>
       <c r="D73" s="2">
         <v>1</v>
       </c>
       <c r="E73" s="18" t="s">
-        <v>237</v>
+        <v>181</v>
       </c>
       <c r="F73" s="18" t="s">
-        <v>238</v>
+        <v>182</v>
       </c>
       <c r="G73" s="19" t="s">
-        <v>239</v>
-      </c>
-    </row>
-    <row r="74" spans="1:9" ht="16.5" x14ac:dyDescent="0.2">
+        <v>183</v>
+      </c>
+    </row>
+    <row r="74" ht="16.5" spans="1:9">
       <c r="A74" s="1">
         <v>5055022</v>
       </c>
@@ -3088,25 +3700,99 @@
         <v>105502</v>
       </c>
       <c r="C74" s="18" t="s">
-        <v>236</v>
+        <v>180</v>
       </c>
       <c r="D74" s="2">
         <v>2</v>
       </c>
       <c r="E74" s="18" t="s">
-        <v>240</v>
+        <v>184</v>
       </c>
       <c r="F74" s="18" t="s">
-        <v>241</v>
+        <v>185</v>
       </c>
       <c r="G74" s="19" t="s">
-        <v>242</v>
-      </c>
+        <v>186</v>
+      </c>
+    </row>
+    <row r="75" customFormat="1" ht="18" customHeight="1" spans="1:9">
+      <c r="A75" s="1">
+        <v>5041001</v>
+      </c>
+      <c r="B75" s="10">
+        <v>104100</v>
+      </c>
+      <c r="C75" t="s">
+        <v>187</v>
+      </c>
+      <c r="D75" s="1">
+        <v>1</v>
+      </c>
+      <c r="E75" t="s">
+        <v>33</v>
+      </c>
+      <c r="F75" t="s">
+        <v>188</v>
+      </c>
+      <c r="G75" t="s">
+        <v>35</v>
+      </c>
+      <c r="H75" s="20"/>
+      <c r="I75" s="20"/>
+    </row>
+    <row r="76" customFormat="1" ht="18" customHeight="1" spans="1:9">
+      <c r="A76" s="1">
+        <v>5042001</v>
+      </c>
+      <c r="B76" s="10">
+        <v>104200</v>
+      </c>
+      <c r="C76" t="s">
+        <v>189</v>
+      </c>
+      <c r="D76" s="1">
+        <v>1</v>
+      </c>
+      <c r="E76" t="s">
+        <v>33</v>
+      </c>
+      <c r="F76" t="s">
+        <v>190</v>
+      </c>
+      <c r="G76" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="H76" s="20"/>
+      <c r="I76" s="20"/>
+    </row>
+    <row r="77" customFormat="1" ht="16.5" spans="1:9">
+      <c r="A77" s="1">
+        <v>5042002</v>
+      </c>
+      <c r="B77" s="10">
+        <v>104200</v>
+      </c>
+      <c r="C77" t="s">
+        <v>189</v>
+      </c>
+      <c r="D77" s="1">
+        <v>2</v>
+      </c>
+      <c r="E77" t="s">
+        <v>191</v>
+      </c>
+      <c r="F77" t="s">
+        <v>192</v>
+      </c>
+      <c r="G77" s="1" t="s">
+        <v>193</v>
+      </c>
+      <c r="H77" s="20"/>
+      <c r="I77" s="20"/>
     </row>
   </sheetData>
-  <phoneticPr fontId="7" type="noConversion"/>
   <conditionalFormatting sqref="H2">
-    <cfRule type="expression" dxfId="1" priority="1">
+    <cfRule type="expression" dxfId="0" priority="1">
       <formula>MOD(MID($A2,1,4),2)=1</formula>
     </cfRule>
   </conditionalFormatting>
@@ -3116,443 +3802,445 @@
     </cfRule>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <legacyDrawing r:id="rId1"/>
+  <headerFooter/>
+  <legacyDrawing r:id="rId2"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
   <dimension ref="A1:E48"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25" outlineLevelCol="4"/>
   <sheetData>
-    <row r="1" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:5">
       <c r="A1" t="s">
-        <v>180</v>
+        <v>194</v>
       </c>
       <c r="D1" t="s">
-        <v>181</v>
-      </c>
-    </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.2">
+        <v>195</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5">
       <c r="A2" t="s">
-        <v>182</v>
+        <v>196</v>
       </c>
       <c r="B2" t="s">
-        <v>183</v>
+        <v>197</v>
       </c>
       <c r="D2" t="s">
-        <v>182</v>
+        <v>196</v>
       </c>
       <c r="E2" t="s">
-        <v>183</v>
-      </c>
-    </row>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.2">
+        <v>197</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5">
       <c r="A3">
         <v>0</v>
       </c>
       <c r="B3" t="s">
-        <v>184</v>
+        <v>198</v>
       </c>
       <c r="D3">
         <v>0</v>
       </c>
       <c r="E3" t="s">
-        <v>185</v>
-      </c>
-    </row>
-    <row r="4" spans="1:5" x14ac:dyDescent="0.2">
+        <v>199</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5">
       <c r="A4">
         <v>1</v>
       </c>
       <c r="B4" t="s">
-        <v>186</v>
+        <v>200</v>
       </c>
       <c r="D4">
         <v>1</v>
       </c>
       <c r="E4" t="s">
-        <v>187</v>
-      </c>
-    </row>
-    <row r="5" spans="1:5" x14ac:dyDescent="0.2">
+        <v>201</v>
+      </c>
+    </row>
+    <row r="5" spans="1:5">
       <c r="A5">
         <v>2</v>
       </c>
       <c r="B5" t="s">
-        <v>188</v>
+        <v>202</v>
       </c>
       <c r="D5">
         <v>2</v>
       </c>
       <c r="E5" t="s">
-        <v>189</v>
-      </c>
-    </row>
-    <row r="6" spans="1:5" x14ac:dyDescent="0.2">
+        <v>203</v>
+      </c>
+    </row>
+    <row r="6" spans="1:5">
       <c r="A6">
         <v>3</v>
       </c>
       <c r="B6" t="s">
-        <v>190</v>
+        <v>204</v>
       </c>
       <c r="D6">
         <v>3</v>
       </c>
       <c r="E6" t="s">
-        <v>191</v>
-      </c>
-    </row>
-    <row r="7" spans="1:5" x14ac:dyDescent="0.2">
+        <v>205</v>
+      </c>
+    </row>
+    <row r="7" spans="1:5">
       <c r="A7">
         <v>4</v>
       </c>
       <c r="B7" t="s">
-        <v>192</v>
+        <v>206</v>
       </c>
       <c r="D7">
         <v>4</v>
       </c>
       <c r="E7" t="s">
-        <v>193</v>
-      </c>
-    </row>
-    <row r="8" spans="1:5" x14ac:dyDescent="0.2">
+        <v>207</v>
+      </c>
+    </row>
+    <row r="8" spans="1:5">
       <c r="A8">
         <v>5</v>
       </c>
       <c r="B8" t="s">
-        <v>194</v>
+        <v>208</v>
       </c>
       <c r="D8">
         <v>5</v>
       </c>
       <c r="E8" t="s">
-        <v>195</v>
-      </c>
-    </row>
-    <row r="9" spans="1:5" x14ac:dyDescent="0.2">
+        <v>209</v>
+      </c>
+    </row>
+    <row r="9" spans="1:5">
       <c r="A9">
         <v>6</v>
       </c>
       <c r="B9" t="s">
-        <v>196</v>
-      </c>
-    </row>
-    <row r="10" spans="1:5" x14ac:dyDescent="0.2">
+        <v>210</v>
+      </c>
+    </row>
+    <row r="10" spans="1:5">
       <c r="A10">
         <v>7</v>
       </c>
       <c r="B10" t="s">
-        <v>197</v>
-      </c>
-    </row>
-    <row r="11" spans="1:5" x14ac:dyDescent="0.2">
+        <v>211</v>
+      </c>
+    </row>
+    <row r="11" spans="1:5">
       <c r="A11">
         <v>8</v>
       </c>
       <c r="B11" t="s">
-        <v>198</v>
-      </c>
-    </row>
-    <row r="12" spans="1:5" x14ac:dyDescent="0.2">
+        <v>212</v>
+      </c>
+    </row>
+    <row r="12" spans="1:5">
       <c r="A12">
         <v>9</v>
       </c>
       <c r="B12" t="s">
-        <v>199</v>
-      </c>
-    </row>
-    <row r="13" spans="1:5" x14ac:dyDescent="0.2">
+        <v>213</v>
+      </c>
+    </row>
+    <row r="13" spans="1:5">
       <c r="A13">
         <v>10</v>
       </c>
       <c r="B13" t="s">
-        <v>200</v>
-      </c>
-    </row>
-    <row r="14" spans="1:5" x14ac:dyDescent="0.2">
+        <v>214</v>
+      </c>
+    </row>
+    <row r="14" spans="1:5">
       <c r="A14">
         <v>11</v>
       </c>
       <c r="B14" t="s">
-        <v>201</v>
-      </c>
-    </row>
-    <row r="15" spans="1:5" x14ac:dyDescent="0.2">
+        <v>215</v>
+      </c>
+    </row>
+    <row r="15" spans="1:5">
       <c r="A15">
         <v>12</v>
       </c>
       <c r="B15" t="s">
-        <v>202</v>
-      </c>
-    </row>
-    <row r="16" spans="1:5" x14ac:dyDescent="0.2">
+        <v>216</v>
+      </c>
+    </row>
+    <row r="16" spans="1:5">
       <c r="A16">
         <v>13</v>
       </c>
       <c r="B16" t="s">
-        <v>203</v>
-      </c>
-    </row>
-    <row r="17" spans="1:2" x14ac:dyDescent="0.2">
+        <v>217</v>
+      </c>
+    </row>
+    <row r="17" spans="1:2">
       <c r="A17">
         <v>14</v>
       </c>
       <c r="B17" t="s">
-        <v>204</v>
-      </c>
-    </row>
-    <row r="18" spans="1:2" x14ac:dyDescent="0.2">
+        <v>218</v>
+      </c>
+    </row>
+    <row r="18" spans="1:2">
       <c r="A18">
         <v>15</v>
       </c>
       <c r="B18" t="s">
-        <v>205</v>
-      </c>
-    </row>
-    <row r="19" spans="1:2" x14ac:dyDescent="0.2">
+        <v>219</v>
+      </c>
+    </row>
+    <row r="19" spans="1:2">
       <c r="A19">
         <v>16</v>
       </c>
       <c r="B19" t="s">
-        <v>206</v>
-      </c>
-    </row>
-    <row r="20" spans="1:2" x14ac:dyDescent="0.2">
+        <v>220</v>
+      </c>
+    </row>
+    <row r="20" spans="1:2">
       <c r="A20">
         <v>17</v>
       </c>
       <c r="B20" t="s">
-        <v>207</v>
-      </c>
-    </row>
-    <row r="21" spans="1:2" x14ac:dyDescent="0.2">
+        <v>221</v>
+      </c>
+    </row>
+    <row r="21" spans="1:2">
       <c r="A21">
         <v>18</v>
       </c>
       <c r="B21" t="s">
-        <v>208</v>
-      </c>
-    </row>
-    <row r="22" spans="1:2" x14ac:dyDescent="0.2">
+        <v>222</v>
+      </c>
+    </row>
+    <row r="22" spans="1:2">
       <c r="A22">
         <v>19</v>
       </c>
       <c r="B22" t="s">
-        <v>209</v>
-      </c>
-    </row>
-    <row r="23" spans="1:2" x14ac:dyDescent="0.2">
+        <v>223</v>
+      </c>
+    </row>
+    <row r="23" spans="1:2">
       <c r="A23">
         <v>20</v>
       </c>
       <c r="B23" t="s">
-        <v>210</v>
-      </c>
-    </row>
-    <row r="24" spans="1:2" x14ac:dyDescent="0.2">
+        <v>224</v>
+      </c>
+    </row>
+    <row r="24" spans="1:2">
       <c r="A24">
         <v>21</v>
       </c>
       <c r="B24" t="s">
-        <v>211</v>
-      </c>
-    </row>
-    <row r="25" spans="1:2" x14ac:dyDescent="0.2">
+        <v>225</v>
+      </c>
+    </row>
+    <row r="25" spans="1:2">
       <c r="A25">
         <v>22</v>
       </c>
       <c r="B25" t="s">
-        <v>212</v>
-      </c>
-    </row>
-    <row r="26" spans="1:2" x14ac:dyDescent="0.2">
+        <v>226</v>
+      </c>
+    </row>
+    <row r="26" spans="1:2">
       <c r="A26">
         <v>23</v>
       </c>
       <c r="B26" t="s">
-        <v>213</v>
-      </c>
-    </row>
-    <row r="27" spans="1:2" x14ac:dyDescent="0.2">
+        <v>227</v>
+      </c>
+    </row>
+    <row r="27" spans="1:2">
       <c r="A27">
         <v>24</v>
       </c>
       <c r="B27" t="s">
-        <v>214</v>
-      </c>
-    </row>
-    <row r="28" spans="1:2" x14ac:dyDescent="0.2">
+        <v>228</v>
+      </c>
+    </row>
+    <row r="28" spans="1:2">
       <c r="A28">
         <v>25</v>
       </c>
       <c r="B28" t="s">
-        <v>215</v>
-      </c>
-    </row>
-    <row r="29" spans="1:2" x14ac:dyDescent="0.2">
+        <v>229</v>
+      </c>
+    </row>
+    <row r="29" spans="1:2">
       <c r="A29">
         <v>26</v>
       </c>
       <c r="B29" t="s">
-        <v>216</v>
-      </c>
-    </row>
-    <row r="30" spans="1:2" x14ac:dyDescent="0.2">
+        <v>230</v>
+      </c>
+    </row>
+    <row r="30" spans="1:2">
       <c r="A30">
         <v>27</v>
       </c>
       <c r="B30" t="s">
-        <v>217</v>
-      </c>
-    </row>
-    <row r="31" spans="1:2" x14ac:dyDescent="0.2">
+        <v>231</v>
+      </c>
+    </row>
+    <row r="31" spans="1:2">
       <c r="A31">
         <v>28</v>
       </c>
       <c r="B31" t="s">
-        <v>218</v>
-      </c>
-    </row>
-    <row r="32" spans="1:2" x14ac:dyDescent="0.2">
+        <v>232</v>
+      </c>
+    </row>
+    <row r="32" spans="1:2">
       <c r="A32">
         <v>29</v>
       </c>
       <c r="B32" t="s">
-        <v>219</v>
-      </c>
-    </row>
-    <row r="33" spans="1:2" x14ac:dyDescent="0.2">
+        <v>233</v>
+      </c>
+    </row>
+    <row r="33" spans="1:2">
       <c r="A33">
         <v>30</v>
       </c>
       <c r="B33" t="s">
-        <v>220</v>
-      </c>
-    </row>
-    <row r="34" spans="1:2" x14ac:dyDescent="0.2">
+        <v>234</v>
+      </c>
+    </row>
+    <row r="34" spans="1:2">
       <c r="A34">
         <v>31</v>
       </c>
       <c r="B34" t="s">
-        <v>221</v>
-      </c>
-    </row>
-    <row r="35" spans="1:2" x14ac:dyDescent="0.2">
+        <v>235</v>
+      </c>
+    </row>
+    <row r="35" spans="1:2">
       <c r="A35">
         <v>32</v>
       </c>
       <c r="B35" t="s">
-        <v>222</v>
-      </c>
-    </row>
-    <row r="36" spans="1:2" x14ac:dyDescent="0.2">
+        <v>236</v>
+      </c>
+    </row>
+    <row r="36" spans="1:2">
       <c r="A36">
         <v>33</v>
       </c>
       <c r="B36" t="s">
-        <v>223</v>
-      </c>
-    </row>
-    <row r="37" spans="1:2" x14ac:dyDescent="0.2">
+        <v>237</v>
+      </c>
+    </row>
+    <row r="37" spans="1:2">
       <c r="A37">
         <v>34</v>
       </c>
       <c r="B37" t="s">
-        <v>224</v>
-      </c>
-    </row>
-    <row r="38" spans="1:2" x14ac:dyDescent="0.2">
+        <v>238</v>
+      </c>
+    </row>
+    <row r="38" spans="1:2">
       <c r="A38">
         <v>35</v>
       </c>
       <c r="B38" t="s">
-        <v>225</v>
-      </c>
-    </row>
-    <row r="39" spans="1:2" x14ac:dyDescent="0.2">
+        <v>239</v>
+      </c>
+    </row>
+    <row r="39" spans="1:2">
       <c r="A39">
         <v>36</v>
       </c>
       <c r="B39" t="s">
-        <v>226</v>
-      </c>
-    </row>
-    <row r="40" spans="1:2" x14ac:dyDescent="0.2">
+        <v>240</v>
+      </c>
+    </row>
+    <row r="40" spans="1:2">
       <c r="A40">
         <v>37</v>
       </c>
       <c r="B40" t="s">
-        <v>227</v>
-      </c>
-    </row>
-    <row r="41" spans="1:2" x14ac:dyDescent="0.2">
+        <v>241</v>
+      </c>
+    </row>
+    <row r="41" spans="1:2">
       <c r="A41">
         <v>38</v>
       </c>
       <c r="B41" t="s">
-        <v>228</v>
-      </c>
-    </row>
-    <row r="42" spans="1:2" x14ac:dyDescent="0.2">
+        <v>242</v>
+      </c>
+    </row>
+    <row r="42" spans="1:2">
       <c r="A42">
         <v>39</v>
       </c>
       <c r="B42" t="s">
-        <v>229</v>
-      </c>
-    </row>
-    <row r="43" spans="1:2" x14ac:dyDescent="0.2">
+        <v>243</v>
+      </c>
+    </row>
+    <row r="43" spans="1:2">
       <c r="A43">
         <v>40</v>
       </c>
       <c r="B43" t="s">
-        <v>230</v>
-      </c>
-    </row>
-    <row r="44" spans="1:2" x14ac:dyDescent="0.2">
+        <v>244</v>
+      </c>
+    </row>
+    <row r="44" spans="1:2">
       <c r="A44">
         <v>41</v>
       </c>
       <c r="B44" t="s">
-        <v>231</v>
-      </c>
-    </row>
-    <row r="45" spans="1:2" x14ac:dyDescent="0.2">
+        <v>245</v>
+      </c>
+    </row>
+    <row r="45" spans="1:2">
       <c r="A45">
         <v>42</v>
       </c>
       <c r="B45" t="s">
-        <v>232</v>
-      </c>
-    </row>
-    <row r="46" spans="1:2" x14ac:dyDescent="0.2">
+        <v>246</v>
+      </c>
+    </row>
+    <row r="46" spans="1:2">
       <c r="A46">
         <v>43</v>
       </c>
       <c r="B46" t="s">
-        <v>233</v>
-      </c>
-    </row>
-    <row r="47" spans="1:2" x14ac:dyDescent="0.2">
+        <v>247</v>
+      </c>
+    </row>
+    <row r="47" spans="1:2">
       <c r="A47">
         <v>44</v>
       </c>
       <c r="B47" t="s">
-        <v>234</v>
-      </c>
-    </row>
-    <row r="48" spans="1:2" x14ac:dyDescent="0.2">
+        <v>248</v>
+      </c>
+    </row>
+    <row r="48" spans="1:2">
       <c r="A48">
         <v>45</v>
       </c>
       <c r="B48" t="s">
-        <v>235</v>
+        <v>249</v>
       </c>
     </row>
   </sheetData>
-  <phoneticPr fontId="7" type="noConversion"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <headerFooter/>
 </worksheet>
 </file>
--- a/slots/resources/sample/SpecialPlay.xlsx
+++ b/slots/resources/sample/SpecialPlay.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="14460" windowHeight="11655"/>
+    <workbookView windowWidth="27945" windowHeight="11925"/>
   </bookViews>
   <sheets>
     <sheet name="SpecialPlay" sheetId="1" r:id="rId1"/>
@@ -391,87 +391,87 @@
     <t>常规模式下，概率触发金钱兔模式特效</t>
   </si>
   <si>
+    <t>模式，概率假进金钱兔模式万分比</t>
+  </si>
+  <si>
+    <t>金钱兔</t>
+  </si>
+  <si>
+    <t>鼠鼠福福</t>
+  </si>
+  <si>
+    <t>常规模式下，概率触发福鼠模式特效</t>
+  </si>
+  <si>
+    <t>模式，概率假进福鼠模式万分比</t>
+  </si>
+  <si>
+    <t>福鼠模式下，获得连线奖励奖返回常规模式</t>
+  </si>
+  <si>
+    <t>2,0_1</t>
+  </si>
+  <si>
+    <t>SpecialMode模式ID，中奖倍率大于x时回到常规模式</t>
+  </si>
+  <si>
+    <t>王牌dj</t>
+  </si>
+  <si>
+    <t>2,13,4_10_10000|5_15_10000|6_20_10000</t>
+  </si>
+  <si>
+    <t>带wild中奖对应得中奖倍率，原赔率乘以此倍率值</t>
+  </si>
+  <si>
+    <t>2_2_2_2_4_6_8_10_12_14_16_18_20_22_24_26_28_30</t>
+  </si>
+  <si>
+    <t>初始为2，2，2，2，每次销毁加2，到达最大值30时，之后每次都为30</t>
+  </si>
+  <si>
+    <t>虎虎生财</t>
+  </si>
+  <si>
+    <t>1_1;2_1;3_1;4_1;5_1;6_1</t>
+  </si>
+  <si>
+    <t>5_3000_2000</t>
+  </si>
+  <si>
+    <t>宙斯vs哈迪斯</t>
+  </si>
+  <si>
+    <t>1020400334,30200009_30200014</t>
+  </si>
+  <si>
+    <t>30200003,30200007|30200008;30200004,30200007|30200008;30200005,30200007|30200006;30200006,30200007|30200008</t>
+  </si>
+  <si>
+    <t>象财神</t>
+  </si>
+  <si>
+    <t>2,10,3_12_10000|4_15_10000|5_20_10000</t>
+  </si>
+  <si>
+    <t>免费游戏下，收集wild个数增加倍率值</t>
+  </si>
+  <si>
+    <t>3_2</t>
+  </si>
+  <si>
+    <t>免费游戏中，每收集3个百搭符号乘倍值将增加2（增加2后将清零重新收集），最多增加至20倍</t>
+  </si>
+  <si>
+    <t>10倍金牛</t>
+  </si>
+  <si>
+    <t>常规模式下，概率触发金牛赐福模式特效</t>
+  </si>
+  <si>
     <t>1,500</t>
   </si>
   <si>
-    <t>模式，概率假进金钱兔模式万分比</t>
-  </si>
-  <si>
-    <t>金钱兔</t>
-  </si>
-  <si>
-    <t>鼠鼠福福</t>
-  </si>
-  <si>
-    <t>常规模式下，概率触发福鼠模式特效</t>
-  </si>
-  <si>
-    <t>模式，概率假进福鼠模式万分比</t>
-  </si>
-  <si>
-    <t>福鼠模式下，获得连线奖励奖返回常规模式</t>
-  </si>
-  <si>
-    <t>2,0_1</t>
-  </si>
-  <si>
-    <t>SpecialMode模式ID，中奖倍率大于x时回到常规模式</t>
-  </si>
-  <si>
-    <t>王牌dj</t>
-  </si>
-  <si>
-    <t>2,13,4_10_10000|5_15_10000|6_20_10000</t>
-  </si>
-  <si>
-    <t>带wild中奖对应得中奖倍率，原赔率乘以此倍率值</t>
-  </si>
-  <si>
-    <t>2_2_2_2_4_6_8_10_12_14_16_18_20_22_24_26_28_30</t>
-  </si>
-  <si>
-    <t>初始为2，2，2，2，每次销毁加2，到达最大值30时，之后每次都为30</t>
-  </si>
-  <si>
-    <t>虎虎生财</t>
-  </si>
-  <si>
-    <t>1_1;2_1;3_1;4_1;5_1;6_1</t>
-  </si>
-  <si>
-    <t>5_3000_2000</t>
-  </si>
-  <si>
-    <t>宙斯vs哈迪斯</t>
-  </si>
-  <si>
-    <t>1020400334,30200009_30200014</t>
-  </si>
-  <si>
-    <t>30200003,30200007|30200008;30200004,30200007|30200008;30200005,30200007|30200006;30200006,30200007|30200008</t>
-  </si>
-  <si>
-    <t>象财神</t>
-  </si>
-  <si>
-    <t>2,10,3_12_10000|4_15_10000|5_20_10000</t>
-  </si>
-  <si>
-    <t>免费游戏下，收集wild个数增加倍率值</t>
-  </si>
-  <si>
-    <t>3_2</t>
-  </si>
-  <si>
-    <t>免费游戏中，每收集3个百搭符号乘倍值将增加2（增加2后将清零重新收集），最多增加至20倍</t>
-  </si>
-  <si>
-    <t>10倍金牛</t>
-  </si>
-  <si>
-    <t>常规模式下，概率触发金牛赐福模式特效</t>
-  </si>
-  <si>
     <t>金牛赐福模式下，玩家获得全屏奖出现的元素及权重</t>
   </si>
   <si>
@@ -676,10 +676,10 @@
     <t>14_1</t>
   </si>
   <si>
-    <t>伽罗宝石1</t>
-  </si>
-  <si>
     <t>伽罗宝石21</t>
+  </si>
+  <si>
+    <t>伽罗宝石31</t>
   </si>
   <si>
     <t>前三轴出现的多格图标及权重</t>
@@ -900,7 +900,7 @@
     <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="176" formatCode="0_ "/>
   </numFmts>
-  <fonts count="28">
+  <fonts count="26">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -924,19 +924,6 @@
       <color rgb="FF000000"/>
       <name val="微软雅黑"/>
       <charset val="134"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <color theme="1"/>
-      <name val="微软雅黑"/>
-      <charset val="134"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="等线"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
     </font>
     <font>
       <u/>
@@ -1083,6 +1070,7 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <b/>
       <sz val="9"/>
       <name val="宋体"/>
       <charset val="134"/>
@@ -1093,13 +1081,12 @@
       <charset val="134"/>
     </font>
     <font>
-      <b/>
       <sz val="9"/>
       <name val="宋体"/>
       <charset val="134"/>
     </font>
   </fonts>
-  <fills count="36">
+  <fills count="34">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -1115,12 +1102,6 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FF00B050"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -1294,12 +1275,6 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor theme="9" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
@@ -1435,140 +1410,140 @@
     <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="5" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="6" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="14" fillId="6" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="7" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="7" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="8" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="35" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="15" fillId="7" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="21">
+  <cellXfs count="19">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
@@ -1616,14 +1591,10 @@
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1"/>
   </cellXfs>
   <cellStyles count="52">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
@@ -2690,10 +2661,10 @@
         <v>83</v>
       </c>
       <c r="F30" s="14" t="s">
+        <v>71</v>
+      </c>
+      <c r="G30" s="1" t="s">
         <v>84</v>
-      </c>
-      <c r="G30" s="1" t="s">
-        <v>85</v>
       </c>
     </row>
     <row r="31" ht="16.5" spans="1:10">
@@ -2704,7 +2675,7 @@
         <v>103501</v>
       </c>
       <c r="C31" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="D31" s="1">
         <v>1</v>
@@ -2713,10 +2684,10 @@
         <v>83</v>
       </c>
       <c r="F31" s="14" t="s">
+        <v>71</v>
+      </c>
+      <c r="G31" s="1" t="s">
         <v>84</v>
-      </c>
-      <c r="G31" s="1" t="s">
-        <v>85</v>
       </c>
     </row>
     <row r="32" ht="16.5" spans="1:10">
@@ -2727,19 +2698,19 @@
         <v>103600</v>
       </c>
       <c r="C32" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="D32" s="1">
         <v>1</v>
       </c>
       <c r="E32" t="s">
+        <v>87</v>
+      </c>
+      <c r="F32" s="14" t="s">
+        <v>71</v>
+      </c>
+      <c r="G32" s="1" t="s">
         <v>88</v>
-      </c>
-      <c r="F32" s="14" t="s">
-        <v>84</v>
-      </c>
-      <c r="G32" s="1" t="s">
-        <v>89</v>
       </c>
     </row>
     <row r="33" ht="16.5" spans="1:10">
@@ -2750,19 +2721,19 @@
         <v>103600</v>
       </c>
       <c r="C33" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="D33" s="1">
         <v>2</v>
       </c>
       <c r="E33" t="s">
+        <v>89</v>
+      </c>
+      <c r="F33" s="14" t="s">
         <v>90</v>
       </c>
-      <c r="F33" s="14" t="s">
+      <c r="G33" s="1" t="s">
         <v>91</v>
-      </c>
-      <c r="G33" s="1" t="s">
-        <v>92</v>
       </c>
     </row>
     <row r="34" ht="16.5" spans="1:10">
@@ -2773,7 +2744,7 @@
         <v>102800</v>
       </c>
       <c r="C34" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="D34" s="1">
         <v>1</v>
@@ -2782,7 +2753,7 @@
         <v>33</v>
       </c>
       <c r="F34" s="14" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="G34" s="1" t="s">
         <v>35</v>
@@ -2796,19 +2767,19 @@
         <v>102800</v>
       </c>
       <c r="C35" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="D35" s="1">
         <v>2</v>
       </c>
       <c r="E35" t="s">
+        <v>94</v>
+      </c>
+      <c r="F35" s="14" t="s">
         <v>95</v>
       </c>
-      <c r="F35" s="14" t="s">
+      <c r="G35" s="1" t="s">
         <v>96</v>
-      </c>
-      <c r="G35" s="1" t="s">
-        <v>97</v>
       </c>
     </row>
     <row r="36" ht="16.5" spans="1:10">
@@ -2819,7 +2790,7 @@
         <v>103401</v>
       </c>
       <c r="C36" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="D36" s="1">
         <v>1</v>
@@ -2842,7 +2813,7 @@
         <v>103402</v>
       </c>
       <c r="C37" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="D37" s="1">
         <v>2</v>
@@ -2851,7 +2822,7 @@
         <v>73</v>
       </c>
       <c r="F37" s="14" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="G37" s="1" t="s">
         <v>75</v>
@@ -2865,7 +2836,7 @@
         <v>103403</v>
       </c>
       <c r="C38" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="D38" s="1">
         <v>3</v>
@@ -2874,7 +2845,7 @@
         <v>76</v>
       </c>
       <c r="F38" s="14" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="G38" s="1" t="s">
         <v>78</v>
@@ -2888,7 +2859,7 @@
         <v>103404</v>
       </c>
       <c r="C39" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="D39" s="1">
         <v>4</v>
@@ -2911,7 +2882,7 @@
         <v>102000</v>
       </c>
       <c r="C40" s="11" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="D40" s="10">
         <v>1</v>
@@ -2920,7 +2891,7 @@
         <v>26</v>
       </c>
       <c r="F40" s="12" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="G40" s="10" t="s">
         <v>28</v>
@@ -2937,13 +2908,13 @@
         <v>102000</v>
       </c>
       <c r="C41" s="11" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="D41" s="10">
         <v>2</v>
       </c>
       <c r="F41" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="H41"/>
       <c r="I41"/>
@@ -2956,7 +2927,7 @@
         <v>102700</v>
       </c>
       <c r="C42" s="11" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="D42" s="10">
         <v>1</v>
@@ -2965,7 +2936,7 @@
         <v>33</v>
       </c>
       <c r="F42" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="G42" t="s">
         <v>35</v>
@@ -2981,19 +2952,19 @@
         <v>102700</v>
       </c>
       <c r="C43" s="11" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="D43" s="10">
         <v>2</v>
       </c>
       <c r="E43" t="s">
+        <v>105</v>
+      </c>
+      <c r="F43" t="s">
         <v>106</v>
       </c>
-      <c r="F43" t="s">
+      <c r="G43" t="s">
         <v>107</v>
-      </c>
-      <c r="G43" t="s">
-        <v>108</v>
       </c>
       <c r="H43"/>
       <c r="I43"/>
@@ -3006,19 +2977,19 @@
         <v>103700</v>
       </c>
       <c r="C44" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="D44" s="1">
         <v>1</v>
       </c>
       <c r="E44" t="s">
+        <v>109</v>
+      </c>
+      <c r="F44" s="14" t="s">
         <v>110</v>
       </c>
-      <c r="F44" s="14" t="s">
-        <v>84</v>
-      </c>
       <c r="G44" s="1" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
     </row>
     <row r="45" ht="16.5" spans="1:10">
@@ -3029,7 +3000,7 @@
         <v>103700</v>
       </c>
       <c r="C45" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="D45" s="1">
         <v>2</v>
@@ -3052,7 +3023,7 @@
         <v>103700</v>
       </c>
       <c r="C46" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="D46" s="1">
         <v>3</v>
@@ -3673,22 +3644,22 @@
       <c r="A73" s="1">
         <v>5055021</v>
       </c>
-      <c r="B73" s="17">
+      <c r="B73" s="10">
         <v>105502</v>
       </c>
-      <c r="C73" s="18" t="s">
+      <c r="C73" s="17" t="s">
         <v>180</v>
       </c>
       <c r="D73" s="2">
         <v>1</v>
       </c>
-      <c r="E73" s="18" t="s">
+      <c r="E73" s="17" t="s">
         <v>181</v>
       </c>
-      <c r="F73" s="18" t="s">
+      <c r="F73" s="17" t="s">
         <v>182</v>
       </c>
-      <c r="G73" s="19" t="s">
+      <c r="G73" s="18" t="s">
         <v>183</v>
       </c>
     </row>
@@ -3696,22 +3667,22 @@
       <c r="A74" s="1">
         <v>5055022</v>
       </c>
-      <c r="B74" s="17">
+      <c r="B74" s="10">
         <v>105502</v>
       </c>
-      <c r="C74" s="18" t="s">
+      <c r="C74" s="17" t="s">
         <v>180</v>
       </c>
       <c r="D74" s="2">
         <v>2</v>
       </c>
-      <c r="E74" s="18" t="s">
+      <c r="E74" s="17" t="s">
         <v>184</v>
       </c>
-      <c r="F74" s="18" t="s">
+      <c r="F74" s="17" t="s">
         <v>185</v>
       </c>
-      <c r="G74" s="19" t="s">
+      <c r="G74" s="18" t="s">
         <v>186</v>
       </c>
     </row>
@@ -3737,8 +3708,8 @@
       <c r="G75" t="s">
         <v>35</v>
       </c>
-      <c r="H75" s="20"/>
-      <c r="I75" s="20"/>
+      <c r="H75" s="4"/>
+      <c r="I75" s="4"/>
     </row>
     <row r="76" customFormat="1" ht="18" customHeight="1" spans="1:9">
       <c r="A76" s="1">
@@ -3762,8 +3733,8 @@
       <c r="G76" s="1" t="s">
         <v>35</v>
       </c>
-      <c r="H76" s="20"/>
-      <c r="I76" s="20"/>
+      <c r="H76" s="4"/>
+      <c r="I76" s="4"/>
     </row>
     <row r="77" customFormat="1" ht="16.5" spans="1:9">
       <c r="A77" s="1">
@@ -3787,8 +3758,8 @@
       <c r="G77" s="1" t="s">
         <v>193</v>
       </c>
-      <c r="H77" s="20"/>
-      <c r="I77" s="20"/>
+      <c r="H77" s="4"/>
+      <c r="I77" s="4"/>
     </row>
   </sheetData>
   <conditionalFormatting sqref="H2">

--- a/slots/resources/sample/SpecialPlay.xlsx
+++ b/slots/resources/sample/SpecialPlay.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="14460" windowHeight="11655"/>
+    <workbookView windowWidth="28800" windowHeight="12255"/>
   </bookViews>
   <sheets>
     <sheet name="SpecialPlay" sheetId="1" r:id="rId1"/>
@@ -137,7 +137,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="371" uniqueCount="250">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="375" uniqueCount="250">
   <si>
     <t>被动游戏ID</t>
   </si>
@@ -391,87 +391,87 @@
     <t>常规模式下，概率触发金钱兔模式特效</t>
   </si>
   <si>
+    <t>模式，概率假进金钱兔模式万分比</t>
+  </si>
+  <si>
+    <t>金钱兔</t>
+  </si>
+  <si>
+    <t>鼠鼠福福</t>
+  </si>
+  <si>
+    <t>常规模式下，概率触发福鼠模式特效</t>
+  </si>
+  <si>
+    <t>模式，概率假进福鼠模式万分比</t>
+  </si>
+  <si>
+    <t>福鼠模式下，获得连线奖励奖返回常规模式</t>
+  </si>
+  <si>
+    <t>2,0_1</t>
+  </si>
+  <si>
+    <t>SpecialMode模式ID，中奖倍率大于x时回到常规模式</t>
+  </si>
+  <si>
+    <t>王牌dj</t>
+  </si>
+  <si>
+    <t>2,13,4_10_10000|5_15_10000|6_20_10000</t>
+  </si>
+  <si>
+    <t>带wild中奖对应得中奖倍率，原赔率乘以此倍率值</t>
+  </si>
+  <si>
+    <t>2_2_2_2_4_6_8_10_12_14_16_18_20_22_24_26_28_30</t>
+  </si>
+  <si>
+    <t>初始为2，2，2，2，每次销毁加2，到达最大值30时，之后每次都为30</t>
+  </si>
+  <si>
+    <t>虎虎生财</t>
+  </si>
+  <si>
+    <t>1_1;2_1;3_1;4_1;5_1;6_1</t>
+  </si>
+  <si>
+    <t>5_3000_2000</t>
+  </si>
+  <si>
+    <t>宙斯vs哈迪斯</t>
+  </si>
+  <si>
+    <t>1020400334,30200009_30200014</t>
+  </si>
+  <si>
+    <t>30200003,30200007|30200008;30200004,30200007|30200008;30200005,30200007|30200006;30200006,30200007|30200008</t>
+  </si>
+  <si>
+    <t>象财神</t>
+  </si>
+  <si>
+    <t>2,10,3_12_10000|4_15_10000|5_20_10000</t>
+  </si>
+  <si>
+    <t>免费游戏下，收集wild个数增加倍率值</t>
+  </si>
+  <si>
+    <t>3_2</t>
+  </si>
+  <si>
+    <t>免费游戏中，每收集3个百搭符号乘倍值将增加2（增加2后将清零重新收集），最多增加至20倍</t>
+  </si>
+  <si>
+    <t>10倍金牛</t>
+  </si>
+  <si>
+    <t>常规模式下，概率触发金牛赐福模式特效</t>
+  </si>
+  <si>
     <t>1,500</t>
   </si>
   <si>
-    <t>模式，概率假进金钱兔模式万分比</t>
-  </si>
-  <si>
-    <t>金钱兔</t>
-  </si>
-  <si>
-    <t>鼠鼠福福</t>
-  </si>
-  <si>
-    <t>常规模式下，概率触发福鼠模式特效</t>
-  </si>
-  <si>
-    <t>模式，概率假进福鼠模式万分比</t>
-  </si>
-  <si>
-    <t>福鼠模式下，获得连线奖励奖返回常规模式</t>
-  </si>
-  <si>
-    <t>2,0_1</t>
-  </si>
-  <si>
-    <t>SpecialMode模式ID，中奖倍率大于x时回到常规模式</t>
-  </si>
-  <si>
-    <t>王牌dj</t>
-  </si>
-  <si>
-    <t>2,13,4_10_10000|5_15_10000|6_20_10000</t>
-  </si>
-  <si>
-    <t>带wild中奖对应得中奖倍率，原赔率乘以此倍率值</t>
-  </si>
-  <si>
-    <t>2_2_2_2_4_6_8_10_12_14_16_18_20_22_24_26_28_30</t>
-  </si>
-  <si>
-    <t>初始为2，2，2，2，每次销毁加2，到达最大值30时，之后每次都为30</t>
-  </si>
-  <si>
-    <t>虎虎生财</t>
-  </si>
-  <si>
-    <t>1_1;2_1;3_1;4_1;5_1;6_1</t>
-  </si>
-  <si>
-    <t>5_3000_2000</t>
-  </si>
-  <si>
-    <t>宙斯vs哈迪斯</t>
-  </si>
-  <si>
-    <t>1020400334,30200009_30200014</t>
-  </si>
-  <si>
-    <t>30200003,30200007|30200008;30200004,30200007|30200008;30200005,30200007|30200006;30200006,30200007|30200008</t>
-  </si>
-  <si>
-    <t>象财神</t>
-  </si>
-  <si>
-    <t>2,10,3_12_10000|4_15_10000|5_20_10000</t>
-  </si>
-  <si>
-    <t>免费游戏下，收集wild个数增加倍率值</t>
-  </si>
-  <si>
-    <t>3_2</t>
-  </si>
-  <si>
-    <t>免费游戏中，每收集3个百搭符号乘倍值将增加2（增加2后将清零重新收集），最多增加至20倍</t>
-  </si>
-  <si>
-    <t>10倍金牛</t>
-  </si>
-  <si>
-    <t>常规模式下，概率触发金牛赐福模式特效</t>
-  </si>
-  <si>
     <t>金牛赐福模式下，玩家获得全屏奖出现的元素及权重</t>
   </si>
   <si>
@@ -676,10 +676,10 @@
     <t>14_1</t>
   </si>
   <si>
-    <t>伽罗宝石1</t>
-  </si>
-  <si>
-    <t>伽罗宝石21</t>
+    <t>伽罗宝石2</t>
+  </si>
+  <si>
+    <t>伽罗宝石3</t>
   </si>
   <si>
     <t>前三轴出现的多格图标及权重</t>
@@ -694,7 +694,7 @@
     <t>前三轴出现的多格图标个数及权重</t>
   </si>
   <si>
-    <t>1_6000|2_4000|3_3000|4_1500|5_1000|6_200|7_100|8_0|9_0</t>
+    <t>0_2000|1_6000|2_4000|3_3000|4_1500|5_1000|6_200|7_100|8_0|9_0</t>
   </si>
   <si>
     <t>多格图标个数_权重</t>
@@ -900,7 +900,7 @@
     <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="176" formatCode="0_ "/>
   </numFmts>
-  <fonts count="28">
+  <fonts count="26">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -924,19 +924,6 @@
       <color rgb="FF000000"/>
       <name val="微软雅黑"/>
       <charset val="134"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <color theme="1"/>
-      <name val="微软雅黑"/>
-      <charset val="134"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="等线"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
     </font>
     <font>
       <u/>
@@ -1083,11 +1070,6 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="9"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-    </font>
-    <font>
       <sz val="10"/>
       <name val="宋体"/>
       <charset val="134"/>
@@ -1098,8 +1080,13 @@
       <name val="宋体"/>
       <charset val="134"/>
     </font>
+    <font>
+      <sz val="9"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+    </font>
   </fonts>
-  <fills count="36">
+  <fills count="34">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -1115,12 +1102,6 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FF00B050"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -1294,12 +1275,6 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor theme="9" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
@@ -1435,140 +1410,140 @@
     <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="5" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="6" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="14" fillId="6" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="7" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="7" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="8" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="35" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="15" fillId="7" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="21">
+  <cellXfs count="19">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
@@ -1616,14 +1591,10 @@
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1"/>
   </cellXfs>
   <cellStyles count="52">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
@@ -1955,9 +1926,10 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:J77"/>
+  <dimension ref="A1:J78"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25"/>
   <cols>
+    <col min="3" max="3" width="10.375" customWidth="1"/>
     <col min="4" max="4" width="9.5" style="3" customWidth="1"/>
     <col min="5" max="5" width="61.75" customWidth="1"/>
     <col min="6" max="6" width="50.875" customWidth="1"/>
@@ -2690,10 +2662,10 @@
         <v>83</v>
       </c>
       <c r="F30" s="14" t="s">
+        <v>71</v>
+      </c>
+      <c r="G30" s="1" t="s">
         <v>84</v>
-      </c>
-      <c r="G30" s="1" t="s">
-        <v>85</v>
       </c>
     </row>
     <row r="31" ht="16.5" spans="1:10">
@@ -2704,7 +2676,7 @@
         <v>103501</v>
       </c>
       <c r="C31" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="D31" s="1">
         <v>1</v>
@@ -2713,10 +2685,10 @@
         <v>83</v>
       </c>
       <c r="F31" s="14" t="s">
+        <v>71</v>
+      </c>
+      <c r="G31" s="1" t="s">
         <v>84</v>
-      </c>
-      <c r="G31" s="1" t="s">
-        <v>85</v>
       </c>
     </row>
     <row r="32" ht="16.5" spans="1:10">
@@ -2727,19 +2699,19 @@
         <v>103600</v>
       </c>
       <c r="C32" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="D32" s="1">
         <v>1</v>
       </c>
       <c r="E32" t="s">
+        <v>87</v>
+      </c>
+      <c r="F32" s="14" t="s">
+        <v>71</v>
+      </c>
+      <c r="G32" s="1" t="s">
         <v>88</v>
-      </c>
-      <c r="F32" s="14" t="s">
-        <v>84</v>
-      </c>
-      <c r="G32" s="1" t="s">
-        <v>89</v>
       </c>
     </row>
     <row r="33" ht="16.5" spans="1:10">
@@ -2750,19 +2722,19 @@
         <v>103600</v>
       </c>
       <c r="C33" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="D33" s="1">
         <v>2</v>
       </c>
       <c r="E33" t="s">
+        <v>89</v>
+      </c>
+      <c r="F33" s="14" t="s">
         <v>90</v>
       </c>
-      <c r="F33" s="14" t="s">
+      <c r="G33" s="1" t="s">
         <v>91</v>
-      </c>
-      <c r="G33" s="1" t="s">
-        <v>92</v>
       </c>
     </row>
     <row r="34" ht="16.5" spans="1:10">
@@ -2773,7 +2745,7 @@
         <v>102800</v>
       </c>
       <c r="C34" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="D34" s="1">
         <v>1</v>
@@ -2782,7 +2754,7 @@
         <v>33</v>
       </c>
       <c r="F34" s="14" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="G34" s="1" t="s">
         <v>35</v>
@@ -2796,19 +2768,19 @@
         <v>102800</v>
       </c>
       <c r="C35" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="D35" s="1">
         <v>2</v>
       </c>
       <c r="E35" t="s">
+        <v>94</v>
+      </c>
+      <c r="F35" s="14" t="s">
         <v>95</v>
       </c>
-      <c r="F35" s="14" t="s">
+      <c r="G35" s="1" t="s">
         <v>96</v>
-      </c>
-      <c r="G35" s="1" t="s">
-        <v>97</v>
       </c>
     </row>
     <row r="36" ht="16.5" spans="1:10">
@@ -2819,7 +2791,7 @@
         <v>103401</v>
       </c>
       <c r="C36" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="D36" s="1">
         <v>1</v>
@@ -2842,7 +2814,7 @@
         <v>103402</v>
       </c>
       <c r="C37" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="D37" s="1">
         <v>2</v>
@@ -2851,7 +2823,7 @@
         <v>73</v>
       </c>
       <c r="F37" s="14" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="G37" s="1" t="s">
         <v>75</v>
@@ -2865,7 +2837,7 @@
         <v>103403</v>
       </c>
       <c r="C38" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="D38" s="1">
         <v>3</v>
@@ -2874,7 +2846,7 @@
         <v>76</v>
       </c>
       <c r="F38" s="14" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="G38" s="1" t="s">
         <v>78</v>
@@ -2888,7 +2860,7 @@
         <v>103404</v>
       </c>
       <c r="C39" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="D39" s="1">
         <v>4</v>
@@ -2911,7 +2883,7 @@
         <v>102000</v>
       </c>
       <c r="C40" s="11" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="D40" s="10">
         <v>1</v>
@@ -2920,7 +2892,7 @@
         <v>26</v>
       </c>
       <c r="F40" s="12" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="G40" s="10" t="s">
         <v>28</v>
@@ -2937,13 +2909,13 @@
         <v>102000</v>
       </c>
       <c r="C41" s="11" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="D41" s="10">
         <v>2</v>
       </c>
       <c r="F41" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="H41"/>
       <c r="I41"/>
@@ -2956,7 +2928,7 @@
         <v>102700</v>
       </c>
       <c r="C42" s="11" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="D42" s="10">
         <v>1</v>
@@ -2965,7 +2937,7 @@
         <v>33</v>
       </c>
       <c r="F42" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="G42" t="s">
         <v>35</v>
@@ -2981,19 +2953,19 @@
         <v>102700</v>
       </c>
       <c r="C43" s="11" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="D43" s="10">
         <v>2</v>
       </c>
       <c r="E43" t="s">
+        <v>105</v>
+      </c>
+      <c r="F43" t="s">
         <v>106</v>
       </c>
-      <c r="F43" t="s">
+      <c r="G43" t="s">
         <v>107</v>
-      </c>
-      <c r="G43" t="s">
-        <v>108</v>
       </c>
       <c r="H43"/>
       <c r="I43"/>
@@ -3006,19 +2978,19 @@
         <v>103700</v>
       </c>
       <c r="C44" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="D44" s="1">
         <v>1</v>
       </c>
       <c r="E44" t="s">
+        <v>109</v>
+      </c>
+      <c r="F44" s="14" t="s">
         <v>110</v>
       </c>
-      <c r="F44" s="14" t="s">
-        <v>84</v>
-      </c>
       <c r="G44" s="1" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
     </row>
     <row r="45" ht="16.5" spans="1:10">
@@ -3029,7 +3001,7 @@
         <v>103700</v>
       </c>
       <c r="C45" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="D45" s="1">
         <v>2</v>
@@ -3052,7 +3024,7 @@
         <v>103700</v>
       </c>
       <c r="C46" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="D46" s="1">
         <v>3</v>
@@ -3673,22 +3645,22 @@
       <c r="A73" s="1">
         <v>5055021</v>
       </c>
-      <c r="B73" s="17">
+      <c r="B73" s="10">
         <v>105502</v>
       </c>
-      <c r="C73" s="18" t="s">
+      <c r="C73" s="17" t="s">
         <v>180</v>
       </c>
       <c r="D73" s="2">
         <v>1</v>
       </c>
-      <c r="E73" s="18" t="s">
+      <c r="E73" s="17" t="s">
         <v>181</v>
       </c>
-      <c r="F73" s="18" t="s">
+      <c r="F73" s="17" t="s">
         <v>182</v>
       </c>
-      <c r="G73" s="19" t="s">
+      <c r="G73" s="18" t="s">
         <v>183</v>
       </c>
     </row>
@@ -3696,59 +3668,59 @@
       <c r="A74" s="1">
         <v>5055022</v>
       </c>
-      <c r="B74" s="17">
+      <c r="B74" s="10">
         <v>105502</v>
       </c>
-      <c r="C74" s="18" t="s">
+      <c r="C74" s="17" t="s">
         <v>180</v>
       </c>
       <c r="D74" s="2">
         <v>2</v>
       </c>
-      <c r="E74" s="18" t="s">
+      <c r="E74" s="17" t="s">
         <v>184</v>
       </c>
-      <c r="F74" s="18" t="s">
+      <c r="F74" s="17" t="s">
         <v>185</v>
       </c>
-      <c r="G74" s="19" t="s">
+      <c r="G74" s="18" t="s">
         <v>186</v>
       </c>
     </row>
     <row r="75" customFormat="1" ht="18" customHeight="1" spans="1:9">
       <c r="A75" s="1">
-        <v>5041001</v>
+        <v>5055023</v>
       </c>
       <c r="B75" s="10">
-        <v>104100</v>
-      </c>
-      <c r="C75" t="s">
-        <v>187</v>
-      </c>
-      <c r="D75" s="1">
-        <v>1</v>
-      </c>
-      <c r="E75" t="s">
-        <v>33</v>
-      </c>
-      <c r="F75" t="s">
-        <v>188</v>
-      </c>
-      <c r="G75" t="s">
-        <v>35</v>
-      </c>
-      <c r="H75" s="20"/>
-      <c r="I75" s="20"/>
+        <v>105502</v>
+      </c>
+      <c r="C75" s="17" t="s">
+        <v>180</v>
+      </c>
+      <c r="D75" s="2">
+        <v>3</v>
+      </c>
+      <c r="E75" s="2" t="s">
+        <v>173</v>
+      </c>
+      <c r="F75" s="2" t="s">
+        <v>174</v>
+      </c>
+      <c r="G75" s="2" t="s">
+        <v>175</v>
+      </c>
+      <c r="H75" s="4"/>
+      <c r="I75" s="4"/>
     </row>
     <row r="76" customFormat="1" ht="18" customHeight="1" spans="1:9">
       <c r="A76" s="1">
-        <v>5042001</v>
+        <v>5041001</v>
       </c>
       <c r="B76" s="10">
-        <v>104200</v>
+        <v>104100</v>
       </c>
       <c r="C76" t="s">
-        <v>189</v>
+        <v>187</v>
       </c>
       <c r="D76" s="1">
         <v>1</v>
@@ -3757,17 +3729,17 @@
         <v>33</v>
       </c>
       <c r="F76" t="s">
-        <v>190</v>
-      </c>
-      <c r="G76" s="1" t="s">
+        <v>188</v>
+      </c>
+      <c r="G76" t="s">
         <v>35</v>
       </c>
-      <c r="H76" s="20"/>
-      <c r="I76" s="20"/>
-    </row>
-    <row r="77" customFormat="1" ht="16.5" spans="1:9">
+      <c r="H76" s="4"/>
+      <c r="I76" s="4"/>
+    </row>
+    <row r="77" customFormat="1" ht="18" customHeight="1" spans="1:9">
       <c r="A77" s="1">
-        <v>5042002</v>
+        <v>5042001</v>
       </c>
       <c r="B77" s="10">
         <v>104200</v>
@@ -3776,19 +3748,44 @@
         <v>189</v>
       </c>
       <c r="D77" s="1">
+        <v>1</v>
+      </c>
+      <c r="E77" t="s">
+        <v>33</v>
+      </c>
+      <c r="F77" t="s">
+        <v>190</v>
+      </c>
+      <c r="G77" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="H77" s="4"/>
+      <c r="I77" s="4"/>
+    </row>
+    <row r="78" customFormat="1" ht="16.5" spans="1:9">
+      <c r="A78" s="1">
+        <v>5042002</v>
+      </c>
+      <c r="B78" s="10">
+        <v>104200</v>
+      </c>
+      <c r="C78" t="s">
+        <v>189</v>
+      </c>
+      <c r="D78" s="1">
         <v>2</v>
       </c>
-      <c r="E77" t="s">
+      <c r="E78" t="s">
         <v>191</v>
       </c>
-      <c r="F77" t="s">
+      <c r="F78" t="s">
         <v>192</v>
       </c>
-      <c r="G77" s="1" t="s">
+      <c r="G78" s="1" t="s">
         <v>193</v>
       </c>
-      <c r="H77" s="20"/>
-      <c r="I77" s="20"/>
+      <c r="H78" s="4"/>
+      <c r="I78" s="4"/>
     </row>
   </sheetData>
   <conditionalFormatting sqref="H2">

--- a/slots/resources/sample/SpecialPlay.xlsx
+++ b/slots/resources/sample/SpecialPlay.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="28800" windowHeight="12255"/>
+    <workbookView windowWidth="27945" windowHeight="12375"/>
   </bookViews>
   <sheets>
     <sheet name="SpecialPlay" sheetId="1" r:id="rId1"/>
@@ -137,7 +137,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="375" uniqueCount="250">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="379" uniqueCount="251">
   <si>
     <t>被动游戏ID</t>
   </si>
@@ -620,6 +620,9 @@
   </si>
   <si>
     <t>麻将胡了2</t>
+  </si>
+  <si>
+    <t>2,11,3_10_10000|4_12_10000|5_14_10000</t>
   </si>
   <si>
     <t>赏金大对决</t>
@@ -1926,7 +1929,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:J78"/>
+  <dimension ref="A1:J79"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25"/>
   <cols>
     <col min="3" max="3" width="10.375" customWidth="1"/>
@@ -3432,320 +3435,318 @@
     </row>
     <row r="64" ht="16.5" spans="1:7">
       <c r="A64" s="1">
-        <v>5057001</v>
+        <v>5053002</v>
       </c>
       <c r="B64" s="10">
-        <v>105700</v>
+        <v>105300</v>
       </c>
       <c r="C64" t="s">
+        <v>160</v>
+      </c>
+      <c r="D64" s="1">
+        <v>5</v>
+      </c>
+      <c r="E64" t="s">
+        <v>33</v>
+      </c>
+      <c r="F64" s="14" t="s">
         <v>161</v>
       </c>
-      <c r="D64" s="1">
-        <v>1</v>
-      </c>
-      <c r="E64" t="s">
-        <v>30</v>
-      </c>
-      <c r="F64" s="14" t="s">
-        <v>162</v>
-      </c>
       <c r="G64" s="1" t="s">
-        <v>32</v>
+        <v>35</v>
       </c>
     </row>
     <row r="65" ht="16.5" spans="1:9">
       <c r="A65" s="1">
-        <v>5057002</v>
+        <v>5057001</v>
       </c>
       <c r="B65" s="10">
         <v>105700</v>
       </c>
       <c r="C65" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="D65" s="1">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E65" t="s">
-        <v>33</v>
-      </c>
-      <c r="F65" t="s">
+        <v>30</v>
+      </c>
+      <c r="F65" s="14" t="s">
         <v>163</v>
       </c>
-      <c r="G65" t="s">
-        <v>35</v>
+      <c r="G65" s="1" t="s">
+        <v>32</v>
       </c>
     </row>
     <row r="66" ht="16.5" spans="1:9">
       <c r="A66" s="1">
-        <v>5057003</v>
+        <v>5057002</v>
       </c>
       <c r="B66" s="10">
         <v>105700</v>
       </c>
       <c r="C66" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="D66" s="1">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E66" t="s">
+        <v>33</v>
+      </c>
+      <c r="F66" t="s">
         <v>164</v>
       </c>
-      <c r="F66" s="14" t="s">
-        <v>165</v>
-      </c>
-      <c r="G66" s="1" t="s">
-        <v>166</v>
+      <c r="G66" t="s">
+        <v>35</v>
       </c>
     </row>
     <row r="67" ht="16.5" spans="1:9">
       <c r="A67" s="1">
-        <v>5058001</v>
+        <v>5057003</v>
       </c>
       <c r="B67" s="10">
-        <v>105800</v>
+        <v>105700</v>
       </c>
       <c r="C67" t="s">
+        <v>162</v>
+      </c>
+      <c r="D67" s="1">
+        <v>3</v>
+      </c>
+      <c r="E67" t="s">
+        <v>165</v>
+      </c>
+      <c r="F67" s="14" t="s">
+        <v>166</v>
+      </c>
+      <c r="G67" s="1" t="s">
         <v>167</v>
-      </c>
-      <c r="D67" s="1">
-        <v>1</v>
-      </c>
-      <c r="E67" t="s">
-        <v>33</v>
-      </c>
-      <c r="F67" t="s">
-        <v>168</v>
-      </c>
-      <c r="G67" t="s">
-        <v>35</v>
       </c>
     </row>
     <row r="68" ht="16.5" spans="1:9">
       <c r="A68" s="1">
-        <v>5058002</v>
+        <v>5058001</v>
       </c>
       <c r="B68" s="10">
         <v>105800</v>
       </c>
       <c r="C68" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="D68" s="1">
+        <v>1</v>
+      </c>
+      <c r="E68" t="s">
+        <v>33</v>
+      </c>
+      <c r="F68" t="s">
+        <v>169</v>
+      </c>
+      <c r="G68" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="69" ht="16.5" spans="1:9">
+      <c r="A69" s="1">
+        <v>5058002</v>
+      </c>
+      <c r="B69" s="10">
+        <v>105800</v>
+      </c>
+      <c r="C69" t="s">
+        <v>168</v>
+      </c>
+      <c r="D69" s="1">
         <v>2</v>
       </c>
-      <c r="E68" t="s">
-        <v>169</v>
-      </c>
-      <c r="F68" t="s">
+      <c r="E69" t="s">
         <v>170</v>
       </c>
-      <c r="G68" t="s">
+      <c r="F69" t="s">
         <v>171</v>
       </c>
-    </row>
-    <row r="69" s="2" customFormat="1" spans="1:9">
-      <c r="A69" s="2">
+      <c r="G69" t="s">
+        <v>172</v>
+      </c>
+    </row>
+    <row r="70" s="2" customFormat="1" spans="1:9">
+      <c r="A70" s="2">
         <v>5055001</v>
       </c>
-      <c r="B69" s="2">
+      <c r="B70" s="2">
         <v>105500</v>
       </c>
-      <c r="C69" s="2" t="s">
-        <v>172</v>
-      </c>
-      <c r="D69" s="2">
+      <c r="C70" s="2" t="s">
+        <v>173</v>
+      </c>
+      <c r="D70" s="2">
         <v>1</v>
       </c>
-      <c r="E69" s="2" t="s">
-        <v>173</v>
-      </c>
-      <c r="F69" s="2" t="s">
+      <c r="E70" s="2" t="s">
         <v>174</v>
       </c>
-      <c r="G69" s="2" t="s">
+      <c r="F70" s="2" t="s">
         <v>175</v>
       </c>
-      <c r="H69" s="16"/>
-      <c r="I69" s="16"/>
-    </row>
-    <row r="70" ht="18" customHeight="1" spans="1:9">
-      <c r="A70" s="1">
+      <c r="G70" s="2" t="s">
+        <v>176</v>
+      </c>
+      <c r="H70" s="16"/>
+      <c r="I70" s="16"/>
+    </row>
+    <row r="71" ht="18" customHeight="1" spans="1:9">
+      <c r="A71" s="1">
         <v>5048001</v>
-      </c>
-      <c r="B70" s="10">
-        <v>104800</v>
-      </c>
-      <c r="C70" t="s">
-        <v>176</v>
-      </c>
-      <c r="D70" s="1">
-        <v>1</v>
-      </c>
-      <c r="E70" t="s">
-        <v>33</v>
-      </c>
-      <c r="F70" t="s">
-        <v>159</v>
-      </c>
-      <c r="G70" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="71" ht="16.5" spans="1:9">
-      <c r="A71" s="1">
-        <v>5048002</v>
       </c>
       <c r="B71" s="10">
         <v>104800</v>
       </c>
       <c r="C71" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="D71" s="1">
+        <v>1</v>
+      </c>
+      <c r="E71" t="s">
+        <v>33</v>
+      </c>
+      <c r="F71" t="s">
+        <v>159</v>
+      </c>
+      <c r="G71" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="72" ht="16.5" spans="1:9">
+      <c r="A72" s="1">
+        <v>5048002</v>
+      </c>
+      <c r="B72" s="10">
+        <v>104800</v>
+      </c>
+      <c r="C72" t="s">
+        <v>177</v>
+      </c>
+      <c r="D72" s="1">
         <v>2</v>
       </c>
-      <c r="E71" t="s">
-        <v>177</v>
-      </c>
-      <c r="F71" t="s">
+      <c r="E72" t="s">
         <v>178</v>
       </c>
-      <c r="G71" t="s">
+      <c r="F72" t="s">
+        <v>179</v>
+      </c>
+      <c r="G72" t="s">
         <v>158</v>
       </c>
     </row>
-    <row r="72" s="2" customFormat="1" spans="1:9">
-      <c r="A72" s="2">
+    <row r="73" s="2" customFormat="1" spans="1:9">
+      <c r="A73" s="2">
         <v>5055011</v>
       </c>
-      <c r="B72" s="2">
+      <c r="B73" s="2">
         <v>105501</v>
       </c>
-      <c r="C72" s="2" t="s">
-        <v>179</v>
-      </c>
-      <c r="D72" s="2">
-        <v>1</v>
-      </c>
-      <c r="E72" s="2" t="s">
-        <v>173</v>
-      </c>
-      <c r="F72" s="2" t="s">
-        <v>174</v>
-      </c>
-      <c r="G72" s="2" t="s">
-        <v>175</v>
-      </c>
-      <c r="H72" s="16"/>
-      <c r="I72" s="16"/>
-    </row>
-    <row r="73" ht="16.5" spans="1:9">
-      <c r="A73" s="1">
-        <v>5055021</v>
-      </c>
-      <c r="B73" s="10">
-        <v>105502</v>
-      </c>
-      <c r="C73" s="17" t="s">
+      <c r="C73" s="2" t="s">
         <v>180</v>
       </c>
       <c r="D73" s="2">
         <v>1</v>
       </c>
-      <c r="E73" s="17" t="s">
-        <v>181</v>
-      </c>
-      <c r="F73" s="17" t="s">
-        <v>182</v>
-      </c>
-      <c r="G73" s="18" t="s">
-        <v>183</v>
-      </c>
+      <c r="E73" s="2" t="s">
+        <v>174</v>
+      </c>
+      <c r="F73" s="2" t="s">
+        <v>175</v>
+      </c>
+      <c r="G73" s="2" t="s">
+        <v>176</v>
+      </c>
+      <c r="H73" s="16"/>
+      <c r="I73" s="16"/>
     </row>
     <row r="74" ht="16.5" spans="1:9">
       <c r="A74" s="1">
-        <v>5055022</v>
+        <v>5055021</v>
       </c>
       <c r="B74" s="10">
         <v>105502</v>
       </c>
       <c r="C74" s="17" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="D74" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E74" s="17" t="s">
+        <v>182</v>
+      </c>
+      <c r="F74" s="17" t="s">
+        <v>183</v>
+      </c>
+      <c r="G74" s="18" t="s">
         <v>184</v>
       </c>
-      <c r="F74" s="17" t="s">
-        <v>185</v>
-      </c>
-      <c r="G74" s="18" t="s">
-        <v>186</v>
-      </c>
-    </row>
-    <row r="75" customFormat="1" ht="18" customHeight="1" spans="1:9">
+    </row>
+    <row r="75" ht="16.5" spans="1:9">
       <c r="A75" s="1">
-        <v>5055023</v>
+        <v>5055022</v>
       </c>
       <c r="B75" s="10">
         <v>105502</v>
       </c>
       <c r="C75" s="17" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="D75" s="2">
-        <v>3</v>
-      </c>
-      <c r="E75" s="2" t="s">
-        <v>173</v>
-      </c>
-      <c r="F75" s="2" t="s">
-        <v>174</v>
-      </c>
-      <c r="G75" s="2" t="s">
-        <v>175</v>
-      </c>
-      <c r="H75" s="4"/>
-      <c r="I75" s="4"/>
+        <v>2</v>
+      </c>
+      <c r="E75" s="17" t="s">
+        <v>185</v>
+      </c>
+      <c r="F75" s="17" t="s">
+        <v>186</v>
+      </c>
+      <c r="G75" s="18" t="s">
+        <v>187</v>
+      </c>
     </row>
     <row r="76" customFormat="1" ht="18" customHeight="1" spans="1:9">
       <c r="A76" s="1">
-        <v>5041001</v>
+        <v>5055023</v>
       </c>
       <c r="B76" s="10">
-        <v>104100</v>
-      </c>
-      <c r="C76" t="s">
-        <v>187</v>
-      </c>
-      <c r="D76" s="1">
-        <v>1</v>
-      </c>
-      <c r="E76" t="s">
-        <v>33</v>
-      </c>
-      <c r="F76" t="s">
-        <v>188</v>
-      </c>
-      <c r="G76" t="s">
-        <v>35</v>
+        <v>105502</v>
+      </c>
+      <c r="C76" s="17" t="s">
+        <v>181</v>
+      </c>
+      <c r="D76" s="2">
+        <v>3</v>
+      </c>
+      <c r="E76" s="2" t="s">
+        <v>174</v>
+      </c>
+      <c r="F76" s="2" t="s">
+        <v>175</v>
+      </c>
+      <c r="G76" s="2" t="s">
+        <v>176</v>
       </c>
       <c r="H76" s="4"/>
       <c r="I76" s="4"/>
     </row>
     <row r="77" customFormat="1" ht="18" customHeight="1" spans="1:9">
       <c r="A77" s="1">
-        <v>5042001</v>
+        <v>5041001</v>
       </c>
       <c r="B77" s="10">
-        <v>104200</v>
+        <v>104100</v>
       </c>
       <c r="C77" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="D77" s="1">
         <v>1</v>
@@ -3754,38 +3755,63 @@
         <v>33</v>
       </c>
       <c r="F77" t="s">
-        <v>190</v>
-      </c>
-      <c r="G77" s="1" t="s">
+        <v>189</v>
+      </c>
+      <c r="G77" t="s">
         <v>35</v>
       </c>
       <c r="H77" s="4"/>
       <c r="I77" s="4"/>
     </row>
-    <row r="78" customFormat="1" ht="16.5" spans="1:9">
+    <row r="78" customFormat="1" ht="18" customHeight="1" spans="1:9">
       <c r="A78" s="1">
-        <v>5042002</v>
+        <v>5042001</v>
       </c>
       <c r="B78" s="10">
         <v>104200</v>
       </c>
       <c r="C78" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="D78" s="1">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E78" t="s">
+        <v>33</v>
+      </c>
+      <c r="F78" t="s">
         <v>191</v>
       </c>
-      <c r="F78" t="s">
-        <v>192</v>
-      </c>
       <c r="G78" s="1" t="s">
-        <v>193</v>
+        <v>35</v>
       </c>
       <c r="H78" s="4"/>
       <c r="I78" s="4"/>
+    </row>
+    <row r="79" customFormat="1" ht="16.5" spans="1:9">
+      <c r="A79" s="1">
+        <v>5042002</v>
+      </c>
+      <c r="B79" s="10">
+        <v>104200</v>
+      </c>
+      <c r="C79" t="s">
+        <v>190</v>
+      </c>
+      <c r="D79" s="1">
+        <v>2</v>
+      </c>
+      <c r="E79" t="s">
+        <v>192</v>
+      </c>
+      <c r="F79" t="s">
+        <v>193</v>
+      </c>
+      <c r="G79" s="1" t="s">
+        <v>194</v>
+      </c>
+      <c r="H79" s="4"/>
+      <c r="I79" s="4"/>
     </row>
   </sheetData>
   <conditionalFormatting sqref="H2">
@@ -3812,24 +3838,24 @@
   <sheetData>
     <row r="1" spans="1:5">
       <c r="A1" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="D1" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
     </row>
     <row r="2" spans="1:5">
       <c r="A2" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="B2" t="s">
+        <v>198</v>
+      </c>
+      <c r="D2" t="s">
         <v>197</v>
       </c>
-      <c r="D2" t="s">
-        <v>196</v>
-      </c>
       <c r="E2" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
     </row>
     <row r="3" spans="1:5">
@@ -3837,13 +3863,13 @@
         <v>0</v>
       </c>
       <c r="B3" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="D3">
         <v>0</v>
       </c>
       <c r="E3" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
     </row>
     <row r="4" spans="1:5">
@@ -3851,13 +3877,13 @@
         <v>1</v>
       </c>
       <c r="B4" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="D4">
         <v>1</v>
       </c>
       <c r="E4" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
     </row>
     <row r="5" spans="1:5">
@@ -3865,13 +3891,13 @@
         <v>2</v>
       </c>
       <c r="B5" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="D5">
         <v>2</v>
       </c>
       <c r="E5" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
     </row>
     <row r="6" spans="1:5">
@@ -3879,13 +3905,13 @@
         <v>3</v>
       </c>
       <c r="B6" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="D6">
         <v>3</v>
       </c>
       <c r="E6" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
     </row>
     <row r="7" spans="1:5">
@@ -3893,13 +3919,13 @@
         <v>4</v>
       </c>
       <c r="B7" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="D7">
         <v>4</v>
       </c>
       <c r="E7" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
     </row>
     <row r="8" spans="1:5">
@@ -3907,13 +3933,13 @@
         <v>5</v>
       </c>
       <c r="B8" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="D8">
         <v>5</v>
       </c>
       <c r="E8" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
     </row>
     <row r="9" spans="1:5">
@@ -3921,7 +3947,7 @@
         <v>6</v>
       </c>
       <c r="B9" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
     </row>
     <row r="10" spans="1:5">
@@ -3929,7 +3955,7 @@
         <v>7</v>
       </c>
       <c r="B10" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
     </row>
     <row r="11" spans="1:5">
@@ -3937,7 +3963,7 @@
         <v>8</v>
       </c>
       <c r="B11" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
     </row>
     <row r="12" spans="1:5">
@@ -3945,7 +3971,7 @@
         <v>9</v>
       </c>
       <c r="B12" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
     </row>
     <row r="13" spans="1:5">
@@ -3953,7 +3979,7 @@
         <v>10</v>
       </c>
       <c r="B13" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
     </row>
     <row r="14" spans="1:5">
@@ -3961,7 +3987,7 @@
         <v>11</v>
       </c>
       <c r="B14" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
     </row>
     <row r="15" spans="1:5">
@@ -3969,7 +3995,7 @@
         <v>12</v>
       </c>
       <c r="B15" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
     </row>
     <row r="16" spans="1:5">
@@ -3977,7 +4003,7 @@
         <v>13</v>
       </c>
       <c r="B16" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
     </row>
     <row r="17" spans="1:2">
@@ -3985,7 +4011,7 @@
         <v>14</v>
       </c>
       <c r="B17" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
     </row>
     <row r="18" spans="1:2">
@@ -3993,7 +4019,7 @@
         <v>15</v>
       </c>
       <c r="B18" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
     </row>
     <row r="19" spans="1:2">
@@ -4001,7 +4027,7 @@
         <v>16</v>
       </c>
       <c r="B19" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
     </row>
     <row r="20" spans="1:2">
@@ -4009,7 +4035,7 @@
         <v>17</v>
       </c>
       <c r="B20" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
     </row>
     <row r="21" spans="1:2">
@@ -4017,7 +4043,7 @@
         <v>18</v>
       </c>
       <c r="B21" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
     </row>
     <row r="22" spans="1:2">
@@ -4025,7 +4051,7 @@
         <v>19</v>
       </c>
       <c r="B22" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
     </row>
     <row r="23" spans="1:2">
@@ -4033,7 +4059,7 @@
         <v>20</v>
       </c>
       <c r="B23" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
     </row>
     <row r="24" spans="1:2">
@@ -4041,7 +4067,7 @@
         <v>21</v>
       </c>
       <c r="B24" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
     </row>
     <row r="25" spans="1:2">
@@ -4049,7 +4075,7 @@
         <v>22</v>
       </c>
       <c r="B25" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
     </row>
     <row r="26" spans="1:2">
@@ -4057,7 +4083,7 @@
         <v>23</v>
       </c>
       <c r="B26" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
     </row>
     <row r="27" spans="1:2">
@@ -4065,7 +4091,7 @@
         <v>24</v>
       </c>
       <c r="B27" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
     </row>
     <row r="28" spans="1:2">
@@ -4073,7 +4099,7 @@
         <v>25</v>
       </c>
       <c r="B28" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
     </row>
     <row r="29" spans="1:2">
@@ -4081,7 +4107,7 @@
         <v>26</v>
       </c>
       <c r="B29" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
     </row>
     <row r="30" spans="1:2">
@@ -4089,7 +4115,7 @@
         <v>27</v>
       </c>
       <c r="B30" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
     </row>
     <row r="31" spans="1:2">
@@ -4097,7 +4123,7 @@
         <v>28</v>
       </c>
       <c r="B31" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
     </row>
     <row r="32" spans="1:2">
@@ -4105,7 +4131,7 @@
         <v>29</v>
       </c>
       <c r="B32" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
     </row>
     <row r="33" spans="1:2">
@@ -4113,7 +4139,7 @@
         <v>30</v>
       </c>
       <c r="B33" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
     </row>
     <row r="34" spans="1:2">
@@ -4121,7 +4147,7 @@
         <v>31</v>
       </c>
       <c r="B34" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
     </row>
     <row r="35" spans="1:2">
@@ -4129,7 +4155,7 @@
         <v>32</v>
       </c>
       <c r="B35" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
     </row>
     <row r="36" spans="1:2">
@@ -4137,7 +4163,7 @@
         <v>33</v>
       </c>
       <c r="B36" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
     </row>
     <row r="37" spans="1:2">
@@ -4145,7 +4171,7 @@
         <v>34</v>
       </c>
       <c r="B37" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
     </row>
     <row r="38" spans="1:2">
@@ -4153,7 +4179,7 @@
         <v>35</v>
       </c>
       <c r="B38" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
     </row>
     <row r="39" spans="1:2">
@@ -4161,7 +4187,7 @@
         <v>36</v>
       </c>
       <c r="B39" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
     </row>
     <row r="40" spans="1:2">
@@ -4169,7 +4195,7 @@
         <v>37</v>
       </c>
       <c r="B40" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
     </row>
     <row r="41" spans="1:2">
@@ -4177,7 +4203,7 @@
         <v>38</v>
       </c>
       <c r="B41" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
     </row>
     <row r="42" spans="1:2">
@@ -4185,7 +4211,7 @@
         <v>39</v>
       </c>
       <c r="B42" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
     </row>
     <row r="43" spans="1:2">
@@ -4193,7 +4219,7 @@
         <v>40</v>
       </c>
       <c r="B43" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
     </row>
     <row r="44" spans="1:2">
@@ -4201,7 +4227,7 @@
         <v>41</v>
       </c>
       <c r="B44" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
     </row>
     <row r="45" spans="1:2">
@@ -4209,7 +4235,7 @@
         <v>42</v>
       </c>
       <c r="B45" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
     </row>
     <row r="46" spans="1:2">
@@ -4217,7 +4243,7 @@
         <v>43</v>
       </c>
       <c r="B46" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
     </row>
     <row r="47" spans="1:2">
@@ -4225,7 +4251,7 @@
         <v>44</v>
       </c>
       <c r="B47" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
     </row>
     <row r="48" spans="1:2">
@@ -4233,7 +4259,7 @@
         <v>45</v>
       </c>
       <c r="B48" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
     </row>
   </sheetData>

--- a/slots/resources/sample/SpecialPlay.xlsx
+++ b/slots/resources/sample/SpecialPlay.xlsx
@@ -664,7 +664,7 @@
     <t>第四轴出现的图标的倍数及权重</t>
   </si>
   <si>
-    <t>10_1_5000|11_2_3000|12_3_0000|13_5_500|14_10_400|15_15_100</t>
+    <t>10_1_5000|11_2_3000|12_3_1000|13_5_500|14_10_400|15_15_100</t>
   </si>
   <si>
     <t>元素ID_图标倍数_权重</t>

--- a/slots/resources/sample/SpecialPlay.xlsx
+++ b/slots/resources/sample/SpecialPlay.xlsx
@@ -137,7 +137,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="379" uniqueCount="251">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="387" uniqueCount="254">
   <si>
     <t>被动游戏ID</t>
   </si>
@@ -634,15 +634,6 @@
     <t>10,3_10_10000|4_12_10000|5_14_10000</t>
   </si>
   <si>
-    <t>常规模式下，金框符号转换为百搭符号</t>
-  </si>
-  <si>
-    <t>9_1_1</t>
-  </si>
-  <si>
-    <t>元素id_金框符号权重_百搭符号权重|元素id_金框符号权重_百搭符号权重|元素id_金框符号权重_百搭符号权重</t>
-  </si>
-  <si>
     <t>极速糖果1000</t>
   </si>
   <si>
@@ -722,6 +713,24 @@
   </si>
   <si>
     <t>目标图案_中奖翻倍</t>
+  </si>
+  <si>
+    <t>德古拉</t>
+  </si>
+  <si>
+    <t>1,1_1|2_2|3_3|4_4|5_5;2,1_3|2_6|3_9|4_12|5_15</t>
+  </si>
+  <si>
+    <t>2,13,4_12_10000|5_14_10000|6_16_10000</t>
+  </si>
+  <si>
+    <t>百搭赐福模式下，随机三个白银符号变成直接变成wild符号</t>
+  </si>
+  <si>
+    <t>3_3</t>
+  </si>
+  <si>
+    <t>模式id_随机白银符号个数</t>
   </si>
   <si>
     <t>旋转标识</t>
@@ -1929,7 +1938,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:J79"/>
+  <dimension ref="A1:J81"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25"/>
   <cols>
     <col min="3" max="3" width="10.375" customWidth="1"/>
@@ -3504,181 +3513,181 @@
     </row>
     <row r="67" ht="16.5" spans="1:9">
       <c r="A67" s="1">
-        <v>5057003</v>
+        <v>5058001</v>
       </c>
       <c r="B67" s="10">
-        <v>105700</v>
+        <v>105800</v>
       </c>
       <c r="C67" t="s">
-        <v>162</v>
+        <v>165</v>
       </c>
       <c r="D67" s="1">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E67" t="s">
-        <v>165</v>
-      </c>
-      <c r="F67" s="14" t="s">
+        <v>33</v>
+      </c>
+      <c r="F67" t="s">
         <v>166</v>
       </c>
-      <c r="G67" s="1" t="s">
-        <v>167</v>
+      <c r="G67" t="s">
+        <v>35</v>
       </c>
     </row>
     <row r="68" ht="16.5" spans="1:9">
       <c r="A68" s="1">
-        <v>5058001</v>
+        <v>5058002</v>
       </c>
       <c r="B68" s="10">
         <v>105800</v>
       </c>
       <c r="C68" t="s">
+        <v>165</v>
+      </c>
+      <c r="D68" s="1">
+        <v>2</v>
+      </c>
+      <c r="E68" t="s">
+        <v>167</v>
+      </c>
+      <c r="F68" t="s">
         <v>168</v>
       </c>
-      <c r="D68" s="1">
+      <c r="G68" t="s">
+        <v>169</v>
+      </c>
+    </row>
+    <row r="69" s="2" customFormat="1" spans="1:9">
+      <c r="A69" s="2">
+        <v>5055001</v>
+      </c>
+      <c r="B69" s="2">
+        <v>105500</v>
+      </c>
+      <c r="C69" s="2" t="s">
+        <v>170</v>
+      </c>
+      <c r="D69" s="2">
         <v>1</v>
       </c>
-      <c r="E68" t="s">
+      <c r="E69" s="2" t="s">
+        <v>171</v>
+      </c>
+      <c r="F69" s="2" t="s">
+        <v>172</v>
+      </c>
+      <c r="G69" s="2" t="s">
+        <v>173</v>
+      </c>
+      <c r="H69" s="16"/>
+      <c r="I69" s="16"/>
+    </row>
+    <row r="70" ht="18" customHeight="1" spans="1:9">
+      <c r="A70" s="1">
+        <v>5048001</v>
+      </c>
+      <c r="B70" s="10">
+        <v>104800</v>
+      </c>
+      <c r="C70" t="s">
+        <v>174</v>
+      </c>
+      <c r="D70" s="1">
+        <v>1</v>
+      </c>
+      <c r="E70" t="s">
         <v>33</v>
       </c>
-      <c r="F68" t="s">
-        <v>169</v>
-      </c>
-      <c r="G68" t="s">
+      <c r="F70" t="s">
+        <v>159</v>
+      </c>
+      <c r="G70" t="s">
         <v>35</v>
       </c>
     </row>
-    <row r="69" ht="16.5" spans="1:9">
-      <c r="A69" s="1">
-        <v>5058002</v>
-      </c>
-      <c r="B69" s="10">
-        <v>105800</v>
-      </c>
-      <c r="C69" t="s">
-        <v>168</v>
-      </c>
-      <c r="D69" s="1">
-        <v>2</v>
-      </c>
-      <c r="E69" t="s">
-        <v>170</v>
-      </c>
-      <c r="F69" t="s">
-        <v>171</v>
-      </c>
-      <c r="G69" t="s">
-        <v>172</v>
-      </c>
-    </row>
-    <row r="70" s="2" customFormat="1" spans="1:9">
-      <c r="A70" s="2">
-        <v>5055001</v>
-      </c>
-      <c r="B70" s="2">
-        <v>105500</v>
-      </c>
-      <c r="C70" s="2" t="s">
-        <v>173</v>
-      </c>
-      <c r="D70" s="2">
-        <v>1</v>
-      </c>
-      <c r="E70" s="2" t="s">
-        <v>174</v>
-      </c>
-      <c r="F70" s="2" t="s">
-        <v>175</v>
-      </c>
-      <c r="G70" s="2" t="s">
-        <v>176</v>
-      </c>
-      <c r="H70" s="16"/>
-      <c r="I70" s="16"/>
-    </row>
-    <row r="71" ht="18" customHeight="1" spans="1:9">
+    <row r="71" ht="16.5" spans="1:9">
       <c r="A71" s="1">
-        <v>5048001</v>
+        <v>5048002</v>
       </c>
       <c r="B71" s="10">
         <v>104800</v>
       </c>
       <c r="C71" t="s">
+        <v>174</v>
+      </c>
+      <c r="D71" s="1">
+        <v>2</v>
+      </c>
+      <c r="E71" t="s">
+        <v>175</v>
+      </c>
+      <c r="F71" t="s">
+        <v>176</v>
+      </c>
+      <c r="G71" t="s">
+        <v>158</v>
+      </c>
+    </row>
+    <row r="72" s="2" customFormat="1" spans="1:9">
+      <c r="A72" s="2">
+        <v>5055011</v>
+      </c>
+      <c r="B72" s="2">
+        <v>105501</v>
+      </c>
+      <c r="C72" s="2" t="s">
         <v>177</v>
       </c>
-      <c r="D71" s="1">
+      <c r="D72" s="2">
         <v>1</v>
       </c>
-      <c r="E71" t="s">
-        <v>33</v>
-      </c>
-      <c r="F71" t="s">
-        <v>159</v>
-      </c>
-      <c r="G71" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="72" ht="16.5" spans="1:9">
-      <c r="A72" s="1">
-        <v>5048002</v>
-      </c>
-      <c r="B72" s="10">
-        <v>104800</v>
-      </c>
-      <c r="C72" t="s">
-        <v>177</v>
-      </c>
-      <c r="D72" s="1">
-        <v>2</v>
-      </c>
-      <c r="E72" t="s">
+      <c r="E72" s="2" t="s">
+        <v>171</v>
+      </c>
+      <c r="F72" s="2" t="s">
+        <v>172</v>
+      </c>
+      <c r="G72" s="2" t="s">
+        <v>173</v>
+      </c>
+      <c r="H72" s="16"/>
+      <c r="I72" s="16"/>
+    </row>
+    <row r="73" ht="16.5" spans="1:9">
+      <c r="A73" s="1">
+        <v>5055021</v>
+      </c>
+      <c r="B73" s="10">
+        <v>105502</v>
+      </c>
+      <c r="C73" s="17" t="s">
         <v>178</v>
-      </c>
-      <c r="F72" t="s">
-        <v>179</v>
-      </c>
-      <c r="G72" t="s">
-        <v>158</v>
-      </c>
-    </row>
-    <row r="73" s="2" customFormat="1" spans="1:9">
-      <c r="A73" s="2">
-        <v>5055011</v>
-      </c>
-      <c r="B73" s="2">
-        <v>105501</v>
-      </c>
-      <c r="C73" s="2" t="s">
-        <v>180</v>
       </c>
       <c r="D73" s="2">
         <v>1</v>
       </c>
-      <c r="E73" s="2" t="s">
-        <v>174</v>
-      </c>
-      <c r="F73" s="2" t="s">
-        <v>175</v>
-      </c>
-      <c r="G73" s="2" t="s">
-        <v>176</v>
-      </c>
-      <c r="H73" s="16"/>
-      <c r="I73" s="16"/>
+      <c r="E73" s="17" t="s">
+        <v>179</v>
+      </c>
+      <c r="F73" s="17" t="s">
+        <v>180</v>
+      </c>
+      <c r="G73" s="18" t="s">
+        <v>181</v>
+      </c>
     </row>
     <row r="74" ht="16.5" spans="1:9">
       <c r="A74" s="1">
-        <v>5055021</v>
+        <v>5055022</v>
       </c>
       <c r="B74" s="10">
         <v>105502</v>
       </c>
       <c r="C74" s="17" t="s">
-        <v>181</v>
+        <v>178</v>
       </c>
       <c r="D74" s="2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E74" s="17" t="s">
         <v>182</v>
@@ -3690,63 +3699,65 @@
         <v>184</v>
       </c>
     </row>
-    <row r="75" ht="16.5" spans="1:9">
+    <row r="75" customFormat="1" ht="18" customHeight="1" spans="1:9">
       <c r="A75" s="1">
-        <v>5055022</v>
+        <v>5055023</v>
       </c>
       <c r="B75" s="10">
         <v>105502</v>
       </c>
       <c r="C75" s="17" t="s">
-        <v>181</v>
+        <v>178</v>
       </c>
       <c r="D75" s="2">
-        <v>2</v>
-      </c>
-      <c r="E75" s="17" t="s">
-        <v>185</v>
-      </c>
-      <c r="F75" s="17" t="s">
-        <v>186</v>
-      </c>
-      <c r="G75" s="18" t="s">
-        <v>187</v>
-      </c>
+        <v>3</v>
+      </c>
+      <c r="E75" s="2" t="s">
+        <v>171</v>
+      </c>
+      <c r="F75" s="2" t="s">
+        <v>172</v>
+      </c>
+      <c r="G75" s="2" t="s">
+        <v>173</v>
+      </c>
+      <c r="H75" s="4"/>
+      <c r="I75" s="4"/>
     </row>
     <row r="76" customFormat="1" ht="18" customHeight="1" spans="1:9">
       <c r="A76" s="1">
-        <v>5055023</v>
+        <v>5041001</v>
       </c>
       <c r="B76" s="10">
-        <v>105502</v>
-      </c>
-      <c r="C76" s="17" t="s">
-        <v>181</v>
-      </c>
-      <c r="D76" s="2">
-        <v>3</v>
-      </c>
-      <c r="E76" s="2" t="s">
-        <v>174</v>
-      </c>
-      <c r="F76" s="2" t="s">
-        <v>175</v>
-      </c>
-      <c r="G76" s="2" t="s">
-        <v>176</v>
+        <v>104100</v>
+      </c>
+      <c r="C76" t="s">
+        <v>185</v>
+      </c>
+      <c r="D76" s="1">
+        <v>1</v>
+      </c>
+      <c r="E76" t="s">
+        <v>33</v>
+      </c>
+      <c r="F76" t="s">
+        <v>186</v>
+      </c>
+      <c r="G76" t="s">
+        <v>35</v>
       </c>
       <c r="H76" s="4"/>
       <c r="I76" s="4"/>
     </row>
     <row r="77" customFormat="1" ht="18" customHeight="1" spans="1:9">
       <c r="A77" s="1">
-        <v>5041001</v>
+        <v>5042001</v>
       </c>
       <c r="B77" s="10">
-        <v>104100</v>
+        <v>104200</v>
       </c>
       <c r="C77" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="D77" s="1">
         <v>1</v>
@@ -3755,63 +3766,113 @@
         <v>33</v>
       </c>
       <c r="F77" t="s">
-        <v>189</v>
-      </c>
-      <c r="G77" t="s">
+        <v>188</v>
+      </c>
+      <c r="G77" s="1" t="s">
         <v>35</v>
       </c>
       <c r="H77" s="4"/>
       <c r="I77" s="4"/>
     </row>
-    <row r="78" customFormat="1" ht="18" customHeight="1" spans="1:9">
+    <row r="78" customFormat="1" ht="16.5" spans="1:9">
       <c r="A78" s="1">
-        <v>5042001</v>
+        <v>5042002</v>
       </c>
       <c r="B78" s="10">
         <v>104200</v>
       </c>
       <c r="C78" t="s">
+        <v>187</v>
+      </c>
+      <c r="D78" s="1">
+        <v>2</v>
+      </c>
+      <c r="E78" t="s">
+        <v>189</v>
+      </c>
+      <c r="F78" t="s">
         <v>190</v>
       </c>
-      <c r="D78" s="1">
-        <v>1</v>
-      </c>
-      <c r="E78" t="s">
-        <v>33</v>
-      </c>
-      <c r="F78" t="s">
+      <c r="G78" s="1" t="s">
         <v>191</v>
-      </c>
-      <c r="G78" s="1" t="s">
-        <v>35</v>
       </c>
       <c r="H78" s="4"/>
       <c r="I78" s="4"/>
     </row>
     <row r="79" customFormat="1" ht="16.5" spans="1:9">
       <c r="A79" s="1">
-        <v>5042002</v>
+        <v>5019001</v>
       </c>
       <c r="B79" s="10">
-        <v>104200</v>
+        <v>101900</v>
       </c>
       <c r="C79" t="s">
-        <v>190</v>
+        <v>192</v>
       </c>
       <c r="D79" s="1">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E79" t="s">
-        <v>192</v>
+        <v>30</v>
       </c>
       <c r="F79" t="s">
         <v>193</v>
       </c>
       <c r="G79" s="1" t="s">
-        <v>194</v>
+        <v>32</v>
       </c>
       <c r="H79" s="4"/>
       <c r="I79" s="4"/>
+    </row>
+    <row r="80" customFormat="1" ht="16.5" spans="1:9">
+      <c r="A80" s="1">
+        <v>5019002</v>
+      </c>
+      <c r="B80" s="10">
+        <v>101900</v>
+      </c>
+      <c r="C80" t="s">
+        <v>192</v>
+      </c>
+      <c r="D80" s="1">
+        <v>2</v>
+      </c>
+      <c r="E80" t="s">
+        <v>33</v>
+      </c>
+      <c r="F80" t="s">
+        <v>194</v>
+      </c>
+      <c r="G80" s="1" t="s">
+        <v>143</v>
+      </c>
+      <c r="H80" s="4"/>
+      <c r="I80" s="4"/>
+    </row>
+    <row r="81" customFormat="1" ht="16.5" spans="1:9">
+      <c r="A81" s="1">
+        <v>5019003</v>
+      </c>
+      <c r="B81" s="10">
+        <v>101900</v>
+      </c>
+      <c r="C81" t="s">
+        <v>192</v>
+      </c>
+      <c r="D81" s="1">
+        <v>3</v>
+      </c>
+      <c r="E81" t="s">
+        <v>195</v>
+      </c>
+      <c r="F81" t="s">
+        <v>196</v>
+      </c>
+      <c r="G81" s="1" t="s">
+        <v>197</v>
+      </c>
+      <c r="H81" s="4"/>
+      <c r="I81" s="4"/>
     </row>
   </sheetData>
   <conditionalFormatting sqref="H2">
@@ -3838,24 +3899,24 @@
   <sheetData>
     <row r="1" spans="1:5">
       <c r="A1" t="s">
-        <v>195</v>
+        <v>198</v>
       </c>
       <c r="D1" t="s">
-        <v>196</v>
+        <v>199</v>
       </c>
     </row>
     <row r="2" spans="1:5">
       <c r="A2" t="s">
-        <v>197</v>
+        <v>200</v>
       </c>
       <c r="B2" t="s">
-        <v>198</v>
+        <v>201</v>
       </c>
       <c r="D2" t="s">
-        <v>197</v>
+        <v>200</v>
       </c>
       <c r="E2" t="s">
-        <v>198</v>
+        <v>201</v>
       </c>
     </row>
     <row r="3" spans="1:5">
@@ -3863,13 +3924,13 @@
         <v>0</v>
       </c>
       <c r="B3" t="s">
-        <v>199</v>
+        <v>202</v>
       </c>
       <c r="D3">
         <v>0</v>
       </c>
       <c r="E3" t="s">
-        <v>200</v>
+        <v>203</v>
       </c>
     </row>
     <row r="4" spans="1:5">
@@ -3877,13 +3938,13 @@
         <v>1</v>
       </c>
       <c r="B4" t="s">
-        <v>201</v>
+        <v>204</v>
       </c>
       <c r="D4">
         <v>1</v>
       </c>
       <c r="E4" t="s">
-        <v>202</v>
+        <v>205</v>
       </c>
     </row>
     <row r="5" spans="1:5">
@@ -3891,13 +3952,13 @@
         <v>2</v>
       </c>
       <c r="B5" t="s">
-        <v>203</v>
+        <v>206</v>
       </c>
       <c r="D5">
         <v>2</v>
       </c>
       <c r="E5" t="s">
-        <v>204</v>
+        <v>207</v>
       </c>
     </row>
     <row r="6" spans="1:5">
@@ -3905,13 +3966,13 @@
         <v>3</v>
       </c>
       <c r="B6" t="s">
-        <v>205</v>
+        <v>208</v>
       </c>
       <c r="D6">
         <v>3</v>
       </c>
       <c r="E6" t="s">
-        <v>206</v>
+        <v>209</v>
       </c>
     </row>
     <row r="7" spans="1:5">
@@ -3919,13 +3980,13 @@
         <v>4</v>
       </c>
       <c r="B7" t="s">
-        <v>207</v>
+        <v>210</v>
       </c>
       <c r="D7">
         <v>4</v>
       </c>
       <c r="E7" t="s">
-        <v>208</v>
+        <v>211</v>
       </c>
     </row>
     <row r="8" spans="1:5">
@@ -3933,13 +3994,13 @@
         <v>5</v>
       </c>
       <c r="B8" t="s">
-        <v>209</v>
+        <v>212</v>
       </c>
       <c r="D8">
         <v>5</v>
       </c>
       <c r="E8" t="s">
-        <v>210</v>
+        <v>213</v>
       </c>
     </row>
     <row r="9" spans="1:5">
@@ -3947,7 +4008,7 @@
         <v>6</v>
       </c>
       <c r="B9" t="s">
-        <v>211</v>
+        <v>214</v>
       </c>
     </row>
     <row r="10" spans="1:5">
@@ -3955,7 +4016,7 @@
         <v>7</v>
       </c>
       <c r="B10" t="s">
-        <v>212</v>
+        <v>215</v>
       </c>
     </row>
     <row r="11" spans="1:5">
@@ -3963,7 +4024,7 @@
         <v>8</v>
       </c>
       <c r="B11" t="s">
-        <v>213</v>
+        <v>216</v>
       </c>
     </row>
     <row r="12" spans="1:5">
@@ -3971,7 +4032,7 @@
         <v>9</v>
       </c>
       <c r="B12" t="s">
-        <v>214</v>
+        <v>217</v>
       </c>
     </row>
     <row r="13" spans="1:5">
@@ -3979,7 +4040,7 @@
         <v>10</v>
       </c>
       <c r="B13" t="s">
-        <v>215</v>
+        <v>218</v>
       </c>
     </row>
     <row r="14" spans="1:5">
@@ -3987,7 +4048,7 @@
         <v>11</v>
       </c>
       <c r="B14" t="s">
-        <v>216</v>
+        <v>219</v>
       </c>
     </row>
     <row r="15" spans="1:5">
@@ -3995,7 +4056,7 @@
         <v>12</v>
       </c>
       <c r="B15" t="s">
-        <v>217</v>
+        <v>220</v>
       </c>
     </row>
     <row r="16" spans="1:5">
@@ -4003,7 +4064,7 @@
         <v>13</v>
       </c>
       <c r="B16" t="s">
-        <v>218</v>
+        <v>221</v>
       </c>
     </row>
     <row r="17" spans="1:2">
@@ -4011,7 +4072,7 @@
         <v>14</v>
       </c>
       <c r="B17" t="s">
-        <v>219</v>
+        <v>222</v>
       </c>
     </row>
     <row r="18" spans="1:2">
@@ -4019,7 +4080,7 @@
         <v>15</v>
       </c>
       <c r="B18" t="s">
-        <v>220</v>
+        <v>223</v>
       </c>
     </row>
     <row r="19" spans="1:2">
@@ -4027,7 +4088,7 @@
         <v>16</v>
       </c>
       <c r="B19" t="s">
-        <v>221</v>
+        <v>224</v>
       </c>
     </row>
     <row r="20" spans="1:2">
@@ -4035,7 +4096,7 @@
         <v>17</v>
       </c>
       <c r="B20" t="s">
-        <v>222</v>
+        <v>225</v>
       </c>
     </row>
     <row r="21" spans="1:2">
@@ -4043,7 +4104,7 @@
         <v>18</v>
       </c>
       <c r="B21" t="s">
-        <v>223</v>
+        <v>226</v>
       </c>
     </row>
     <row r="22" spans="1:2">
@@ -4051,7 +4112,7 @@
         <v>19</v>
       </c>
       <c r="B22" t="s">
-        <v>224</v>
+        <v>227</v>
       </c>
     </row>
     <row r="23" spans="1:2">
@@ -4059,7 +4120,7 @@
         <v>20</v>
       </c>
       <c r="B23" t="s">
-        <v>225</v>
+        <v>228</v>
       </c>
     </row>
     <row r="24" spans="1:2">
@@ -4067,7 +4128,7 @@
         <v>21</v>
       </c>
       <c r="B24" t="s">
-        <v>226</v>
+        <v>229</v>
       </c>
     </row>
     <row r="25" spans="1:2">
@@ -4075,7 +4136,7 @@
         <v>22</v>
       </c>
       <c r="B25" t="s">
-        <v>227</v>
+        <v>230</v>
       </c>
     </row>
     <row r="26" spans="1:2">
@@ -4083,7 +4144,7 @@
         <v>23</v>
       </c>
       <c r="B26" t="s">
-        <v>228</v>
+        <v>231</v>
       </c>
     </row>
     <row r="27" spans="1:2">
@@ -4091,7 +4152,7 @@
         <v>24</v>
       </c>
       <c r="B27" t="s">
-        <v>229</v>
+        <v>232</v>
       </c>
     </row>
     <row r="28" spans="1:2">
@@ -4099,7 +4160,7 @@
         <v>25</v>
       </c>
       <c r="B28" t="s">
-        <v>230</v>
+        <v>233</v>
       </c>
     </row>
     <row r="29" spans="1:2">
@@ -4107,7 +4168,7 @@
         <v>26</v>
       </c>
       <c r="B29" t="s">
-        <v>231</v>
+        <v>234</v>
       </c>
     </row>
     <row r="30" spans="1:2">
@@ -4115,7 +4176,7 @@
         <v>27</v>
       </c>
       <c r="B30" t="s">
-        <v>232</v>
+        <v>235</v>
       </c>
     </row>
     <row r="31" spans="1:2">
@@ -4123,7 +4184,7 @@
         <v>28</v>
       </c>
       <c r="B31" t="s">
-        <v>233</v>
+        <v>236</v>
       </c>
     </row>
     <row r="32" spans="1:2">
@@ -4131,7 +4192,7 @@
         <v>29</v>
       </c>
       <c r="B32" t="s">
-        <v>234</v>
+        <v>237</v>
       </c>
     </row>
     <row r="33" spans="1:2">
@@ -4139,7 +4200,7 @@
         <v>30</v>
       </c>
       <c r="B33" t="s">
-        <v>235</v>
+        <v>238</v>
       </c>
     </row>
     <row r="34" spans="1:2">
@@ -4147,7 +4208,7 @@
         <v>31</v>
       </c>
       <c r="B34" t="s">
-        <v>236</v>
+        <v>239</v>
       </c>
     </row>
     <row r="35" spans="1:2">
@@ -4155,7 +4216,7 @@
         <v>32</v>
       </c>
       <c r="B35" t="s">
-        <v>237</v>
+        <v>240</v>
       </c>
     </row>
     <row r="36" spans="1:2">
@@ -4163,7 +4224,7 @@
         <v>33</v>
       </c>
       <c r="B36" t="s">
-        <v>238</v>
+        <v>241</v>
       </c>
     </row>
     <row r="37" spans="1:2">
@@ -4171,7 +4232,7 @@
         <v>34</v>
       </c>
       <c r="B37" t="s">
-        <v>239</v>
+        <v>242</v>
       </c>
     </row>
     <row r="38" spans="1:2">
@@ -4179,7 +4240,7 @@
         <v>35</v>
       </c>
       <c r="B38" t="s">
-        <v>240</v>
+        <v>243</v>
       </c>
     </row>
     <row r="39" spans="1:2">
@@ -4187,7 +4248,7 @@
         <v>36</v>
       </c>
       <c r="B39" t="s">
-        <v>241</v>
+        <v>244</v>
       </c>
     </row>
     <row r="40" spans="1:2">
@@ -4195,7 +4256,7 @@
         <v>37</v>
       </c>
       <c r="B40" t="s">
-        <v>242</v>
+        <v>245</v>
       </c>
     </row>
     <row r="41" spans="1:2">
@@ -4203,7 +4264,7 @@
         <v>38</v>
       </c>
       <c r="B41" t="s">
-        <v>243</v>
+        <v>246</v>
       </c>
     </row>
     <row r="42" spans="1:2">
@@ -4211,7 +4272,7 @@
         <v>39</v>
       </c>
       <c r="B42" t="s">
-        <v>244</v>
+        <v>247</v>
       </c>
     </row>
     <row r="43" spans="1:2">
@@ -4219,7 +4280,7 @@
         <v>40</v>
       </c>
       <c r="B43" t="s">
-        <v>245</v>
+        <v>248</v>
       </c>
     </row>
     <row r="44" spans="1:2">
@@ -4227,7 +4288,7 @@
         <v>41</v>
       </c>
       <c r="B44" t="s">
-        <v>246</v>
+        <v>249</v>
       </c>
     </row>
     <row r="45" spans="1:2">
@@ -4235,7 +4296,7 @@
         <v>42</v>
       </c>
       <c r="B45" t="s">
-        <v>247</v>
+        <v>250</v>
       </c>
     </row>
     <row r="46" spans="1:2">
@@ -4243,7 +4304,7 @@
         <v>43</v>
       </c>
       <c r="B46" t="s">
-        <v>248</v>
+        <v>251</v>
       </c>
     </row>
     <row r="47" spans="1:2">
@@ -4251,7 +4312,7 @@
         <v>44</v>
       </c>
       <c r="B47" t="s">
-        <v>249</v>
+        <v>252</v>
       </c>
     </row>
     <row r="48" spans="1:2">
@@ -4259,7 +4320,7 @@
         <v>45</v>
       </c>
       <c r="B48" t="s">
-        <v>250</v>
+        <v>253</v>
       </c>
     </row>
   </sheetData>

--- a/slots/resources/sample/SpecialPlay.xlsx
+++ b/slots/resources/sample/SpecialPlay.xlsx
@@ -137,7 +137,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="387" uniqueCount="254">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="387" uniqueCount="255">
   <si>
     <t>被动游戏ID</t>
   </si>
@@ -667,7 +667,10 @@
     <t>消除带有方框符号，获得神秘符号奖励乘以神秘符号个数，出现多个此符号，倍数相加</t>
   </si>
   <si>
-    <t>14_1</t>
+    <t>3,1,14_74_75</t>
+  </si>
+  <si>
+    <t>3个神秘符号及以上神秘符号触发消除转换，触发时每个神秘符号获得1倍奖励（所有神秘符号累加）_神秘符号id_神秘符号id_神秘符号id</t>
   </si>
   <si>
     <t>伽罗宝石2</t>
@@ -688,7 +691,7 @@
     <t>前三轴出现的多格图标个数及权重</t>
   </si>
   <si>
-    <t>0_2000|1_6000|2_4000|3_3000|4_1500|5_1000|6_200|7_100|8_0|9_0</t>
+    <t>1_6000|2_4000|3_3000|4_1500|5_1000|6_200|7_100|8_0|9_0</t>
   </si>
   <si>
     <t>多格图标个数_权重</t>
@@ -1087,12 +1090,12 @@
       <charset val="134"/>
     </font>
     <font>
-      <b/>
       <sz val="9"/>
       <name val="宋体"/>
       <charset val="134"/>
     </font>
     <font>
+      <b/>
       <sz val="9"/>
       <name val="宋体"/>
       <charset val="134"/>
@@ -3625,7 +3628,7 @@
         <v>176</v>
       </c>
       <c r="G71" t="s">
-        <v>158</v>
+        <v>177</v>
       </c>
     </row>
     <row r="72" s="2" customFormat="1" spans="1:9">
@@ -3636,7 +3639,7 @@
         <v>105501</v>
       </c>
       <c r="C72" s="2" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="D72" s="2">
         <v>1</v>
@@ -3661,19 +3664,19 @@
         <v>105502</v>
       </c>
       <c r="C73" s="17" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="D73" s="2">
         <v>1</v>
       </c>
       <c r="E73" s="17" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="F73" s="17" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="G73" s="18" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
     </row>
     <row r="74" ht="16.5" spans="1:9">
@@ -3684,19 +3687,19 @@
         <v>105502</v>
       </c>
       <c r="C74" s="17" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="D74" s="2">
         <v>2</v>
       </c>
       <c r="E74" s="17" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="F74" s="17" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="G74" s="18" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
     </row>
     <row r="75" customFormat="1" ht="18" customHeight="1" spans="1:9">
@@ -3707,7 +3710,7 @@
         <v>105502</v>
       </c>
       <c r="C75" s="17" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="D75" s="2">
         <v>3</v>
@@ -3732,7 +3735,7 @@
         <v>104100</v>
       </c>
       <c r="C76" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="D76" s="1">
         <v>1</v>
@@ -3741,7 +3744,7 @@
         <v>33</v>
       </c>
       <c r="F76" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="G76" t="s">
         <v>35</v>
@@ -3757,7 +3760,7 @@
         <v>104200</v>
       </c>
       <c r="C77" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="D77" s="1">
         <v>1</v>
@@ -3766,7 +3769,7 @@
         <v>33</v>
       </c>
       <c r="F77" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="G77" s="1" t="s">
         <v>35</v>
@@ -3782,19 +3785,19 @@
         <v>104200</v>
       </c>
       <c r="C78" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="D78" s="1">
         <v>2</v>
       </c>
       <c r="E78" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="F78" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="G78" s="1" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="H78" s="4"/>
       <c r="I78" s="4"/>
@@ -3807,7 +3810,7 @@
         <v>101900</v>
       </c>
       <c r="C79" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="D79" s="1">
         <v>1</v>
@@ -3816,7 +3819,7 @@
         <v>30</v>
       </c>
       <c r="F79" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="G79" s="1" t="s">
         <v>32</v>
@@ -3832,7 +3835,7 @@
         <v>101900</v>
       </c>
       <c r="C80" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="D80" s="1">
         <v>2</v>
@@ -3841,7 +3844,7 @@
         <v>33</v>
       </c>
       <c r="F80" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="G80" s="1" t="s">
         <v>143</v>
@@ -3857,19 +3860,19 @@
         <v>101900</v>
       </c>
       <c r="C81" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="D81" s="1">
         <v>3</v>
       </c>
       <c r="E81" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="F81" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="G81" s="1" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="H81" s="4"/>
       <c r="I81" s="4"/>
@@ -3899,24 +3902,24 @@
   <sheetData>
     <row r="1" spans="1:5">
       <c r="A1" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="D1" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
     </row>
     <row r="2" spans="1:5">
       <c r="A2" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="B2" t="s">
+        <v>202</v>
+      </c>
+      <c r="D2" t="s">
         <v>201</v>
       </c>
-      <c r="D2" t="s">
-        <v>200</v>
-      </c>
       <c r="E2" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
     </row>
     <row r="3" spans="1:5">
@@ -3924,13 +3927,13 @@
         <v>0</v>
       </c>
       <c r="B3" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="D3">
         <v>0</v>
       </c>
       <c r="E3" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
     </row>
     <row r="4" spans="1:5">
@@ -3938,13 +3941,13 @@
         <v>1</v>
       </c>
       <c r="B4" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="D4">
         <v>1</v>
       </c>
       <c r="E4" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
     </row>
     <row r="5" spans="1:5">
@@ -3952,13 +3955,13 @@
         <v>2</v>
       </c>
       <c r="B5" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="D5">
         <v>2</v>
       </c>
       <c r="E5" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
     </row>
     <row r="6" spans="1:5">
@@ -3966,13 +3969,13 @@
         <v>3</v>
       </c>
       <c r="B6" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="D6">
         <v>3</v>
       </c>
       <c r="E6" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
     </row>
     <row r="7" spans="1:5">
@@ -3980,13 +3983,13 @@
         <v>4</v>
       </c>
       <c r="B7" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="D7">
         <v>4</v>
       </c>
       <c r="E7" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
     </row>
     <row r="8" spans="1:5">
@@ -3994,13 +3997,13 @@
         <v>5</v>
       </c>
       <c r="B8" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="D8">
         <v>5</v>
       </c>
       <c r="E8" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
     </row>
     <row r="9" spans="1:5">
@@ -4008,7 +4011,7 @@
         <v>6</v>
       </c>
       <c r="B9" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
     </row>
     <row r="10" spans="1:5">
@@ -4016,7 +4019,7 @@
         <v>7</v>
       </c>
       <c r="B10" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
     </row>
     <row r="11" spans="1:5">
@@ -4024,7 +4027,7 @@
         <v>8</v>
       </c>
       <c r="B11" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
     </row>
     <row r="12" spans="1:5">
@@ -4032,7 +4035,7 @@
         <v>9</v>
       </c>
       <c r="B12" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
     </row>
     <row r="13" spans="1:5">
@@ -4040,7 +4043,7 @@
         <v>10</v>
       </c>
       <c r="B13" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
     </row>
     <row r="14" spans="1:5">
@@ -4048,7 +4051,7 @@
         <v>11</v>
       </c>
       <c r="B14" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
     </row>
     <row r="15" spans="1:5">
@@ -4056,7 +4059,7 @@
         <v>12</v>
       </c>
       <c r="B15" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
     </row>
     <row r="16" spans="1:5">
@@ -4064,7 +4067,7 @@
         <v>13</v>
       </c>
       <c r="B16" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
     </row>
     <row r="17" spans="1:2">
@@ -4072,7 +4075,7 @@
         <v>14</v>
       </c>
       <c r="B17" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
     </row>
     <row r="18" spans="1:2">
@@ -4080,7 +4083,7 @@
         <v>15</v>
       </c>
       <c r="B18" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
     </row>
     <row r="19" spans="1:2">
@@ -4088,7 +4091,7 @@
         <v>16</v>
       </c>
       <c r="B19" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
     </row>
     <row r="20" spans="1:2">
@@ -4096,7 +4099,7 @@
         <v>17</v>
       </c>
       <c r="B20" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
     </row>
     <row r="21" spans="1:2">
@@ -4104,7 +4107,7 @@
         <v>18</v>
       </c>
       <c r="B21" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
     </row>
     <row r="22" spans="1:2">
@@ -4112,7 +4115,7 @@
         <v>19</v>
       </c>
       <c r="B22" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
     </row>
     <row r="23" spans="1:2">
@@ -4120,7 +4123,7 @@
         <v>20</v>
       </c>
       <c r="B23" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
     </row>
     <row r="24" spans="1:2">
@@ -4128,7 +4131,7 @@
         <v>21</v>
       </c>
       <c r="B24" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
     </row>
     <row r="25" spans="1:2">
@@ -4136,7 +4139,7 @@
         <v>22</v>
       </c>
       <c r="B25" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
     </row>
     <row r="26" spans="1:2">
@@ -4144,7 +4147,7 @@
         <v>23</v>
       </c>
       <c r="B26" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
     </row>
     <row r="27" spans="1:2">
@@ -4152,7 +4155,7 @@
         <v>24</v>
       </c>
       <c r="B27" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
     </row>
     <row r="28" spans="1:2">
@@ -4160,7 +4163,7 @@
         <v>25</v>
       </c>
       <c r="B28" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
     </row>
     <row r="29" spans="1:2">
@@ -4168,7 +4171,7 @@
         <v>26</v>
       </c>
       <c r="B29" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
     </row>
     <row r="30" spans="1:2">
@@ -4176,7 +4179,7 @@
         <v>27</v>
       </c>
       <c r="B30" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
     </row>
     <row r="31" spans="1:2">
@@ -4184,7 +4187,7 @@
         <v>28</v>
       </c>
       <c r="B31" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
     </row>
     <row r="32" spans="1:2">
@@ -4192,7 +4195,7 @@
         <v>29</v>
       </c>
       <c r="B32" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
     </row>
     <row r="33" spans="1:2">
@@ -4200,7 +4203,7 @@
         <v>30</v>
       </c>
       <c r="B33" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
     </row>
     <row r="34" spans="1:2">
@@ -4208,7 +4211,7 @@
         <v>31</v>
       </c>
       <c r="B34" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
     </row>
     <row r="35" spans="1:2">
@@ -4216,7 +4219,7 @@
         <v>32</v>
       </c>
       <c r="B35" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
     </row>
     <row r="36" spans="1:2">
@@ -4224,7 +4227,7 @@
         <v>33</v>
       </c>
       <c r="B36" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
     </row>
     <row r="37" spans="1:2">
@@ -4232,7 +4235,7 @@
         <v>34</v>
       </c>
       <c r="B37" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
     </row>
     <row r="38" spans="1:2">
@@ -4240,7 +4243,7 @@
         <v>35</v>
       </c>
       <c r="B38" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
     </row>
     <row r="39" spans="1:2">
@@ -4248,7 +4251,7 @@
         <v>36</v>
       </c>
       <c r="B39" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
     </row>
     <row r="40" spans="1:2">
@@ -4256,7 +4259,7 @@
         <v>37</v>
       </c>
       <c r="B40" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
     </row>
     <row r="41" spans="1:2">
@@ -4264,7 +4267,7 @@
         <v>38</v>
       </c>
       <c r="B41" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
     </row>
     <row r="42" spans="1:2">
@@ -4272,7 +4275,7 @@
         <v>39</v>
       </c>
       <c r="B42" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
     </row>
     <row r="43" spans="1:2">
@@ -4280,7 +4283,7 @@
         <v>40</v>
       </c>
       <c r="B43" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
     </row>
     <row r="44" spans="1:2">
@@ -4288,7 +4291,7 @@
         <v>41</v>
       </c>
       <c r="B44" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
     </row>
     <row r="45" spans="1:2">
@@ -4296,7 +4299,7 @@
         <v>42</v>
       </c>
       <c r="B45" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
     </row>
     <row r="46" spans="1:2">
@@ -4304,7 +4307,7 @@
         <v>43</v>
       </c>
       <c r="B46" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
     </row>
     <row r="47" spans="1:2">
@@ -4312,7 +4315,7 @@
         <v>44</v>
       </c>
       <c r="B47" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
     </row>
     <row r="48" spans="1:2">
@@ -4320,7 +4323,7 @@
         <v>45</v>
       </c>
       <c r="B48" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
     </row>
   </sheetData>

--- a/slots/resources/sample/SpecialPlay.xlsx
+++ b/slots/resources/sample/SpecialPlay.xlsx
@@ -137,7 +137,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="387" uniqueCount="255">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="379" uniqueCount="251">
   <si>
     <t>被动游戏ID</t>
   </si>
@@ -634,6 +634,15 @@
     <t>10,3_10_10000|4_12_10000|5_14_10000</t>
   </si>
   <si>
+    <t>常规模式下，金框符号转换为百搭符号</t>
+  </si>
+  <si>
+    <t>9_1_1</t>
+  </si>
+  <si>
+    <t>元素id_金框符号权重_百搭符号权重|元素id_金框符号权重_百搭符号权重|元素id_金框符号权重_百搭符号权重</t>
+  </si>
+  <si>
     <t>极速糖果1000</t>
   </si>
   <si>
@@ -667,10 +676,7 @@
     <t>消除带有方框符号，获得神秘符号奖励乘以神秘符号个数，出现多个此符号，倍数相加</t>
   </si>
   <si>
-    <t>3,1,14_74_75</t>
-  </si>
-  <si>
-    <t>3个神秘符号及以上神秘符号触发消除转换，触发时每个神秘符号获得1倍奖励（所有神秘符号累加）_神秘符号id_神秘符号id_神秘符号id</t>
+    <t>14_1</t>
   </si>
   <si>
     <t>伽罗宝石2</t>
@@ -691,7 +697,7 @@
     <t>前三轴出现的多格图标个数及权重</t>
   </si>
   <si>
-    <t>1_6000|2_4000|3_3000|4_1500|5_1000|6_200|7_100|8_0|9_0</t>
+    <t>0_2000|1_6000|2_4000|3_3000|4_1500|5_1000|6_200|7_100|8_0|9_0</t>
   </si>
   <si>
     <t>多格图标个数_权重</t>
@@ -716,24 +722,6 @@
   </si>
   <si>
     <t>目标图案_中奖翻倍</t>
-  </si>
-  <si>
-    <t>德古拉</t>
-  </si>
-  <si>
-    <t>1,1_1|2_2|3_3|4_4|5_5;2,1_3|2_6|3_9|4_12|5_15</t>
-  </si>
-  <si>
-    <t>2,13,4_12_10000|5_14_10000|6_16_10000</t>
-  </si>
-  <si>
-    <t>百搭赐福模式下，随机三个白银符号变成直接变成wild符号</t>
-  </si>
-  <si>
-    <t>3_3</t>
-  </si>
-  <si>
-    <t>模式id_随机白银符号个数</t>
   </si>
   <si>
     <t>旋转标识</t>
@@ -1090,12 +1078,12 @@
       <charset val="134"/>
     </font>
     <font>
+      <b/>
       <sz val="9"/>
       <name val="宋体"/>
       <charset val="134"/>
     </font>
     <font>
-      <b/>
       <sz val="9"/>
       <name val="宋体"/>
       <charset val="134"/>
@@ -1941,7 +1929,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:J81"/>
+  <dimension ref="A1:J79"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25"/>
   <cols>
     <col min="3" max="3" width="10.375" customWidth="1"/>
@@ -3516,248 +3504,246 @@
     </row>
     <row r="67" ht="16.5" spans="1:9">
       <c r="A67" s="1">
-        <v>5058001</v>
+        <v>5057003</v>
       </c>
       <c r="B67" s="10">
-        <v>105800</v>
+        <v>105700</v>
       </c>
       <c r="C67" t="s">
+        <v>162</v>
+      </c>
+      <c r="D67" s="1">
+        <v>3</v>
+      </c>
+      <c r="E67" t="s">
         <v>165</v>
       </c>
-      <c r="D67" s="1">
-        <v>1</v>
-      </c>
-      <c r="E67" t="s">
-        <v>33</v>
-      </c>
-      <c r="F67" t="s">
+      <c r="F67" s="14" t="s">
         <v>166</v>
       </c>
-      <c r="G67" t="s">
-        <v>35</v>
+      <c r="G67" s="1" t="s">
+        <v>167</v>
       </c>
     </row>
     <row r="68" ht="16.5" spans="1:9">
       <c r="A68" s="1">
-        <v>5058002</v>
+        <v>5058001</v>
       </c>
       <c r="B68" s="10">
         <v>105800</v>
       </c>
       <c r="C68" t="s">
-        <v>165</v>
+        <v>168</v>
       </c>
       <c r="D68" s="1">
+        <v>1</v>
+      </c>
+      <c r="E68" t="s">
+        <v>33</v>
+      </c>
+      <c r="F68" t="s">
+        <v>169</v>
+      </c>
+      <c r="G68" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="69" ht="16.5" spans="1:9">
+      <c r="A69" s="1">
+        <v>5058002</v>
+      </c>
+      <c r="B69" s="10">
+        <v>105800</v>
+      </c>
+      <c r="C69" t="s">
+        <v>168</v>
+      </c>
+      <c r="D69" s="1">
         <v>2</v>
       </c>
-      <c r="E68" t="s">
-        <v>167</v>
-      </c>
-      <c r="F68" t="s">
-        <v>168</v>
-      </c>
-      <c r="G68" t="s">
-        <v>169</v>
-      </c>
-    </row>
-    <row r="69" s="2" customFormat="1" spans="1:9">
-      <c r="A69" s="2">
+      <c r="E69" t="s">
+        <v>170</v>
+      </c>
+      <c r="F69" t="s">
+        <v>171</v>
+      </c>
+      <c r="G69" t="s">
+        <v>172</v>
+      </c>
+    </row>
+    <row r="70" s="2" customFormat="1" spans="1:9">
+      <c r="A70" s="2">
         <v>5055001</v>
       </c>
-      <c r="B69" s="2">
+      <c r="B70" s="2">
         <v>105500</v>
       </c>
-      <c r="C69" s="2" t="s">
-        <v>170</v>
-      </c>
-      <c r="D69" s="2">
+      <c r="C70" s="2" t="s">
+        <v>173</v>
+      </c>
+      <c r="D70" s="2">
         <v>1</v>
       </c>
-      <c r="E69" s="2" t="s">
-        <v>171</v>
-      </c>
-      <c r="F69" s="2" t="s">
-        <v>172</v>
-      </c>
-      <c r="G69" s="2" t="s">
-        <v>173</v>
-      </c>
-      <c r="H69" s="16"/>
-      <c r="I69" s="16"/>
-    </row>
-    <row r="70" ht="18" customHeight="1" spans="1:9">
-      <c r="A70" s="1">
+      <c r="E70" s="2" t="s">
+        <v>174</v>
+      </c>
+      <c r="F70" s="2" t="s">
+        <v>175</v>
+      </c>
+      <c r="G70" s="2" t="s">
+        <v>176</v>
+      </c>
+      <c r="H70" s="16"/>
+      <c r="I70" s="16"/>
+    </row>
+    <row r="71" ht="18" customHeight="1" spans="1:9">
+      <c r="A71" s="1">
         <v>5048001</v>
-      </c>
-      <c r="B70" s="10">
-        <v>104800</v>
-      </c>
-      <c r="C70" t="s">
-        <v>174</v>
-      </c>
-      <c r="D70" s="1">
-        <v>1</v>
-      </c>
-      <c r="E70" t="s">
-        <v>33</v>
-      </c>
-      <c r="F70" t="s">
-        <v>159</v>
-      </c>
-      <c r="G70" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="71" ht="16.5" spans="1:9">
-      <c r="A71" s="1">
-        <v>5048002</v>
       </c>
       <c r="B71" s="10">
         <v>104800</v>
       </c>
       <c r="C71" t="s">
-        <v>174</v>
+        <v>177</v>
       </c>
       <c r="D71" s="1">
+        <v>1</v>
+      </c>
+      <c r="E71" t="s">
+        <v>33</v>
+      </c>
+      <c r="F71" t="s">
+        <v>159</v>
+      </c>
+      <c r="G71" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="72" ht="16.5" spans="1:9">
+      <c r="A72" s="1">
+        <v>5048002</v>
+      </c>
+      <c r="B72" s="10">
+        <v>104800</v>
+      </c>
+      <c r="C72" t="s">
+        <v>177</v>
+      </c>
+      <c r="D72" s="1">
         <v>2</v>
       </c>
-      <c r="E71" t="s">
-        <v>175</v>
-      </c>
-      <c r="F71" t="s">
-        <v>176</v>
-      </c>
-      <c r="G71" t="s">
-        <v>177</v>
-      </c>
-    </row>
-    <row r="72" s="2" customFormat="1" spans="1:9">
-      <c r="A72" s="2">
+      <c r="E72" t="s">
+        <v>178</v>
+      </c>
+      <c r="F72" t="s">
+        <v>179</v>
+      </c>
+      <c r="G72" t="s">
+        <v>158</v>
+      </c>
+    </row>
+    <row r="73" s="2" customFormat="1" spans="1:9">
+      <c r="A73" s="2">
         <v>5055011</v>
       </c>
-      <c r="B72" s="2">
+      <c r="B73" s="2">
         <v>105501</v>
       </c>
-      <c r="C72" s="2" t="s">
-        <v>178</v>
-      </c>
-      <c r="D72" s="2">
-        <v>1</v>
-      </c>
-      <c r="E72" s="2" t="s">
-        <v>171</v>
-      </c>
-      <c r="F72" s="2" t="s">
-        <v>172</v>
-      </c>
-      <c r="G72" s="2" t="s">
-        <v>173</v>
-      </c>
-      <c r="H72" s="16"/>
-      <c r="I72" s="16"/>
-    </row>
-    <row r="73" ht="16.5" spans="1:9">
-      <c r="A73" s="1">
-        <v>5055021</v>
-      </c>
-      <c r="B73" s="10">
-        <v>105502</v>
-      </c>
-      <c r="C73" s="17" t="s">
-        <v>179</v>
+      <c r="C73" s="2" t="s">
+        <v>180</v>
       </c>
       <c r="D73" s="2">
         <v>1</v>
       </c>
-      <c r="E73" s="17" t="s">
-        <v>180</v>
-      </c>
-      <c r="F73" s="17" t="s">
-        <v>181</v>
-      </c>
-      <c r="G73" s="18" t="s">
-        <v>182</v>
-      </c>
+      <c r="E73" s="2" t="s">
+        <v>174</v>
+      </c>
+      <c r="F73" s="2" t="s">
+        <v>175</v>
+      </c>
+      <c r="G73" s="2" t="s">
+        <v>176</v>
+      </c>
+      <c r="H73" s="16"/>
+      <c r="I73" s="16"/>
     </row>
     <row r="74" ht="16.5" spans="1:9">
       <c r="A74" s="1">
-        <v>5055022</v>
+        <v>5055021</v>
       </c>
       <c r="B74" s="10">
         <v>105502</v>
       </c>
       <c r="C74" s="17" t="s">
-        <v>179</v>
+        <v>181</v>
       </c>
       <c r="D74" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E74" s="17" t="s">
+        <v>182</v>
+      </c>
+      <c r="F74" s="17" t="s">
         <v>183</v>
       </c>
-      <c r="F74" s="17" t="s">
+      <c r="G74" s="18" t="s">
         <v>184</v>
       </c>
-      <c r="G74" s="18" t="s">
-        <v>185</v>
-      </c>
-    </row>
-    <row r="75" customFormat="1" ht="18" customHeight="1" spans="1:9">
+    </row>
+    <row r="75" ht="16.5" spans="1:9">
       <c r="A75" s="1">
-        <v>5055023</v>
+        <v>5055022</v>
       </c>
       <c r="B75" s="10">
         <v>105502</v>
       </c>
       <c r="C75" s="17" t="s">
-        <v>179</v>
+        <v>181</v>
       </c>
       <c r="D75" s="2">
-        <v>3</v>
-      </c>
-      <c r="E75" s="2" t="s">
-        <v>171</v>
-      </c>
-      <c r="F75" s="2" t="s">
-        <v>172</v>
-      </c>
-      <c r="G75" s="2" t="s">
-        <v>173</v>
-      </c>
-      <c r="H75" s="4"/>
-      <c r="I75" s="4"/>
+        <v>2</v>
+      </c>
+      <c r="E75" s="17" t="s">
+        <v>185</v>
+      </c>
+      <c r="F75" s="17" t="s">
+        <v>186</v>
+      </c>
+      <c r="G75" s="18" t="s">
+        <v>187</v>
+      </c>
     </row>
     <row r="76" customFormat="1" ht="18" customHeight="1" spans="1:9">
       <c r="A76" s="1">
-        <v>5041001</v>
+        <v>5055023</v>
       </c>
       <c r="B76" s="10">
-        <v>104100</v>
-      </c>
-      <c r="C76" t="s">
-        <v>186</v>
-      </c>
-      <c r="D76" s="1">
-        <v>1</v>
-      </c>
-      <c r="E76" t="s">
-        <v>33</v>
-      </c>
-      <c r="F76" t="s">
-        <v>187</v>
-      </c>
-      <c r="G76" t="s">
-        <v>35</v>
+        <v>105502</v>
+      </c>
+      <c r="C76" s="17" t="s">
+        <v>181</v>
+      </c>
+      <c r="D76" s="2">
+        <v>3</v>
+      </c>
+      <c r="E76" s="2" t="s">
+        <v>174</v>
+      </c>
+      <c r="F76" s="2" t="s">
+        <v>175</v>
+      </c>
+      <c r="G76" s="2" t="s">
+        <v>176</v>
       </c>
       <c r="H76" s="4"/>
       <c r="I76" s="4"/>
     </row>
     <row r="77" customFormat="1" ht="18" customHeight="1" spans="1:9">
       <c r="A77" s="1">
-        <v>5042001</v>
+        <v>5041001</v>
       </c>
       <c r="B77" s="10">
-        <v>104200</v>
+        <v>104100</v>
       </c>
       <c r="C77" t="s">
         <v>188</v>
@@ -3771,111 +3757,61 @@
       <c r="F77" t="s">
         <v>189</v>
       </c>
-      <c r="G77" s="1" t="s">
+      <c r="G77" t="s">
         <v>35</v>
       </c>
       <c r="H77" s="4"/>
       <c r="I77" s="4"/>
     </row>
-    <row r="78" customFormat="1" ht="16.5" spans="1:9">
+    <row r="78" customFormat="1" ht="18" customHeight="1" spans="1:9">
       <c r="A78" s="1">
-        <v>5042002</v>
+        <v>5042001</v>
       </c>
       <c r="B78" s="10">
         <v>104200</v>
       </c>
       <c r="C78" t="s">
-        <v>188</v>
+        <v>190</v>
       </c>
       <c r="D78" s="1">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E78" t="s">
-        <v>190</v>
+        <v>33</v>
       </c>
       <c r="F78" t="s">
         <v>191</v>
       </c>
       <c r="G78" s="1" t="s">
-        <v>192</v>
+        <v>35</v>
       </c>
       <c r="H78" s="4"/>
       <c r="I78" s="4"/>
     </row>
     <row r="79" customFormat="1" ht="16.5" spans="1:9">
       <c r="A79" s="1">
-        <v>5019001</v>
+        <v>5042002</v>
       </c>
       <c r="B79" s="10">
-        <v>101900</v>
+        <v>104200</v>
       </c>
       <c r="C79" t="s">
+        <v>190</v>
+      </c>
+      <c r="D79" s="1">
+        <v>2</v>
+      </c>
+      <c r="E79" t="s">
+        <v>192</v>
+      </c>
+      <c r="F79" t="s">
         <v>193</v>
       </c>
-      <c r="D79" s="1">
-        <v>1</v>
-      </c>
-      <c r="E79" t="s">
-        <v>30</v>
-      </c>
-      <c r="F79" t="s">
+      <c r="G79" s="1" t="s">
         <v>194</v>
-      </c>
-      <c r="G79" s="1" t="s">
-        <v>32</v>
       </c>
       <c r="H79" s="4"/>
       <c r="I79" s="4"/>
-    </row>
-    <row r="80" customFormat="1" ht="16.5" spans="1:9">
-      <c r="A80" s="1">
-        <v>5019002</v>
-      </c>
-      <c r="B80" s="10">
-        <v>101900</v>
-      </c>
-      <c r="C80" t="s">
-        <v>193</v>
-      </c>
-      <c r="D80" s="1">
-        <v>2</v>
-      </c>
-      <c r="E80" t="s">
-        <v>33</v>
-      </c>
-      <c r="F80" t="s">
-        <v>195</v>
-      </c>
-      <c r="G80" s="1" t="s">
-        <v>143</v>
-      </c>
-      <c r="H80" s="4"/>
-      <c r="I80" s="4"/>
-    </row>
-    <row r="81" customFormat="1" ht="16.5" spans="1:9">
-      <c r="A81" s="1">
-        <v>5019003</v>
-      </c>
-      <c r="B81" s="10">
-        <v>101900</v>
-      </c>
-      <c r="C81" t="s">
-        <v>193</v>
-      </c>
-      <c r="D81" s="1">
-        <v>3</v>
-      </c>
-      <c r="E81" t="s">
-        <v>196</v>
-      </c>
-      <c r="F81" t="s">
-        <v>197</v>
-      </c>
-      <c r="G81" s="1" t="s">
-        <v>198</v>
-      </c>
-      <c r="H81" s="4"/>
-      <c r="I81" s="4"/>
     </row>
   </sheetData>
   <conditionalFormatting sqref="H2">
@@ -3902,24 +3838,24 @@
   <sheetData>
     <row r="1" spans="1:5">
       <c r="A1" t="s">
-        <v>199</v>
+        <v>195</v>
       </c>
       <c r="D1" t="s">
-        <v>200</v>
+        <v>196</v>
       </c>
     </row>
     <row r="2" spans="1:5">
       <c r="A2" t="s">
-        <v>201</v>
+        <v>197</v>
       </c>
       <c r="B2" t="s">
-        <v>202</v>
+        <v>198</v>
       </c>
       <c r="D2" t="s">
-        <v>201</v>
+        <v>197</v>
       </c>
       <c r="E2" t="s">
-        <v>202</v>
+        <v>198</v>
       </c>
     </row>
     <row r="3" spans="1:5">
@@ -3927,13 +3863,13 @@
         <v>0</v>
       </c>
       <c r="B3" t="s">
-        <v>203</v>
+        <v>199</v>
       </c>
       <c r="D3">
         <v>0</v>
       </c>
       <c r="E3" t="s">
-        <v>204</v>
+        <v>200</v>
       </c>
     </row>
     <row r="4" spans="1:5">
@@ -3941,13 +3877,13 @@
         <v>1</v>
       </c>
       <c r="B4" t="s">
-        <v>205</v>
+        <v>201</v>
       </c>
       <c r="D4">
         <v>1</v>
       </c>
       <c r="E4" t="s">
-        <v>206</v>
+        <v>202</v>
       </c>
     </row>
     <row r="5" spans="1:5">
@@ -3955,13 +3891,13 @@
         <v>2</v>
       </c>
       <c r="B5" t="s">
-        <v>207</v>
+        <v>203</v>
       </c>
       <c r="D5">
         <v>2</v>
       </c>
       <c r="E5" t="s">
-        <v>208</v>
+        <v>204</v>
       </c>
     </row>
     <row r="6" spans="1:5">
@@ -3969,13 +3905,13 @@
         <v>3</v>
       </c>
       <c r="B6" t="s">
-        <v>209</v>
+        <v>205</v>
       </c>
       <c r="D6">
         <v>3</v>
       </c>
       <c r="E6" t="s">
-        <v>210</v>
+        <v>206</v>
       </c>
     </row>
     <row r="7" spans="1:5">
@@ -3983,13 +3919,13 @@
         <v>4</v>
       </c>
       <c r="B7" t="s">
-        <v>211</v>
+        <v>207</v>
       </c>
       <c r="D7">
         <v>4</v>
       </c>
       <c r="E7" t="s">
-        <v>212</v>
+        <v>208</v>
       </c>
     </row>
     <row r="8" spans="1:5">
@@ -3997,13 +3933,13 @@
         <v>5</v>
       </c>
       <c r="B8" t="s">
-        <v>213</v>
+        <v>209</v>
       </c>
       <c r="D8">
         <v>5</v>
       </c>
       <c r="E8" t="s">
-        <v>214</v>
+        <v>210</v>
       </c>
     </row>
     <row r="9" spans="1:5">
@@ -4011,7 +3947,7 @@
         <v>6</v>
       </c>
       <c r="B9" t="s">
-        <v>215</v>
+        <v>211</v>
       </c>
     </row>
     <row r="10" spans="1:5">
@@ -4019,7 +3955,7 @@
         <v>7</v>
       </c>
       <c r="B10" t="s">
-        <v>216</v>
+        <v>212</v>
       </c>
     </row>
     <row r="11" spans="1:5">
@@ -4027,7 +3963,7 @@
         <v>8</v>
       </c>
       <c r="B11" t="s">
-        <v>217</v>
+        <v>213</v>
       </c>
     </row>
     <row r="12" spans="1:5">
@@ -4035,7 +3971,7 @@
         <v>9</v>
       </c>
       <c r="B12" t="s">
-        <v>218</v>
+        <v>214</v>
       </c>
     </row>
     <row r="13" spans="1:5">
@@ -4043,7 +3979,7 @@
         <v>10</v>
       </c>
       <c r="B13" t="s">
-        <v>219</v>
+        <v>215</v>
       </c>
     </row>
     <row r="14" spans="1:5">
@@ -4051,7 +3987,7 @@
         <v>11</v>
       </c>
       <c r="B14" t="s">
-        <v>220</v>
+        <v>216</v>
       </c>
     </row>
     <row r="15" spans="1:5">
@@ -4059,7 +3995,7 @@
         <v>12</v>
       </c>
       <c r="B15" t="s">
-        <v>221</v>
+        <v>217</v>
       </c>
     </row>
     <row r="16" spans="1:5">
@@ -4067,7 +4003,7 @@
         <v>13</v>
       </c>
       <c r="B16" t="s">
-        <v>222</v>
+        <v>218</v>
       </c>
     </row>
     <row r="17" spans="1:2">
@@ -4075,7 +4011,7 @@
         <v>14</v>
       </c>
       <c r="B17" t="s">
-        <v>223</v>
+        <v>219</v>
       </c>
     </row>
     <row r="18" spans="1:2">
@@ -4083,7 +4019,7 @@
         <v>15</v>
       </c>
       <c r="B18" t="s">
-        <v>224</v>
+        <v>220</v>
       </c>
     </row>
     <row r="19" spans="1:2">
@@ -4091,7 +4027,7 @@
         <v>16</v>
       </c>
       <c r="B19" t="s">
-        <v>225</v>
+        <v>221</v>
       </c>
     </row>
     <row r="20" spans="1:2">
@@ -4099,7 +4035,7 @@
         <v>17</v>
       </c>
       <c r="B20" t="s">
-        <v>226</v>
+        <v>222</v>
       </c>
     </row>
     <row r="21" spans="1:2">
@@ -4107,7 +4043,7 @@
         <v>18</v>
       </c>
       <c r="B21" t="s">
-        <v>227</v>
+        <v>223</v>
       </c>
     </row>
     <row r="22" spans="1:2">
@@ -4115,7 +4051,7 @@
         <v>19</v>
       </c>
       <c r="B22" t="s">
-        <v>228</v>
+        <v>224</v>
       </c>
     </row>
     <row r="23" spans="1:2">
@@ -4123,7 +4059,7 @@
         <v>20</v>
       </c>
       <c r="B23" t="s">
-        <v>229</v>
+        <v>225</v>
       </c>
     </row>
     <row r="24" spans="1:2">
@@ -4131,7 +4067,7 @@
         <v>21</v>
       </c>
       <c r="B24" t="s">
-        <v>230</v>
+        <v>226</v>
       </c>
     </row>
     <row r="25" spans="1:2">
@@ -4139,7 +4075,7 @@
         <v>22</v>
       </c>
       <c r="B25" t="s">
-        <v>231</v>
+        <v>227</v>
       </c>
     </row>
     <row r="26" spans="1:2">
@@ -4147,7 +4083,7 @@
         <v>23</v>
       </c>
       <c r="B26" t="s">
-        <v>232</v>
+        <v>228</v>
       </c>
     </row>
     <row r="27" spans="1:2">
@@ -4155,7 +4091,7 @@
         <v>24</v>
       </c>
       <c r="B27" t="s">
-        <v>233</v>
+        <v>229</v>
       </c>
     </row>
     <row r="28" spans="1:2">
@@ -4163,7 +4099,7 @@
         <v>25</v>
       </c>
       <c r="B28" t="s">
-        <v>234</v>
+        <v>230</v>
       </c>
     </row>
     <row r="29" spans="1:2">
@@ -4171,7 +4107,7 @@
         <v>26</v>
       </c>
       <c r="B29" t="s">
-        <v>235</v>
+        <v>231</v>
       </c>
     </row>
     <row r="30" spans="1:2">
@@ -4179,7 +4115,7 @@
         <v>27</v>
       </c>
       <c r="B30" t="s">
-        <v>236</v>
+        <v>232</v>
       </c>
     </row>
     <row r="31" spans="1:2">
@@ -4187,7 +4123,7 @@
         <v>28</v>
       </c>
       <c r="B31" t="s">
-        <v>237</v>
+        <v>233</v>
       </c>
     </row>
     <row r="32" spans="1:2">
@@ -4195,7 +4131,7 @@
         <v>29</v>
       </c>
       <c r="B32" t="s">
-        <v>238</v>
+        <v>234</v>
       </c>
     </row>
     <row r="33" spans="1:2">
@@ -4203,7 +4139,7 @@
         <v>30</v>
       </c>
       <c r="B33" t="s">
-        <v>239</v>
+        <v>235</v>
       </c>
     </row>
     <row r="34" spans="1:2">
@@ -4211,7 +4147,7 @@
         <v>31</v>
       </c>
       <c r="B34" t="s">
-        <v>240</v>
+        <v>236</v>
       </c>
     </row>
     <row r="35" spans="1:2">
@@ -4219,7 +4155,7 @@
         <v>32</v>
       </c>
       <c r="B35" t="s">
-        <v>241</v>
+        <v>237</v>
       </c>
     </row>
     <row r="36" spans="1:2">
@@ -4227,7 +4163,7 @@
         <v>33</v>
       </c>
       <c r="B36" t="s">
-        <v>242</v>
+        <v>238</v>
       </c>
     </row>
     <row r="37" spans="1:2">
@@ -4235,7 +4171,7 @@
         <v>34</v>
       </c>
       <c r="B37" t="s">
-        <v>243</v>
+        <v>239</v>
       </c>
     </row>
     <row r="38" spans="1:2">
@@ -4243,7 +4179,7 @@
         <v>35</v>
       </c>
       <c r="B38" t="s">
-        <v>244</v>
+        <v>240</v>
       </c>
     </row>
     <row r="39" spans="1:2">
@@ -4251,7 +4187,7 @@
         <v>36</v>
       </c>
       <c r="B39" t="s">
-        <v>245</v>
+        <v>241</v>
       </c>
     </row>
     <row r="40" spans="1:2">
@@ -4259,7 +4195,7 @@
         <v>37</v>
       </c>
       <c r="B40" t="s">
-        <v>246</v>
+        <v>242</v>
       </c>
     </row>
     <row r="41" spans="1:2">
@@ -4267,7 +4203,7 @@
         <v>38</v>
       </c>
       <c r="B41" t="s">
-        <v>247</v>
+        <v>243</v>
       </c>
     </row>
     <row r="42" spans="1:2">
@@ -4275,7 +4211,7 @@
         <v>39</v>
       </c>
       <c r="B42" t="s">
-        <v>248</v>
+        <v>244</v>
       </c>
     </row>
     <row r="43" spans="1:2">
@@ -4283,7 +4219,7 @@
         <v>40</v>
       </c>
       <c r="B43" t="s">
-        <v>249</v>
+        <v>245</v>
       </c>
     </row>
     <row r="44" spans="1:2">
@@ -4291,7 +4227,7 @@
         <v>41</v>
       </c>
       <c r="B44" t="s">
-        <v>250</v>
+        <v>246</v>
       </c>
     </row>
     <row r="45" spans="1:2">
@@ -4299,7 +4235,7 @@
         <v>42</v>
       </c>
       <c r="B45" t="s">
-        <v>251</v>
+        <v>247</v>
       </c>
     </row>
     <row r="46" spans="1:2">
@@ -4307,7 +4243,7 @@
         <v>43</v>
       </c>
       <c r="B46" t="s">
-        <v>252</v>
+        <v>248</v>
       </c>
     </row>
     <row r="47" spans="1:2">
@@ -4315,7 +4251,7 @@
         <v>44</v>
       </c>
       <c r="B47" t="s">
-        <v>253</v>
+        <v>249</v>
       </c>
     </row>
     <row r="48" spans="1:2">
@@ -4323,7 +4259,7 @@
         <v>45</v>
       </c>
       <c r="B48" t="s">
-        <v>254</v>
+        <v>250</v>
       </c>
     </row>
   </sheetData>
